--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -1711,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117524187</v>
+        <v>117524180</v>
       </c>
       <c r="B12" t="n">
-        <v>78217</v>
+        <v>90464</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1723,25 +1723,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>746577</v>
+        <v>746038</v>
       </c>
       <c r="R12" t="n">
-        <v>7151343</v>
+        <v>7151191</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1813,10 +1813,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117524180</v>
+        <v>117524187</v>
       </c>
       <c r="B13" t="n">
-        <v>90464</v>
+        <v>78217</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1825,25 +1825,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746038</v>
+        <v>746577</v>
       </c>
       <c r="R13" t="n">
-        <v>7151191</v>
+        <v>7151343</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117545037</v>
+        <v>117545308</v>
       </c>
       <c r="B17" t="n">
-        <v>82259</v>
+        <v>78480</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>746778</v>
+        <v>746467</v>
       </c>
       <c r="R17" t="n">
-        <v>7151306</v>
+        <v>7151334</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117545020</v>
+        <v>117545016</v>
       </c>
       <c r="B18" t="n">
-        <v>90499</v>
+        <v>78480</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2351,21 +2351,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117545393</v>
+        <v>117545037</v>
       </c>
       <c r="B19" t="n">
-        <v>91962</v>
+        <v>82259</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2457,21 +2457,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746185</v>
+        <v>746778</v>
       </c>
       <c r="R19" t="n">
-        <v>7151374</v>
+        <v>7151306</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117545126</v>
+        <v>117545020</v>
       </c>
       <c r="B20" t="n">
-        <v>91962</v>
+        <v>90499</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746663</v>
+        <v>746778</v>
       </c>
       <c r="R20" t="n">
-        <v>7151376</v>
+        <v>7151306</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,7 +2653,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117545206</v>
+        <v>117545393</v>
       </c>
       <c r="B21" t="n">
         <v>91962</v>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>746602</v>
+        <v>746185</v>
       </c>
       <c r="R21" t="n">
-        <v>7151380</v>
+        <v>7151374</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,10 +2759,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117545308</v>
+        <v>117545126</v>
       </c>
       <c r="B22" t="n">
-        <v>78480</v>
+        <v>91962</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2802,10 +2802,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>746467</v>
+        <v>746663</v>
       </c>
       <c r="R22" t="n">
-        <v>7151334</v>
+        <v>7151376</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117545016</v>
+        <v>117545206</v>
       </c>
       <c r="B23" t="n">
-        <v>78480</v>
+        <v>91962</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2881,21 +2881,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>746778</v>
+        <v>746602</v>
       </c>
       <c r="R23" t="n">
-        <v>7151306</v>
+        <v>7151380</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117545679</v>
+        <v>117545351</v>
       </c>
       <c r="B41" t="n">
-        <v>78480</v>
+        <v>57303</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4797,26 +4797,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4824,10 +4829,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746425</v>
+        <v>746294</v>
       </c>
       <c r="R41" t="n">
-        <v>7151306</v>
+        <v>7151340</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4868,7 +4873,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4887,7 +4891,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117545001</v>
+        <v>117545679</v>
       </c>
       <c r="B42" t="n">
         <v>78480</v>
@@ -4922,11 +4926,7 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746795</v>
+        <v>746425</v>
       </c>
       <c r="R42" t="n">
-        <v>7151298</v>
+        <v>7151306</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4997,10 +4997,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117545351</v>
+        <v>117545001</v>
       </c>
       <c r="B43" t="n">
-        <v>57303</v>
+        <v>78480</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5013,29 +5013,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5045,10 +5044,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746294</v>
+        <v>746795</v>
       </c>
       <c r="R43" t="n">
-        <v>7151340</v>
+        <v>7151298</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5089,6 +5088,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117524192</v>
+        <v>117524184</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>57303</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746862</v>
+        <v>746524</v>
       </c>
       <c r="R2" t="n">
-        <v>7151254</v>
+        <v>7151386</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117524183</v>
+        <v>117524190</v>
       </c>
       <c r="B4" t="n">
-        <v>57303</v>
+        <v>78480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,42 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746086</v>
+        <v>746257</v>
       </c>
       <c r="R4" t="n">
-        <v>7151181</v>
+        <v>7151339</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117524190</v>
+        <v>117524180</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>90464</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,25 +1001,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>746257</v>
+        <v>746038</v>
       </c>
       <c r="R5" t="n">
-        <v>7151339</v>
+        <v>7151191</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117524191</v>
+        <v>117524187</v>
       </c>
       <c r="B6" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,21 +1107,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746648</v>
+        <v>746577</v>
       </c>
       <c r="R6" t="n">
-        <v>7151376</v>
+        <v>7151343</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117524186</v>
+        <v>117524193</v>
       </c>
       <c r="B7" t="n">
-        <v>78217</v>
+        <v>90743</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,25 +1205,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746456</v>
+        <v>746383</v>
       </c>
       <c r="R7" t="n">
-        <v>7151357</v>
+        <v>7151352</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117524184</v>
+        <v>117524186</v>
       </c>
       <c r="B8" t="n">
-        <v>57303</v>
+        <v>78217</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,42 +1311,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746524</v>
+        <v>746456</v>
       </c>
       <c r="R8" t="n">
-        <v>7151386</v>
+        <v>7151357</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1405,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117524185</v>
+        <v>117524191</v>
       </c>
       <c r="B9" t="n">
-        <v>91962</v>
+        <v>78480</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,21 +1413,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>746480</v>
+        <v>746648</v>
       </c>
       <c r="R9" t="n">
-        <v>7151410</v>
+        <v>7151376</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1507,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117524194</v>
+        <v>117524189</v>
       </c>
       <c r="B10" t="n">
-        <v>91772</v>
+        <v>78480</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1519,25 +1511,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>746112</v>
+        <v>746165</v>
       </c>
       <c r="R10" t="n">
-        <v>7151271</v>
+        <v>7151172</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1609,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117524189</v>
+        <v>117524194</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>91772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1621,25 +1613,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1649,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>746165</v>
+        <v>746112</v>
       </c>
       <c r="R11" t="n">
-        <v>7151172</v>
+        <v>7151271</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1711,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117524180</v>
+        <v>117524183</v>
       </c>
       <c r="B12" t="n">
-        <v>90464</v>
+        <v>57303</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1723,38 +1715,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>746038</v>
+        <v>746086</v>
       </c>
       <c r="R12" t="n">
-        <v>7151191</v>
+        <v>7151181</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1813,10 +1813,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117524187</v>
+        <v>117524192</v>
       </c>
       <c r="B13" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746577</v>
+        <v>746862</v>
       </c>
       <c r="R13" t="n">
-        <v>7151343</v>
+        <v>7151254</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117524193</v>
+        <v>117524185</v>
       </c>
       <c r="B14" t="n">
-        <v>90743</v>
+        <v>91962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1927,25 +1927,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>746383</v>
+        <v>746480</v>
       </c>
       <c r="R14" t="n">
-        <v>7151352</v>
+        <v>7151410</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117545329</v>
+        <v>117545351</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>57303</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,26 +2033,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2060,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>746339</v>
+        <v>746294</v>
       </c>
       <c r="R15" t="n">
-        <v>7151351</v>
+        <v>7151340</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,7 +2109,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2123,7 +2127,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117545170</v>
+        <v>117544917</v>
       </c>
       <c r="B16" t="n">
         <v>78480</v>
@@ -2166,10 +2170,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>746627</v>
+        <v>746804</v>
       </c>
       <c r="R16" t="n">
-        <v>7151373</v>
+        <v>7151278</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,7 +2233,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117545308</v>
+        <v>117545443</v>
       </c>
       <c r="B17" t="n">
         <v>78480</v>
@@ -2272,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>746467</v>
+        <v>746180</v>
       </c>
       <c r="R17" t="n">
-        <v>7151334</v>
+        <v>7151366</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,10 +2339,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117545016</v>
+        <v>117545393</v>
       </c>
       <c r="B18" t="n">
-        <v>78480</v>
+        <v>91962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2351,21 +2355,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2378,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>746778</v>
+        <v>746185</v>
       </c>
       <c r="R18" t="n">
-        <v>7151306</v>
+        <v>7151374</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2441,10 +2445,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117545037</v>
+        <v>117545024</v>
       </c>
       <c r="B19" t="n">
-        <v>82259</v>
+        <v>90841</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2453,25 +2457,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>2062</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2547,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117545020</v>
+        <v>117545343</v>
       </c>
       <c r="B20" t="n">
-        <v>90499</v>
+        <v>90517</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2563,21 +2567,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2590,10 +2594,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746778</v>
+        <v>746294</v>
       </c>
       <c r="R20" t="n">
-        <v>7151306</v>
+        <v>7151340</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,10 +2657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117545393</v>
+        <v>117545242</v>
       </c>
       <c r="B21" t="n">
-        <v>91962</v>
+        <v>78480</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2669,21 +2673,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2696,10 +2700,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>746185</v>
+        <v>746514</v>
       </c>
       <c r="R21" t="n">
-        <v>7151374</v>
+        <v>7151399</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,10 +2763,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117545126</v>
+        <v>117545666</v>
       </c>
       <c r="B22" t="n">
-        <v>91962</v>
+        <v>78480</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2775,21 +2779,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2802,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>746663</v>
+        <v>746425</v>
       </c>
       <c r="R22" t="n">
-        <v>7151376</v>
+        <v>7151306</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,7 +2869,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117545206</v>
+        <v>117545126</v>
       </c>
       <c r="B23" t="n">
         <v>91962</v>
@@ -2908,10 +2912,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>746602</v>
+        <v>746663</v>
       </c>
       <c r="R23" t="n">
-        <v>7151380</v>
+        <v>7151376</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2971,7 +2975,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117545069</v>
+        <v>117545513</v>
       </c>
       <c r="B24" t="n">
         <v>78480</v>
@@ -3014,10 +3018,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>746760</v>
+        <v>746253</v>
       </c>
       <c r="R24" t="n">
-        <v>7151309</v>
+        <v>7151174</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3077,7 +3081,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117545705</v>
+        <v>117545216</v>
       </c>
       <c r="B25" t="n">
         <v>78480</v>
@@ -3120,10 +3124,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>746468</v>
+        <v>746539</v>
       </c>
       <c r="R25" t="n">
-        <v>7151282</v>
+        <v>7151362</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3183,10 +3187,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117544954</v>
+        <v>117545366</v>
       </c>
       <c r="B26" t="n">
-        <v>78480</v>
+        <v>57303</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3199,26 +3203,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3226,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>746804</v>
+        <v>746190</v>
       </c>
       <c r="R26" t="n">
-        <v>7151278</v>
+        <v>7151377</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3270,7 +3279,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3289,10 +3297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117545372</v>
+        <v>117545202</v>
       </c>
       <c r="B27" t="n">
-        <v>78480</v>
+        <v>90743</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3301,25 +3309,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3332,10 +3340,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>746190</v>
+        <v>746602</v>
       </c>
       <c r="R27" t="n">
-        <v>7151377</v>
+        <v>7151380</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,7 +3403,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117545242</v>
+        <v>117545255</v>
       </c>
       <c r="B28" t="n">
         <v>78480</v>
@@ -3438,10 +3446,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>746514</v>
+        <v>746504</v>
       </c>
       <c r="R28" t="n">
-        <v>7151399</v>
+        <v>7151437</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3501,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117545187</v>
+        <v>117545705</v>
       </c>
       <c r="B29" t="n">
-        <v>90464</v>
+        <v>78480</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3513,25 +3521,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3544,10 +3552,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746603</v>
+        <v>746468</v>
       </c>
       <c r="R29" t="n">
-        <v>7151388</v>
+        <v>7151282</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3607,7 +3615,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117545269</v>
+        <v>117545069</v>
       </c>
       <c r="B30" t="n">
         <v>78480</v>
@@ -3650,10 +3658,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746495</v>
+        <v>746760</v>
       </c>
       <c r="R30" t="n">
-        <v>7151425</v>
+        <v>7151309</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3713,7 +3721,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117545366</v>
+        <v>117545228</v>
       </c>
       <c r="B31" t="n">
         <v>57303</v>
@@ -3761,10 +3769,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746190</v>
+        <v>746539</v>
       </c>
       <c r="R31" t="n">
-        <v>7151377</v>
+        <v>7151362</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,7 +3831,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117545155</v>
+        <v>117545617</v>
       </c>
       <c r="B32" t="n">
         <v>78480</v>
@@ -3866,10 +3874,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746647</v>
+        <v>746353</v>
       </c>
       <c r="R32" t="n">
-        <v>7151373</v>
+        <v>7151231</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3929,7 +3937,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117545315</v>
+        <v>117545467</v>
       </c>
       <c r="B33" t="n">
         <v>78480</v>
@@ -3972,10 +3980,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>746378</v>
+        <v>746175</v>
       </c>
       <c r="R33" t="n">
-        <v>7151348</v>
+        <v>7151164</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4035,10 +4043,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117545209</v>
+        <v>117545187</v>
       </c>
       <c r="B34" t="n">
-        <v>78480</v>
+        <v>90464</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4047,25 +4055,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4078,10 +4086,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746602</v>
+        <v>746603</v>
       </c>
       <c r="R34" t="n">
-        <v>7151380</v>
+        <v>7151388</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,7 +4149,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117545216</v>
+        <v>117545001</v>
       </c>
       <c r="B35" t="n">
         <v>78480</v>
@@ -4176,7 +4184,11 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4184,10 +4196,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>746539</v>
+        <v>746795</v>
       </c>
       <c r="R35" t="n">
-        <v>7151362</v>
+        <v>7151298</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4247,10 +4259,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117545024</v>
+        <v>117545098</v>
       </c>
       <c r="B36" t="n">
-        <v>90841</v>
+        <v>78480</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4259,25 +4271,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4290,10 +4302,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746778</v>
+        <v>746745</v>
       </c>
       <c r="R36" t="n">
-        <v>7151306</v>
+        <v>7151321</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4353,10 +4365,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117545228</v>
+        <v>117545269</v>
       </c>
       <c r="B37" t="n">
-        <v>57303</v>
+        <v>78480</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4369,31 +4381,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4401,10 +4408,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746539</v>
+        <v>746495</v>
       </c>
       <c r="R37" t="n">
-        <v>7151362</v>
+        <v>7151425</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4445,6 +4452,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4463,10 +4471,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117545617</v>
+        <v>117545020</v>
       </c>
       <c r="B38" t="n">
-        <v>78480</v>
+        <v>90499</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4479,21 +4487,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4506,10 +4514,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746353</v>
+        <v>746778</v>
       </c>
       <c r="R38" t="n">
-        <v>7151231</v>
+        <v>7151306</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4569,7 +4577,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117545513</v>
+        <v>117545016</v>
       </c>
       <c r="B39" t="n">
         <v>78480</v>
@@ -4612,10 +4620,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746253</v>
+        <v>746778</v>
       </c>
       <c r="R39" t="n">
-        <v>7151174</v>
+        <v>7151306</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4675,7 +4683,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117545098</v>
+        <v>117545308</v>
       </c>
       <c r="B40" t="n">
         <v>78480</v>
@@ -4718,10 +4726,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746745</v>
+        <v>746467</v>
       </c>
       <c r="R40" t="n">
-        <v>7151321</v>
+        <v>7151334</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4781,10 +4789,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117545351</v>
+        <v>117545170</v>
       </c>
       <c r="B41" t="n">
-        <v>57303</v>
+        <v>78480</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4797,31 +4805,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4829,10 +4832,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746294</v>
+        <v>746627</v>
       </c>
       <c r="R41" t="n">
-        <v>7151340</v>
+        <v>7151373</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4873,6 +4876,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4891,7 +4895,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117545679</v>
+        <v>117545209</v>
       </c>
       <c r="B42" t="n">
         <v>78480</v>
@@ -4934,10 +4938,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746425</v>
+        <v>746602</v>
       </c>
       <c r="R42" t="n">
-        <v>7151306</v>
+        <v>7151380</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4997,10 +5001,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117545001</v>
+        <v>117545409</v>
       </c>
       <c r="B43" t="n">
-        <v>78480</v>
+        <v>91962</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5013,30 +5017,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746795</v>
+        <v>746180</v>
       </c>
       <c r="R43" t="n">
-        <v>7151298</v>
+        <v>7151366</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5107,10 +5107,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117545343</v>
+        <v>117545586</v>
       </c>
       <c r="B44" t="n">
-        <v>90517</v>
+        <v>91962</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5123,21 +5123,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>2079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746294</v>
+        <v>746302</v>
       </c>
       <c r="R44" t="n">
-        <v>7151340</v>
+        <v>7151180</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5213,7 +5213,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117545443</v>
+        <v>117545372</v>
       </c>
       <c r="B45" t="n">
         <v>78480</v>
@@ -5256,10 +5256,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746180</v>
+        <v>746190</v>
       </c>
       <c r="R45" t="n">
-        <v>7151366</v>
+        <v>7151377</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5319,7 +5319,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117545255</v>
+        <v>117545315</v>
       </c>
       <c r="B46" t="n">
         <v>78480</v>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746504</v>
+        <v>746378</v>
       </c>
       <c r="R46" t="n">
-        <v>7151437</v>
+        <v>7151348</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5425,10 +5425,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117545409</v>
+        <v>117545155</v>
       </c>
       <c r="B47" t="n">
-        <v>91962</v>
+        <v>78480</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5441,21 +5441,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746180</v>
+        <v>746647</v>
       </c>
       <c r="R47" t="n">
-        <v>7151366</v>
+        <v>7151373</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117545467</v>
+        <v>117545658</v>
       </c>
       <c r="B48" t="n">
         <v>78480</v>
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746175</v>
+        <v>746412</v>
       </c>
       <c r="R48" t="n">
-        <v>7151164</v>
+        <v>7151271</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5637,10 +5637,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117545586</v>
+        <v>117545329</v>
       </c>
       <c r="B49" t="n">
-        <v>91962</v>
+        <v>78480</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5653,21 +5653,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5680,10 +5680,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>746302</v>
+        <v>746339</v>
       </c>
       <c r="R49" t="n">
-        <v>7151180</v>
+        <v>7151351</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5743,10 +5743,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117545658</v>
+        <v>117545206</v>
       </c>
       <c r="B50" t="n">
-        <v>78480</v>
+        <v>91962</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5759,21 +5759,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>746412</v>
+        <v>746602</v>
       </c>
       <c r="R50" t="n">
-        <v>7151271</v>
+        <v>7151380</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,10 +5849,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117545202</v>
+        <v>117545037</v>
       </c>
       <c r="B51" t="n">
-        <v>90743</v>
+        <v>82259</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5861,25 +5861,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>65</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5892,10 +5892,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>746602</v>
+        <v>746778</v>
       </c>
       <c r="R51" t="n">
-        <v>7151380</v>
+        <v>7151306</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117676761</v>
+        <v>117676627</v>
       </c>
       <c r="B53" t="n">
-        <v>82259</v>
+        <v>90519</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6081,21 +6081,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>746776</v>
+        <v>746462</v>
       </c>
       <c r="R53" t="n">
-        <v>7151305</v>
+        <v>7151345</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6175,10 +6175,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117676749</v>
+        <v>117676727</v>
       </c>
       <c r="B54" t="n">
-        <v>78480</v>
+        <v>82259</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6191,34 +6191,30 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6226,10 +6222,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>746699</v>
+        <v>746598</v>
       </c>
       <c r="R54" t="n">
-        <v>7151334</v>
+        <v>7151380</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6262,11 +6258,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>rikligt och fertil!</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6294,10 +6285,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117676654</v>
+        <v>117676761</v>
       </c>
       <c r="B55" t="n">
-        <v>90513</v>
+        <v>82259</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6310,21 +6301,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6341,10 +6332,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>746499</v>
+        <v>746776</v>
       </c>
       <c r="R55" t="n">
-        <v>7151327</v>
+        <v>7151305</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6404,10 +6395,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117676727</v>
+        <v>117676749</v>
       </c>
       <c r="B56" t="n">
-        <v>82259</v>
+        <v>78480</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6420,30 +6411,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6451,10 +6446,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>746598</v>
+        <v>746699</v>
       </c>
       <c r="R56" t="n">
-        <v>7151380</v>
+        <v>7151334</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6487,6 +6482,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>rikligt och fertil!</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6624,10 +6624,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117676743</v>
+        <v>117676664</v>
       </c>
       <c r="B58" t="n">
-        <v>57303</v>
+        <v>90499</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6640,27 +6640,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6668,10 +6671,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>746699</v>
+        <v>746509</v>
       </c>
       <c r="R58" t="n">
-        <v>7151334</v>
+        <v>7151174</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6706,17 +6709,13 @@
           <t>2024-06-03</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6735,10 +6734,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117676779</v>
+        <v>117676654</v>
       </c>
       <c r="B59" t="n">
-        <v>90499</v>
+        <v>90513</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6751,21 +6750,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6782,10 +6781,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746778</v>
+        <v>746499</v>
       </c>
       <c r="R59" t="n">
-        <v>7151297</v>
+        <v>7151327</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6845,10 +6844,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117676627</v>
+        <v>117676743</v>
       </c>
       <c r="B60" t="n">
-        <v>90519</v>
+        <v>57303</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6861,30 +6860,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6892,10 +6888,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746462</v>
+        <v>746699</v>
       </c>
       <c r="R60" t="n">
-        <v>7151345</v>
+        <v>7151334</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6930,13 +6926,17 @@
           <t>2024-06-03</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6955,7 +6955,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117676664</v>
+        <v>117676779</v>
       </c>
       <c r="B61" t="n">
         <v>90499</v>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>746509</v>
+        <v>746778</v>
       </c>
       <c r="R61" t="n">
-        <v>7151174</v>
+        <v>7151297</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117524184</v>
+        <v>117524189</v>
       </c>
       <c r="B2" t="n">
-        <v>57303</v>
+        <v>78482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746524</v>
+        <v>746165</v>
       </c>
       <c r="R2" t="n">
-        <v>7151386</v>
+        <v>7151172</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -785,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117524188</v>
+        <v>117524183</v>
       </c>
       <c r="B3" t="n">
-        <v>90513</v>
+        <v>57304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746687</v>
+        <v>746086</v>
       </c>
       <c r="R3" t="n">
-        <v>7151251</v>
+        <v>7151181</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117524190</v>
+        <v>117524188</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>90515</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746257</v>
+        <v>746687</v>
       </c>
       <c r="R4" t="n">
-        <v>7151339</v>
+        <v>7151251</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117524180</v>
+        <v>117524192</v>
       </c>
       <c r="B5" t="n">
-        <v>90464</v>
+        <v>78482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,25 +1001,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>746038</v>
+        <v>746862</v>
       </c>
       <c r="R5" t="n">
-        <v>7151191</v>
+        <v>7151254</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117524187</v>
+        <v>117524194</v>
       </c>
       <c r="B6" t="n">
-        <v>78217</v>
+        <v>91774</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,25 +1103,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746577</v>
+        <v>746112</v>
       </c>
       <c r="R6" t="n">
-        <v>7151343</v>
+        <v>7151271</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117524193</v>
+        <v>117524191</v>
       </c>
       <c r="B7" t="n">
-        <v>90743</v>
+        <v>78482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,25 +1205,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746383</v>
+        <v>746648</v>
       </c>
       <c r="R7" t="n">
-        <v>7151352</v>
+        <v>7151376</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117524186</v>
+        <v>117524180</v>
       </c>
       <c r="B8" t="n">
-        <v>78217</v>
+        <v>90466</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,25 +1307,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746456</v>
+        <v>746038</v>
       </c>
       <c r="R8" t="n">
-        <v>7151357</v>
+        <v>7151191</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1397,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117524191</v>
+        <v>117524186</v>
       </c>
       <c r="B9" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1413,21 +1413,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>746648</v>
+        <v>746456</v>
       </c>
       <c r="R9" t="n">
-        <v>7151376</v>
+        <v>7151357</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117524189</v>
+        <v>117524185</v>
       </c>
       <c r="B10" t="n">
-        <v>78480</v>
+        <v>91964</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,21 +1515,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>746165</v>
+        <v>746480</v>
       </c>
       <c r="R10" t="n">
-        <v>7151172</v>
+        <v>7151410</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1601,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117524194</v>
+        <v>117524193</v>
       </c>
       <c r="B11" t="n">
-        <v>91772</v>
+        <v>90745</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1613,25 +1613,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>746112</v>
+        <v>746383</v>
       </c>
       <c r="R11" t="n">
-        <v>7151271</v>
+        <v>7151352</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117524183</v>
+        <v>117524184</v>
       </c>
       <c r="B12" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>746086</v>
+        <v>746524</v>
       </c>
       <c r="R12" t="n">
-        <v>7151181</v>
+        <v>7151386</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1813,10 +1813,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117524192</v>
+        <v>117524190</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746862</v>
+        <v>746257</v>
       </c>
       <c r="R13" t="n">
-        <v>7151254</v>
+        <v>7151339</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117524185</v>
+        <v>117524187</v>
       </c>
       <c r="B14" t="n">
-        <v>91962</v>
+        <v>78219</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,21 +1931,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>746480</v>
+        <v>746577</v>
       </c>
       <c r="R14" t="n">
-        <v>7151410</v>
+        <v>7151343</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117545351</v>
+        <v>117545037</v>
       </c>
       <c r="B15" t="n">
-        <v>57303</v>
+        <v>82261</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,31 +2033,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2065,10 +2060,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>746294</v>
+        <v>746778</v>
       </c>
       <c r="R15" t="n">
-        <v>7151340</v>
+        <v>7151306</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,6 +2104,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2127,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117544917</v>
+        <v>117545016</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2170,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>746804</v>
+        <v>746778</v>
       </c>
       <c r="R16" t="n">
-        <v>7151278</v>
+        <v>7151306</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117545443</v>
+        <v>117545308</v>
       </c>
       <c r="B17" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>746180</v>
+        <v>746467</v>
       </c>
       <c r="R17" t="n">
-        <v>7151366</v>
+        <v>7151334</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117545393</v>
+        <v>117545170</v>
       </c>
       <c r="B18" t="n">
-        <v>91962</v>
+        <v>78482</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2355,21 +2351,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2382,10 +2378,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>746185</v>
+        <v>746627</v>
       </c>
       <c r="R18" t="n">
-        <v>7151374</v>
+        <v>7151373</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,10 +2441,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117545024</v>
+        <v>117545372</v>
       </c>
       <c r="B19" t="n">
-        <v>90841</v>
+        <v>78482</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2457,25 +2453,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2488,10 +2484,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746778</v>
+        <v>746190</v>
       </c>
       <c r="R19" t="n">
-        <v>7151306</v>
+        <v>7151377</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2551,10 +2547,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117545343</v>
+        <v>117544917</v>
       </c>
       <c r="B20" t="n">
-        <v>90517</v>
+        <v>78482</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2567,21 +2563,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2594,10 +2590,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746294</v>
+        <v>746804</v>
       </c>
       <c r="R20" t="n">
-        <v>7151340</v>
+        <v>7151278</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117545242</v>
+        <v>117545069</v>
       </c>
       <c r="B21" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2700,10 +2696,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>746514</v>
+        <v>746760</v>
       </c>
       <c r="R21" t="n">
-        <v>7151399</v>
+        <v>7151309</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,10 +2759,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117545666</v>
+        <v>117545393</v>
       </c>
       <c r="B22" t="n">
-        <v>78480</v>
+        <v>91964</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2779,21 +2775,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2806,10 +2802,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>746425</v>
+        <v>746185</v>
       </c>
       <c r="R22" t="n">
-        <v>7151306</v>
+        <v>7151374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,10 +2865,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117545126</v>
+        <v>117545586</v>
       </c>
       <c r="B23" t="n">
-        <v>91962</v>
+        <v>91964</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2912,10 +2908,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>746663</v>
+        <v>746302</v>
       </c>
       <c r="R23" t="n">
-        <v>7151376</v>
+        <v>7151180</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2975,10 +2971,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117545513</v>
+        <v>117545351</v>
       </c>
       <c r="B24" t="n">
-        <v>78480</v>
+        <v>57304</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2991,26 +2987,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3018,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>746253</v>
+        <v>746294</v>
       </c>
       <c r="R24" t="n">
-        <v>7151174</v>
+        <v>7151340</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3062,7 +3063,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117545216</v>
+        <v>117545187</v>
       </c>
       <c r="B25" t="n">
-        <v>78480</v>
+        <v>90466</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3093,25 +3093,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>746539</v>
+        <v>746603</v>
       </c>
       <c r="R25" t="n">
-        <v>7151362</v>
+        <v>7151388</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3187,10 +3187,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117545366</v>
+        <v>117545155</v>
       </c>
       <c r="B26" t="n">
-        <v>57303</v>
+        <v>78482</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3203,31 +3203,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3235,10 +3230,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>746190</v>
+        <v>746647</v>
       </c>
       <c r="R26" t="n">
-        <v>7151377</v>
+        <v>7151373</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3279,6 +3274,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3297,10 +3293,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117545202</v>
+        <v>117545255</v>
       </c>
       <c r="B27" t="n">
-        <v>90743</v>
+        <v>78482</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3309,25 +3305,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3340,10 +3336,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>746602</v>
+        <v>746504</v>
       </c>
       <c r="R27" t="n">
-        <v>7151380</v>
+        <v>7151437</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3403,10 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117545255</v>
+        <v>117545705</v>
       </c>
       <c r="B28" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3446,10 +3442,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>746504</v>
+        <v>746468</v>
       </c>
       <c r="R28" t="n">
-        <v>7151437</v>
+        <v>7151282</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3509,10 +3505,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117545705</v>
+        <v>117545001</v>
       </c>
       <c r="B29" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3544,7 +3540,11 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746468</v>
+        <v>746795</v>
       </c>
       <c r="R29" t="n">
-        <v>7151282</v>
+        <v>7151298</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3615,10 +3615,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117545069</v>
+        <v>117545216</v>
       </c>
       <c r="B30" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746760</v>
+        <v>746539</v>
       </c>
       <c r="R30" t="n">
-        <v>7151309</v>
+        <v>7151362</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,10 +3721,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117545228</v>
+        <v>117545209</v>
       </c>
       <c r="B31" t="n">
-        <v>57303</v>
+        <v>78482</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3737,31 +3737,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3769,10 +3764,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746539</v>
+        <v>746602</v>
       </c>
       <c r="R31" t="n">
-        <v>7151362</v>
+        <v>7151380</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3813,6 +3808,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3831,10 +3827,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117545617</v>
+        <v>117545666</v>
       </c>
       <c r="B32" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3874,10 +3870,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746353</v>
+        <v>746425</v>
       </c>
       <c r="R32" t="n">
-        <v>7151231</v>
+        <v>7151306</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3937,10 +3933,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117545467</v>
+        <v>117545617</v>
       </c>
       <c r="B33" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3980,10 +3976,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>746175</v>
+        <v>746353</v>
       </c>
       <c r="R33" t="n">
-        <v>7151164</v>
+        <v>7151231</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4043,10 +4039,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117545187</v>
+        <v>117545202</v>
       </c>
       <c r="B34" t="n">
-        <v>90464</v>
+        <v>90745</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4055,25 +4051,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>65</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4086,10 +4082,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746603</v>
+        <v>746602</v>
       </c>
       <c r="R34" t="n">
-        <v>7151388</v>
+        <v>7151380</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4149,10 +4145,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117545001</v>
+        <v>117545228</v>
       </c>
       <c r="B35" t="n">
-        <v>78480</v>
+        <v>57304</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4165,28 +4161,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4196,10 +4193,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>746795</v>
+        <v>746539</v>
       </c>
       <c r="R35" t="n">
-        <v>7151298</v>
+        <v>7151362</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4240,7 +4237,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4259,10 +4255,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117545098</v>
+        <v>117545315</v>
       </c>
       <c r="B36" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4302,10 +4298,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746745</v>
+        <v>746378</v>
       </c>
       <c r="R36" t="n">
-        <v>7151321</v>
+        <v>7151348</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,10 +4361,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117545269</v>
+        <v>117545366</v>
       </c>
       <c r="B37" t="n">
-        <v>78480</v>
+        <v>57304</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4381,26 +4377,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4408,10 +4409,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746495</v>
+        <v>746190</v>
       </c>
       <c r="R37" t="n">
-        <v>7151425</v>
+        <v>7151377</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4452,7 +4453,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4471,10 +4471,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117545020</v>
+        <v>117545024</v>
       </c>
       <c r="B38" t="n">
-        <v>90499</v>
+        <v>90843</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4483,25 +4483,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117545016</v>
+        <v>117545098</v>
       </c>
       <c r="B39" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746778</v>
+        <v>746745</v>
       </c>
       <c r="R39" t="n">
-        <v>7151306</v>
+        <v>7151321</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4683,10 +4683,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117545308</v>
+        <v>117545658</v>
       </c>
       <c r="B40" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746467</v>
+        <v>746412</v>
       </c>
       <c r="R40" t="n">
-        <v>7151334</v>
+        <v>7151271</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117545170</v>
+        <v>117545343</v>
       </c>
       <c r="B41" t="n">
-        <v>78480</v>
+        <v>90519</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4805,21 +4805,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746627</v>
+        <v>746294</v>
       </c>
       <c r="R41" t="n">
-        <v>7151373</v>
+        <v>7151340</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4895,10 +4895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117545209</v>
+        <v>117545513</v>
       </c>
       <c r="B42" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746602</v>
+        <v>746253</v>
       </c>
       <c r="R42" t="n">
-        <v>7151380</v>
+        <v>7151174</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117545409</v>
+        <v>117545329</v>
       </c>
       <c r="B43" t="n">
-        <v>91962</v>
+        <v>78482</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746180</v>
+        <v>746339</v>
       </c>
       <c r="R43" t="n">
-        <v>7151366</v>
+        <v>7151351</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5107,10 +5107,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117545586</v>
+        <v>117545409</v>
       </c>
       <c r="B44" t="n">
-        <v>91962</v>
+        <v>91964</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746302</v>
+        <v>746180</v>
       </c>
       <c r="R44" t="n">
-        <v>7151180</v>
+        <v>7151366</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5213,10 +5213,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117545372</v>
+        <v>117545126</v>
       </c>
       <c r="B45" t="n">
-        <v>78480</v>
+        <v>91964</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5229,21 +5229,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5256,10 +5256,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746190</v>
+        <v>746663</v>
       </c>
       <c r="R45" t="n">
-        <v>7151377</v>
+        <v>7151376</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5319,10 +5319,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117545315</v>
+        <v>117545206</v>
       </c>
       <c r="B46" t="n">
-        <v>78480</v>
+        <v>91964</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5335,21 +5335,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746378</v>
+        <v>746602</v>
       </c>
       <c r="R46" t="n">
-        <v>7151348</v>
+        <v>7151380</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5425,10 +5425,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117545155</v>
+        <v>117545242</v>
       </c>
       <c r="B47" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746647</v>
+        <v>746514</v>
       </c>
       <c r="R47" t="n">
-        <v>7151373</v>
+        <v>7151399</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5531,10 +5531,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117545658</v>
+        <v>117545467</v>
       </c>
       <c r="B48" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746412</v>
+        <v>746175</v>
       </c>
       <c r="R48" t="n">
-        <v>7151271</v>
+        <v>7151164</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5637,10 +5637,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117545329</v>
+        <v>117545269</v>
       </c>
       <c r="B49" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5680,10 +5680,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>746339</v>
+        <v>746495</v>
       </c>
       <c r="R49" t="n">
-        <v>7151351</v>
+        <v>7151425</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5743,10 +5743,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117545206</v>
+        <v>117545443</v>
       </c>
       <c r="B50" t="n">
-        <v>91962</v>
+        <v>78482</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5759,21 +5759,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>746602</v>
+        <v>746180</v>
       </c>
       <c r="R50" t="n">
-        <v>7151380</v>
+        <v>7151366</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,10 +5849,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117545037</v>
+        <v>117545020</v>
       </c>
       <c r="B51" t="n">
-        <v>82259</v>
+        <v>90501</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5958,7 +5958,7 @@
         <v>117588581</v>
       </c>
       <c r="B52" t="n">
-        <v>56549</v>
+        <v>56550</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117676627</v>
+        <v>117676749</v>
       </c>
       <c r="B53" t="n">
-        <v>90519</v>
+        <v>78482</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6081,30 +6081,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6112,10 +6116,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>746462</v>
+        <v>746699</v>
       </c>
       <c r="R53" t="n">
-        <v>7151345</v>
+        <v>7151334</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6148,6 +6152,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>rikligt och fertil!</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6175,10 +6184,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117676727</v>
+        <v>117676664</v>
       </c>
       <c r="B54" t="n">
-        <v>82259</v>
+        <v>90501</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6191,21 +6200,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6222,10 +6231,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>746598</v>
+        <v>746509</v>
       </c>
       <c r="R54" t="n">
-        <v>7151380</v>
+        <v>7151174</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6285,10 +6294,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117676761</v>
+        <v>117676654</v>
       </c>
       <c r="B55" t="n">
-        <v>82259</v>
+        <v>90515</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6301,21 +6310,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6332,10 +6341,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>746776</v>
+        <v>746499</v>
       </c>
       <c r="R55" t="n">
-        <v>7151305</v>
+        <v>7151327</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6395,10 +6404,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117676749</v>
+        <v>117676743</v>
       </c>
       <c r="B56" t="n">
-        <v>78480</v>
+        <v>57304</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6411,34 +6420,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6486,7 +6488,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>rikligt och fertil!</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6495,7 +6497,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6514,10 +6515,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117676735</v>
+        <v>117676779</v>
       </c>
       <c r="B57" t="n">
-        <v>90743</v>
+        <v>90501</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6526,25 +6527,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>65</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6561,10 +6562,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>746615</v>
+        <v>746778</v>
       </c>
       <c r="R57" t="n">
-        <v>7151397</v>
+        <v>7151297</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6624,10 +6625,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117676664</v>
+        <v>117676727</v>
       </c>
       <c r="B58" t="n">
-        <v>90499</v>
+        <v>82261</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6640,21 +6641,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6671,10 +6672,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>746509</v>
+        <v>746598</v>
       </c>
       <c r="R58" t="n">
-        <v>7151174</v>
+        <v>7151380</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6734,10 +6735,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117676654</v>
+        <v>117676735</v>
       </c>
       <c r="B59" t="n">
-        <v>90513</v>
+        <v>90745</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6746,25 +6747,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>65</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6781,10 +6782,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746499</v>
+        <v>746615</v>
       </c>
       <c r="R59" t="n">
-        <v>7151327</v>
+        <v>7151397</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6844,10 +6845,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117676743</v>
+        <v>117676627</v>
       </c>
       <c r="B60" t="n">
-        <v>57303</v>
+        <v>90521</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6860,27 +6861,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6888,10 +6892,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746699</v>
+        <v>746462</v>
       </c>
       <c r="R60" t="n">
-        <v>7151334</v>
+        <v>7151345</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6926,17 +6930,13 @@
           <t>2024-06-03</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6955,10 +6955,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117676779</v>
+        <v>117676761</v>
       </c>
       <c r="B61" t="n">
-        <v>90499</v>
+        <v>82261</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6971,21 +6971,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>746778</v>
+        <v>746776</v>
       </c>
       <c r="R61" t="n">
-        <v>7151297</v>
+        <v>7151305</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -3933,10 +3933,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117545617</v>
+        <v>117545202</v>
       </c>
       <c r="B33" t="n">
-        <v>78482</v>
+        <v>90745</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3945,25 +3945,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>746353</v>
+        <v>746602</v>
       </c>
       <c r="R33" t="n">
-        <v>7151231</v>
+        <v>7151380</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4039,10 +4039,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117545202</v>
+        <v>117545617</v>
       </c>
       <c r="B34" t="n">
-        <v>90745</v>
+        <v>78482</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4051,25 +4051,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4082,10 +4082,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746602</v>
+        <v>746353</v>
       </c>
       <c r="R34" t="n">
-        <v>7151380</v>
+        <v>7151231</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -7068,7 +7068,7 @@
         <v>118676972</v>
       </c>
       <c r="B62" t="n">
-        <v>90524</v>
+        <v>90531</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -7176,10 +7176,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120063383</v>
+        <v>120061583</v>
       </c>
       <c r="B63" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7188,25 +7188,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746303</v>
+        <v>746472</v>
       </c>
       <c r="R63" t="n">
-        <v>7151246</v>
+        <v>7151401</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7288,10 +7288,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120061583</v>
+        <v>120062044</v>
       </c>
       <c r="B64" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7300,25 +7300,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7328,10 +7328,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746472</v>
+        <v>746344</v>
       </c>
       <c r="R64" t="n">
-        <v>7151401</v>
+        <v>7151353</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7400,10 +7400,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120062044</v>
+        <v>120063383</v>
       </c>
       <c r="B65" t="n">
-        <v>91884</v>
+        <v>91863</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7416,21 +7416,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746344</v>
+        <v>746303</v>
       </c>
       <c r="R65" t="n">
-        <v>7151353</v>
+        <v>7151246</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7736,10 +7736,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120061233</v>
+        <v>120062185</v>
       </c>
       <c r="B68" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7748,25 +7748,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746597</v>
+        <v>746401</v>
       </c>
       <c r="R68" t="n">
-        <v>7151440</v>
+        <v>7151292</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7848,10 +7848,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120062185</v>
+        <v>120061233</v>
       </c>
       <c r="B69" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7860,25 +7860,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7888,10 +7888,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746401</v>
+        <v>746597</v>
       </c>
       <c r="R69" t="n">
-        <v>7151292</v>
+        <v>7151440</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7960,10 +7960,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120064386</v>
+        <v>120061607</v>
       </c>
       <c r="B70" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7972,41 +7972,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
+          <t>Vintjärnen, Vintjärnen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746535</v>
+        <v>746453</v>
       </c>
       <c r="R70" t="n">
-        <v>7151171</v>
+        <v>7151408</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8060,22 +8060,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120061607</v>
+        <v>120061725</v>
       </c>
       <c r="B71" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746453</v>
+        <v>746444</v>
       </c>
       <c r="R71" t="n">
-        <v>7151408</v>
+        <v>7151382</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8184,10 +8184,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120061725</v>
+        <v>120064386</v>
       </c>
       <c r="B72" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8196,41 +8196,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vintjärnen, Vintjärnen, Vb</t>
+          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746444</v>
+        <v>746535</v>
       </c>
       <c r="R72" t="n">
-        <v>7151382</v>
+        <v>7151171</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8284,12 +8284,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8968,10 +8968,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120061645</v>
+        <v>120059872</v>
       </c>
       <c r="B79" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8980,25 +8980,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746450</v>
+        <v>746557</v>
       </c>
       <c r="R79" t="n">
-        <v>7151380</v>
+        <v>7151556</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9080,10 +9080,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120059872</v>
+        <v>120061645</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9092,25 +9092,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746557</v>
+        <v>746450</v>
       </c>
       <c r="R80" t="n">
-        <v>7151556</v>
+        <v>7151380</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9192,7 +9192,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120063693</v>
+        <v>120063963</v>
       </c>
       <c r="B81" t="n">
         <v>91840</v>
@@ -9232,13 +9232,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746319</v>
+        <v>746301</v>
       </c>
       <c r="R81" t="n">
-        <v>7151210</v>
+        <v>7151207</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9292,19 +9292,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120063963</v>
+        <v>120063693</v>
       </c>
       <c r="B82" t="n">
         <v>91840</v>
@@ -9344,13 +9344,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746301</v>
+        <v>746319</v>
       </c>
       <c r="R82" t="n">
-        <v>7151207</v>
+        <v>7151210</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9404,12 +9404,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -12056,10 +12056,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120079799</v>
+        <v>120080310</v>
       </c>
       <c r="B107" t="n">
-        <v>90562</v>
+        <v>91821</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12068,41 +12068,44 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>6055</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>746840</v>
+        <v>746772</v>
       </c>
       <c r="R107" t="n">
-        <v>7151151</v>
+        <v>7151182</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12134,34 +12137,40 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120079814</v>
+        <v>120079799</v>
       </c>
       <c r="B108" t="n">
-        <v>91840</v>
+        <v>90562</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12170,25 +12179,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12198,10 +12207,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>746510</v>
+        <v>746840</v>
       </c>
       <c r="R108" t="n">
-        <v>7151225</v>
+        <v>7151151</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -12260,10 +12269,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120086264</v>
+        <v>120079814</v>
       </c>
       <c r="B109" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12272,25 +12281,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12300,13 +12309,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>746539</v>
+        <v>746510</v>
       </c>
       <c r="R109" t="n">
-        <v>7151522</v>
+        <v>7151225</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12350,22 +12359,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120086243</v>
+        <v>120086264</v>
       </c>
       <c r="B110" t="n">
-        <v>91463</v>
+        <v>92030</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12378,21 +12387,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4745</v>
+        <v>2079</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12402,10 +12411,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>746316</v>
+        <v>746539</v>
       </c>
       <c r="R110" t="n">
-        <v>7151209</v>
+        <v>7151522</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12464,10 +12473,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120080310</v>
+        <v>120086243</v>
       </c>
       <c r="B111" t="n">
-        <v>91821</v>
+        <v>91463</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12476,41 +12485,38 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6055</v>
+        <v>4745</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>746772</v>
+        <v>746316</v>
       </c>
       <c r="R111" t="n">
-        <v>7151182</v>
+        <v>7151209</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12545,40 +12551,34 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120079816</v>
+        <v>120094137</v>
       </c>
       <c r="B112" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12587,41 +12587,44 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>746534</v>
+        <v>746535</v>
       </c>
       <c r="R112" t="n">
-        <v>7151288</v>
+        <v>7151504</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12659,25 +12662,26 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120080359</v>
+        <v>120079816</v>
       </c>
       <c r="B113" t="n">
         <v>91834</v>
@@ -12710,24 +12714,20 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>746291</v>
+        <v>746534</v>
       </c>
       <c r="R113" t="n">
-        <v>7151137</v>
+        <v>7151288</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12771,22 +12771,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120080328</v>
+        <v>120080359</v>
       </c>
       <c r="B114" t="n">
-        <v>89964</v>
+        <v>91834</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12795,38 +12795,42 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5685</v>
+        <v>4362</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>746590</v>
+        <v>746291</v>
       </c>
       <c r="R114" t="n">
-        <v>7151225</v>
+        <v>7151137</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12869,21 +12873,6 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -12900,10 +12889,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120086268</v>
+        <v>120080328</v>
       </c>
       <c r="B115" t="n">
-        <v>91863</v>
+        <v>89964</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12912,25 +12901,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5966</v>
+        <v>5685</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12940,10 +12929,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>746563</v>
+        <v>746590</v>
       </c>
       <c r="R115" t="n">
-        <v>7151464</v>
+        <v>7151225</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12987,25 +12976,40 @@
       <c r="AG115" t="b">
         <v>0</v>
       </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120086271</v>
+        <v>120086268</v>
       </c>
       <c r="B116" t="n">
-        <v>57421</v>
+        <v>91863</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13014,46 +13018,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103031</v>
+        <v>5966</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>746500</v>
+        <v>746563</v>
       </c>
       <c r="R116" t="n">
-        <v>7151560</v>
+        <v>7151464</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13112,10 +13108,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120086232</v>
+        <v>120086271</v>
       </c>
       <c r="B117" t="n">
-        <v>89633</v>
+        <v>57421</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13124,38 +13120,46 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1962</v>
+        <v>103031</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>746551</v>
+        <v>746500</v>
       </c>
       <c r="R117" t="n">
-        <v>7151485</v>
+        <v>7151560</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13214,10 +13218,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120086303</v>
+        <v>120086232</v>
       </c>
       <c r="B118" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13226,25 +13230,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13254,10 +13258,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>746555</v>
+        <v>746551</v>
       </c>
       <c r="R118" t="n">
-        <v>7151578</v>
+        <v>7151485</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13316,10 +13320,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120086239</v>
+        <v>120086303</v>
       </c>
       <c r="B119" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13328,50 +13332,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>746532</v>
+        <v>746555</v>
       </c>
       <c r="R119" t="n">
-        <v>7151493</v>
+        <v>7151578</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13430,10 +13422,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120094137</v>
+        <v>120086239</v>
       </c>
       <c r="B120" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13442,30 +13434,39 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -13473,10 +13474,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>746535</v>
+        <v>746532</v>
       </c>
       <c r="R120" t="n">
-        <v>7151504</v>
+        <v>7151493</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13517,7 +13518,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13536,10 +13536,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120080331</v>
+        <v>120094355</v>
       </c>
       <c r="B121" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13552,34 +13552,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>746936</v>
+        <v>746451</v>
       </c>
       <c r="R121" t="n">
-        <v>7151139</v>
+        <v>7151341</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13614,51 +13617,32 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120080355</v>
+        <v>120094266</v>
       </c>
       <c r="B122" t="n">
         <v>91840</v>
@@ -13692,16 +13676,19 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>746527</v>
+        <v>746491</v>
       </c>
       <c r="R122" t="n">
-        <v>7151203</v>
+        <v>7151452</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13742,28 +13729,29 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120080333</v>
+        <v>120080331</v>
       </c>
       <c r="B123" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13772,42 +13760,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>746569</v>
+        <v>746936</v>
       </c>
       <c r="R123" t="n">
-        <v>7151265</v>
+        <v>7151139</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13844,7 +13828,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Minst, stort mycel</t>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13855,6 +13839,21 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
@@ -13871,7 +13870,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120080357</v>
+        <v>120080355</v>
       </c>
       <c r="B124" t="n">
         <v>91840</v>
@@ -13911,10 +13910,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>746301</v>
+        <v>746527</v>
       </c>
       <c r="R124" t="n">
-        <v>7151209</v>
+        <v>7151203</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13973,10 +13972,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120086270</v>
+        <v>120080333</v>
       </c>
       <c r="B125" t="n">
-        <v>57421</v>
+        <v>91840</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13989,46 +13988,38 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>746671</v>
+        <v>746569</v>
       </c>
       <c r="R125" t="n">
-        <v>7151554</v>
+        <v>7151265</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14063,6 +14054,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Minst, stort mycel</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -14075,22 +14071,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120086256</v>
+        <v>120080357</v>
       </c>
       <c r="B126" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14103,21 +14099,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14127,10 +14123,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>746576</v>
+        <v>746301</v>
       </c>
       <c r="R126" t="n">
-        <v>7151444</v>
+        <v>7151209</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14177,22 +14173,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120094355</v>
+        <v>120086270</v>
       </c>
       <c r="B127" t="n">
-        <v>91884</v>
+        <v>57421</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14201,30 +14197,39 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5449</v>
+        <v>103031</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -14232,10 +14237,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>746451</v>
+        <v>746671</v>
       </c>
       <c r="R127" t="n">
-        <v>7151341</v>
+        <v>7151554</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14276,7 +14281,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -14295,10 +14299,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120094266</v>
+        <v>120086256</v>
       </c>
       <c r="B128" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14311,37 +14315,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>746491</v>
+        <v>746576</v>
       </c>
       <c r="R128" t="n">
-        <v>7151452</v>
+        <v>7151444</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14382,7 +14383,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -15037,10 +15037,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120094483</v>
+        <v>120080332</v>
       </c>
       <c r="B135" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15049,41 +15049,42 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>746321</v>
+        <v>746560</v>
       </c>
       <c r="R135" t="n">
-        <v>7151245</v>
+        <v>7151291</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15124,26 +15125,25 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120094276</v>
+        <v>120080356</v>
       </c>
       <c r="B136" t="n">
         <v>91840</v>
@@ -15177,19 +15177,16 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>746476</v>
+        <v>746499</v>
       </c>
       <c r="R136" t="n">
-        <v>7151446</v>
+        <v>7151195</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15230,29 +15227,28 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120080332</v>
+        <v>120094483</v>
       </c>
       <c r="B137" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15261,42 +15257,41 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>746560</v>
+        <v>746321</v>
       </c>
       <c r="R137" t="n">
-        <v>7151291</v>
+        <v>7151245</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15337,25 +15332,26 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120080356</v>
+        <v>120094276</v>
       </c>
       <c r="B138" t="n">
         <v>91840</v>
@@ -15389,16 +15385,19 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>746499</v>
+        <v>746476</v>
       </c>
       <c r="R138" t="n">
-        <v>7151195</v>
+        <v>7151446</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15439,18 +15438,19 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -15968,7 +15968,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120086301</v>
+        <v>120080334</v>
       </c>
       <c r="B144" t="n">
         <v>91840</v>
@@ -16001,17 +16001,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>746566</v>
+        <v>746537</v>
       </c>
       <c r="R144" t="n">
-        <v>7151468</v>
+        <v>7151303</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16058,22 +16062,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120086235</v>
+        <v>120086301</v>
       </c>
       <c r="B145" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16082,25 +16086,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16110,10 +16114,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>746515</v>
+        <v>746566</v>
       </c>
       <c r="R145" t="n">
-        <v>7151568</v>
+        <v>7151468</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16172,10 +16176,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120080334</v>
+        <v>120086235</v>
       </c>
       <c r="B146" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16184,42 +16188,38 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>746537</v>
+        <v>746515</v>
       </c>
       <c r="R146" t="n">
-        <v>7151303</v>
+        <v>7151568</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16266,12 +16266,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -16609,10 +16609,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120094777</v>
+        <v>120086237</v>
       </c>
       <c r="B150" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16621,41 +16621,38 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>746478</v>
+        <v>746561</v>
       </c>
       <c r="R150" t="n">
-        <v>7151377</v>
+        <v>7151472</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16696,7 +16693,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16715,10 +16711,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120086237</v>
+        <v>120094777</v>
       </c>
       <c r="B151" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16727,38 +16723,41 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>746561</v>
+        <v>746478</v>
       </c>
       <c r="R151" t="n">
-        <v>7151472</v>
+        <v>7151377</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16799,6 +16798,7 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -7176,7 +7176,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120061583</v>
+        <v>120064725</v>
       </c>
       <c r="B63" t="n">
         <v>91840</v>
@@ -7212,17 +7212,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vintjärnen, Vintjärnen, Vb</t>
+          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746472</v>
+        <v>746535</v>
       </c>
       <c r="R63" t="n">
-        <v>7151401</v>
+        <v>7151171</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7276,22 +7276,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120062044</v>
+        <v>120061686</v>
       </c>
       <c r="B64" t="n">
-        <v>91884</v>
+        <v>91863</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7304,21 +7304,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7328,10 +7328,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746344</v>
+        <v>746448</v>
       </c>
       <c r="R64" t="n">
-        <v>7151353</v>
+        <v>7151388</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7512,10 +7512,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120061686</v>
+        <v>120062185</v>
       </c>
       <c r="B66" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7524,25 +7524,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746448</v>
+        <v>746401</v>
       </c>
       <c r="R66" t="n">
-        <v>7151388</v>
+        <v>7151292</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7624,7 +7624,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120059636</v>
+        <v>120061860</v>
       </c>
       <c r="B67" t="n">
         <v>91840</v>
@@ -7664,10 +7664,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746602</v>
+        <v>746423</v>
       </c>
       <c r="R67" t="n">
-        <v>7151535</v>
+        <v>7151350</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7736,7 +7736,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120062185</v>
+        <v>120064407</v>
       </c>
       <c r="B68" t="n">
         <v>91840</v>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746401</v>
+        <v>746440</v>
       </c>
       <c r="R68" t="n">
-        <v>7151292</v>
+        <v>7151291</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7848,10 +7848,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120061233</v>
+        <v>120059872</v>
       </c>
       <c r="B69" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7860,25 +7860,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7888,10 +7888,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746597</v>
+        <v>746557</v>
       </c>
       <c r="R69" t="n">
-        <v>7151440</v>
+        <v>7151556</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7960,10 +7960,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120061607</v>
+        <v>120062044</v>
       </c>
       <c r="B70" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7976,21 +7976,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746453</v>
+        <v>746344</v>
       </c>
       <c r="R70" t="n">
-        <v>7151408</v>
+        <v>7151353</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8184,7 +8184,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120064386</v>
+        <v>120061534</v>
       </c>
       <c r="B72" t="n">
         <v>91840</v>
@@ -8220,17 +8220,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
+          <t>Vintjärnen, Vintjärnen, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746535</v>
+        <v>746467</v>
       </c>
       <c r="R72" t="n">
-        <v>7151171</v>
+        <v>7151403</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8284,22 +8284,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120063287</v>
+        <v>120061233</v>
       </c>
       <c r="B73" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8312,21 +8312,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8336,10 +8336,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746369</v>
+        <v>746597</v>
       </c>
       <c r="R73" t="n">
-        <v>7151254</v>
+        <v>7151440</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8408,7 +8408,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120061860</v>
+        <v>120061583</v>
       </c>
       <c r="B74" t="n">
         <v>91840</v>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746423</v>
+        <v>746472</v>
       </c>
       <c r="R74" t="n">
-        <v>7151350</v>
+        <v>7151401</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8520,10 +8520,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120063487</v>
+        <v>120063728</v>
       </c>
       <c r="B75" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8536,21 +8536,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746300</v>
+        <v>746298</v>
       </c>
       <c r="R75" t="n">
-        <v>7151231</v>
+        <v>7151222</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8632,10 +8632,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120061247</v>
+        <v>120063551</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8644,25 +8644,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746541</v>
+        <v>746308</v>
       </c>
       <c r="R76" t="n">
-        <v>7151441</v>
+        <v>7151219</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8744,10 +8744,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120059794</v>
+        <v>120062389</v>
       </c>
       <c r="B77" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8756,25 +8756,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746567</v>
+        <v>746426</v>
       </c>
       <c r="R77" t="n">
-        <v>7151566</v>
+        <v>7151309</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8856,10 +8856,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120062963</v>
+        <v>120062274</v>
       </c>
       <c r="B78" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8868,25 +8868,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746369</v>
+        <v>746394</v>
       </c>
       <c r="R78" t="n">
-        <v>7151279</v>
+        <v>7151307</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8968,7 +8968,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120059872</v>
+        <v>120062963</v>
       </c>
       <c r="B79" t="n">
         <v>91840</v>
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746557</v>
+        <v>746369</v>
       </c>
       <c r="R79" t="n">
-        <v>7151556</v>
+        <v>7151279</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9080,10 +9080,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120061645</v>
+        <v>120063963</v>
       </c>
       <c r="B80" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9092,25 +9092,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746450</v>
+        <v>746301</v>
       </c>
       <c r="R80" t="n">
-        <v>7151380</v>
+        <v>7151207</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9192,10 +9192,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120063963</v>
+        <v>120061607</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9204,25 +9204,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746301</v>
+        <v>746453</v>
       </c>
       <c r="R81" t="n">
-        <v>7151207</v>
+        <v>7151408</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9304,10 +9304,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120063693</v>
+        <v>120063487</v>
       </c>
       <c r="B82" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9316,25 +9316,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9344,13 +9344,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746319</v>
+        <v>746300</v>
       </c>
       <c r="R82" t="n">
-        <v>7151210</v>
+        <v>7151231</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9404,19 +9404,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120061534</v>
+        <v>120062338</v>
       </c>
       <c r="B83" t="n">
         <v>91840</v>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>746467</v>
+        <v>746390</v>
       </c>
       <c r="R83" t="n">
-        <v>7151403</v>
+        <v>7151301</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9528,10 +9528,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120063728</v>
+        <v>120059636</v>
       </c>
       <c r="B84" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9540,25 +9540,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9568,10 +9568,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746298</v>
+        <v>746602</v>
       </c>
       <c r="R84" t="n">
-        <v>7151222</v>
+        <v>7151535</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9640,7 +9640,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120062274</v>
+        <v>120061645</v>
       </c>
       <c r="B85" t="n">
         <v>91884</v>
@@ -9680,10 +9680,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746394</v>
+        <v>746450</v>
       </c>
       <c r="R85" t="n">
-        <v>7151307</v>
+        <v>7151380</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9752,7 +9752,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120062338</v>
+        <v>120061247</v>
       </c>
       <c r="B86" t="n">
         <v>91840</v>
@@ -9792,10 +9792,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>746390</v>
+        <v>746541</v>
       </c>
       <c r="R86" t="n">
-        <v>7151301</v>
+        <v>7151441</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9864,10 +9864,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120062932</v>
+        <v>120060888</v>
       </c>
       <c r="B87" t="n">
-        <v>91884</v>
+        <v>96868</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9876,25 +9876,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5449</v>
+        <v>221941</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>746422</v>
+        <v>746566</v>
       </c>
       <c r="R87" t="n">
-        <v>7151289</v>
+        <v>7151484</v>
       </c>
       <c r="S87" t="n">
         <v>1</v>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9976,10 +9976,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120063442</v>
+        <v>120059956</v>
       </c>
       <c r="B88" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9988,25 +9988,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>746297</v>
+        <v>746535</v>
       </c>
       <c r="R88" t="n">
-        <v>7151223</v>
+        <v>7151537</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10088,10 +10088,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120059956</v>
+        <v>120063442</v>
       </c>
       <c r="B89" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10100,25 +10100,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10128,10 +10128,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>746535</v>
+        <v>746297</v>
       </c>
       <c r="R89" t="n">
-        <v>7151537</v>
+        <v>7151223</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10200,10 +10200,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120060888</v>
+        <v>120063693</v>
       </c>
       <c r="B90" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10216,21 +10216,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10240,13 +10240,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>746566</v>
+        <v>746319</v>
       </c>
       <c r="R90" t="n">
-        <v>7151484</v>
+        <v>7151210</v>
       </c>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10300,22 +10300,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120059683</v>
+        <v>120063439</v>
       </c>
       <c r="B91" t="n">
-        <v>91884</v>
+        <v>91828</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10324,25 +10324,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5449</v>
+        <v>149</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10352,10 +10352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>746569</v>
+        <v>746303</v>
       </c>
       <c r="R91" t="n">
-        <v>7151549</v>
+        <v>7151241</v>
       </c>
       <c r="S91" t="n">
         <v>1</v>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10424,10 +10424,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120062389</v>
+        <v>120061458</v>
       </c>
       <c r="B92" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10436,25 +10436,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>746426</v>
+        <v>746495</v>
       </c>
       <c r="R92" t="n">
-        <v>7151309</v>
+        <v>7151424</v>
       </c>
       <c r="S92" t="n">
         <v>1</v>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10536,7 +10536,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120061458</v>
+        <v>120063287</v>
       </c>
       <c r="B93" t="n">
         <v>91884</v>
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>746495</v>
+        <v>746369</v>
       </c>
       <c r="R93" t="n">
-        <v>7151424</v>
+        <v>7151254</v>
       </c>
       <c r="S93" t="n">
         <v>1</v>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10648,10 +10648,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120063439</v>
+        <v>120059683</v>
       </c>
       <c r="B94" t="n">
-        <v>91828</v>
+        <v>91884</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10660,25 +10660,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>149</v>
+        <v>5449</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>746303</v>
+        <v>746569</v>
       </c>
       <c r="R94" t="n">
-        <v>7151241</v>
+        <v>7151549</v>
       </c>
       <c r="S94" t="n">
         <v>1</v>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10760,7 +10760,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120063551</v>
+        <v>120063671</v>
       </c>
       <c r="B95" t="n">
         <v>91856</v>
@@ -10800,10 +10800,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>746308</v>
+        <v>746309</v>
       </c>
       <c r="R95" t="n">
-        <v>7151219</v>
+        <v>7151221</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10872,10 +10872,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120064407</v>
+        <v>120059794</v>
       </c>
       <c r="B96" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10884,25 +10884,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>746440</v>
+        <v>746567</v>
       </c>
       <c r="R96" t="n">
-        <v>7151291</v>
+        <v>7151566</v>
       </c>
       <c r="S96" t="n">
         <v>1</v>
@@ -10947,7 +10947,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10984,10 +10984,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120063671</v>
+        <v>120062932</v>
       </c>
       <c r="B97" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11000,21 +11000,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11024,10 +11024,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>746309</v>
+        <v>746422</v>
       </c>
       <c r="R97" t="n">
-        <v>7151221</v>
+        <v>7151289</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11096,10 +11096,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120079811</v>
+        <v>120080303</v>
       </c>
       <c r="B98" t="n">
-        <v>90807</v>
+        <v>91886</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11112,37 +11112,41 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>65</v>
+        <v>232140</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>746751</v>
+        <v>746331</v>
       </c>
       <c r="R98" t="n">
-        <v>7151208</v>
+        <v>7151256</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11174,32 +11178,36 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Under tunn äldre tallgren på mager, torr mark</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120080296</v>
+        <v>120080297</v>
       </c>
       <c r="B99" t="n">
         <v>57463</v>
@@ -11232,25 +11240,26 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>746527</v>
+        <v>746612</v>
       </c>
       <c r="R99" t="n">
-        <v>7151199</v>
+        <v>7151234</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11309,10 +11318,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120094359</v>
+        <v>120086241</v>
       </c>
       <c r="B100" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11321,41 +11330,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>746451</v>
+        <v>746383</v>
       </c>
       <c r="R100" t="n">
-        <v>7151341</v>
+        <v>7151288</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11396,7 +11402,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11415,10 +11420,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120094170</v>
+        <v>120086232</v>
       </c>
       <c r="B101" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11427,41 +11432,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>746562</v>
+        <v>746551</v>
       </c>
       <c r="R101" t="n">
-        <v>7151492</v>
+        <v>7151485</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11502,7 +11504,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11521,10 +11522,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120086281</v>
+        <v>120086261</v>
       </c>
       <c r="B102" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11537,21 +11538,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11561,10 +11562,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>746371</v>
+        <v>746574</v>
       </c>
       <c r="R102" t="n">
-        <v>7151235</v>
+        <v>7151495</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11623,10 +11624,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120080297</v>
+        <v>120094266</v>
       </c>
       <c r="B103" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11635,47 +11636,41 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>746612</v>
+        <v>746491</v>
       </c>
       <c r="R103" t="n">
-        <v>7151234</v>
+        <v>7151452</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11716,28 +11711,29 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120079807</v>
+        <v>120086281</v>
       </c>
       <c r="B104" t="n">
-        <v>57421</v>
+        <v>78526</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11746,49 +11742,41 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>746368</v>
+        <v>746371</v>
       </c>
       <c r="R104" t="n">
-        <v>7151283</v>
+        <v>7151235</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11832,22 +11820,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120094677</v>
+        <v>120079799</v>
       </c>
       <c r="B105" t="n">
-        <v>91840</v>
+        <v>90562</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11856,44 +11844,41 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>746351</v>
+        <v>746840</v>
       </c>
       <c r="R105" t="n">
-        <v>7151225</v>
+        <v>7151151</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11931,26 +11916,25 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120094102</v>
+        <v>120094276</v>
       </c>
       <c r="B106" t="n">
         <v>91840</v>
@@ -11993,10 +11977,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>746539</v>
+        <v>746476</v>
       </c>
       <c r="R106" t="n">
-        <v>7151513</v>
+        <v>7151446</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12056,10 +12040,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120080310</v>
+        <v>120080353</v>
       </c>
       <c r="B107" t="n">
-        <v>91821</v>
+        <v>91840</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12068,41 +12052,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>746772</v>
+        <v>746577</v>
       </c>
       <c r="R107" t="n">
-        <v>7151182</v>
+        <v>7151220</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12137,18 +12118,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -12167,10 +12142,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120079799</v>
+        <v>120086257</v>
       </c>
       <c r="B108" t="n">
-        <v>90562</v>
+        <v>91852</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12179,25 +12154,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>4366</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12207,13 +12182,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>746840</v>
+        <v>746575</v>
       </c>
       <c r="R108" t="n">
-        <v>7151151</v>
+        <v>7151554</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12257,22 +12232,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120079814</v>
+        <v>120086268</v>
       </c>
       <c r="B109" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12281,25 +12256,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12309,13 +12284,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>746510</v>
+        <v>746563</v>
       </c>
       <c r="R109" t="n">
-        <v>7151225</v>
+        <v>7151464</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12359,22 +12334,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120086264</v>
+        <v>120080332</v>
       </c>
       <c r="B110" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12383,38 +12358,42 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>746539</v>
+        <v>746560</v>
       </c>
       <c r="R110" t="n">
-        <v>7151522</v>
+        <v>7151291</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12461,22 +12440,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120086243</v>
+        <v>120086303</v>
       </c>
       <c r="B111" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12485,25 +12464,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12513,10 +12492,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>746316</v>
+        <v>746555</v>
       </c>
       <c r="R111" t="n">
-        <v>7151209</v>
+        <v>7151578</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12575,7 +12554,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120094137</v>
+        <v>120094170</v>
       </c>
       <c r="B112" t="n">
         <v>91840</v>
@@ -12618,10 +12597,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>746535</v>
+        <v>746562</v>
       </c>
       <c r="R112" t="n">
-        <v>7151504</v>
+        <v>7151492</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12681,10 +12660,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120079816</v>
+        <v>120086237</v>
       </c>
       <c r="B113" t="n">
-        <v>91834</v>
+        <v>89275</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12693,25 +12672,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12721,13 +12700,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>746534</v>
+        <v>746561</v>
       </c>
       <c r="R113" t="n">
-        <v>7151288</v>
+        <v>7151472</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12771,19 +12750,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120080359</v>
+        <v>120086306</v>
       </c>
       <c r="B114" t="n">
         <v>91834</v>
@@ -12816,21 +12795,17 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>746291</v>
+        <v>746371</v>
       </c>
       <c r="R114" t="n">
-        <v>7151137</v>
+        <v>7151274</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12877,22 +12852,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120080328</v>
+        <v>120086243</v>
       </c>
       <c r="B115" t="n">
-        <v>89964</v>
+        <v>91463</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12901,25 +12876,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5685</v>
+        <v>4745</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12929,10 +12904,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>746590</v>
+        <v>746316</v>
       </c>
       <c r="R115" t="n">
-        <v>7151225</v>
+        <v>7151209</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12976,40 +12951,25 @@
       <c r="AG115" t="b">
         <v>0</v>
       </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120086268</v>
+        <v>120094355</v>
       </c>
       <c r="B116" t="n">
-        <v>91863</v>
+        <v>91884</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13022,34 +12982,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>746563</v>
+        <v>746451</v>
       </c>
       <c r="R116" t="n">
-        <v>7151464</v>
+        <v>7151341</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13090,6 +13053,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13108,10 +13072,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120086271</v>
+        <v>120086288</v>
       </c>
       <c r="B117" t="n">
-        <v>57421</v>
+        <v>78526</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13120,46 +13084,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>746500</v>
+        <v>746630</v>
       </c>
       <c r="R117" t="n">
-        <v>7151560</v>
+        <v>7151524</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13218,10 +13174,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120086232</v>
+        <v>120086290</v>
       </c>
       <c r="B118" t="n">
-        <v>89633</v>
+        <v>78526</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13234,21 +13190,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13258,10 +13214,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>746551</v>
+        <v>746657</v>
       </c>
       <c r="R118" t="n">
-        <v>7151485</v>
+        <v>7151562</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13320,10 +13276,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120086303</v>
+        <v>120086289</v>
       </c>
       <c r="B119" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13332,25 +13288,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13360,10 +13316,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>746555</v>
+        <v>746670</v>
       </c>
       <c r="R119" t="n">
-        <v>7151578</v>
+        <v>7151555</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13422,10 +13378,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120086239</v>
+        <v>120086271</v>
       </c>
       <c r="B120" t="n">
-        <v>57463</v>
+        <v>57421</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13434,32 +13390,28 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
@@ -13474,10 +13426,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>746532</v>
+        <v>746500</v>
       </c>
       <c r="R120" t="n">
-        <v>7151493</v>
+        <v>7151560</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13536,10 +13488,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120094355</v>
+        <v>120086252</v>
       </c>
       <c r="B121" t="n">
-        <v>91884</v>
+        <v>91844</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13548,41 +13500,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>746451</v>
+        <v>746575</v>
       </c>
       <c r="R121" t="n">
-        <v>7151341</v>
+        <v>7151485</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13623,7 +13572,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13642,10 +13590,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120094266</v>
+        <v>120086285</v>
       </c>
       <c r="B122" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13654,41 +13602,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>746491</v>
+        <v>746576</v>
       </c>
       <c r="R122" t="n">
-        <v>7151452</v>
+        <v>7151476</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13729,7 +13674,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13748,10 +13692,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120080331</v>
+        <v>120079807</v>
       </c>
       <c r="B123" t="n">
-        <v>78526</v>
+        <v>57421</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13760,41 +13704,49 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>746936</v>
+        <v>746368</v>
       </c>
       <c r="R123" t="n">
-        <v>7151139</v>
+        <v>7151283</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13826,11 +13778,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
@@ -13839,38 +13786,23 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120080355</v>
+        <v>120094292</v>
       </c>
       <c r="B124" t="n">
         <v>91840</v>
@@ -13904,16 +13836,19 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>746527</v>
+        <v>746478</v>
       </c>
       <c r="R124" t="n">
-        <v>7151203</v>
+        <v>7151421</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13954,25 +13889,26 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120080333</v>
+        <v>120086300</v>
       </c>
       <c r="B125" t="n">
         <v>91840</v>
@@ -14005,21 +13941,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>746569</v>
+        <v>746381</v>
       </c>
       <c r="R125" t="n">
-        <v>7151265</v>
+        <v>7151336</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14054,11 +13986,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Minst, stort mycel</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -14071,22 +13998,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120080357</v>
+        <v>120086234</v>
       </c>
       <c r="B126" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14095,25 +14022,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14123,10 +14050,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>746301</v>
+        <v>746539</v>
       </c>
       <c r="R126" t="n">
-        <v>7151209</v>
+        <v>7151522</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14173,22 +14100,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120086270</v>
+        <v>120079808</v>
       </c>
       <c r="B127" t="n">
-        <v>57421</v>
+        <v>90576</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14197,53 +14124,41 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>103031</v>
+        <v>1204</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>746671</v>
+        <v>746668</v>
       </c>
       <c r="R127" t="n">
-        <v>7151554</v>
+        <v>7151253</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14287,22 +14202,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120086256</v>
+        <v>120094677</v>
       </c>
       <c r="B128" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14315,34 +14230,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>746576</v>
+        <v>746351</v>
       </c>
       <c r="R128" t="n">
-        <v>7151444</v>
+        <v>7151225</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14383,6 +14301,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -14401,7 +14320,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120080358</v>
+        <v>120080352</v>
       </c>
       <c r="B129" t="n">
         <v>91840</v>
@@ -14441,10 +14360,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>746699</v>
+        <v>746834</v>
       </c>
       <c r="R129" t="n">
-        <v>7151240</v>
+        <v>7151121</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14503,10 +14422,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120080291</v>
+        <v>120094305</v>
       </c>
       <c r="B130" t="n">
-        <v>91254</v>
+        <v>91840</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14519,38 +14438,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3298</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>746393</v>
+        <v>746472</v>
       </c>
       <c r="R130" t="n">
-        <v>7151288</v>
+        <v>7151410</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14585,54 +14503,35 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Basen av levande gran</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120086284</v>
+        <v>120079803</v>
       </c>
       <c r="B131" t="n">
-        <v>78526</v>
+        <v>91844</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14641,25 +14540,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14669,13 +14568,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>746563</v>
+        <v>746316</v>
       </c>
       <c r="R131" t="n">
-        <v>7151464</v>
+        <v>7151248</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14719,22 +14618,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120086234</v>
+        <v>120086254</v>
       </c>
       <c r="B132" t="n">
-        <v>89633</v>
+        <v>91844</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14743,25 +14642,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14771,10 +14670,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>746539</v>
+        <v>746678</v>
       </c>
       <c r="R132" t="n">
-        <v>7151522</v>
+        <v>7151537</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14833,10 +14732,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120086254</v>
+        <v>120079816</v>
       </c>
       <c r="B133" t="n">
-        <v>91844</v>
+        <v>91834</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14845,25 +14744,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14873,13 +14772,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>746678</v>
+        <v>746534</v>
       </c>
       <c r="R133" t="n">
-        <v>7151537</v>
+        <v>7151288</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14923,22 +14822,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120086304</v>
+        <v>120086253</v>
       </c>
       <c r="B134" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14947,25 +14846,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14975,10 +14874,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>746589</v>
+        <v>746539</v>
       </c>
       <c r="R134" t="n">
-        <v>7151537</v>
+        <v>7151522</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15037,7 +14936,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120080332</v>
+        <v>120080334</v>
       </c>
       <c r="B135" t="n">
         <v>91840</v>
@@ -15072,7 +14971,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -15081,10 +14980,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>746560</v>
+        <v>746537</v>
       </c>
       <c r="R135" t="n">
-        <v>7151291</v>
+        <v>7151303</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15143,7 +15042,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120080356</v>
+        <v>120086299</v>
       </c>
       <c r="B136" t="n">
         <v>91840</v>
@@ -15183,10 +15082,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>746499</v>
+        <v>746314</v>
       </c>
       <c r="R136" t="n">
-        <v>7151195</v>
+        <v>7151238</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15233,22 +15132,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120094483</v>
+        <v>120080333</v>
       </c>
       <c r="B137" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15257,41 +15156,42 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>746321</v>
+        <v>746569</v>
       </c>
       <c r="R137" t="n">
-        <v>7151245</v>
+        <v>7151265</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15326,35 +15226,39 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Minst, stort mycel</t>
+        </is>
+      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120094276</v>
+        <v>120086287</v>
       </c>
       <c r="B138" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15363,41 +15267,38 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>746476</v>
+        <v>746567</v>
       </c>
       <c r="R138" t="n">
-        <v>7151446</v>
+        <v>7151554</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15438,7 +15339,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -15457,10 +15357,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120079801</v>
+        <v>120086282</v>
       </c>
       <c r="B139" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15473,21 +15373,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15497,13 +15397,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>746598</v>
+        <v>746368</v>
       </c>
       <c r="R139" t="n">
-        <v>7151227</v>
+        <v>7151288</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15541,29 +15441,28 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120086285</v>
+        <v>120080309</v>
       </c>
       <c r="B140" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15576,34 +15475,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>746576</v>
+        <v>746663</v>
       </c>
       <c r="R140" t="n">
-        <v>7151476</v>
+        <v>7151255</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15638,6 +15542,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Äldre födohack i basen</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15646,26 +15555,41 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120086273</v>
+        <v>120086283</v>
       </c>
       <c r="B141" t="n">
-        <v>90712</v>
+        <v>78526</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15674,25 +15598,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15702,10 +15626,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>746551</v>
+        <v>746566</v>
       </c>
       <c r="R141" t="n">
-        <v>7151485</v>
+        <v>7151468</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15764,10 +15688,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120086306</v>
+        <v>120080331</v>
       </c>
       <c r="B142" t="n">
-        <v>91834</v>
+        <v>78526</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15780,21 +15704,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15804,10 +15728,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>746371</v>
+        <v>746936</v>
       </c>
       <c r="R142" t="n">
-        <v>7151274</v>
+        <v>7151139</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15842,6 +15766,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15850,26 +15779,41 @@
       </c>
       <c r="AG142" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120086248</v>
+        <v>120080296</v>
       </c>
       <c r="B143" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15882,34 +15826,42 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>746537</v>
+        <v>746527</v>
       </c>
       <c r="R143" t="n">
-        <v>7151592</v>
+        <v>7151199</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15956,22 +15908,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120080334</v>
+        <v>120080291</v>
       </c>
       <c r="B144" t="n">
-        <v>91840</v>
+        <v>91254</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15984,26 +15936,26 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>3298</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -16012,10 +15964,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>746537</v>
+        <v>746393</v>
       </c>
       <c r="R144" t="n">
-        <v>7151303</v>
+        <v>7151288</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16050,6 +16002,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Basen av levande gran</t>
+        </is>
+      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
@@ -16058,6 +16015,21 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
@@ -16074,10 +16046,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120086301</v>
+        <v>120086308</v>
       </c>
       <c r="B145" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16086,25 +16058,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16114,10 +16086,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>746566</v>
+        <v>746492</v>
       </c>
       <c r="R145" t="n">
-        <v>7151468</v>
+        <v>7151446</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16176,10 +16148,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120086235</v>
+        <v>120086293</v>
       </c>
       <c r="B146" t="n">
-        <v>89633</v>
+        <v>78171</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16192,21 +16164,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16216,10 +16188,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>746515</v>
+        <v>746636</v>
       </c>
       <c r="R146" t="n">
-        <v>7151568</v>
+        <v>7151518</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16278,10 +16250,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120086244</v>
+        <v>120086307</v>
       </c>
       <c r="B147" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16290,25 +16262,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16318,10 +16290,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>746576</v>
+        <v>746483</v>
       </c>
       <c r="R147" t="n">
-        <v>7151444</v>
+        <v>7151420</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16380,7 +16352,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120080354</v>
+        <v>120080356</v>
       </c>
       <c r="B148" t="n">
         <v>91840</v>
@@ -16420,10 +16392,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>746559</v>
+        <v>746499</v>
       </c>
       <c r="R148" t="n">
-        <v>7151216</v>
+        <v>7151195</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16482,10 +16454,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120080309</v>
+        <v>120086235</v>
       </c>
       <c r="B149" t="n">
-        <v>57326</v>
+        <v>89633</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16498,39 +16470,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>1962</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>746663</v>
+        <v>746515</v>
       </c>
       <c r="R149" t="n">
-        <v>7151255</v>
+        <v>7151568</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16565,11 +16532,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Äldre födohack i basen</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
@@ -16578,41 +16540,26 @@
       </c>
       <c r="AG149" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120086237</v>
+        <v>120080308</v>
       </c>
       <c r="B150" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16621,25 +16568,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16649,10 +16596,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>746561</v>
+        <v>746368</v>
       </c>
       <c r="R150" t="n">
-        <v>7151472</v>
+        <v>7151279</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16699,22 +16646,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120094777</v>
+        <v>120086262</v>
       </c>
       <c r="B151" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16727,37 +16674,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>746478</v>
+        <v>746555</v>
       </c>
       <c r="R151" t="n">
-        <v>7151377</v>
+        <v>7151590</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16798,7 +16742,6 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -16817,10 +16760,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120086300</v>
+        <v>120086251</v>
       </c>
       <c r="B152" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16829,25 +16772,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16857,10 +16800,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>746381</v>
+        <v>746297</v>
       </c>
       <c r="R152" t="n">
-        <v>7151336</v>
+        <v>7151200</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16919,10 +16862,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120086262</v>
+        <v>120094241</v>
       </c>
       <c r="B153" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16931,38 +16874,41 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>746555</v>
+        <v>746515</v>
       </c>
       <c r="R153" t="n">
-        <v>7151590</v>
+        <v>7151443</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17003,6 +16949,7 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -17021,10 +16968,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120086257</v>
+        <v>120094137</v>
       </c>
       <c r="B154" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17037,34 +16984,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>746575</v>
+        <v>746535</v>
       </c>
       <c r="R154" t="n">
-        <v>7151554</v>
+        <v>7151504</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17105,6 +17055,7 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17123,10 +17074,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120094292</v>
+        <v>120086273</v>
       </c>
       <c r="B155" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17135,41 +17086,38 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>746478</v>
+        <v>746551</v>
       </c>
       <c r="R155" t="n">
-        <v>7151421</v>
+        <v>7151485</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17210,7 +17158,6 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -17229,10 +17176,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120086307</v>
+        <v>120086270</v>
       </c>
       <c r="B156" t="n">
-        <v>91834</v>
+        <v>57421</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17241,38 +17188,50 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4362</v>
+        <v>103031</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>746483</v>
+        <v>746671</v>
       </c>
       <c r="R156" t="n">
-        <v>7151420</v>
+        <v>7151554</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17331,10 +17290,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120094241</v>
+        <v>120094483</v>
       </c>
       <c r="B157" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17343,25 +17302,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17374,10 +17333,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>746515</v>
+        <v>746321</v>
       </c>
       <c r="R157" t="n">
-        <v>7151443</v>
+        <v>7151245</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17437,10 +17396,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120080353</v>
+        <v>120086260</v>
       </c>
       <c r="B158" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17449,25 +17408,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17477,10 +17436,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>746577</v>
+        <v>746378</v>
       </c>
       <c r="R158" t="n">
-        <v>7151220</v>
+        <v>7151283</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17527,22 +17486,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120094371</v>
+        <v>120094591</v>
       </c>
       <c r="B159" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17551,25 +17510,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17582,10 +17541,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>746383</v>
+        <v>746294</v>
       </c>
       <c r="R159" t="n">
-        <v>7151297</v>
+        <v>7151228</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17645,10 +17604,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120079810</v>
+        <v>120086256</v>
       </c>
       <c r="B160" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17657,25 +17616,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17685,13 +17644,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>746645</v>
+        <v>746576</v>
       </c>
       <c r="R160" t="n">
-        <v>7151221</v>
+        <v>7151444</v>
       </c>
       <c r="S160" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17735,22 +17694,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120086267</v>
+        <v>120086249</v>
       </c>
       <c r="B161" t="n">
-        <v>91863</v>
+        <v>91884</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17763,21 +17722,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17787,10 +17746,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>746492</v>
+        <v>746568</v>
       </c>
       <c r="R161" t="n">
-        <v>7151446</v>
+        <v>7151535</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17849,10 +17808,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120086308</v>
+        <v>120094359</v>
       </c>
       <c r="B162" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17861,38 +17820,41 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>746492</v>
+        <v>746451</v>
       </c>
       <c r="R162" t="n">
-        <v>7151446</v>
+        <v>7151341</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17933,6 +17895,7 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -17951,10 +17914,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120086283</v>
+        <v>120080335</v>
       </c>
       <c r="B163" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17963,38 +17926,42 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>746566</v>
+        <v>746321</v>
       </c>
       <c r="R163" t="n">
-        <v>7151468</v>
+        <v>7151233</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18041,22 +18008,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120094190</v>
+        <v>120080358</v>
       </c>
       <c r="B164" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18065,41 +18032,38 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>746572</v>
+        <v>746699</v>
       </c>
       <c r="R164" t="n">
-        <v>7151479</v>
+        <v>7151240</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18140,29 +18104,28 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120094591</v>
+        <v>120086267</v>
       </c>
       <c r="B165" t="n">
-        <v>91834</v>
+        <v>91863</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18175,37 +18138,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>746294</v>
+        <v>746492</v>
       </c>
       <c r="R165" t="n">
-        <v>7151228</v>
+        <v>7151446</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18246,7 +18206,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -18265,10 +18224,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120086287</v>
+        <v>120086264</v>
       </c>
       <c r="B166" t="n">
-        <v>78526</v>
+        <v>92030</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18281,21 +18240,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18305,10 +18264,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>746567</v>
+        <v>746539</v>
       </c>
       <c r="R166" t="n">
-        <v>7151554</v>
+        <v>7151522</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18367,10 +18326,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120086249</v>
+        <v>120079815</v>
       </c>
       <c r="B167" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18379,25 +18338,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18407,13 +18366,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>746568</v>
+        <v>746896</v>
       </c>
       <c r="R167" t="n">
-        <v>7151535</v>
+        <v>7151149</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18457,22 +18416,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120086290</v>
+        <v>120086239</v>
       </c>
       <c r="B168" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18485,34 +18444,46 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>746657</v>
+        <v>746532</v>
       </c>
       <c r="R168" t="n">
-        <v>7151562</v>
+        <v>7151493</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18571,10 +18542,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120086231</v>
+        <v>120079811</v>
       </c>
       <c r="B169" t="n">
-        <v>90527</v>
+        <v>90807</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18583,25 +18554,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5447</v>
+        <v>65</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18611,13 +18582,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>746676</v>
+        <v>746751</v>
       </c>
       <c r="R169" t="n">
-        <v>7151534</v>
+        <v>7151208</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18655,25 +18626,26 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120079815</v>
+        <v>120094102</v>
       </c>
       <c r="B170" t="n">
         <v>91840</v>
@@ -18707,19 +18679,22 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>746896</v>
+        <v>746539</v>
       </c>
       <c r="R170" t="n">
-        <v>7151149</v>
+        <v>7151513</v>
       </c>
       <c r="S170" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18757,25 +18732,26 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120080352</v>
+        <v>120080357</v>
       </c>
       <c r="B171" t="n">
         <v>91840</v>
@@ -18815,10 +18791,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>746834</v>
+        <v>746301</v>
       </c>
       <c r="R171" t="n">
-        <v>7151121</v>
+        <v>7151209</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18877,10 +18853,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120086282</v>
+        <v>120086248</v>
       </c>
       <c r="B172" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18893,21 +18869,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18917,10 +18893,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>746368</v>
+        <v>746537</v>
       </c>
       <c r="R172" t="n">
-        <v>7151288</v>
+        <v>7151592</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18979,10 +18955,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>120086299</v>
+        <v>120086231</v>
       </c>
       <c r="B173" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18995,21 +18971,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19019,10 +18995,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>746314</v>
+        <v>746676</v>
       </c>
       <c r="R173" t="n">
-        <v>7151238</v>
+        <v>7151534</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19081,10 +19057,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120086247</v>
+        <v>120080359</v>
       </c>
       <c r="B174" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19097,34 +19073,38 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>746385</v>
+        <v>746291</v>
       </c>
       <c r="R174" t="n">
-        <v>7151299</v>
+        <v>7151137</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19171,22 +19151,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120080303</v>
+        <v>120079810</v>
       </c>
       <c r="B175" t="n">
-        <v>91886</v>
+        <v>78526</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19195,45 +19175,41 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>232140</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>746331</v>
+        <v>746645</v>
       </c>
       <c r="R175" t="n">
-        <v>7151256</v>
+        <v>7151221</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19263,11 +19239,6 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Under tunn äldre tallgren på mager, torr mark</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19282,22 +19253,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120086293</v>
+        <v>120086244</v>
       </c>
       <c r="B176" t="n">
-        <v>78171</v>
+        <v>91828</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19306,25 +19277,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>353</v>
+        <v>149</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19334,10 +19305,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>746636</v>
+        <v>746576</v>
       </c>
       <c r="R176" t="n">
-        <v>7151518</v>
+        <v>7151444</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19396,10 +19367,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120086260</v>
+        <v>120086301</v>
       </c>
       <c r="B177" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19408,25 +19379,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19436,10 +19407,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>746378</v>
+        <v>746566</v>
       </c>
       <c r="R177" t="n">
-        <v>7151283</v>
+        <v>7151468</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19498,10 +19469,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120086286</v>
+        <v>120080310</v>
       </c>
       <c r="B178" t="n">
-        <v>78526</v>
+        <v>91821</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19510,38 +19481,41 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>6055</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>746555</v>
+        <v>746772</v>
       </c>
       <c r="R178" t="n">
-        <v>7151578</v>
+        <v>7151182</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19576,34 +19550,40 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat</t>
+        </is>
+      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120086261</v>
+        <v>120094371</v>
       </c>
       <c r="B179" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19612,38 +19592,41 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>746574</v>
+        <v>746383</v>
       </c>
       <c r="R179" t="n">
-        <v>7151495</v>
+        <v>7151297</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19684,6 +19667,7 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -19702,7 +19686,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120080335</v>
+        <v>120079814</v>
       </c>
       <c r="B180" t="n">
         <v>91840</v>
@@ -19735,24 +19719,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>746321</v>
+        <v>746510</v>
       </c>
       <c r="R180" t="n">
-        <v>7151233</v>
+        <v>7151225</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19796,19 +19776,19 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120080308</v>
+        <v>120086247</v>
       </c>
       <c r="B181" t="n">
         <v>91884</v>
@@ -19848,10 +19828,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>746368</v>
+        <v>746385</v>
       </c>
       <c r="R181" t="n">
-        <v>7151279</v>
+        <v>7151299</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19898,22 +19878,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120079798</v>
+        <v>120094190</v>
       </c>
       <c r="B182" t="n">
-        <v>89633</v>
+        <v>91884</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19926,37 +19906,40 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>746310</v>
+        <v>746572</v>
       </c>
       <c r="R182" t="n">
-        <v>7151135</v>
+        <v>7151479</v>
       </c>
       <c r="S182" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19994,28 +19977,29 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
+      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120094305</v>
+        <v>120079801</v>
       </c>
       <c r="B183" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20024,44 +20008,41 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>746472</v>
+        <v>746598</v>
       </c>
       <c r="R183" t="n">
-        <v>7151410</v>
+        <v>7151227</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20106,22 +20087,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120086289</v>
+        <v>120080328</v>
       </c>
       <c r="B184" t="n">
-        <v>78526</v>
+        <v>89964</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20130,25 +20111,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20158,10 +20139,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>746670</v>
+        <v>746590</v>
       </c>
       <c r="R184" t="n">
-        <v>7151555</v>
+        <v>7151225</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20205,25 +20186,40 @@
       <c r="AG184" t="b">
         <v>0</v>
       </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120086252</v>
+        <v>120086304</v>
       </c>
       <c r="B185" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20232,25 +20228,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20260,10 +20256,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>746575</v>
+        <v>746589</v>
       </c>
       <c r="R185" t="n">
-        <v>7151485</v>
+        <v>7151537</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20322,10 +20318,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120080330</v>
+        <v>120086286</v>
       </c>
       <c r="B186" t="n">
-        <v>90712</v>
+        <v>78526</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20334,25 +20330,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20362,10 +20358,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>746624</v>
+        <v>746555</v>
       </c>
       <c r="R186" t="n">
-        <v>7151217</v>
+        <v>7151578</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20400,11 +20396,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Nedbruten tallåga, kollekt taget</t>
-        </is>
-      </c>
       <c r="AD186" t="b">
         <v>0</v>
       </c>
@@ -20413,41 +20404,26 @@
       </c>
       <c r="AG186" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO186" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120086253</v>
+        <v>120086284</v>
       </c>
       <c r="B187" t="n">
-        <v>91844</v>
+        <v>78526</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20456,25 +20432,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20484,10 +20460,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>746539</v>
+        <v>746563</v>
       </c>
       <c r="R187" t="n">
-        <v>7151522</v>
+        <v>7151464</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20546,10 +20522,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120086288</v>
+        <v>120080330</v>
       </c>
       <c r="B188" t="n">
-        <v>78526</v>
+        <v>90712</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20558,25 +20534,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20586,10 +20562,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>746630</v>
+        <v>746624</v>
       </c>
       <c r="R188" t="n">
-        <v>7151524</v>
+        <v>7151217</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20624,6 +20600,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Nedbruten tallåga, kollekt taget</t>
+        </is>
+      </c>
       <c r="AD188" t="b">
         <v>0</v>
       </c>
@@ -20632,26 +20613,41 @@
       </c>
       <c r="AG188" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120086251</v>
+        <v>120080354</v>
       </c>
       <c r="B189" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20660,25 +20656,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20688,10 +20684,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>746297</v>
+        <v>746559</v>
       </c>
       <c r="R189" t="n">
-        <v>7151200</v>
+        <v>7151216</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20738,22 +20734,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>120086241</v>
+        <v>120080355</v>
       </c>
       <c r="B190" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20762,25 +20758,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20790,10 +20786,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>746383</v>
+        <v>746527</v>
       </c>
       <c r="R190" t="n">
-        <v>7151288</v>
+        <v>7151203</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20840,22 +20836,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>120079808</v>
+        <v>120079798</v>
       </c>
       <c r="B191" t="n">
-        <v>90576</v>
+        <v>89633</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20868,21 +20864,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1204</v>
+        <v>1962</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20892,10 +20888,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>746668</v>
+        <v>746310</v>
       </c>
       <c r="R191" t="n">
-        <v>7151253</v>
+        <v>7151135</v>
       </c>
       <c r="S191" t="n">
         <v>15</v>
@@ -20954,10 +20950,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>120079803</v>
+        <v>120094777</v>
       </c>
       <c r="B192" t="n">
-        <v>91844</v>
+        <v>91884</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20966,41 +20962,44 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>746316</v>
+        <v>746478</v>
       </c>
       <c r="R192" t="n">
-        <v>7151248</v>
+        <v>7151377</v>
       </c>
       <c r="S192" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21038,18 +21037,19 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
+      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -8632,10 +8632,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120063551</v>
+        <v>120062389</v>
       </c>
       <c r="B76" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8644,25 +8644,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746308</v>
+        <v>746426</v>
       </c>
       <c r="R76" t="n">
-        <v>7151219</v>
+        <v>7151309</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8744,10 +8744,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120062389</v>
+        <v>120063551</v>
       </c>
       <c r="B77" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8756,25 +8756,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746426</v>
+        <v>746308</v>
       </c>
       <c r="R77" t="n">
-        <v>7151309</v>
+        <v>7151219</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9864,10 +9864,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120060888</v>
+        <v>120063442</v>
       </c>
       <c r="B87" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9880,21 +9880,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>746566</v>
+        <v>746297</v>
       </c>
       <c r="R87" t="n">
-        <v>7151484</v>
+        <v>7151223</v>
       </c>
       <c r="S87" t="n">
         <v>1</v>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10088,10 +10088,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120063442</v>
+        <v>120060888</v>
       </c>
       <c r="B89" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10104,21 +10104,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10128,10 +10128,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>746297</v>
+        <v>746566</v>
       </c>
       <c r="R89" t="n">
-        <v>7151223</v>
+        <v>7151484</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10872,7 +10872,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120059794</v>
+        <v>120062932</v>
       </c>
       <c r="B96" t="n">
         <v>91884</v>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>746567</v>
+        <v>746422</v>
       </c>
       <c r="R96" t="n">
-        <v>7151566</v>
+        <v>7151289</v>
       </c>
       <c r="S96" t="n">
         <v>1</v>
@@ -10947,7 +10947,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10984,7 +10984,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120062932</v>
+        <v>120059794</v>
       </c>
       <c r="B97" t="n">
         <v>91884</v>
@@ -11024,10 +11024,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>746422</v>
+        <v>746567</v>
       </c>
       <c r="R97" t="n">
-        <v>7151289</v>
+        <v>7151566</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11096,10 +11096,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120080303</v>
+        <v>120080297</v>
       </c>
       <c r="B98" t="n">
-        <v>91886</v>
+        <v>57463</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11108,30 +11108,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>232140</v>
+        <v>103021</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11140,10 +11145,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>746331</v>
+        <v>746612</v>
       </c>
       <c r="R98" t="n">
-        <v>7151256</v>
+        <v>7151234</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11176,11 +11181,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Under tunn äldre tallgren på mager, torr mark</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11207,10 +11207,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120080297</v>
+        <v>120080303</v>
       </c>
       <c r="B99" t="n">
-        <v>57463</v>
+        <v>91886</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11219,35 +11219,30 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103021</v>
+        <v>232140</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11256,10 +11251,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>746612</v>
+        <v>746331</v>
       </c>
       <c r="R99" t="n">
-        <v>7151234</v>
+        <v>7151256</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11292,6 +11287,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Under tunn äldre tallgren på mager, torr mark</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -14010,10 +14010,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120086234</v>
+        <v>120079808</v>
       </c>
       <c r="B126" t="n">
-        <v>89633</v>
+        <v>90576</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14026,21 +14026,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14050,13 +14050,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>746539</v>
+        <v>746668</v>
       </c>
       <c r="R126" t="n">
-        <v>7151522</v>
+        <v>7151253</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14100,22 +14100,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120079808</v>
+        <v>120094677</v>
       </c>
       <c r="B127" t="n">
-        <v>90576</v>
+        <v>91840</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14124,41 +14124,44 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>746668</v>
+        <v>746351</v>
       </c>
       <c r="R127" t="n">
-        <v>7151253</v>
+        <v>7151225</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14196,25 +14199,26 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120094677</v>
+        <v>120080352</v>
       </c>
       <c r="B128" t="n">
         <v>91840</v>
@@ -14248,19 +14252,16 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>746351</v>
+        <v>746834</v>
       </c>
       <c r="R128" t="n">
-        <v>7151225</v>
+        <v>7151121</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14301,26 +14302,25 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120080352</v>
+        <v>120094305</v>
       </c>
       <c r="B129" t="n">
         <v>91840</v>
@@ -14354,16 +14354,19 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>746834</v>
+        <v>746472</v>
       </c>
       <c r="R129" t="n">
-        <v>7151121</v>
+        <v>7151410</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14404,28 +14407,29 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120094305</v>
+        <v>120086234</v>
       </c>
       <c r="B130" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14434,41 +14438,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>746472</v>
+        <v>746539</v>
       </c>
       <c r="R130" t="n">
-        <v>7151410</v>
+        <v>7151522</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14509,7 +14510,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14732,10 +14732,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120079816</v>
+        <v>120086253</v>
       </c>
       <c r="B133" t="n">
-        <v>91834</v>
+        <v>91844</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14744,25 +14744,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14772,13 +14772,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>746534</v>
+        <v>746539</v>
       </c>
       <c r="R133" t="n">
-        <v>7151288</v>
+        <v>7151522</v>
       </c>
       <c r="S133" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14822,22 +14822,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120086253</v>
+        <v>120080334</v>
       </c>
       <c r="B134" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14846,38 +14846,42 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>746539</v>
+        <v>746537</v>
       </c>
       <c r="R134" t="n">
-        <v>7151522</v>
+        <v>7151303</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14924,22 +14928,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120080334</v>
+        <v>120079816</v>
       </c>
       <c r="B135" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14948,45 +14952,41 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>746537</v>
+        <v>746534</v>
       </c>
       <c r="R135" t="n">
-        <v>7151303</v>
+        <v>7151288</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15030,22 +15030,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120086299</v>
+        <v>120080309</v>
       </c>
       <c r="B136" t="n">
-        <v>91840</v>
+        <v>57326</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15054,38 +15054,43 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>746314</v>
+        <v>746663</v>
       </c>
       <c r="R136" t="n">
-        <v>7151238</v>
+        <v>7151255</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15120,6 +15125,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Äldre födohack i basen</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -15128,23 +15138,38 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120080333</v>
+        <v>120086299</v>
       </c>
       <c r="B137" t="n">
         <v>91840</v>
@@ -15177,21 +15202,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>746569</v>
+        <v>746314</v>
       </c>
       <c r="R137" t="n">
-        <v>7151265</v>
+        <v>7151238</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15226,11 +15247,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Minst, stort mycel</t>
-        </is>
-      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
@@ -15243,22 +15259,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120086287</v>
+        <v>120080333</v>
       </c>
       <c r="B138" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15267,38 +15283,42 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>746567</v>
+        <v>746569</v>
       </c>
       <c r="R138" t="n">
-        <v>7151554</v>
+        <v>7151265</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15333,6 +15353,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Minst, stort mycel</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -15345,19 +15370,19 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120086282</v>
+        <v>120086287</v>
       </c>
       <c r="B139" t="n">
         <v>78526</v>
@@ -15397,10 +15422,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>746368</v>
+        <v>746567</v>
       </c>
       <c r="R139" t="n">
-        <v>7151288</v>
+        <v>7151554</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15459,10 +15484,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120080309</v>
+        <v>120086282</v>
       </c>
       <c r="B140" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15475,39 +15500,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>746663</v>
+        <v>746368</v>
       </c>
       <c r="R140" t="n">
-        <v>7151255</v>
+        <v>7151288</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15542,11 +15562,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Äldre födohack i basen</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15555,31 +15570,16 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -16862,10 +16862,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120094241</v>
+        <v>120086273</v>
       </c>
       <c r="B153" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16874,41 +16874,38 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>746515</v>
+        <v>746551</v>
       </c>
       <c r="R153" t="n">
-        <v>7151443</v>
+        <v>7151485</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16949,7 +16946,6 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -16968,7 +16964,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120094137</v>
+        <v>120094241</v>
       </c>
       <c r="B154" t="n">
         <v>91840</v>
@@ -17011,10 +17007,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>746535</v>
+        <v>746515</v>
       </c>
       <c r="R154" t="n">
-        <v>7151504</v>
+        <v>7151443</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17074,10 +17070,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120086273</v>
+        <v>120094137</v>
       </c>
       <c r="B155" t="n">
-        <v>90712</v>
+        <v>91840</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17086,38 +17082,41 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>746551</v>
+        <v>746535</v>
       </c>
       <c r="R155" t="n">
-        <v>7151485</v>
+        <v>7151504</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17158,6 +17157,7 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -17808,10 +17808,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120094359</v>
+        <v>120086264</v>
       </c>
       <c r="B162" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17820,41 +17820,38 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>746451</v>
+        <v>746539</v>
       </c>
       <c r="R162" t="n">
-        <v>7151341</v>
+        <v>7151522</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17895,7 +17892,6 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -17914,7 +17910,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120080335</v>
+        <v>120094359</v>
       </c>
       <c r="B163" t="n">
         <v>91840</v>
@@ -17947,21 +17943,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>746321</v>
+        <v>746451</v>
       </c>
       <c r="R163" t="n">
-        <v>7151233</v>
+        <v>7151341</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18002,25 +17997,26 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120080358</v>
+        <v>120080335</v>
       </c>
       <c r="B164" t="n">
         <v>91840</v>
@@ -18053,17 +18049,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>746699</v>
+        <v>746321</v>
       </c>
       <c r="R164" t="n">
-        <v>7151240</v>
+        <v>7151233</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18122,10 +18122,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120086267</v>
+        <v>120080358</v>
       </c>
       <c r="B165" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18134,25 +18134,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18162,10 +18162,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>746492</v>
+        <v>746699</v>
       </c>
       <c r="R165" t="n">
-        <v>7151446</v>
+        <v>7151240</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18212,22 +18212,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120086264</v>
+        <v>120086267</v>
       </c>
       <c r="B166" t="n">
-        <v>92030</v>
+        <v>91863</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18240,21 +18240,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2079</v>
+        <v>5966</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18264,10 +18264,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>746539</v>
+        <v>746492</v>
       </c>
       <c r="R166" t="n">
-        <v>7151522</v>
+        <v>7151446</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19057,10 +19057,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120080359</v>
+        <v>120086244</v>
       </c>
       <c r="B174" t="n">
-        <v>91834</v>
+        <v>91828</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19069,42 +19069,38 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>746291</v>
+        <v>746576</v>
       </c>
       <c r="R174" t="n">
-        <v>7151137</v>
+        <v>7151444</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19151,22 +19147,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120079810</v>
+        <v>120080359</v>
       </c>
       <c r="B175" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19179,37 +19175,41 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>746645</v>
+        <v>746291</v>
       </c>
       <c r="R175" t="n">
-        <v>7151221</v>
+        <v>7151137</v>
       </c>
       <c r="S175" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19253,22 +19253,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120086244</v>
+        <v>120086301</v>
       </c>
       <c r="B176" t="n">
-        <v>91828</v>
+        <v>91840</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19277,25 +19277,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>149</v>
+        <v>4364</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19305,10 +19305,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>746576</v>
+        <v>746566</v>
       </c>
       <c r="R176" t="n">
-        <v>7151444</v>
+        <v>7151468</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19367,10 +19367,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120086301</v>
+        <v>120079810</v>
       </c>
       <c r="B177" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19379,25 +19379,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19407,13 +19407,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>746566</v>
+        <v>746645</v>
       </c>
       <c r="R177" t="n">
-        <v>7151468</v>
+        <v>7151221</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19457,12 +19457,12 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
@@ -20522,10 +20522,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120080330</v>
+        <v>120094777</v>
       </c>
       <c r="B188" t="n">
-        <v>90712</v>
+        <v>91884</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20534,38 +20534,41 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1503</v>
+        <v>5449</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>746624</v>
+        <v>746478</v>
       </c>
       <c r="R188" t="n">
-        <v>7151217</v>
+        <v>7151377</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20600,54 +20603,35 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Nedbruten tallåga, kollekt taget</t>
-        </is>
-      </c>
       <c r="AD188" t="b">
         <v>0</v>
       </c>
       <c r="AE188" t="b">
         <v>0</v>
       </c>
+      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ188" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK188" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO188" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120080354</v>
+        <v>120080330</v>
       </c>
       <c r="B189" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20656,25 +20640,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20684,10 +20668,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>746559</v>
+        <v>746624</v>
       </c>
       <c r="R189" t="n">
-        <v>7151216</v>
+        <v>7151217</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20722,6 +20706,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Nedbruten tallåga, kollekt taget</t>
+        </is>
+      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
@@ -20730,6 +20719,21 @@
       </c>
       <c r="AG189" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
@@ -20746,7 +20750,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>120080355</v>
+        <v>120080354</v>
       </c>
       <c r="B190" t="n">
         <v>91840</v>
@@ -20786,10 +20790,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>746527</v>
+        <v>746559</v>
       </c>
       <c r="R190" t="n">
-        <v>7151203</v>
+        <v>7151216</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20848,10 +20852,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>120079798</v>
+        <v>120080355</v>
       </c>
       <c r="B191" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20860,25 +20864,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20888,13 +20892,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>746310</v>
+        <v>746527</v>
       </c>
       <c r="R191" t="n">
-        <v>7151135</v>
+        <v>7151203</v>
       </c>
       <c r="S191" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20938,22 +20942,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>120094777</v>
+        <v>120079798</v>
       </c>
       <c r="B192" t="n">
-        <v>91884</v>
+        <v>89633</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20966,40 +20970,37 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>746478</v>
+        <v>746310</v>
       </c>
       <c r="R192" t="n">
-        <v>7151377</v>
+        <v>7151135</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21037,19 +21038,18 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -7176,10 +7176,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120064725</v>
+        <v>120062044</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7188,41 +7188,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
+          <t>Vintjärnen, Vintjärnen, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746535</v>
+        <v>746344</v>
       </c>
       <c r="R63" t="n">
-        <v>7151171</v>
+        <v>7151353</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7276,22 +7276,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120061686</v>
+        <v>120063487</v>
       </c>
       <c r="B64" t="n">
-        <v>91863</v>
+        <v>91834</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7304,21 +7304,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7328,10 +7328,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746448</v>
+        <v>746300</v>
       </c>
       <c r="R64" t="n">
-        <v>7151388</v>
+        <v>7151231</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7400,10 +7400,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120063383</v>
+        <v>120061607</v>
       </c>
       <c r="B65" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7416,21 +7416,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746303</v>
+        <v>746453</v>
       </c>
       <c r="R65" t="n">
-        <v>7151246</v>
+        <v>7151408</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7512,10 +7512,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120062185</v>
+        <v>120063439</v>
       </c>
       <c r="B66" t="n">
-        <v>91840</v>
+        <v>91828</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7524,25 +7524,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>149</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746401</v>
+        <v>746303</v>
       </c>
       <c r="R66" t="n">
-        <v>7151292</v>
+        <v>7151241</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120061860</v>
+        <v>120061725</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7636,25 +7636,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7664,10 +7664,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746423</v>
+        <v>746444</v>
       </c>
       <c r="R67" t="n">
-        <v>7151350</v>
+        <v>7151382</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7736,7 +7736,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120064407</v>
+        <v>120063442</v>
       </c>
       <c r="B68" t="n">
         <v>91840</v>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746440</v>
+        <v>746297</v>
       </c>
       <c r="R68" t="n">
-        <v>7151291</v>
+        <v>7151223</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7848,7 +7848,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120059872</v>
+        <v>120064681</v>
       </c>
       <c r="B69" t="n">
         <v>91840</v>
@@ -7884,17 +7884,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vintjärnen, Vintjärnen, Vb</t>
+          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746557</v>
+        <v>746535</v>
       </c>
       <c r="R69" t="n">
-        <v>7151556</v>
+        <v>7151171</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7948,19 +7948,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120062044</v>
+        <v>120062932</v>
       </c>
       <c r="B70" t="n">
         <v>91884</v>
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746344</v>
+        <v>746422</v>
       </c>
       <c r="R70" t="n">
-        <v>7151353</v>
+        <v>7151289</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8072,10 +8072,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120061725</v>
+        <v>120063551</v>
       </c>
       <c r="B71" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746444</v>
+        <v>746308</v>
       </c>
       <c r="R71" t="n">
-        <v>7151382</v>
+        <v>7151219</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8184,7 +8184,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120061534</v>
+        <v>120061247</v>
       </c>
       <c r="B72" t="n">
         <v>91840</v>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746467</v>
+        <v>746541</v>
       </c>
       <c r="R72" t="n">
-        <v>7151403</v>
+        <v>7151441</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8296,10 +8296,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120061233</v>
+        <v>120061458</v>
       </c>
       <c r="B73" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8312,21 +8312,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8336,10 +8336,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746597</v>
+        <v>746495</v>
       </c>
       <c r="R73" t="n">
-        <v>7151440</v>
+        <v>7151424</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8408,7 +8408,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120061583</v>
+        <v>120061534</v>
       </c>
       <c r="B74" t="n">
         <v>91840</v>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746472</v>
+        <v>746467</v>
       </c>
       <c r="R74" t="n">
-        <v>7151401</v>
+        <v>7151403</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8520,10 +8520,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120063728</v>
+        <v>120060888</v>
       </c>
       <c r="B75" t="n">
-        <v>91884</v>
+        <v>96868</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8532,25 +8532,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5449</v>
+        <v>221941</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746298</v>
+        <v>746566</v>
       </c>
       <c r="R75" t="n">
-        <v>7151222</v>
+        <v>7151484</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8632,7 +8632,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120062389</v>
+        <v>120062185</v>
       </c>
       <c r="B76" t="n">
         <v>91840</v>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746426</v>
+        <v>746401</v>
       </c>
       <c r="R76" t="n">
-        <v>7151309</v>
+        <v>7151292</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8744,10 +8744,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120063551</v>
+        <v>120063963</v>
       </c>
       <c r="B77" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8756,25 +8756,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746308</v>
+        <v>746301</v>
       </c>
       <c r="R77" t="n">
-        <v>7151219</v>
+        <v>7151207</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8856,10 +8856,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120062274</v>
+        <v>120059872</v>
       </c>
       <c r="B78" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8868,25 +8868,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746394</v>
+        <v>746557</v>
       </c>
       <c r="R78" t="n">
-        <v>7151307</v>
+        <v>7151556</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8968,7 +8968,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120062963</v>
+        <v>120064407</v>
       </c>
       <c r="B79" t="n">
         <v>91840</v>
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746369</v>
+        <v>746440</v>
       </c>
       <c r="R79" t="n">
-        <v>7151279</v>
+        <v>7151291</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9080,7 +9080,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120063963</v>
+        <v>120061583</v>
       </c>
       <c r="B80" t="n">
         <v>91840</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746301</v>
+        <v>746472</v>
       </c>
       <c r="R80" t="n">
-        <v>7151207</v>
+        <v>7151401</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9192,10 +9192,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120061607</v>
+        <v>120062389</v>
       </c>
       <c r="B81" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9204,25 +9204,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746453</v>
+        <v>746426</v>
       </c>
       <c r="R81" t="n">
-        <v>7151408</v>
+        <v>7151309</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9304,10 +9304,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120063487</v>
+        <v>120059636</v>
       </c>
       <c r="B82" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9316,25 +9316,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746300</v>
+        <v>746602</v>
       </c>
       <c r="R82" t="n">
-        <v>7151231</v>
+        <v>7151535</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9416,10 +9416,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120062338</v>
+        <v>120059683</v>
       </c>
       <c r="B83" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9428,25 +9428,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>746390</v>
+        <v>746569</v>
       </c>
       <c r="R83" t="n">
-        <v>7151301</v>
+        <v>7151549</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9528,10 +9528,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120059636</v>
+        <v>120062274</v>
       </c>
       <c r="B84" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9540,25 +9540,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9568,10 +9568,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746602</v>
+        <v>746394</v>
       </c>
       <c r="R84" t="n">
-        <v>7151535</v>
+        <v>7151307</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9640,10 +9640,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120061645</v>
+        <v>120062963</v>
       </c>
       <c r="B85" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9652,25 +9652,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9680,10 +9680,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746450</v>
+        <v>746369</v>
       </c>
       <c r="R85" t="n">
-        <v>7151380</v>
+        <v>7151279</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9752,10 +9752,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120061247</v>
+        <v>120063383</v>
       </c>
       <c r="B86" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9764,25 +9764,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9792,10 +9792,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>746541</v>
+        <v>746303</v>
       </c>
       <c r="R86" t="n">
-        <v>7151441</v>
+        <v>7151246</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9864,10 +9864,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120063442</v>
+        <v>120061233</v>
       </c>
       <c r="B87" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9876,25 +9876,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>746297</v>
+        <v>746597</v>
       </c>
       <c r="R87" t="n">
-        <v>7151223</v>
+        <v>7151440</v>
       </c>
       <c r="S87" t="n">
         <v>1</v>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9976,10 +9976,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120059956</v>
+        <v>120063693</v>
       </c>
       <c r="B88" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9988,25 +9988,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10016,13 +10016,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>746535</v>
+        <v>746319</v>
       </c>
       <c r="R88" t="n">
-        <v>7151537</v>
+        <v>7151210</v>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10076,22 +10076,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120060888</v>
+        <v>120062338</v>
       </c>
       <c r="B89" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10104,21 +10104,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10128,10 +10128,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>746566</v>
+        <v>746390</v>
       </c>
       <c r="R89" t="n">
-        <v>7151484</v>
+        <v>7151301</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10200,10 +10200,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120063693</v>
+        <v>120063728</v>
       </c>
       <c r="B90" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10212,25 +10212,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10240,13 +10240,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>746319</v>
+        <v>746298</v>
       </c>
       <c r="R90" t="n">
-        <v>7151210</v>
+        <v>7151222</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10300,22 +10300,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120063439</v>
+        <v>120061645</v>
       </c>
       <c r="B91" t="n">
-        <v>91828</v>
+        <v>91884</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10324,25 +10324,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>149</v>
+        <v>5449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10352,10 +10352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>746303</v>
+        <v>746450</v>
       </c>
       <c r="R91" t="n">
-        <v>7151241</v>
+        <v>7151380</v>
       </c>
       <c r="S91" t="n">
         <v>1</v>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10424,7 +10424,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120061458</v>
+        <v>120063287</v>
       </c>
       <c r="B92" t="n">
         <v>91884</v>
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>746495</v>
+        <v>746369</v>
       </c>
       <c r="R92" t="n">
-        <v>7151424</v>
+        <v>7151254</v>
       </c>
       <c r="S92" t="n">
         <v>1</v>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10536,10 +10536,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120063287</v>
+        <v>120063671</v>
       </c>
       <c r="B93" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10552,21 +10552,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>746369</v>
+        <v>746309</v>
       </c>
       <c r="R93" t="n">
-        <v>7151254</v>
+        <v>7151221</v>
       </c>
       <c r="S93" t="n">
         <v>1</v>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10648,7 +10648,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120059683</v>
+        <v>120059794</v>
       </c>
       <c r="B94" t="n">
         <v>91884</v>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>746569</v>
+        <v>746567</v>
       </c>
       <c r="R94" t="n">
-        <v>7151549</v>
+        <v>7151566</v>
       </c>
       <c r="S94" t="n">
         <v>1</v>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10760,10 +10760,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120063671</v>
+        <v>120061860</v>
       </c>
       <c r="B95" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10772,25 +10772,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10800,10 +10800,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>746309</v>
+        <v>746423</v>
       </c>
       <c r="R95" t="n">
-        <v>7151221</v>
+        <v>7151350</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10872,10 +10872,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120062932</v>
+        <v>120059956</v>
       </c>
       <c r="B96" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10888,21 +10888,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>746422</v>
+        <v>746535</v>
       </c>
       <c r="R96" t="n">
-        <v>7151289</v>
+        <v>7151537</v>
       </c>
       <c r="S96" t="n">
         <v>1</v>
@@ -10947,7 +10947,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10984,10 +10984,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120059794</v>
+        <v>120061686</v>
       </c>
       <c r="B97" t="n">
-        <v>91884</v>
+        <v>91863</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11000,21 +11000,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11024,10 +11024,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>746567</v>
+        <v>746448</v>
       </c>
       <c r="R97" t="n">
-        <v>7151566</v>
+        <v>7151388</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11096,10 +11096,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120080297</v>
+        <v>120079808</v>
       </c>
       <c r="B98" t="n">
-        <v>57463</v>
+        <v>90576</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11112,46 +11112,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>746612</v>
+        <v>746668</v>
       </c>
       <c r="R98" t="n">
-        <v>7151234</v>
+        <v>7151253</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11195,22 +11186,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120080303</v>
+        <v>120094292</v>
       </c>
       <c r="B99" t="n">
-        <v>91886</v>
+        <v>91840</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11219,42 +11210,41 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>746331</v>
+        <v>746478</v>
       </c>
       <c r="R99" t="n">
-        <v>7151256</v>
+        <v>7151421</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11289,39 +11279,35 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Under tunn äldre tallgren på mager, torr mark</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120086241</v>
+        <v>120086256</v>
       </c>
       <c r="B100" t="n">
-        <v>91826</v>
+        <v>91852</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11330,25 +11316,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11358,10 +11344,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>746383</v>
+        <v>746576</v>
       </c>
       <c r="R100" t="n">
-        <v>7151288</v>
+        <v>7151444</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11420,10 +11406,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120086232</v>
+        <v>120079807</v>
       </c>
       <c r="B101" t="n">
-        <v>89633</v>
+        <v>57421</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11432,41 +11418,49 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1962</v>
+        <v>103031</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>746551</v>
+        <v>746368</v>
       </c>
       <c r="R101" t="n">
-        <v>7151485</v>
+        <v>7151283</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11510,22 +11504,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120086261</v>
+        <v>120086267</v>
       </c>
       <c r="B102" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11538,21 +11532,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11562,10 +11556,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>746574</v>
+        <v>746492</v>
       </c>
       <c r="R102" t="n">
-        <v>7151495</v>
+        <v>7151446</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11624,10 +11618,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120094266</v>
+        <v>120086283</v>
       </c>
       <c r="B103" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11636,41 +11630,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>746491</v>
+        <v>746566</v>
       </c>
       <c r="R103" t="n">
-        <v>7151452</v>
+        <v>7151468</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11711,7 +11702,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11730,10 +11720,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120086281</v>
+        <v>120094102</v>
       </c>
       <c r="B104" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11742,38 +11732,41 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>746371</v>
+        <v>746539</v>
       </c>
       <c r="R104" t="n">
-        <v>7151235</v>
+        <v>7151513</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11814,6 +11807,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11832,10 +11826,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120079799</v>
+        <v>120080358</v>
       </c>
       <c r="B105" t="n">
-        <v>90562</v>
+        <v>91840</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11844,25 +11838,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11872,13 +11866,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>746840</v>
+        <v>746699</v>
       </c>
       <c r="R105" t="n">
-        <v>7151151</v>
+        <v>7151240</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11922,19 +11916,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120094276</v>
+        <v>120094677</v>
       </c>
       <c r="B106" t="n">
         <v>91840</v>
@@ -11977,10 +11971,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>746476</v>
+        <v>746351</v>
       </c>
       <c r="R106" t="n">
-        <v>7151446</v>
+        <v>7151225</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12040,7 +12034,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120080353</v>
+        <v>120080333</v>
       </c>
       <c r="B107" t="n">
         <v>91840</v>
@@ -12073,17 +12067,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>746577</v>
+        <v>746569</v>
       </c>
       <c r="R107" t="n">
-        <v>7151220</v>
+        <v>7151265</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12116,6 +12114,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Minst, stort mycel</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12142,10 +12145,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120086257</v>
+        <v>120094190</v>
       </c>
       <c r="B108" t="n">
-        <v>91852</v>
+        <v>91884</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12154,38 +12157,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>746575</v>
+        <v>746572</v>
       </c>
       <c r="R108" t="n">
-        <v>7151554</v>
+        <v>7151479</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12226,6 +12232,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -12244,10 +12251,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120086268</v>
+        <v>120086253</v>
       </c>
       <c r="B109" t="n">
-        <v>91863</v>
+        <v>91844</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12256,25 +12263,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5966</v>
+        <v>4365</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12284,10 +12291,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>746563</v>
+        <v>746539</v>
       </c>
       <c r="R109" t="n">
-        <v>7151464</v>
+        <v>7151522</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12346,7 +12353,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120080332</v>
+        <v>120079814</v>
       </c>
       <c r="B110" t="n">
         <v>91840</v>
@@ -12379,24 +12386,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>746560</v>
+        <v>746510</v>
       </c>
       <c r="R110" t="n">
-        <v>7151291</v>
+        <v>7151225</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12440,22 +12443,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120086303</v>
+        <v>120094591</v>
       </c>
       <c r="B111" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12464,38 +12467,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>746555</v>
+        <v>746294</v>
       </c>
       <c r="R111" t="n">
-        <v>7151578</v>
+        <v>7151228</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12536,6 +12542,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12554,10 +12561,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120094170</v>
+        <v>120086287</v>
       </c>
       <c r="B112" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12566,41 +12573,38 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>746562</v>
+        <v>746567</v>
       </c>
       <c r="R112" t="n">
-        <v>7151492</v>
+        <v>7151554</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12641,7 +12645,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12660,10 +12663,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120086237</v>
+        <v>120080335</v>
       </c>
       <c r="B113" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12672,38 +12675,42 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>746561</v>
+        <v>746321</v>
       </c>
       <c r="R113" t="n">
-        <v>7151472</v>
+        <v>7151233</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12750,22 +12757,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120086306</v>
+        <v>120080352</v>
       </c>
       <c r="B114" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12774,25 +12781,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12802,10 +12809,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>746371</v>
+        <v>746834</v>
       </c>
       <c r="R114" t="n">
-        <v>7151274</v>
+        <v>7151121</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12852,22 +12859,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120086243</v>
+        <v>120086260</v>
       </c>
       <c r="B115" t="n">
-        <v>91463</v>
+        <v>91832</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12880,21 +12887,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12904,10 +12911,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>746316</v>
+        <v>746378</v>
       </c>
       <c r="R115" t="n">
-        <v>7151209</v>
+        <v>7151283</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12966,10 +12973,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120094355</v>
+        <v>120086299</v>
       </c>
       <c r="B116" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12978,41 +12985,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>746451</v>
+        <v>746314</v>
       </c>
       <c r="R116" t="n">
-        <v>7151341</v>
+        <v>7151238</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13053,7 +13057,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13072,10 +13075,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120086288</v>
+        <v>120094371</v>
       </c>
       <c r="B117" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13084,38 +13087,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>746630</v>
+        <v>746383</v>
       </c>
       <c r="R117" t="n">
-        <v>7151524</v>
+        <v>7151297</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13156,6 +13162,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13174,10 +13181,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120086290</v>
+        <v>120079801</v>
       </c>
       <c r="B118" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13190,21 +13197,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13214,13 +13221,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>746657</v>
+        <v>746598</v>
       </c>
       <c r="R118" t="n">
-        <v>7151562</v>
+        <v>7151227</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13258,28 +13265,29 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120086289</v>
+        <v>120080309</v>
       </c>
       <c r="B119" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13292,34 +13300,39 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>746670</v>
+        <v>746663</v>
       </c>
       <c r="R119" t="n">
-        <v>7151555</v>
+        <v>7151255</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13354,6 +13367,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Äldre födohack i basen</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -13362,26 +13380,41 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120086271</v>
+        <v>120094170</v>
       </c>
       <c r="B120" t="n">
-        <v>57421</v>
+        <v>91840</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13394,31 +13427,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -13426,10 +13454,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>746500</v>
+        <v>746562</v>
       </c>
       <c r="R120" t="n">
-        <v>7151560</v>
+        <v>7151492</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13470,6 +13498,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13488,10 +13517,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120086252</v>
+        <v>120086284</v>
       </c>
       <c r="B121" t="n">
-        <v>91844</v>
+        <v>78526</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13500,25 +13529,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13528,10 +13557,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>746575</v>
+        <v>746563</v>
       </c>
       <c r="R121" t="n">
-        <v>7151485</v>
+        <v>7151464</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13590,10 +13619,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120086285</v>
+        <v>120080297</v>
       </c>
       <c r="B122" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13606,34 +13635,43 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>746576</v>
+        <v>746612</v>
       </c>
       <c r="R122" t="n">
-        <v>7151476</v>
+        <v>7151234</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13680,19 +13718,19 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120079807</v>
+        <v>120086270</v>
       </c>
       <c r="B123" t="n">
         <v>57421</v>
@@ -13727,12 +13765,16 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13740,13 +13782,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>746368</v>
+        <v>746671</v>
       </c>
       <c r="R123" t="n">
-        <v>7151283</v>
+        <v>7151554</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13790,22 +13832,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120094292</v>
+        <v>120079803</v>
       </c>
       <c r="B124" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13814,44 +13856,41 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>746478</v>
+        <v>746316</v>
       </c>
       <c r="R124" t="n">
-        <v>7151421</v>
+        <v>7151248</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13889,26 +13928,25 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120086300</v>
+        <v>120094359</v>
       </c>
       <c r="B125" t="n">
         <v>91840</v>
@@ -13942,16 +13980,19 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>746381</v>
+        <v>746451</v>
       </c>
       <c r="R125" t="n">
-        <v>7151336</v>
+        <v>7151341</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13992,6 +14033,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -14010,10 +14052,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120079808</v>
+        <v>120094305</v>
       </c>
       <c r="B126" t="n">
-        <v>90576</v>
+        <v>91840</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14022,41 +14064,44 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>746668</v>
+        <v>746472</v>
       </c>
       <c r="R126" t="n">
-        <v>7151253</v>
+        <v>7151410</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14094,28 +14139,29 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120094677</v>
+        <v>120086251</v>
       </c>
       <c r="B127" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14124,41 +14170,38 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>746351</v>
+        <v>746297</v>
       </c>
       <c r="R127" t="n">
-        <v>7151225</v>
+        <v>7151200</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14199,7 +14242,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -14218,10 +14260,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120080352</v>
+        <v>120086249</v>
       </c>
       <c r="B128" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14230,25 +14272,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14258,10 +14300,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>746834</v>
+        <v>746568</v>
       </c>
       <c r="R128" t="n">
-        <v>7151121</v>
+        <v>7151535</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14308,22 +14350,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120094305</v>
+        <v>120086288</v>
       </c>
       <c r="B129" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14332,41 +14374,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>746472</v>
+        <v>746630</v>
       </c>
       <c r="R129" t="n">
-        <v>7151410</v>
+        <v>7151524</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14407,7 +14446,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14426,7 +14464,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120086234</v>
+        <v>120079798</v>
       </c>
       <c r="B130" t="n">
         <v>89633</v>
@@ -14466,13 +14504,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>746539</v>
+        <v>746310</v>
       </c>
       <c r="R130" t="n">
-        <v>7151522</v>
+        <v>7151135</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14516,22 +14554,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120079803</v>
+        <v>120086232</v>
       </c>
       <c r="B131" t="n">
-        <v>91844</v>
+        <v>89633</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14540,25 +14578,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14568,13 +14606,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>746316</v>
+        <v>746551</v>
       </c>
       <c r="R131" t="n">
-        <v>7151248</v>
+        <v>7151485</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14618,22 +14656,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120086254</v>
+        <v>120086264</v>
       </c>
       <c r="B132" t="n">
-        <v>91844</v>
+        <v>92030</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14642,25 +14680,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4365</v>
+        <v>2079</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14670,10 +14708,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>746678</v>
+        <v>746539</v>
       </c>
       <c r="R132" t="n">
-        <v>7151537</v>
+        <v>7151522</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14732,10 +14770,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120086253</v>
+        <v>120086301</v>
       </c>
       <c r="B133" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14744,25 +14782,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14772,10 +14810,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>746539</v>
+        <v>746566</v>
       </c>
       <c r="R133" t="n">
-        <v>7151522</v>
+        <v>7151468</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14834,7 +14872,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120080334</v>
+        <v>120080357</v>
       </c>
       <c r="B134" t="n">
         <v>91840</v>
@@ -14867,21 +14905,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>746537</v>
+        <v>746301</v>
       </c>
       <c r="R134" t="n">
-        <v>7151303</v>
+        <v>7151209</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14940,10 +14974,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120079816</v>
+        <v>120086290</v>
       </c>
       <c r="B135" t="n">
-        <v>91834</v>
+        <v>78526</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14956,21 +14990,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14980,13 +15014,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>746534</v>
+        <v>746657</v>
       </c>
       <c r="R135" t="n">
-        <v>7151288</v>
+        <v>7151562</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15030,22 +15064,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120080309</v>
+        <v>120080359</v>
       </c>
       <c r="B136" t="n">
-        <v>57326</v>
+        <v>91834</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15058,27 +15092,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -15087,10 +15120,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>746663</v>
+        <v>746291</v>
       </c>
       <c r="R136" t="n">
-        <v>7151255</v>
+        <v>7151137</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15125,11 +15158,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Äldre födohack i basen</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -15138,21 +15166,6 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
@@ -15169,10 +15182,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120086299</v>
+        <v>120079816</v>
       </c>
       <c r="B137" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15181,25 +15194,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15209,13 +15222,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>746314</v>
+        <v>746534</v>
       </c>
       <c r="R137" t="n">
-        <v>7151238</v>
+        <v>7151288</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15259,22 +15272,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120080333</v>
+        <v>120086241</v>
       </c>
       <c r="B138" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15283,42 +15296,38 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>746569</v>
+        <v>746383</v>
       </c>
       <c r="R138" t="n">
-        <v>7151265</v>
+        <v>7151288</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15353,11 +15362,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Minst, stort mycel</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -15370,22 +15374,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120086287</v>
+        <v>120086304</v>
       </c>
       <c r="B139" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15394,25 +15398,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15422,10 +15426,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>746567</v>
+        <v>746589</v>
       </c>
       <c r="R139" t="n">
-        <v>7151554</v>
+        <v>7151537</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15484,10 +15488,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120086282</v>
+        <v>120086268</v>
       </c>
       <c r="B140" t="n">
-        <v>78526</v>
+        <v>91863</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15500,21 +15504,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15524,10 +15528,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>746368</v>
+        <v>746563</v>
       </c>
       <c r="R140" t="n">
-        <v>7151288</v>
+        <v>7151464</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15586,7 +15590,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120086283</v>
+        <v>120086289</v>
       </c>
       <c r="B141" t="n">
         <v>78526</v>
@@ -15626,10 +15630,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>746566</v>
+        <v>746670</v>
       </c>
       <c r="R141" t="n">
-        <v>7151468</v>
+        <v>7151555</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15688,10 +15692,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120080331</v>
+        <v>120086248</v>
       </c>
       <c r="B142" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15704,21 +15708,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15728,10 +15732,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>746936</v>
+        <v>746537</v>
       </c>
       <c r="R142" t="n">
-        <v>7151139</v>
+        <v>7151592</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15766,11 +15770,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15779,41 +15778,26 @@
       </c>
       <c r="AG142" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120080296</v>
+        <v>120094355</v>
       </c>
       <c r="B143" t="n">
-        <v>57463</v>
+        <v>91884</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15826,31 +15810,26 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -15858,10 +15837,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>746527</v>
+        <v>746451</v>
       </c>
       <c r="R143" t="n">
-        <v>7151199</v>
+        <v>7151341</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15902,28 +15881,29 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120080291</v>
+        <v>120086303</v>
       </c>
       <c r="B144" t="n">
-        <v>91254</v>
+        <v>91840</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15936,38 +15916,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3298</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>746393</v>
+        <v>746555</v>
       </c>
       <c r="R144" t="n">
-        <v>7151288</v>
+        <v>7151578</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16002,11 +15978,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Basen av levande gran</t>
-        </is>
-      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
@@ -16015,41 +15986,26 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120086308</v>
+        <v>120086254</v>
       </c>
       <c r="B145" t="n">
-        <v>91834</v>
+        <v>91844</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16058,25 +16014,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16086,10 +16042,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>746492</v>
+        <v>746678</v>
       </c>
       <c r="R145" t="n">
-        <v>7151446</v>
+        <v>7151537</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16148,10 +16104,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120086293</v>
+        <v>120080354</v>
       </c>
       <c r="B146" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16160,25 +16116,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16188,10 +16144,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>746636</v>
+        <v>746559</v>
       </c>
       <c r="R146" t="n">
-        <v>7151518</v>
+        <v>7151216</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16238,22 +16194,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120086307</v>
+        <v>120086247</v>
       </c>
       <c r="B147" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16266,21 +16222,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16290,10 +16246,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>746483</v>
+        <v>746385</v>
       </c>
       <c r="R147" t="n">
-        <v>7151420</v>
+        <v>7151299</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16352,10 +16308,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120080356</v>
+        <v>120086306</v>
       </c>
       <c r="B148" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16364,25 +16320,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16392,10 +16348,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>746499</v>
+        <v>746371</v>
       </c>
       <c r="R148" t="n">
-        <v>7151195</v>
+        <v>7151274</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16442,12 +16398,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -16556,10 +16512,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120080308</v>
+        <v>120086243</v>
       </c>
       <c r="B150" t="n">
-        <v>91884</v>
+        <v>91463</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16572,21 +16528,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16596,10 +16552,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>746368</v>
+        <v>746316</v>
       </c>
       <c r="R150" t="n">
-        <v>7151279</v>
+        <v>7151209</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16646,22 +16602,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120086262</v>
+        <v>120094241</v>
       </c>
       <c r="B151" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16670,38 +16626,41 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>746555</v>
+        <v>746515</v>
       </c>
       <c r="R151" t="n">
-        <v>7151590</v>
+        <v>7151443</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16742,6 +16701,7 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -16760,10 +16720,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120086251</v>
+        <v>120080310</v>
       </c>
       <c r="B152" t="n">
-        <v>91844</v>
+        <v>91821</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16776,34 +16736,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4365</v>
+        <v>6055</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>746297</v>
+        <v>746772</v>
       </c>
       <c r="R152" t="n">
-        <v>7151200</v>
+        <v>7151182</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16838,34 +16801,40 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120086273</v>
+        <v>120094777</v>
       </c>
       <c r="B153" t="n">
-        <v>90712</v>
+        <v>91884</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16874,38 +16843,41 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1503</v>
+        <v>5449</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>746551</v>
+        <v>746478</v>
       </c>
       <c r="R153" t="n">
-        <v>7151485</v>
+        <v>7151377</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16946,6 +16918,7 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -16964,10 +16937,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120094241</v>
+        <v>120079799</v>
       </c>
       <c r="B154" t="n">
-        <v>91840</v>
+        <v>90562</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16976,44 +16949,41 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>746515</v>
+        <v>746840</v>
       </c>
       <c r="R154" t="n">
-        <v>7151443</v>
+        <v>7151151</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17051,29 +17021,28 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120094137</v>
+        <v>120080331</v>
       </c>
       <c r="B155" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17082,41 +17051,38 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>746535</v>
+        <v>746936</v>
       </c>
       <c r="R155" t="n">
-        <v>7151504</v>
+        <v>7151139</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17151,35 +17117,54 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
+        </is>
+      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120086270</v>
+        <v>120086282</v>
       </c>
       <c r="B156" t="n">
-        <v>57421</v>
+        <v>78526</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17188,50 +17173,38 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>746671</v>
+        <v>746368</v>
       </c>
       <c r="R156" t="n">
-        <v>7151554</v>
+        <v>7151288</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17290,10 +17263,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120094483</v>
+        <v>120079810</v>
       </c>
       <c r="B157" t="n">
-        <v>91834</v>
+        <v>78526</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17306,40 +17279,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>746321</v>
+        <v>746645</v>
       </c>
       <c r="R157" t="n">
-        <v>7151245</v>
+        <v>7151221</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17377,29 +17347,28 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120086260</v>
+        <v>120086273</v>
       </c>
       <c r="B158" t="n">
-        <v>91832</v>
+        <v>90712</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17408,25 +17377,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4361</v>
+        <v>1503</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17436,10 +17405,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>746378</v>
+        <v>746551</v>
       </c>
       <c r="R158" t="n">
-        <v>7151283</v>
+        <v>7151485</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17498,10 +17467,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120094591</v>
+        <v>120080303</v>
       </c>
       <c r="B159" t="n">
-        <v>91834</v>
+        <v>91886</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17510,41 +17479,42 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4362</v>
+        <v>232140</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>746294</v>
+        <v>746331</v>
       </c>
       <c r="R159" t="n">
-        <v>7151228</v>
+        <v>7151256</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17579,35 +17549,39 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Under tunn äldre tallgren på mager, torr mark</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120086256</v>
+        <v>120079811</v>
       </c>
       <c r="B160" t="n">
-        <v>91852</v>
+        <v>90807</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17616,25 +17590,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4366</v>
+        <v>65</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17644,13 +17618,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>746576</v>
+        <v>746751</v>
       </c>
       <c r="R160" t="n">
-        <v>7151444</v>
+        <v>7151208</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17688,28 +17662,29 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120086249</v>
+        <v>120094266</v>
       </c>
       <c r="B161" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17718,38 +17693,41 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>746568</v>
+        <v>746491</v>
       </c>
       <c r="R161" t="n">
-        <v>7151535</v>
+        <v>7151452</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17790,6 +17768,7 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -17808,10 +17787,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120086264</v>
+        <v>120086257</v>
       </c>
       <c r="B162" t="n">
-        <v>92030</v>
+        <v>91852</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17820,25 +17799,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2079</v>
+        <v>4366</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17848,10 +17827,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>746539</v>
+        <v>746575</v>
       </c>
       <c r="R162" t="n">
-        <v>7151522</v>
+        <v>7151554</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17910,7 +17889,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120094359</v>
+        <v>120080334</v>
       </c>
       <c r="B163" t="n">
         <v>91840</v>
@@ -17943,20 +17922,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>746451</v>
+        <v>746537</v>
       </c>
       <c r="R163" t="n">
-        <v>7151341</v>
+        <v>7151303</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17997,29 +17977,28 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120080335</v>
+        <v>120086252</v>
       </c>
       <c r="B164" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18028,42 +18007,38 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>746321</v>
+        <v>746575</v>
       </c>
       <c r="R164" t="n">
-        <v>7151233</v>
+        <v>7151485</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18110,19 +18085,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120080358</v>
+        <v>120086300</v>
       </c>
       <c r="B165" t="n">
         <v>91840</v>
@@ -18162,10 +18137,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>746699</v>
+        <v>746381</v>
       </c>
       <c r="R165" t="n">
-        <v>7151240</v>
+        <v>7151336</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18212,22 +18187,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120086267</v>
+        <v>120086286</v>
       </c>
       <c r="B166" t="n">
-        <v>91863</v>
+        <v>78526</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18240,21 +18215,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18264,10 +18239,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>746492</v>
+        <v>746555</v>
       </c>
       <c r="R166" t="n">
-        <v>7151446</v>
+        <v>7151578</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18326,10 +18301,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120079815</v>
+        <v>120080296</v>
       </c>
       <c r="B167" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18338,41 +18313,49 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>746896</v>
+        <v>746527</v>
       </c>
       <c r="R167" t="n">
-        <v>7151149</v>
+        <v>7151199</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18416,22 +18399,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120086239</v>
+        <v>120086307</v>
       </c>
       <c r="B168" t="n">
-        <v>57463</v>
+        <v>91834</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18444,46 +18427,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>746532</v>
+        <v>746483</v>
       </c>
       <c r="R168" t="n">
-        <v>7151493</v>
+        <v>7151420</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18542,10 +18513,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120079811</v>
+        <v>120094483</v>
       </c>
       <c r="B169" t="n">
-        <v>90807</v>
+        <v>91834</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18554,41 +18525,44 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>65</v>
+        <v>4362</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>746751</v>
+        <v>746321</v>
       </c>
       <c r="R169" t="n">
-        <v>7151208</v>
+        <v>7151245</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18633,19 +18607,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120094102</v>
+        <v>120080356</v>
       </c>
       <c r="B170" t="n">
         <v>91840</v>
@@ -18679,19 +18653,16 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>746539</v>
+        <v>746499</v>
       </c>
       <c r="R170" t="n">
-        <v>7151513</v>
+        <v>7151195</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18732,29 +18703,28 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120080357</v>
+        <v>120086244</v>
       </c>
       <c r="B171" t="n">
-        <v>91840</v>
+        <v>91828</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18763,25 +18733,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4364</v>
+        <v>149</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18791,10 +18761,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>746301</v>
+        <v>746576</v>
       </c>
       <c r="R171" t="n">
-        <v>7151209</v>
+        <v>7151444</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18841,22 +18811,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120086248</v>
+        <v>120086293</v>
       </c>
       <c r="B172" t="n">
-        <v>91884</v>
+        <v>78171</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18869,21 +18839,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18893,10 +18863,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>746537</v>
+        <v>746636</v>
       </c>
       <c r="R172" t="n">
-        <v>7151592</v>
+        <v>7151518</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18955,10 +18925,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>120086231</v>
+        <v>120086237</v>
       </c>
       <c r="B173" t="n">
-        <v>90527</v>
+        <v>89275</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18967,25 +18937,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5447</v>
+        <v>6286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18995,10 +18965,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>746676</v>
+        <v>746561</v>
       </c>
       <c r="R173" t="n">
-        <v>7151534</v>
+        <v>7151472</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19057,10 +19027,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120086244</v>
+        <v>120080328</v>
       </c>
       <c r="B174" t="n">
-        <v>91828</v>
+        <v>89964</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19069,25 +19039,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>149</v>
+        <v>5685</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19097,10 +19067,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>746576</v>
+        <v>746590</v>
       </c>
       <c r="R174" t="n">
-        <v>7151444</v>
+        <v>7151225</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19144,25 +19114,40 @@
       <c r="AG174" t="b">
         <v>0</v>
       </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120080359</v>
+        <v>120080291</v>
       </c>
       <c r="B175" t="n">
-        <v>91834</v>
+        <v>91254</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19171,30 +19156,30 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4362</v>
+        <v>3298</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -19203,10 +19188,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>746291</v>
+        <v>746393</v>
       </c>
       <c r="R175" t="n">
-        <v>7151137</v>
+        <v>7151288</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19241,6 +19226,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Basen av levande gran</t>
+        </is>
+      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
@@ -19249,6 +19239,21 @@
       </c>
       <c r="AG175" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
@@ -19265,10 +19270,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120086301</v>
+        <v>120086262</v>
       </c>
       <c r="B176" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19277,25 +19282,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19305,10 +19310,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>746566</v>
+        <v>746555</v>
       </c>
       <c r="R176" t="n">
-        <v>7151468</v>
+        <v>7151590</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19367,10 +19372,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120079810</v>
+        <v>120094137</v>
       </c>
       <c r="B177" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19379,41 +19384,44 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>746645</v>
+        <v>746535</v>
       </c>
       <c r="R177" t="n">
-        <v>7151221</v>
+        <v>7151504</v>
       </c>
       <c r="S177" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19451,28 +19459,29 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120080310</v>
+        <v>120086239</v>
       </c>
       <c r="B178" t="n">
-        <v>91821</v>
+        <v>57463</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19481,30 +19490,39 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6055</v>
+        <v>103021</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
@@ -19512,10 +19530,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>746772</v>
+        <v>746532</v>
       </c>
       <c r="R178" t="n">
-        <v>7151182</v>
+        <v>7151493</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19550,40 +19568,34 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat</t>
-        </is>
-      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120094371</v>
+        <v>120086271</v>
       </c>
       <c r="B179" t="n">
-        <v>91840</v>
+        <v>57421</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19596,26 +19608,31 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
@@ -19623,10 +19640,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>746383</v>
+        <v>746500</v>
       </c>
       <c r="R179" t="n">
-        <v>7151297</v>
+        <v>7151560</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19667,7 +19684,6 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
-      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -19686,10 +19702,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120079814</v>
+        <v>120086308</v>
       </c>
       <c r="B180" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19698,25 +19714,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19726,13 +19742,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>746510</v>
+        <v>746492</v>
       </c>
       <c r="R180" t="n">
-        <v>7151225</v>
+        <v>7151446</v>
       </c>
       <c r="S180" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19776,22 +19792,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120086247</v>
+        <v>120080330</v>
       </c>
       <c r="B181" t="n">
-        <v>91884</v>
+        <v>90712</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19800,25 +19816,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5449</v>
+        <v>1503</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19828,10 +19844,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>746385</v>
+        <v>746624</v>
       </c>
       <c r="R181" t="n">
-        <v>7151299</v>
+        <v>7151217</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19866,6 +19882,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Nedbruten tallåga, kollekt taget</t>
+        </is>
+      </c>
       <c r="AD181" t="b">
         <v>0</v>
       </c>
@@ -19874,26 +19895,41 @@
       </c>
       <c r="AG181" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120094190</v>
+        <v>120079815</v>
       </c>
       <c r="B182" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19902,44 +19938,41 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>746572</v>
+        <v>746896</v>
       </c>
       <c r="R182" t="n">
-        <v>7151479</v>
+        <v>7151149</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19977,29 +20010,28 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120079801</v>
+        <v>120080355</v>
       </c>
       <c r="B183" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20008,25 +20040,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20036,13 +20068,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>746598</v>
+        <v>746527</v>
       </c>
       <c r="R183" t="n">
-        <v>7151227</v>
+        <v>7151203</v>
       </c>
       <c r="S183" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20080,29 +20112,28 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120080328</v>
+        <v>120086285</v>
       </c>
       <c r="B184" t="n">
-        <v>89964</v>
+        <v>78526</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20111,25 +20142,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20139,10 +20170,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>746590</v>
+        <v>746576</v>
       </c>
       <c r="R184" t="n">
-        <v>7151225</v>
+        <v>7151476</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20186,40 +20217,25 @@
       <c r="AG184" t="b">
         <v>0</v>
       </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120086304</v>
+        <v>120086281</v>
       </c>
       <c r="B185" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20228,25 +20244,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20256,10 +20272,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>746589</v>
+        <v>746371</v>
       </c>
       <c r="R185" t="n">
-        <v>7151537</v>
+        <v>7151235</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20318,10 +20334,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120086286</v>
+        <v>120094276</v>
       </c>
       <c r="B186" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20330,38 +20346,41 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>746555</v>
+        <v>746476</v>
       </c>
       <c r="R186" t="n">
-        <v>7151578</v>
+        <v>7151446</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20402,6 +20421,7 @@
       <c r="AE186" t="b">
         <v>0</v>
       </c>
+      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>
@@ -20420,10 +20440,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120086284</v>
+        <v>120080308</v>
       </c>
       <c r="B187" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20436,21 +20456,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20460,10 +20480,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>746563</v>
+        <v>746368</v>
       </c>
       <c r="R187" t="n">
-        <v>7151464</v>
+        <v>7151279</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20510,22 +20530,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120094777</v>
+        <v>120086231</v>
       </c>
       <c r="B188" t="n">
-        <v>91884</v>
+        <v>90527</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20534,41 +20554,38 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>746478</v>
+        <v>746676</v>
       </c>
       <c r="R188" t="n">
-        <v>7151377</v>
+        <v>7151534</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20609,7 +20626,6 @@
       <c r="AE188" t="b">
         <v>0</v>
       </c>
-      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
@@ -20628,10 +20644,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120080330</v>
+        <v>120086234</v>
       </c>
       <c r="B189" t="n">
-        <v>90712</v>
+        <v>89633</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20640,25 +20656,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20668,10 +20684,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>746624</v>
+        <v>746539</v>
       </c>
       <c r="R189" t="n">
-        <v>7151217</v>
+        <v>7151522</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20706,11 +20722,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Nedbruten tallåga, kollekt taget</t>
-        </is>
-      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
@@ -20719,38 +20730,23 @@
       </c>
       <c r="AG189" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO189" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>120080354</v>
+        <v>120080332</v>
       </c>
       <c r="B190" t="n">
         <v>91840</v>
@@ -20783,17 +20779,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>746559</v>
+        <v>746560</v>
       </c>
       <c r="R190" t="n">
-        <v>7151216</v>
+        <v>7151291</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20852,7 +20852,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>120080355</v>
+        <v>120080353</v>
       </c>
       <c r="B191" t="n">
         <v>91840</v>
@@ -20892,10 +20892,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>746527</v>
+        <v>746577</v>
       </c>
       <c r="R191" t="n">
-        <v>7151203</v>
+        <v>7151220</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20954,10 +20954,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>120079798</v>
+        <v>120086261</v>
       </c>
       <c r="B192" t="n">
-        <v>89633</v>
+        <v>91832</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20970,21 +20970,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20994,13 +20994,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>746310</v>
+        <v>746574</v>
       </c>
       <c r="R192" t="n">
-        <v>7151135</v>
+        <v>7151495</v>
       </c>
       <c r="S192" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21044,12 +21044,12 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -7400,10 +7400,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120061607</v>
+        <v>120063439</v>
       </c>
       <c r="B65" t="n">
-        <v>91832</v>
+        <v>91828</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7412,25 +7412,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746453</v>
+        <v>746303</v>
       </c>
       <c r="R65" t="n">
-        <v>7151408</v>
+        <v>7151241</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7512,10 +7512,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120063439</v>
+        <v>120061607</v>
       </c>
       <c r="B66" t="n">
-        <v>91828</v>
+        <v>91832</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7524,25 +7524,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>149</v>
+        <v>4361</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746303</v>
+        <v>746453</v>
       </c>
       <c r="R66" t="n">
-        <v>7151241</v>
+        <v>7151408</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7960,10 +7960,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120062932</v>
+        <v>120063551</v>
       </c>
       <c r="B70" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7976,21 +7976,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746422</v>
+        <v>746308</v>
       </c>
       <c r="R70" t="n">
-        <v>7151289</v>
+        <v>7151219</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8072,10 +8072,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120063551</v>
+        <v>120062932</v>
       </c>
       <c r="B71" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746308</v>
+        <v>746422</v>
       </c>
       <c r="R71" t="n">
-        <v>7151219</v>
+        <v>7151289</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -12251,10 +12251,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120086253</v>
+        <v>120094591</v>
       </c>
       <c r="B109" t="n">
-        <v>91844</v>
+        <v>91834</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12263,38 +12263,41 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>746539</v>
+        <v>746294</v>
       </c>
       <c r="R109" t="n">
-        <v>7151522</v>
+        <v>7151228</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12335,6 +12338,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -12353,10 +12357,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120079814</v>
+        <v>120086253</v>
       </c>
       <c r="B110" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12365,25 +12369,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12393,13 +12397,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>746510</v>
+        <v>746539</v>
       </c>
       <c r="R110" t="n">
-        <v>7151225</v>
+        <v>7151522</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12443,22 +12447,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120094591</v>
+        <v>120079814</v>
       </c>
       <c r="B111" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12467,44 +12471,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>746294</v>
+        <v>746510</v>
       </c>
       <c r="R111" t="n">
-        <v>7151228</v>
+        <v>7151225</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12542,19 +12543,18 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -12663,10 +12663,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120080335</v>
+        <v>120086260</v>
       </c>
       <c r="B113" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12675,42 +12675,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>746321</v>
+        <v>746378</v>
       </c>
       <c r="R113" t="n">
-        <v>7151233</v>
+        <v>7151283</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12757,19 +12753,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120080352</v>
+        <v>120080335</v>
       </c>
       <c r="B114" t="n">
         <v>91840</v>
@@ -12802,17 +12798,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>746834</v>
+        <v>746321</v>
       </c>
       <c r="R114" t="n">
-        <v>7151121</v>
+        <v>7151233</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12871,10 +12871,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120086260</v>
+        <v>120080352</v>
       </c>
       <c r="B115" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12883,25 +12883,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12911,10 +12911,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>746378</v>
+        <v>746834</v>
       </c>
       <c r="R115" t="n">
-        <v>7151283</v>
+        <v>7151121</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12961,12 +12961,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -14260,10 +14260,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120086249</v>
+        <v>120086288</v>
       </c>
       <c r="B128" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14276,21 +14276,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14300,10 +14300,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>746568</v>
+        <v>746630</v>
       </c>
       <c r="R128" t="n">
-        <v>7151535</v>
+        <v>7151524</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14362,10 +14362,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120086288</v>
+        <v>120086249</v>
       </c>
       <c r="B129" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14378,21 +14378,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>746630</v>
+        <v>746568</v>
       </c>
       <c r="R129" t="n">
-        <v>7151524</v>
+        <v>7151535</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15182,10 +15182,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120079816</v>
+        <v>120086304</v>
       </c>
       <c r="B137" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15194,25 +15194,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15222,13 +15222,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>746534</v>
+        <v>746589</v>
       </c>
       <c r="R137" t="n">
-        <v>7151288</v>
+        <v>7151537</v>
       </c>
       <c r="S137" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15272,22 +15272,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120086241</v>
+        <v>120086268</v>
       </c>
       <c r="B138" t="n">
-        <v>91826</v>
+        <v>91863</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15300,21 +15300,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3100</v>
+        <v>5966</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15324,10 +15324,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>746383</v>
+        <v>746563</v>
       </c>
       <c r="R138" t="n">
-        <v>7151288</v>
+        <v>7151464</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15386,10 +15386,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120086304</v>
+        <v>120086289</v>
       </c>
       <c r="B139" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15398,25 +15398,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15426,10 +15426,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>746589</v>
+        <v>746670</v>
       </c>
       <c r="R139" t="n">
-        <v>7151537</v>
+        <v>7151555</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15488,10 +15488,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120086268</v>
+        <v>120079816</v>
       </c>
       <c r="B140" t="n">
-        <v>91863</v>
+        <v>91834</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15504,21 +15504,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15528,13 +15528,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>746563</v>
+        <v>746534</v>
       </c>
       <c r="R140" t="n">
-        <v>7151464</v>
+        <v>7151288</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15578,22 +15578,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120086289</v>
+        <v>120086241</v>
       </c>
       <c r="B141" t="n">
-        <v>78526</v>
+        <v>91826</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15606,21 +15606,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>3100</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15630,10 +15630,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>746670</v>
+        <v>746383</v>
       </c>
       <c r="R141" t="n">
-        <v>7151555</v>
+        <v>7151288</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16831,10 +16831,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120094777</v>
+        <v>120079799</v>
       </c>
       <c r="B153" t="n">
-        <v>91884</v>
+        <v>90562</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16847,40 +16847,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>746478</v>
+        <v>746840</v>
       </c>
       <c r="R153" t="n">
-        <v>7151377</v>
+        <v>7151151</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16918,29 +16915,28 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120079799</v>
+        <v>120094777</v>
       </c>
       <c r="B154" t="n">
-        <v>90562</v>
+        <v>91884</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16953,37 +16949,40 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>5449</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>746840</v>
+        <v>746478</v>
       </c>
       <c r="R154" t="n">
-        <v>7151151</v>
+        <v>7151377</v>
       </c>
       <c r="S154" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17021,18 +17020,19 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -7176,10 +7176,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120062044</v>
+        <v>120064407</v>
       </c>
       <c r="B63" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7188,25 +7188,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746344</v>
+        <v>746440</v>
       </c>
       <c r="R63" t="n">
-        <v>7151353</v>
+        <v>7151291</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7288,10 +7288,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120063487</v>
+        <v>120063671</v>
       </c>
       <c r="B64" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7304,21 +7304,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7328,10 +7328,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746300</v>
+        <v>746309</v>
       </c>
       <c r="R64" t="n">
-        <v>7151231</v>
+        <v>7151221</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7400,10 +7400,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120063439</v>
+        <v>120061247</v>
       </c>
       <c r="B65" t="n">
-        <v>91828</v>
+        <v>91840</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7412,25 +7412,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>149</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746303</v>
+        <v>746541</v>
       </c>
       <c r="R65" t="n">
-        <v>7151241</v>
+        <v>7151441</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7512,10 +7512,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120061607</v>
+        <v>120063487</v>
       </c>
       <c r="B66" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7528,21 +7528,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746453</v>
+        <v>746300</v>
       </c>
       <c r="R66" t="n">
-        <v>7151408</v>
+        <v>7151231</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120061725</v>
+        <v>120063287</v>
       </c>
       <c r="B67" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7640,21 +7640,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7664,10 +7664,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746444</v>
+        <v>746369</v>
       </c>
       <c r="R67" t="n">
-        <v>7151382</v>
+        <v>7151254</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7736,10 +7736,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120063442</v>
+        <v>120061458</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7748,25 +7748,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746297</v>
+        <v>746495</v>
       </c>
       <c r="R68" t="n">
-        <v>7151223</v>
+        <v>7151424</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7848,7 +7848,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120064681</v>
+        <v>120064386</v>
       </c>
       <c r="B69" t="n">
         <v>91840</v>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7960,10 +7960,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120063551</v>
+        <v>120062185</v>
       </c>
       <c r="B70" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7972,25 +7972,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746308</v>
+        <v>746401</v>
       </c>
       <c r="R70" t="n">
-        <v>7151219</v>
+        <v>7151292</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8072,7 +8072,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120062932</v>
+        <v>120059683</v>
       </c>
       <c r="B71" t="n">
         <v>91884</v>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746422</v>
+        <v>746569</v>
       </c>
       <c r="R71" t="n">
-        <v>7151289</v>
+        <v>7151549</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8184,7 +8184,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120061247</v>
+        <v>120059636</v>
       </c>
       <c r="B72" t="n">
         <v>91840</v>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746541</v>
+        <v>746602</v>
       </c>
       <c r="R72" t="n">
-        <v>7151441</v>
+        <v>7151535</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8296,7 +8296,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120061458</v>
+        <v>120061645</v>
       </c>
       <c r="B73" t="n">
         <v>91884</v>
@@ -8336,10 +8336,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746495</v>
+        <v>746450</v>
       </c>
       <c r="R73" t="n">
-        <v>7151424</v>
+        <v>7151380</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8408,10 +8408,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120061534</v>
+        <v>120062932</v>
       </c>
       <c r="B74" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8420,25 +8420,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746467</v>
+        <v>746422</v>
       </c>
       <c r="R74" t="n">
-        <v>7151403</v>
+        <v>7151289</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8520,10 +8520,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120060888</v>
+        <v>120061534</v>
       </c>
       <c r="B75" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8536,21 +8536,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746566</v>
+        <v>746467</v>
       </c>
       <c r="R75" t="n">
-        <v>7151484</v>
+        <v>7151403</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8632,10 +8632,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120062185</v>
+        <v>120063551</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8644,25 +8644,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746401</v>
+        <v>746308</v>
       </c>
       <c r="R76" t="n">
-        <v>7151292</v>
+        <v>7151219</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8744,10 +8744,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120063963</v>
+        <v>120059794</v>
       </c>
       <c r="B77" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8756,25 +8756,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746301</v>
+        <v>746567</v>
       </c>
       <c r="R77" t="n">
-        <v>7151207</v>
+        <v>7151566</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8856,7 +8856,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120059872</v>
+        <v>120063693</v>
       </c>
       <c r="B78" t="n">
         <v>91840</v>
@@ -8896,13 +8896,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746557</v>
+        <v>746319</v>
       </c>
       <c r="R78" t="n">
-        <v>7151556</v>
+        <v>7151210</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8956,22 +8956,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120064407</v>
+        <v>120061725</v>
       </c>
       <c r="B79" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8980,25 +8980,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746440</v>
+        <v>746444</v>
       </c>
       <c r="R79" t="n">
-        <v>7151291</v>
+        <v>7151382</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9080,7 +9080,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120061583</v>
+        <v>120063442</v>
       </c>
       <c r="B80" t="n">
         <v>91840</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746472</v>
+        <v>746297</v>
       </c>
       <c r="R80" t="n">
-        <v>7151401</v>
+        <v>7151223</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9192,7 +9192,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120062389</v>
+        <v>120062963</v>
       </c>
       <c r="B81" t="n">
         <v>91840</v>
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746426</v>
+        <v>746369</v>
       </c>
       <c r="R81" t="n">
-        <v>7151309</v>
+        <v>7151279</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9304,7 +9304,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120059636</v>
+        <v>120062338</v>
       </c>
       <c r="B82" t="n">
         <v>91840</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746602</v>
+        <v>746390</v>
       </c>
       <c r="R82" t="n">
-        <v>7151535</v>
+        <v>7151301</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9416,10 +9416,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120059683</v>
+        <v>120060888</v>
       </c>
       <c r="B83" t="n">
-        <v>91884</v>
+        <v>96868</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9428,25 +9428,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5449</v>
+        <v>221941</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>746569</v>
+        <v>746566</v>
       </c>
       <c r="R83" t="n">
-        <v>7151549</v>
+        <v>7151484</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9528,7 +9528,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120062274</v>
+        <v>120063728</v>
       </c>
       <c r="B84" t="n">
         <v>91884</v>
@@ -9568,10 +9568,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746394</v>
+        <v>746298</v>
       </c>
       <c r="R84" t="n">
-        <v>7151307</v>
+        <v>7151222</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9640,10 +9640,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120062963</v>
+        <v>120062274</v>
       </c>
       <c r="B85" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9652,25 +9652,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9680,10 +9680,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746369</v>
+        <v>746394</v>
       </c>
       <c r="R85" t="n">
-        <v>7151279</v>
+        <v>7151307</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9752,10 +9752,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120063383</v>
+        <v>120061607</v>
       </c>
       <c r="B86" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9768,21 +9768,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9792,10 +9792,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>746303</v>
+        <v>746453</v>
       </c>
       <c r="R86" t="n">
-        <v>7151246</v>
+        <v>7151408</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9864,10 +9864,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120061233</v>
+        <v>120061860</v>
       </c>
       <c r="B87" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9876,25 +9876,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>746597</v>
+        <v>746423</v>
       </c>
       <c r="R87" t="n">
-        <v>7151440</v>
+        <v>7151350</v>
       </c>
       <c r="S87" t="n">
         <v>1</v>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9976,7 +9976,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120063693</v>
+        <v>120061583</v>
       </c>
       <c r="B88" t="n">
         <v>91840</v>
@@ -10016,13 +10016,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>746319</v>
+        <v>746472</v>
       </c>
       <c r="R88" t="n">
-        <v>7151210</v>
+        <v>7151401</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10076,19 +10076,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120062338</v>
+        <v>120059872</v>
       </c>
       <c r="B89" t="n">
         <v>91840</v>
@@ -10128,10 +10128,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>746390</v>
+        <v>746557</v>
       </c>
       <c r="R89" t="n">
-        <v>7151301</v>
+        <v>7151556</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10200,10 +10200,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120063728</v>
+        <v>120062389</v>
       </c>
       <c r="B90" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10212,25 +10212,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10240,10 +10240,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>746298</v>
+        <v>746426</v>
       </c>
       <c r="R90" t="n">
-        <v>7151222</v>
+        <v>7151309</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
@@ -10275,7 +10275,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10312,7 +10312,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120061645</v>
+        <v>120062044</v>
       </c>
       <c r="B91" t="n">
         <v>91884</v>
@@ -10352,10 +10352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>746450</v>
+        <v>746344</v>
       </c>
       <c r="R91" t="n">
-        <v>7151380</v>
+        <v>7151353</v>
       </c>
       <c r="S91" t="n">
         <v>1</v>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10424,10 +10424,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120063287</v>
+        <v>120063383</v>
       </c>
       <c r="B92" t="n">
-        <v>91884</v>
+        <v>91863</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10440,21 +10440,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>746369</v>
+        <v>746303</v>
       </c>
       <c r="R92" t="n">
-        <v>7151254</v>
+        <v>7151246</v>
       </c>
       <c r="S92" t="n">
         <v>1</v>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10536,10 +10536,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120063671</v>
+        <v>120061686</v>
       </c>
       <c r="B93" t="n">
-        <v>91856</v>
+        <v>91863</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10552,21 +10552,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>746309</v>
+        <v>746448</v>
       </c>
       <c r="R93" t="n">
-        <v>7151221</v>
+        <v>7151388</v>
       </c>
       <c r="S93" t="n">
         <v>1</v>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10648,10 +10648,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120059794</v>
+        <v>120059956</v>
       </c>
       <c r="B94" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10664,21 +10664,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>746567</v>
+        <v>746535</v>
       </c>
       <c r="R94" t="n">
-        <v>7151566</v>
+        <v>7151537</v>
       </c>
       <c r="S94" t="n">
         <v>1</v>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10760,10 +10760,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120061860</v>
+        <v>120061233</v>
       </c>
       <c r="B95" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10772,25 +10772,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10800,10 +10800,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>746423</v>
+        <v>746597</v>
       </c>
       <c r="R95" t="n">
-        <v>7151350</v>
+        <v>7151440</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10872,10 +10872,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120059956</v>
+        <v>120063439</v>
       </c>
       <c r="B96" t="n">
-        <v>91832</v>
+        <v>91828</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10884,25 +10884,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>746535</v>
+        <v>746303</v>
       </c>
       <c r="R96" t="n">
-        <v>7151537</v>
+        <v>7151241</v>
       </c>
       <c r="S96" t="n">
         <v>1</v>
@@ -10947,7 +10947,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10984,10 +10984,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120061686</v>
+        <v>120063963</v>
       </c>
       <c r="B97" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10996,25 +10996,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11024,10 +11024,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>746448</v>
+        <v>746301</v>
       </c>
       <c r="R97" t="n">
-        <v>7151388</v>
+        <v>7151207</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11096,10 +11096,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120079808</v>
+        <v>120094137</v>
       </c>
       <c r="B98" t="n">
-        <v>90576</v>
+        <v>91840</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11108,41 +11108,44 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>746668</v>
+        <v>746535</v>
       </c>
       <c r="R98" t="n">
-        <v>7151253</v>
+        <v>7151504</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11180,25 +11183,26 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120094292</v>
+        <v>120094305</v>
       </c>
       <c r="B99" t="n">
         <v>91840</v>
@@ -11241,10 +11245,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>746478</v>
+        <v>746472</v>
       </c>
       <c r="R99" t="n">
-        <v>7151421</v>
+        <v>7151410</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11304,10 +11308,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120086256</v>
+        <v>120086232</v>
       </c>
       <c r="B100" t="n">
-        <v>91852</v>
+        <v>89633</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11316,25 +11320,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11344,10 +11348,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>746576</v>
+        <v>746551</v>
       </c>
       <c r="R100" t="n">
-        <v>7151444</v>
+        <v>7151485</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11406,10 +11410,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120079807</v>
+        <v>120086307</v>
       </c>
       <c r="B101" t="n">
-        <v>57421</v>
+        <v>91834</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11418,49 +11422,41 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103031</v>
+        <v>4362</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>746368</v>
+        <v>746483</v>
       </c>
       <c r="R101" t="n">
-        <v>7151283</v>
+        <v>7151420</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11504,22 +11500,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120086267</v>
+        <v>120094276</v>
       </c>
       <c r="B102" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11528,35 +11524,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>746492</v>
+        <v>746476</v>
       </c>
       <c r="R102" t="n">
         <v>7151446</v>
@@ -11600,6 +11599,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11618,10 +11618,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120086283</v>
+        <v>120086243</v>
       </c>
       <c r="B103" t="n">
-        <v>78526</v>
+        <v>91463</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11634,21 +11634,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11658,10 +11658,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>746566</v>
+        <v>746316</v>
       </c>
       <c r="R103" t="n">
-        <v>7151468</v>
+        <v>7151209</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11720,10 +11720,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120094102</v>
+        <v>120086257</v>
       </c>
       <c r="B104" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11736,37 +11736,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>746539</v>
+        <v>746575</v>
       </c>
       <c r="R104" t="n">
-        <v>7151513</v>
+        <v>7151554</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11807,7 +11804,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11826,10 +11822,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120080358</v>
+        <v>120080359</v>
       </c>
       <c r="B105" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11838,38 +11834,42 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>746699</v>
+        <v>746291</v>
       </c>
       <c r="R105" t="n">
-        <v>7151240</v>
+        <v>7151137</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11928,10 +11928,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120094677</v>
+        <v>120079801</v>
       </c>
       <c r="B106" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11940,44 +11940,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>746351</v>
+        <v>746598</v>
       </c>
       <c r="R106" t="n">
-        <v>7151225</v>
+        <v>7151227</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12022,19 +12019,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120080333</v>
+        <v>120080353</v>
       </c>
       <c r="B107" t="n">
         <v>91840</v>
@@ -12067,21 +12064,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>746569</v>
+        <v>746577</v>
       </c>
       <c r="R107" t="n">
-        <v>7151265</v>
+        <v>7151220</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12114,11 +12107,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Minst, stort mycel</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12145,7 +12133,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120094190</v>
+        <v>120094777</v>
       </c>
       <c r="B108" t="n">
         <v>91884</v>
@@ -12188,10 +12176,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>746572</v>
+        <v>746478</v>
       </c>
       <c r="R108" t="n">
-        <v>7151479</v>
+        <v>7151377</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12251,10 +12239,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120094591</v>
+        <v>120094102</v>
       </c>
       <c r="B109" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12263,25 +12251,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12294,10 +12282,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>746294</v>
+        <v>746539</v>
       </c>
       <c r="R109" t="n">
-        <v>7151228</v>
+        <v>7151513</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12357,10 +12345,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120086253</v>
+        <v>120086267</v>
       </c>
       <c r="B110" t="n">
-        <v>91844</v>
+        <v>91863</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12369,25 +12357,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4365</v>
+        <v>5966</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12397,10 +12385,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>746539</v>
+        <v>746492</v>
       </c>
       <c r="R110" t="n">
-        <v>7151522</v>
+        <v>7151446</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12459,10 +12447,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120079814</v>
+        <v>120086286</v>
       </c>
       <c r="B111" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12471,25 +12459,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12499,13 +12487,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>746510</v>
+        <v>746555</v>
       </c>
       <c r="R111" t="n">
-        <v>7151225</v>
+        <v>7151578</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12549,22 +12537,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120086287</v>
+        <v>120079798</v>
       </c>
       <c r="B112" t="n">
-        <v>78526</v>
+        <v>89633</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12577,21 +12565,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12601,13 +12589,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>746567</v>
+        <v>746310</v>
       </c>
       <c r="R112" t="n">
-        <v>7151554</v>
+        <v>7151135</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12651,22 +12639,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120086260</v>
+        <v>120086308</v>
       </c>
       <c r="B113" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12679,21 +12667,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12703,10 +12691,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>746378</v>
+        <v>746492</v>
       </c>
       <c r="R113" t="n">
-        <v>7151283</v>
+        <v>7151446</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12765,10 +12753,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120080335</v>
+        <v>120086273</v>
       </c>
       <c r="B114" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12777,42 +12765,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>746321</v>
+        <v>746551</v>
       </c>
       <c r="R114" t="n">
-        <v>7151233</v>
+        <v>7151485</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12859,22 +12843,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120080352</v>
+        <v>120080308</v>
       </c>
       <c r="B115" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12883,25 +12867,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12911,10 +12895,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>746834</v>
+        <v>746368</v>
       </c>
       <c r="R115" t="n">
-        <v>7151121</v>
+        <v>7151279</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12973,7 +12957,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120086299</v>
+        <v>120094292</v>
       </c>
       <c r="B116" t="n">
         <v>91840</v>
@@ -13007,16 +12991,19 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>746314</v>
+        <v>746478</v>
       </c>
       <c r="R116" t="n">
-        <v>7151238</v>
+        <v>7151421</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13057,6 +13044,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13075,7 +13063,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120094371</v>
+        <v>120094359</v>
       </c>
       <c r="B117" t="n">
         <v>91840</v>
@@ -13118,10 +13106,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>746383</v>
+        <v>746451</v>
       </c>
       <c r="R117" t="n">
-        <v>7151297</v>
+        <v>7151341</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13181,10 +13169,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120079801</v>
+        <v>120080356</v>
       </c>
       <c r="B118" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13193,25 +13181,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13221,13 +13209,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>746598</v>
+        <v>746499</v>
       </c>
       <c r="R118" t="n">
-        <v>7151227</v>
+        <v>7151195</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13265,29 +13253,28 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120080309</v>
+        <v>120086303</v>
       </c>
       <c r="B119" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13296,43 +13283,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>746663</v>
+        <v>746555</v>
       </c>
       <c r="R119" t="n">
-        <v>7151255</v>
+        <v>7151578</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13367,11 +13349,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Äldre födohack i basen</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -13380,38 +13357,23 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120094170</v>
+        <v>120080357</v>
       </c>
       <c r="B120" t="n">
         <v>91840</v>
@@ -13445,19 +13407,16 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>746562</v>
+        <v>746301</v>
       </c>
       <c r="R120" t="n">
-        <v>7151492</v>
+        <v>7151209</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13498,29 +13457,28 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120086284</v>
+        <v>120080291</v>
       </c>
       <c r="B121" t="n">
-        <v>78526</v>
+        <v>91254</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13529,38 +13487,42 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>746563</v>
+        <v>746393</v>
       </c>
       <c r="R121" t="n">
-        <v>7151464</v>
+        <v>7151288</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13595,6 +13557,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Basen av levande gran</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -13603,26 +13570,41 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120080297</v>
+        <v>120080309</v>
       </c>
       <c r="B122" t="n">
-        <v>57463</v>
+        <v>57326</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13635,31 +13617,27 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13668,10 +13646,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>746612</v>
+        <v>746663</v>
       </c>
       <c r="R122" t="n">
-        <v>7151234</v>
+        <v>7151255</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13706,6 +13684,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Äldre födohack i basen</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -13714,6 +13697,21 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
@@ -13730,10 +13728,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120086270</v>
+        <v>120080330</v>
       </c>
       <c r="B123" t="n">
-        <v>57421</v>
+        <v>90712</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13742,50 +13740,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103031</v>
+        <v>1503</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>746671</v>
+        <v>746624</v>
       </c>
       <c r="R123" t="n">
-        <v>7151554</v>
+        <v>7151217</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13820,6 +13806,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Nedbruten tallåga, kollekt taget</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
@@ -13828,26 +13819,41 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120079803</v>
+        <v>120080310</v>
       </c>
       <c r="B124" t="n">
-        <v>91844</v>
+        <v>91821</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13860,37 +13866,40 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4365</v>
+        <v>6055</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>746316</v>
+        <v>746772</v>
       </c>
       <c r="R124" t="n">
-        <v>7151248</v>
+        <v>7151182</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13922,34 +13931,40 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120094359</v>
+        <v>120079810</v>
       </c>
       <c r="B125" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13958,44 +13973,41 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>746451</v>
+        <v>746645</v>
       </c>
       <c r="R125" t="n">
-        <v>7151341</v>
+        <v>7151221</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14033,29 +14045,28 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120094305</v>
+        <v>120079799</v>
       </c>
       <c r="B126" t="n">
-        <v>91840</v>
+        <v>90562</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14064,44 +14075,41 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>746472</v>
+        <v>746840</v>
       </c>
       <c r="R126" t="n">
-        <v>7151410</v>
+        <v>7151151</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14139,29 +14147,28 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120086251</v>
+        <v>120086248</v>
       </c>
       <c r="B127" t="n">
-        <v>91844</v>
+        <v>91884</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14170,25 +14177,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14198,10 +14205,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>746297</v>
+        <v>746537</v>
       </c>
       <c r="R127" t="n">
-        <v>7151200</v>
+        <v>7151592</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14260,10 +14267,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120086288</v>
+        <v>120080328</v>
       </c>
       <c r="B128" t="n">
-        <v>78526</v>
+        <v>89964</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14272,25 +14279,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14300,10 +14307,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>746630</v>
+        <v>746590</v>
       </c>
       <c r="R128" t="n">
-        <v>7151524</v>
+        <v>7151225</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14347,25 +14354,40 @@
       <c r="AG128" t="b">
         <v>0</v>
       </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120086249</v>
+        <v>120086239</v>
       </c>
       <c r="B129" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14378,34 +14400,46 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>746568</v>
+        <v>746532</v>
       </c>
       <c r="R129" t="n">
-        <v>7151535</v>
+        <v>7151493</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14464,10 +14498,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120079798</v>
+        <v>120094170</v>
       </c>
       <c r="B130" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14476,41 +14510,44 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>746310</v>
+        <v>746562</v>
       </c>
       <c r="R130" t="n">
-        <v>7151135</v>
+        <v>7151492</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14548,28 +14585,29 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120086232</v>
+        <v>120080334</v>
       </c>
       <c r="B131" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14578,38 +14616,42 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>746551</v>
+        <v>746537</v>
       </c>
       <c r="R131" t="n">
-        <v>7151485</v>
+        <v>7151303</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14656,22 +14698,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120086264</v>
+        <v>120086241</v>
       </c>
       <c r="B132" t="n">
-        <v>92030</v>
+        <v>91826</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14684,21 +14726,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2079</v>
+        <v>3100</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14708,10 +14750,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>746539</v>
+        <v>746383</v>
       </c>
       <c r="R132" t="n">
-        <v>7151522</v>
+        <v>7151288</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14770,10 +14812,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120086301</v>
+        <v>120094338</v>
       </c>
       <c r="B133" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14782,38 +14824,41 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>746566</v>
+        <v>746451</v>
       </c>
       <c r="R133" t="n">
-        <v>7151468</v>
+        <v>7151341</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14854,6 +14899,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14872,10 +14918,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120080357</v>
+        <v>120086247</v>
       </c>
       <c r="B134" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14884,25 +14930,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14912,10 +14958,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>746301</v>
+        <v>746385</v>
       </c>
       <c r="R134" t="n">
-        <v>7151209</v>
+        <v>7151299</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14962,19 +15008,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120086290</v>
+        <v>120086288</v>
       </c>
       <c r="B135" t="n">
         <v>78526</v>
@@ -15014,10 +15060,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>746657</v>
+        <v>746630</v>
       </c>
       <c r="R135" t="n">
-        <v>7151562</v>
+        <v>7151524</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15076,10 +15122,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120080359</v>
+        <v>120094266</v>
       </c>
       <c r="B136" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15088,42 +15134,41 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>746291</v>
+        <v>746491</v>
       </c>
       <c r="R136" t="n">
-        <v>7151137</v>
+        <v>7151452</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15164,28 +15209,29 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120086304</v>
+        <v>120086260</v>
       </c>
       <c r="B137" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15194,25 +15240,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15222,10 +15268,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>746589</v>
+        <v>746378</v>
       </c>
       <c r="R137" t="n">
-        <v>7151537</v>
+        <v>7151283</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15284,10 +15330,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120086268</v>
+        <v>120079807</v>
       </c>
       <c r="B138" t="n">
-        <v>91863</v>
+        <v>57421</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15296,41 +15342,49 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5966</v>
+        <v>103031</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>746563</v>
+        <v>746368</v>
       </c>
       <c r="R138" t="n">
-        <v>7151464</v>
+        <v>7151283</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15374,22 +15428,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120086289</v>
+        <v>120086271</v>
       </c>
       <c r="B139" t="n">
-        <v>78526</v>
+        <v>57421</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15398,38 +15452,46 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>746670</v>
+        <v>746500</v>
       </c>
       <c r="R139" t="n">
-        <v>7151555</v>
+        <v>7151560</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15488,10 +15550,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120079816</v>
+        <v>120094241</v>
       </c>
       <c r="B140" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15500,41 +15562,44 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>746534</v>
+        <v>746515</v>
       </c>
       <c r="R140" t="n">
-        <v>7151288</v>
+        <v>7151443</v>
       </c>
       <c r="S140" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15572,28 +15637,29 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120086241</v>
+        <v>120080355</v>
       </c>
       <c r="B141" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15602,25 +15668,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15630,10 +15696,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>746383</v>
+        <v>746527</v>
       </c>
       <c r="R141" t="n">
-        <v>7151288</v>
+        <v>7151203</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15680,22 +15746,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120086248</v>
+        <v>120086264</v>
       </c>
       <c r="B142" t="n">
-        <v>91884</v>
+        <v>92030</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15708,21 +15774,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5449</v>
+        <v>2079</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15732,10 +15798,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>746537</v>
+        <v>746539</v>
       </c>
       <c r="R142" t="n">
-        <v>7151592</v>
+        <v>7151522</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15794,10 +15860,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120094355</v>
+        <v>120080297</v>
       </c>
       <c r="B143" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15810,37 +15876,43 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>746451</v>
+        <v>746612</v>
       </c>
       <c r="R143" t="n">
-        <v>7151341</v>
+        <v>7151234</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15881,26 +15953,25 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120086303</v>
+        <v>120094677</v>
       </c>
       <c r="B144" t="n">
         <v>91840</v>
@@ -15934,16 +16005,19 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>746555</v>
+        <v>746351</v>
       </c>
       <c r="R144" t="n">
-        <v>7151578</v>
+        <v>7151225</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15984,6 +16058,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -16002,10 +16077,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120086254</v>
+        <v>120094483</v>
       </c>
       <c r="B145" t="n">
-        <v>91844</v>
+        <v>91834</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16014,38 +16089,41 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>746678</v>
+        <v>746321</v>
       </c>
       <c r="R145" t="n">
-        <v>7151537</v>
+        <v>7151245</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16086,6 +16164,7 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -16104,10 +16183,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120080354</v>
+        <v>120094591</v>
       </c>
       <c r="B146" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16116,38 +16195,41 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>746559</v>
+        <v>746294</v>
       </c>
       <c r="R146" t="n">
-        <v>7151216</v>
+        <v>7151228</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16188,28 +16270,29 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120086247</v>
+        <v>120086287</v>
       </c>
       <c r="B147" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16222,21 +16305,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16246,10 +16329,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>746385</v>
+        <v>746567</v>
       </c>
       <c r="R147" t="n">
-        <v>7151299</v>
+        <v>7151554</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16308,10 +16391,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120086306</v>
+        <v>120086253</v>
       </c>
       <c r="B148" t="n">
-        <v>91834</v>
+        <v>91844</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16320,25 +16403,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16348,10 +16431,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>746371</v>
+        <v>746539</v>
       </c>
       <c r="R148" t="n">
-        <v>7151274</v>
+        <v>7151522</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16410,10 +16493,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120086235</v>
+        <v>120086252</v>
       </c>
       <c r="B149" t="n">
-        <v>89633</v>
+        <v>91844</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16422,25 +16505,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16450,10 +16533,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>746515</v>
+        <v>746575</v>
       </c>
       <c r="R149" t="n">
-        <v>7151568</v>
+        <v>7151485</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16512,10 +16595,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120086243</v>
+        <v>120079815</v>
       </c>
       <c r="B150" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16524,25 +16607,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16552,13 +16635,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>746316</v>
+        <v>746896</v>
       </c>
       <c r="R150" t="n">
-        <v>7151209</v>
+        <v>7151149</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16602,22 +16685,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120094241</v>
+        <v>120086281</v>
       </c>
       <c r="B151" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16626,41 +16709,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>746515</v>
+        <v>746371</v>
       </c>
       <c r="R151" t="n">
-        <v>7151443</v>
+        <v>7151235</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16701,7 +16781,6 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -16720,10 +16799,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120080310</v>
+        <v>120086289</v>
       </c>
       <c r="B152" t="n">
-        <v>91821</v>
+        <v>78526</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16732,41 +16811,38 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6055</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>746772</v>
+        <v>746670</v>
       </c>
       <c r="R152" t="n">
-        <v>7151182</v>
+        <v>7151555</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16801,40 +16877,34 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120079799</v>
+        <v>120080303</v>
       </c>
       <c r="B153" t="n">
-        <v>90562</v>
+        <v>91886</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16843,41 +16913,45 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>232140</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>746840</v>
+        <v>746331</v>
       </c>
       <c r="R153" t="n">
-        <v>7151151</v>
+        <v>7151256</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16907,6 +16981,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Under tunn äldre tallgren på mager, torr mark</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16921,19 +17000,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120094777</v>
+        <v>120094190</v>
       </c>
       <c r="B154" t="n">
         <v>91884</v>
@@ -16976,10 +17055,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>746478</v>
+        <v>746572</v>
       </c>
       <c r="R154" t="n">
-        <v>7151377</v>
+        <v>7151479</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17039,10 +17118,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120080331</v>
+        <v>120080296</v>
       </c>
       <c r="B155" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17055,34 +17134,42 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>746936</v>
+        <v>746527</v>
       </c>
       <c r="R155" t="n">
-        <v>7151139</v>
+        <v>7151199</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17117,11 +17204,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
-        </is>
-      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
@@ -17130,21 +17212,6 @@
       </c>
       <c r="AG155" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
@@ -17161,10 +17228,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120086282</v>
+        <v>120086234</v>
       </c>
       <c r="B156" t="n">
-        <v>78526</v>
+        <v>89633</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17177,21 +17244,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17201,10 +17268,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>746368</v>
+        <v>746539</v>
       </c>
       <c r="R156" t="n">
-        <v>7151288</v>
+        <v>7151522</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17263,10 +17330,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120079810</v>
+        <v>120086262</v>
       </c>
       <c r="B157" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17279,21 +17346,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17303,13 +17370,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>746645</v>
+        <v>746555</v>
       </c>
       <c r="R157" t="n">
-        <v>7151221</v>
+        <v>7151590</v>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17353,22 +17420,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120086273</v>
+        <v>120086244</v>
       </c>
       <c r="B158" t="n">
-        <v>90712</v>
+        <v>91828</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17381,21 +17448,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1503</v>
+        <v>149</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17405,10 +17472,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>746551</v>
+        <v>746576</v>
       </c>
       <c r="R158" t="n">
-        <v>7151485</v>
+        <v>7151444</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17467,10 +17534,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120080303</v>
+        <v>120086268</v>
       </c>
       <c r="B159" t="n">
-        <v>91886</v>
+        <v>91863</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17479,42 +17546,38 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>232140</v>
+        <v>5966</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>746331</v>
+        <v>746563</v>
       </c>
       <c r="R159" t="n">
-        <v>7151256</v>
+        <v>7151464</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17549,11 +17612,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Under tunn äldre tallgren på mager, torr mark</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
@@ -17566,22 +17624,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120079811</v>
+        <v>120086299</v>
       </c>
       <c r="B160" t="n">
-        <v>90807</v>
+        <v>91840</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17590,25 +17648,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17618,13 +17676,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>746751</v>
+        <v>746314</v>
       </c>
       <c r="R160" t="n">
-        <v>7151208</v>
+        <v>7151238</v>
       </c>
       <c r="S160" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17662,29 +17720,28 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120094266</v>
+        <v>120086249</v>
       </c>
       <c r="B161" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17693,41 +17750,38 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>746491</v>
+        <v>746568</v>
       </c>
       <c r="R161" t="n">
-        <v>7151452</v>
+        <v>7151535</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17768,7 +17822,6 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -17787,10 +17840,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120086257</v>
+        <v>120086283</v>
       </c>
       <c r="B162" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17799,25 +17852,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17827,10 +17880,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>746575</v>
+        <v>746566</v>
       </c>
       <c r="R162" t="n">
-        <v>7151554</v>
+        <v>7151468</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17889,10 +17942,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120080334</v>
+        <v>120086237</v>
       </c>
       <c r="B163" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17901,42 +17954,38 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>746537</v>
+        <v>746561</v>
       </c>
       <c r="R163" t="n">
-        <v>7151303</v>
+        <v>7151472</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17983,22 +18032,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120086252</v>
+        <v>120086231</v>
       </c>
       <c r="B164" t="n">
-        <v>91844</v>
+        <v>90527</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18007,25 +18056,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4365</v>
+        <v>5447</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18035,10 +18084,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>746575</v>
+        <v>746676</v>
       </c>
       <c r="R164" t="n">
-        <v>7151485</v>
+        <v>7151534</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18097,10 +18146,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120086300</v>
+        <v>120079811</v>
       </c>
       <c r="B165" t="n">
-        <v>91840</v>
+        <v>90807</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18109,25 +18158,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18137,13 +18186,13 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>746381</v>
+        <v>746751</v>
       </c>
       <c r="R165" t="n">
-        <v>7151336</v>
+        <v>7151208</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18181,28 +18230,29 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120086286</v>
+        <v>120086256</v>
       </c>
       <c r="B166" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18211,25 +18261,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18239,10 +18289,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>746555</v>
+        <v>746576</v>
       </c>
       <c r="R166" t="n">
-        <v>7151578</v>
+        <v>7151444</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18301,10 +18351,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120080296</v>
+        <v>120086254</v>
       </c>
       <c r="B167" t="n">
-        <v>57463</v>
+        <v>91844</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18313,46 +18363,38 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>746527</v>
+        <v>746678</v>
       </c>
       <c r="R167" t="n">
-        <v>7151199</v>
+        <v>7151537</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18399,22 +18441,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120086307</v>
+        <v>120086235</v>
       </c>
       <c r="B168" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18427,21 +18469,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18451,10 +18493,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>746483</v>
+        <v>746515</v>
       </c>
       <c r="R168" t="n">
-        <v>7151420</v>
+        <v>7151568</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18513,10 +18555,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120094483</v>
+        <v>120086261</v>
       </c>
       <c r="B169" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18529,37 +18571,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>746321</v>
+        <v>746574</v>
       </c>
       <c r="R169" t="n">
-        <v>7151245</v>
+        <v>7151495</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18600,7 +18639,6 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -18619,10 +18657,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120080356</v>
+        <v>120079803</v>
       </c>
       <c r="B170" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18631,25 +18669,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18659,13 +18697,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>746499</v>
+        <v>746316</v>
       </c>
       <c r="R170" t="n">
-        <v>7151195</v>
+        <v>7151248</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18709,22 +18747,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120086244</v>
+        <v>120080335</v>
       </c>
       <c r="B171" t="n">
-        <v>91828</v>
+        <v>91840</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18733,38 +18771,42 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>149</v>
+        <v>4364</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>746576</v>
+        <v>746321</v>
       </c>
       <c r="R171" t="n">
-        <v>7151444</v>
+        <v>7151233</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18811,22 +18853,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120086293</v>
+        <v>120086251</v>
       </c>
       <c r="B172" t="n">
-        <v>78171</v>
+        <v>91844</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18835,25 +18877,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18863,10 +18905,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>746636</v>
+        <v>746297</v>
       </c>
       <c r="R172" t="n">
-        <v>7151518</v>
+        <v>7151200</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18925,10 +18967,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>120086237</v>
+        <v>120079814</v>
       </c>
       <c r="B173" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18937,25 +18979,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18965,13 +19007,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>746561</v>
+        <v>746510</v>
       </c>
       <c r="R173" t="n">
-        <v>7151472</v>
+        <v>7151225</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19015,22 +19057,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120080328</v>
+        <v>120080331</v>
       </c>
       <c r="B174" t="n">
-        <v>89964</v>
+        <v>78526</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19039,25 +19081,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19067,10 +19109,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>746590</v>
+        <v>746936</v>
       </c>
       <c r="R174" t="n">
-        <v>7151225</v>
+        <v>7151139</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19103,6 +19145,11 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19144,10 +19191,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120080291</v>
+        <v>120086284</v>
       </c>
       <c r="B175" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19156,42 +19203,38 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>746393</v>
+        <v>746563</v>
       </c>
       <c r="R175" t="n">
-        <v>7151288</v>
+        <v>7151464</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19226,11 +19269,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Basen av levande gran</t>
-        </is>
-      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
@@ -19239,41 +19277,26 @@
       </c>
       <c r="AG175" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120086262</v>
+        <v>120086301</v>
       </c>
       <c r="B176" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19282,25 +19305,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19310,10 +19333,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>746555</v>
+        <v>746566</v>
       </c>
       <c r="R176" t="n">
-        <v>7151590</v>
+        <v>7151468</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19372,7 +19395,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120094137</v>
+        <v>120080354</v>
       </c>
       <c r="B177" t="n">
         <v>91840</v>
@@ -19406,19 +19429,16 @@
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>746535</v>
+        <v>746559</v>
       </c>
       <c r="R177" t="n">
-        <v>7151504</v>
+        <v>7151216</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19459,29 +19479,28 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120086239</v>
+        <v>120086285</v>
       </c>
       <c r="B178" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19494,46 +19513,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>746532</v>
+        <v>746576</v>
       </c>
       <c r="R178" t="n">
-        <v>7151493</v>
+        <v>7151476</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19592,10 +19599,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120086271</v>
+        <v>120079808</v>
       </c>
       <c r="B179" t="n">
-        <v>57421</v>
+        <v>90576</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19604,49 +19611,41 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>103031</v>
+        <v>1204</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>746500</v>
+        <v>746668</v>
       </c>
       <c r="R179" t="n">
-        <v>7151560</v>
+        <v>7151253</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19690,22 +19689,22 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120086308</v>
+        <v>120086304</v>
       </c>
       <c r="B180" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19714,25 +19713,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19742,10 +19741,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>746492</v>
+        <v>746589</v>
       </c>
       <c r="R180" t="n">
-        <v>7151446</v>
+        <v>7151537</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19804,10 +19803,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120080330</v>
+        <v>120086300</v>
       </c>
       <c r="B181" t="n">
-        <v>90712</v>
+        <v>91840</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19816,25 +19815,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19844,10 +19843,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>746624</v>
+        <v>746381</v>
       </c>
       <c r="R181" t="n">
-        <v>7151217</v>
+        <v>7151336</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19882,11 +19881,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Nedbruten tallåga, kollekt taget</t>
-        </is>
-      </c>
       <c r="AD181" t="b">
         <v>0</v>
       </c>
@@ -19895,38 +19889,23 @@
       </c>
       <c r="AG181" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120079815</v>
+        <v>120080332</v>
       </c>
       <c r="B182" t="n">
         <v>91840</v>
@@ -19959,20 +19938,24 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>746896</v>
+        <v>746560</v>
       </c>
       <c r="R182" t="n">
-        <v>7151149</v>
+        <v>7151291</v>
       </c>
       <c r="S182" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20016,19 +19999,19 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120080355</v>
+        <v>120080333</v>
       </c>
       <c r="B183" t="n">
         <v>91840</v>
@@ -20061,17 +20044,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>746527</v>
+        <v>746569</v>
       </c>
       <c r="R183" t="n">
-        <v>7151203</v>
+        <v>7151265</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20104,6 +20091,11 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Minst, stort mycel</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20130,10 +20122,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120086285</v>
+        <v>120086270</v>
       </c>
       <c r="B184" t="n">
-        <v>78526</v>
+        <v>57421</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20142,38 +20134,50 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>746576</v>
+        <v>746671</v>
       </c>
       <c r="R184" t="n">
-        <v>7151476</v>
+        <v>7151554</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20232,10 +20236,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120086281</v>
+        <v>120086293</v>
       </c>
       <c r="B185" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20248,21 +20252,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20272,10 +20276,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>746371</v>
+        <v>746636</v>
       </c>
       <c r="R185" t="n">
-        <v>7151235</v>
+        <v>7151518</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20334,10 +20338,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120094276</v>
+        <v>120086306</v>
       </c>
       <c r="B186" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20346,41 +20350,38 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>746476</v>
+        <v>746371</v>
       </c>
       <c r="R186" t="n">
-        <v>7151446</v>
+        <v>7151274</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20421,7 +20422,6 @@
       <c r="AE186" t="b">
         <v>0</v>
       </c>
-      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>
@@ -20440,10 +20440,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120080308</v>
+        <v>120080358</v>
       </c>
       <c r="B187" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20452,25 +20452,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20480,10 +20480,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>746368</v>
+        <v>746699</v>
       </c>
       <c r="R187" t="n">
-        <v>7151279</v>
+        <v>7151240</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20542,10 +20542,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120086231</v>
+        <v>120080352</v>
       </c>
       <c r="B188" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20558,21 +20558,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20582,10 +20582,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>746676</v>
+        <v>746834</v>
       </c>
       <c r="R188" t="n">
-        <v>7151534</v>
+        <v>7151121</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20632,22 +20632,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120086234</v>
+        <v>120094371</v>
       </c>
       <c r="B189" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20656,38 +20656,41 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>746539</v>
+        <v>746383</v>
       </c>
       <c r="R189" t="n">
-        <v>7151522</v>
+        <v>7151297</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20728,6 +20731,7 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -20746,10 +20750,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>120080332</v>
+        <v>120086290</v>
       </c>
       <c r="B190" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20758,42 +20762,38 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>746560</v>
+        <v>746657</v>
       </c>
       <c r="R190" t="n">
-        <v>7151291</v>
+        <v>7151562</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20840,22 +20840,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>120080353</v>
+        <v>120086282</v>
       </c>
       <c r="B191" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20864,25 +20864,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20892,10 +20892,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>746577</v>
+        <v>746368</v>
       </c>
       <c r="R191" t="n">
-        <v>7151220</v>
+        <v>7151288</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20942,22 +20942,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>120086261</v>
+        <v>120079816</v>
       </c>
       <c r="B192" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20970,21 +20970,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20994,13 +20994,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>746574</v>
+        <v>746534</v>
       </c>
       <c r="R192" t="n">
-        <v>7151495</v>
+        <v>7151288</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21044,12 +21044,12 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY192"/>
+  <dimension ref="A1:AY202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8184,10 +8184,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120059636</v>
+        <v>120061645</v>
       </c>
       <c r="B72" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8196,25 +8196,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746602</v>
+        <v>746450</v>
       </c>
       <c r="R72" t="n">
-        <v>7151535</v>
+        <v>7151380</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8296,10 +8296,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120061645</v>
+        <v>120059636</v>
       </c>
       <c r="B73" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8308,25 +8308,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8336,10 +8336,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746450</v>
+        <v>746602</v>
       </c>
       <c r="R73" t="n">
-        <v>7151380</v>
+        <v>7151535</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10424,10 +10424,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120063383</v>
+        <v>120059956</v>
       </c>
       <c r="B92" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10440,21 +10440,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>746303</v>
+        <v>746535</v>
       </c>
       <c r="R92" t="n">
-        <v>7151246</v>
+        <v>7151537</v>
       </c>
       <c r="S92" t="n">
         <v>1</v>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10536,10 +10536,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120061686</v>
+        <v>120061233</v>
       </c>
       <c r="B93" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10552,21 +10552,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>746448</v>
+        <v>746597</v>
       </c>
       <c r="R93" t="n">
-        <v>7151388</v>
+        <v>7151440</v>
       </c>
       <c r="S93" t="n">
         <v>1</v>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10648,10 +10648,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120059956</v>
+        <v>120063383</v>
       </c>
       <c r="B94" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10664,21 +10664,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>746535</v>
+        <v>746303</v>
       </c>
       <c r="R94" t="n">
-        <v>7151537</v>
+        <v>7151246</v>
       </c>
       <c r="S94" t="n">
         <v>1</v>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10760,10 +10760,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120061233</v>
+        <v>120061686</v>
       </c>
       <c r="B95" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10776,21 +10776,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10800,10 +10800,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>746597</v>
+        <v>746448</v>
       </c>
       <c r="R95" t="n">
-        <v>7151440</v>
+        <v>7151388</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13169,10 +13169,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120080356</v>
+        <v>120080330</v>
       </c>
       <c r="B118" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13181,25 +13181,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13209,10 +13209,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>746499</v>
+        <v>746624</v>
       </c>
       <c r="R118" t="n">
-        <v>7151195</v>
+        <v>7151217</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13247,6 +13247,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Nedbruten tallåga, kollekt taget</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -13255,6 +13260,21 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -13271,7 +13291,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120086303</v>
+        <v>120080356</v>
       </c>
       <c r="B119" t="n">
         <v>91840</v>
@@ -13311,10 +13331,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>746555</v>
+        <v>746499</v>
       </c>
       <c r="R119" t="n">
-        <v>7151578</v>
+        <v>7151195</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13361,19 +13381,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120080357</v>
+        <v>120086303</v>
       </c>
       <c r="B120" t="n">
         <v>91840</v>
@@ -13413,10 +13433,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>746301</v>
+        <v>746555</v>
       </c>
       <c r="R120" t="n">
-        <v>7151209</v>
+        <v>7151578</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13463,22 +13483,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120080291</v>
+        <v>120080357</v>
       </c>
       <c r="B121" t="n">
-        <v>91254</v>
+        <v>91840</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13491,38 +13511,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3298</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>746393</v>
+        <v>746301</v>
       </c>
       <c r="R121" t="n">
-        <v>7151288</v>
+        <v>7151209</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13557,11 +13573,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Basen av levande gran</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -13570,21 +13581,6 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
@@ -13728,10 +13724,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120080330</v>
+        <v>120080291</v>
       </c>
       <c r="B123" t="n">
-        <v>90712</v>
+        <v>91254</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13740,38 +13736,42 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1503</v>
+        <v>3298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>746624</v>
+        <v>746393</v>
       </c>
       <c r="R123" t="n">
-        <v>7151217</v>
+        <v>7151288</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Nedbruten tallåga, kollekt taget</t>
+          <t>Basen av levande gran</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13822,17 +13822,17 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -13850,10 +13850,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120080310</v>
+        <v>120086248</v>
       </c>
       <c r="B124" t="n">
-        <v>91821</v>
+        <v>91884</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13862,41 +13862,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6055</v>
+        <v>5449</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>746772</v>
+        <v>746537</v>
       </c>
       <c r="R124" t="n">
-        <v>7151182</v>
+        <v>7151592</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13931,40 +13928,34 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120079810</v>
+        <v>120080328</v>
       </c>
       <c r="B125" t="n">
-        <v>78526</v>
+        <v>89964</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13973,25 +13964,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14001,13 +13992,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>746645</v>
+        <v>746590</v>
       </c>
       <c r="R125" t="n">
-        <v>7151221</v>
+        <v>7151225</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14047,26 +14038,41 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120079799</v>
+        <v>120086239</v>
       </c>
       <c r="B126" t="n">
-        <v>90562</v>
+        <v>57463</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14079,37 +14085,49 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>746840</v>
+        <v>746532</v>
       </c>
       <c r="R126" t="n">
-        <v>7151151</v>
+        <v>7151493</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14153,22 +14171,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120086248</v>
+        <v>120079799</v>
       </c>
       <c r="B127" t="n">
-        <v>91884</v>
+        <v>90562</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14181,21 +14199,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14205,13 +14223,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>746537</v>
+        <v>746840</v>
       </c>
       <c r="R127" t="n">
-        <v>7151592</v>
+        <v>7151151</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14255,22 +14273,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120080328</v>
+        <v>120080310</v>
       </c>
       <c r="B128" t="n">
-        <v>89964</v>
+        <v>91821</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14279,38 +14297,41 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5685</v>
+        <v>6055</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>746590</v>
+        <v>746772</v>
       </c>
       <c r="R128" t="n">
-        <v>7151225</v>
+        <v>7151182</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14345,29 +14366,20 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
@@ -14384,10 +14396,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120086239</v>
+        <v>120079810</v>
       </c>
       <c r="B129" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14400,49 +14412,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>746532</v>
+        <v>746645</v>
       </c>
       <c r="R129" t="n">
-        <v>7151493</v>
+        <v>7151221</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14486,12 +14486,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -15330,10 +15330,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120079807</v>
+        <v>120094241</v>
       </c>
       <c r="B138" t="n">
-        <v>57421</v>
+        <v>91840</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15346,31 +15346,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -15378,13 +15373,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>746368</v>
+        <v>746515</v>
       </c>
       <c r="R138" t="n">
-        <v>7151283</v>
+        <v>7151443</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15422,28 +15417,29 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120086271</v>
+        <v>120080355</v>
       </c>
       <c r="B139" t="n">
-        <v>57421</v>
+        <v>91840</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15456,42 +15452,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>746500</v>
+        <v>746527</v>
       </c>
       <c r="R139" t="n">
-        <v>7151560</v>
+        <v>7151203</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15538,22 +15526,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120094241</v>
+        <v>120086264</v>
       </c>
       <c r="B140" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15562,41 +15550,38 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>746515</v>
+        <v>746539</v>
       </c>
       <c r="R140" t="n">
-        <v>7151443</v>
+        <v>7151522</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15637,7 +15622,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15656,10 +15640,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120080355</v>
+        <v>120079807</v>
       </c>
       <c r="B141" t="n">
-        <v>91840</v>
+        <v>57421</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15672,37 +15656,45 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>746527</v>
+        <v>746368</v>
       </c>
       <c r="R141" t="n">
-        <v>7151203</v>
+        <v>7151283</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15746,22 +15738,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120086264</v>
+        <v>120086271</v>
       </c>
       <c r="B142" t="n">
-        <v>92030</v>
+        <v>57421</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15770,38 +15762,46 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2079</v>
+        <v>103031</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>746539</v>
+        <v>746500</v>
       </c>
       <c r="R142" t="n">
-        <v>7151522</v>
+        <v>7151560</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16391,10 +16391,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120086253</v>
+        <v>120080296</v>
       </c>
       <c r="B148" t="n">
-        <v>91844</v>
+        <v>57463</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16403,38 +16403,46 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>746539</v>
+        <v>746527</v>
       </c>
       <c r="R148" t="n">
-        <v>7151522</v>
+        <v>7151199</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16481,22 +16489,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120086252</v>
+        <v>120080303</v>
       </c>
       <c r="B149" t="n">
-        <v>91844</v>
+        <v>91886</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16509,34 +16517,38 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>746575</v>
+        <v>746331</v>
       </c>
       <c r="R149" t="n">
-        <v>7151485</v>
+        <v>7151256</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16571,6 +16583,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Under tunn äldre tallgren på mager, torr mark</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
@@ -16583,22 +16600,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120079815</v>
+        <v>120086253</v>
       </c>
       <c r="B150" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16607,25 +16624,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16635,13 +16652,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>746896</v>
+        <v>746539</v>
       </c>
       <c r="R150" t="n">
-        <v>7151149</v>
+        <v>7151522</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16685,22 +16702,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120086281</v>
+        <v>120086252</v>
       </c>
       <c r="B151" t="n">
-        <v>78526</v>
+        <v>91844</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16709,25 +16726,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16737,10 +16754,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>746371</v>
+        <v>746575</v>
       </c>
       <c r="R151" t="n">
-        <v>7151235</v>
+        <v>7151485</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16799,10 +16816,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120086289</v>
+        <v>120079815</v>
       </c>
       <c r="B152" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16811,25 +16828,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16839,13 +16856,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>746670</v>
+        <v>746896</v>
       </c>
       <c r="R152" t="n">
-        <v>7151555</v>
+        <v>7151149</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16889,22 +16906,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120080303</v>
+        <v>120086281</v>
       </c>
       <c r="B153" t="n">
-        <v>91886</v>
+        <v>78526</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16913,42 +16930,38 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>232140</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>746331</v>
+        <v>746371</v>
       </c>
       <c r="R153" t="n">
-        <v>7151256</v>
+        <v>7151235</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16983,11 +16996,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Under tunn äldre tallgren på mager, torr mark</t>
-        </is>
-      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -17000,22 +17008,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120094190</v>
+        <v>120086289</v>
       </c>
       <c r="B154" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17028,37 +17036,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>746572</v>
+        <v>746670</v>
       </c>
       <c r="R154" t="n">
-        <v>7151479</v>
+        <v>7151555</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17099,7 +17104,6 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17118,10 +17122,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120080296</v>
+        <v>120094190</v>
       </c>
       <c r="B155" t="n">
-        <v>57463</v>
+        <v>91884</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17134,31 +17138,26 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -17166,10 +17165,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>746527</v>
+        <v>746572</v>
       </c>
       <c r="R155" t="n">
-        <v>7151199</v>
+        <v>7151479</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17210,18 +17209,19 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
@@ -21054,6 +21054,1236 @@
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>120256310</v>
+      </c>
+      <c r="B193" t="n">
+        <v>91856</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>746490</v>
+      </c>
+      <c r="R193" t="n">
+        <v>7151210</v>
+      </c>
+      <c r="S193" t="n">
+        <v>5</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF193" t="inlineStr"/>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>120256082</v>
+      </c>
+      <c r="B194" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>746608</v>
+      </c>
+      <c r="R194" t="n">
+        <v>7151217</v>
+      </c>
+      <c r="S194" t="n">
+        <v>5</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF194" t="inlineStr"/>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>120256105</v>
+      </c>
+      <c r="B195" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>746595</v>
+      </c>
+      <c r="R195" t="n">
+        <v>7151214</v>
+      </c>
+      <c r="S195" t="n">
+        <v>5</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>120256409</v>
+      </c>
+      <c r="B196" t="n">
+        <v>91861</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>746483</v>
+      </c>
+      <c r="R196" t="n">
+        <v>7151210</v>
+      </c>
+      <c r="S196" t="n">
+        <v>5</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF196" t="inlineStr"/>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>120256184</v>
+      </c>
+      <c r="B197" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>746540</v>
+      </c>
+      <c r="R197" t="n">
+        <v>7151228</v>
+      </c>
+      <c r="S197" t="n">
+        <v>5</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF197" t="inlineStr"/>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>120256026</v>
+      </c>
+      <c r="B198" t="n">
+        <v>91834</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>746595</v>
+      </c>
+      <c r="R198" t="n">
+        <v>7151275</v>
+      </c>
+      <c r="S198" t="n">
+        <v>5</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF198" t="inlineStr"/>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>120256212</v>
+      </c>
+      <c r="B199" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>746530</v>
+      </c>
+      <c r="R199" t="n">
+        <v>7151223</v>
+      </c>
+      <c r="S199" t="n">
+        <v>5</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF199" t="inlineStr"/>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>120256251</v>
+      </c>
+      <c r="B200" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>746516</v>
+      </c>
+      <c r="R200" t="n">
+        <v>7151220</v>
+      </c>
+      <c r="S200" t="n">
+        <v>5</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF200" t="inlineStr"/>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>120256146</v>
+      </c>
+      <c r="B201" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>746617</v>
+      </c>
+      <c r="R201" t="n">
+        <v>7151234</v>
+      </c>
+      <c r="S201" t="n">
+        <v>5</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF201" t="inlineStr"/>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>120256287</v>
+      </c>
+      <c r="B202" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>746490</v>
+      </c>
+      <c r="R202" t="n">
+        <v>7151210</v>
+      </c>
+      <c r="S202" t="n">
+        <v>5</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF202" t="inlineStr"/>
+      <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -7736,10 +7736,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120061458</v>
+        <v>120064386</v>
       </c>
       <c r="B68" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7748,41 +7748,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vintjärnen, Vintjärnen, Vb</t>
+          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746495</v>
+        <v>746535</v>
       </c>
       <c r="R68" t="n">
-        <v>7151424</v>
+        <v>7151171</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7836,19 +7836,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120064386</v>
+        <v>120062185</v>
       </c>
       <c r="B69" t="n">
         <v>91840</v>
@@ -7884,17 +7884,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
+          <t>Vintjärnen, Vintjärnen, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746535</v>
+        <v>746401</v>
       </c>
       <c r="R69" t="n">
-        <v>7151171</v>
+        <v>7151292</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7948,22 +7948,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120062185</v>
+        <v>120061458</v>
       </c>
       <c r="B70" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7972,25 +7972,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746401</v>
+        <v>746495</v>
       </c>
       <c r="R70" t="n">
-        <v>7151292</v>
+        <v>7151424</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8184,10 +8184,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120061645</v>
+        <v>120059636</v>
       </c>
       <c r="B72" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8196,25 +8196,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746450</v>
+        <v>746602</v>
       </c>
       <c r="R72" t="n">
-        <v>7151380</v>
+        <v>7151535</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8296,10 +8296,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120059636</v>
+        <v>120061645</v>
       </c>
       <c r="B73" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8308,25 +8308,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8336,10 +8336,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746602</v>
+        <v>746450</v>
       </c>
       <c r="R73" t="n">
-        <v>7151535</v>
+        <v>7151380</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10424,10 +10424,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120059956</v>
+        <v>120063383</v>
       </c>
       <c r="B92" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10440,21 +10440,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>746535</v>
+        <v>746303</v>
       </c>
       <c r="R92" t="n">
-        <v>7151537</v>
+        <v>7151246</v>
       </c>
       <c r="S92" t="n">
         <v>1</v>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10536,10 +10536,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120061233</v>
+        <v>120061686</v>
       </c>
       <c r="B93" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10552,21 +10552,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>746597</v>
+        <v>746448</v>
       </c>
       <c r="R93" t="n">
-        <v>7151440</v>
+        <v>7151388</v>
       </c>
       <c r="S93" t="n">
         <v>1</v>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10648,10 +10648,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120063383</v>
+        <v>120059956</v>
       </c>
       <c r="B94" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10664,21 +10664,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>746303</v>
+        <v>746535</v>
       </c>
       <c r="R94" t="n">
-        <v>7151246</v>
+        <v>7151537</v>
       </c>
       <c r="S94" t="n">
         <v>1</v>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10760,10 +10760,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120061686</v>
+        <v>120061233</v>
       </c>
       <c r="B95" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10776,21 +10776,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10800,10 +10800,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>746448</v>
+        <v>746597</v>
       </c>
       <c r="R95" t="n">
-        <v>7151388</v>
+        <v>7151440</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11308,10 +11308,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120086232</v>
+        <v>120086307</v>
       </c>
       <c r="B100" t="n">
-        <v>89633</v>
+        <v>91834</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11324,21 +11324,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11348,10 +11348,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>746551</v>
+        <v>746483</v>
       </c>
       <c r="R100" t="n">
-        <v>7151485</v>
+        <v>7151420</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11410,10 +11410,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120086307</v>
+        <v>120086232</v>
       </c>
       <c r="B101" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11426,21 +11426,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11450,10 +11450,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>746483</v>
+        <v>746551</v>
       </c>
       <c r="R101" t="n">
-        <v>7151420</v>
+        <v>7151485</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13169,10 +13169,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120080330</v>
+        <v>120080356</v>
       </c>
       <c r="B118" t="n">
-        <v>90712</v>
+        <v>91840</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13181,25 +13181,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13209,10 +13209,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>746624</v>
+        <v>746499</v>
       </c>
       <c r="R118" t="n">
-        <v>7151217</v>
+        <v>7151195</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13247,11 +13247,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Nedbruten tallåga, kollekt taget</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -13260,21 +13255,6 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -13291,7 +13271,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120080356</v>
+        <v>120086303</v>
       </c>
       <c r="B119" t="n">
         <v>91840</v>
@@ -13331,10 +13311,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>746499</v>
+        <v>746555</v>
       </c>
       <c r="R119" t="n">
-        <v>7151195</v>
+        <v>7151578</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13381,19 +13361,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120086303</v>
+        <v>120080357</v>
       </c>
       <c r="B120" t="n">
         <v>91840</v>
@@ -13433,10 +13413,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>746555</v>
+        <v>746301</v>
       </c>
       <c r="R120" t="n">
-        <v>7151578</v>
+        <v>7151209</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13483,22 +13463,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120080357</v>
+        <v>120080291</v>
       </c>
       <c r="B121" t="n">
-        <v>91840</v>
+        <v>91254</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13511,34 +13491,38 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>3298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>746301</v>
+        <v>746393</v>
       </c>
       <c r="R121" t="n">
-        <v>7151209</v>
+        <v>7151288</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13573,6 +13557,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Basen av levande gran</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -13581,6 +13570,21 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
@@ -13724,10 +13728,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120080291</v>
+        <v>120080330</v>
       </c>
       <c r="B123" t="n">
-        <v>91254</v>
+        <v>90712</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13736,42 +13740,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3298</v>
+        <v>1503</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>746393</v>
+        <v>746624</v>
       </c>
       <c r="R123" t="n">
-        <v>7151288</v>
+        <v>7151217</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Basen av levande gran</t>
+          <t>Nedbruten tallåga, kollekt taget</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13822,17 +13822,17 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -13850,10 +13850,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120086248</v>
+        <v>120080310</v>
       </c>
       <c r="B124" t="n">
-        <v>91884</v>
+        <v>91821</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13862,38 +13862,41 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5449</v>
+        <v>6055</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>746537</v>
+        <v>746772</v>
       </c>
       <c r="R124" t="n">
-        <v>7151592</v>
+        <v>7151182</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13928,34 +13931,40 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120080328</v>
+        <v>120079810</v>
       </c>
       <c r="B125" t="n">
-        <v>89964</v>
+        <v>78526</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13964,25 +13973,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13992,13 +14001,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>746590</v>
+        <v>746645</v>
       </c>
       <c r="R125" t="n">
-        <v>7151225</v>
+        <v>7151221</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14038,41 +14047,26 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120086239</v>
+        <v>120079799</v>
       </c>
       <c r="B126" t="n">
-        <v>57463</v>
+        <v>90562</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14085,49 +14079,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>746532</v>
+        <v>746840</v>
       </c>
       <c r="R126" t="n">
-        <v>7151493</v>
+        <v>7151151</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14171,22 +14153,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120079799</v>
+        <v>120086248</v>
       </c>
       <c r="B127" t="n">
-        <v>90562</v>
+        <v>91884</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14199,21 +14181,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>5449</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14223,13 +14205,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>746840</v>
+        <v>746537</v>
       </c>
       <c r="R127" t="n">
-        <v>7151151</v>
+        <v>7151592</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14273,22 +14255,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120080310</v>
+        <v>120080328</v>
       </c>
       <c r="B128" t="n">
-        <v>91821</v>
+        <v>89964</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14297,41 +14279,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6055</v>
+        <v>5685</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>746772</v>
+        <v>746590</v>
       </c>
       <c r="R128" t="n">
-        <v>7151182</v>
+        <v>7151225</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14366,20 +14345,29 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
@@ -14396,10 +14384,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120079810</v>
+        <v>120086239</v>
       </c>
       <c r="B129" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14412,37 +14400,49 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>746645</v>
+        <v>746532</v>
       </c>
       <c r="R129" t="n">
-        <v>7151221</v>
+        <v>7151493</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14486,12 +14486,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -15330,10 +15330,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120094241</v>
+        <v>120079807</v>
       </c>
       <c r="B138" t="n">
-        <v>91840</v>
+        <v>57421</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15346,26 +15346,31 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -15373,13 +15378,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>746515</v>
+        <v>746368</v>
       </c>
       <c r="R138" t="n">
-        <v>7151443</v>
+        <v>7151283</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15417,29 +15422,28 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120080355</v>
+        <v>120086271</v>
       </c>
       <c r="B139" t="n">
-        <v>91840</v>
+        <v>57421</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15452,34 +15456,42 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>746527</v>
+        <v>746500</v>
       </c>
       <c r="R139" t="n">
-        <v>7151203</v>
+        <v>7151560</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15526,22 +15538,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120086264</v>
+        <v>120094241</v>
       </c>
       <c r="B140" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15550,38 +15562,41 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>746539</v>
+        <v>746515</v>
       </c>
       <c r="R140" t="n">
-        <v>7151522</v>
+        <v>7151443</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15622,6 +15637,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15640,10 +15656,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120079807</v>
+        <v>120080355</v>
       </c>
       <c r="B141" t="n">
-        <v>57421</v>
+        <v>91840</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15656,45 +15672,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>746368</v>
+        <v>746527</v>
       </c>
       <c r="R141" t="n">
-        <v>7151283</v>
+        <v>7151203</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15738,22 +15746,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120086271</v>
+        <v>120086264</v>
       </c>
       <c r="B142" t="n">
-        <v>57421</v>
+        <v>92030</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15762,46 +15770,38 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103031</v>
+        <v>2079</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>746500</v>
+        <v>746539</v>
       </c>
       <c r="R142" t="n">
-        <v>7151560</v>
+        <v>7151522</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16391,10 +16391,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120080296</v>
+        <v>120086253</v>
       </c>
       <c r="B148" t="n">
-        <v>57463</v>
+        <v>91844</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16403,46 +16403,38 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>746527</v>
+        <v>746539</v>
       </c>
       <c r="R148" t="n">
-        <v>7151199</v>
+        <v>7151522</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16489,22 +16481,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120080303</v>
+        <v>120086252</v>
       </c>
       <c r="B149" t="n">
-        <v>91886</v>
+        <v>91844</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16517,38 +16509,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>746331</v>
+        <v>746575</v>
       </c>
       <c r="R149" t="n">
-        <v>7151256</v>
+        <v>7151485</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16583,11 +16571,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Under tunn äldre tallgren på mager, torr mark</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
@@ -16600,22 +16583,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120086253</v>
+        <v>120079815</v>
       </c>
       <c r="B150" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16624,25 +16607,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16652,13 +16635,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>746539</v>
+        <v>746896</v>
       </c>
       <c r="R150" t="n">
-        <v>7151522</v>
+        <v>7151149</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16702,22 +16685,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120086252</v>
+        <v>120086281</v>
       </c>
       <c r="B151" t="n">
-        <v>91844</v>
+        <v>78526</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16726,25 +16709,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16754,10 +16737,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>746575</v>
+        <v>746371</v>
       </c>
       <c r="R151" t="n">
-        <v>7151485</v>
+        <v>7151235</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16816,10 +16799,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120079815</v>
+        <v>120086289</v>
       </c>
       <c r="B152" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16828,25 +16811,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16856,13 +16839,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>746896</v>
+        <v>746670</v>
       </c>
       <c r="R152" t="n">
-        <v>7151149</v>
+        <v>7151555</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16906,22 +16889,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120086281</v>
+        <v>120080303</v>
       </c>
       <c r="B153" t="n">
-        <v>78526</v>
+        <v>91886</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16930,38 +16913,42 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>232140</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>746371</v>
+        <v>746331</v>
       </c>
       <c r="R153" t="n">
-        <v>7151235</v>
+        <v>7151256</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16996,6 +16983,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Under tunn äldre tallgren på mager, torr mark</t>
+        </is>
+      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -17008,22 +17000,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120086289</v>
+        <v>120094190</v>
       </c>
       <c r="B154" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17036,34 +17028,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>746670</v>
+        <v>746572</v>
       </c>
       <c r="R154" t="n">
-        <v>7151555</v>
+        <v>7151479</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17104,6 +17099,7 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17122,10 +17118,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120094190</v>
+        <v>120080296</v>
       </c>
       <c r="B155" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17138,26 +17134,31 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -17165,10 +17166,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>746572</v>
+        <v>746527</v>
       </c>
       <c r="R155" t="n">
-        <v>7151479</v>
+        <v>7151199</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17209,29 +17210,28 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120086234</v>
+        <v>120086249</v>
       </c>
       <c r="B156" t="n">
-        <v>89633</v>
+        <v>91884</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17244,21 +17244,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17268,10 +17268,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>746539</v>
+        <v>746568</v>
       </c>
       <c r="R156" t="n">
-        <v>7151522</v>
+        <v>7151535</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17330,10 +17330,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120086262</v>
+        <v>120086234</v>
       </c>
       <c r="B157" t="n">
-        <v>91832</v>
+        <v>89633</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17346,21 +17346,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17370,10 +17370,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>746555</v>
+        <v>746539</v>
       </c>
       <c r="R157" t="n">
-        <v>7151590</v>
+        <v>7151522</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17432,10 +17432,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120086244</v>
+        <v>120086262</v>
       </c>
       <c r="B158" t="n">
-        <v>91828</v>
+        <v>91832</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17444,25 +17444,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>149</v>
+        <v>4361</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17472,10 +17472,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>746576</v>
+        <v>746555</v>
       </c>
       <c r="R158" t="n">
-        <v>7151444</v>
+        <v>7151590</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17534,10 +17534,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120086268</v>
+        <v>120086244</v>
       </c>
       <c r="B159" t="n">
-        <v>91863</v>
+        <v>91828</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17546,25 +17546,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5966</v>
+        <v>149</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17574,10 +17574,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>746563</v>
+        <v>746576</v>
       </c>
       <c r="R159" t="n">
-        <v>7151464</v>
+        <v>7151444</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17636,10 +17636,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120086299</v>
+        <v>120086268</v>
       </c>
       <c r="B160" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17648,25 +17648,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17676,10 +17676,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>746314</v>
+        <v>746563</v>
       </c>
       <c r="R160" t="n">
-        <v>7151238</v>
+        <v>7151464</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17738,10 +17738,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120086249</v>
+        <v>120086299</v>
       </c>
       <c r="B161" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17750,25 +17750,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17778,10 +17778,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>746568</v>
+        <v>746314</v>
       </c>
       <c r="R161" t="n">
-        <v>7151535</v>
+        <v>7151238</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -8968,10 +8968,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120061725</v>
+        <v>120063442</v>
       </c>
       <c r="B79" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8980,25 +8980,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746444</v>
+        <v>746297</v>
       </c>
       <c r="R79" t="n">
-        <v>7151382</v>
+        <v>7151223</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9080,7 +9080,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120063442</v>
+        <v>120062963</v>
       </c>
       <c r="B80" t="n">
         <v>91840</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746297</v>
+        <v>746369</v>
       </c>
       <c r="R80" t="n">
-        <v>7151223</v>
+        <v>7151279</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9192,7 +9192,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120062963</v>
+        <v>120062338</v>
       </c>
       <c r="B81" t="n">
         <v>91840</v>
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746369</v>
+        <v>746390</v>
       </c>
       <c r="R81" t="n">
-        <v>7151279</v>
+        <v>7151301</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9304,10 +9304,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120062338</v>
+        <v>120061725</v>
       </c>
       <c r="B82" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9316,25 +9316,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746390</v>
+        <v>746444</v>
       </c>
       <c r="R82" t="n">
-        <v>7151301</v>
+        <v>7151382</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10424,10 +10424,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120063383</v>
+        <v>120059956</v>
       </c>
       <c r="B92" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10440,21 +10440,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>746303</v>
+        <v>746535</v>
       </c>
       <c r="R92" t="n">
-        <v>7151246</v>
+        <v>7151537</v>
       </c>
       <c r="S92" t="n">
         <v>1</v>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10536,10 +10536,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120061686</v>
+        <v>120061233</v>
       </c>
       <c r="B93" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10552,21 +10552,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>746448</v>
+        <v>746597</v>
       </c>
       <c r="R93" t="n">
-        <v>7151388</v>
+        <v>7151440</v>
       </c>
       <c r="S93" t="n">
         <v>1</v>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10648,10 +10648,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120059956</v>
+        <v>120063383</v>
       </c>
       <c r="B94" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10664,21 +10664,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>746535</v>
+        <v>746303</v>
       </c>
       <c r="R94" t="n">
-        <v>7151537</v>
+        <v>7151246</v>
       </c>
       <c r="S94" t="n">
         <v>1</v>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10760,10 +10760,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120061233</v>
+        <v>120061686</v>
       </c>
       <c r="B95" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10776,21 +10776,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10800,10 +10800,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>746597</v>
+        <v>746448</v>
       </c>
       <c r="R95" t="n">
-        <v>7151440</v>
+        <v>7151388</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12239,10 +12239,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120094102</v>
+        <v>120086308</v>
       </c>
       <c r="B109" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12251,41 +12251,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>746539</v>
+        <v>746492</v>
       </c>
       <c r="R109" t="n">
-        <v>7151513</v>
+        <v>7151446</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12326,7 +12323,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -12345,10 +12341,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120086267</v>
+        <v>120094102</v>
       </c>
       <c r="B110" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12357,38 +12353,41 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>746492</v>
+        <v>746539</v>
       </c>
       <c r="R110" t="n">
-        <v>7151446</v>
+        <v>7151513</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12429,6 +12428,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12447,10 +12447,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120086286</v>
+        <v>120086267</v>
       </c>
       <c r="B111" t="n">
-        <v>78526</v>
+        <v>91863</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12463,21 +12463,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12487,10 +12487,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>746555</v>
+        <v>746492</v>
       </c>
       <c r="R111" t="n">
-        <v>7151578</v>
+        <v>7151446</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12549,10 +12549,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120079798</v>
+        <v>120086286</v>
       </c>
       <c r="B112" t="n">
-        <v>89633</v>
+        <v>78526</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12565,21 +12565,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12589,13 +12589,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>746310</v>
+        <v>746555</v>
       </c>
       <c r="R112" t="n">
-        <v>7151135</v>
+        <v>7151578</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12639,22 +12639,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120086308</v>
+        <v>120079798</v>
       </c>
       <c r="B113" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12667,21 +12667,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12691,13 +12691,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>746492</v>
+        <v>746310</v>
       </c>
       <c r="R113" t="n">
-        <v>7151446</v>
+        <v>7151135</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12741,22 +12741,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120086273</v>
+        <v>120094292</v>
       </c>
       <c r="B114" t="n">
-        <v>90712</v>
+        <v>91840</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12765,38 +12765,41 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>746551</v>
+        <v>746478</v>
       </c>
       <c r="R114" t="n">
-        <v>7151485</v>
+        <v>7151421</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12837,6 +12840,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12855,10 +12859,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120080308</v>
+        <v>120094359</v>
       </c>
       <c r="B115" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12867,38 +12871,41 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>746368</v>
+        <v>746451</v>
       </c>
       <c r="R115" t="n">
-        <v>7151279</v>
+        <v>7151341</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12939,28 +12946,29 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120094292</v>
+        <v>120080308</v>
       </c>
       <c r="B116" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12969,41 +12977,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>746478</v>
+        <v>746368</v>
       </c>
       <c r="R116" t="n">
-        <v>7151421</v>
+        <v>7151279</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13044,29 +13049,28 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120094359</v>
+        <v>120086273</v>
       </c>
       <c r="B117" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13075,41 +13079,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>746451</v>
+        <v>746551</v>
       </c>
       <c r="R117" t="n">
-        <v>7151341</v>
+        <v>7151485</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13150,7 +13151,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -15330,10 +15330,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120079807</v>
+        <v>120094241</v>
       </c>
       <c r="B138" t="n">
-        <v>57421</v>
+        <v>91840</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15346,31 +15346,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -15378,13 +15373,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>746368</v>
+        <v>746515</v>
       </c>
       <c r="R138" t="n">
-        <v>7151283</v>
+        <v>7151443</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15422,28 +15417,29 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120086271</v>
+        <v>120080355</v>
       </c>
       <c r="B139" t="n">
-        <v>57421</v>
+        <v>91840</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15456,42 +15452,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>746500</v>
+        <v>746527</v>
       </c>
       <c r="R139" t="n">
-        <v>7151560</v>
+        <v>7151203</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15538,22 +15526,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120094241</v>
+        <v>120086264</v>
       </c>
       <c r="B140" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15562,41 +15550,38 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>746515</v>
+        <v>746539</v>
       </c>
       <c r="R140" t="n">
-        <v>7151443</v>
+        <v>7151522</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15637,7 +15622,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15656,10 +15640,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120080355</v>
+        <v>120079807</v>
       </c>
       <c r="B141" t="n">
-        <v>91840</v>
+        <v>57421</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15672,37 +15656,45 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>746527</v>
+        <v>746368</v>
       </c>
       <c r="R141" t="n">
-        <v>7151203</v>
+        <v>7151283</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15746,22 +15738,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120086264</v>
+        <v>120086271</v>
       </c>
       <c r="B142" t="n">
-        <v>92030</v>
+        <v>57421</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15770,38 +15762,46 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2079</v>
+        <v>103031</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>746539</v>
+        <v>746500</v>
       </c>
       <c r="R142" t="n">
-        <v>7151522</v>
+        <v>7151560</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17228,10 +17228,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120086249</v>
+        <v>120086299</v>
       </c>
       <c r="B156" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17240,25 +17240,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17268,10 +17268,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>746568</v>
+        <v>746314</v>
       </c>
       <c r="R156" t="n">
-        <v>7151535</v>
+        <v>7151238</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17330,10 +17330,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120086234</v>
+        <v>120086262</v>
       </c>
       <c r="B157" t="n">
-        <v>89633</v>
+        <v>91832</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17346,21 +17346,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17370,10 +17370,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>746539</v>
+        <v>746555</v>
       </c>
       <c r="R157" t="n">
-        <v>7151522</v>
+        <v>7151590</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17432,10 +17432,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120086262</v>
+        <v>120086244</v>
       </c>
       <c r="B158" t="n">
-        <v>91832</v>
+        <v>91828</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17444,25 +17444,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17472,10 +17472,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>746555</v>
+        <v>746576</v>
       </c>
       <c r="R158" t="n">
-        <v>7151590</v>
+        <v>7151444</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17534,10 +17534,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120086244</v>
+        <v>120086268</v>
       </c>
       <c r="B159" t="n">
-        <v>91828</v>
+        <v>91863</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17546,25 +17546,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>149</v>
+        <v>5966</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17574,10 +17574,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>746576</v>
+        <v>746563</v>
       </c>
       <c r="R159" t="n">
-        <v>7151444</v>
+        <v>7151464</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17636,10 +17636,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120086268</v>
+        <v>120086234</v>
       </c>
       <c r="B160" t="n">
-        <v>91863</v>
+        <v>89633</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17652,21 +17652,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17676,10 +17676,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>746563</v>
+        <v>746539</v>
       </c>
       <c r="R160" t="n">
-        <v>7151464</v>
+        <v>7151522</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17738,10 +17738,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120086299</v>
+        <v>120086249</v>
       </c>
       <c r="B161" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17750,25 +17750,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17778,10 +17778,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>746314</v>
+        <v>746568</v>
       </c>
       <c r="R161" t="n">
-        <v>7151238</v>
+        <v>7151535</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18865,10 +18865,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120086251</v>
+        <v>120086284</v>
       </c>
       <c r="B172" t="n">
-        <v>91844</v>
+        <v>78526</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18877,25 +18877,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18905,10 +18905,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>746297</v>
+        <v>746563</v>
       </c>
       <c r="R172" t="n">
-        <v>7151200</v>
+        <v>7151464</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19069,10 +19069,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120080331</v>
+        <v>120086251</v>
       </c>
       <c r="B174" t="n">
-        <v>78526</v>
+        <v>91844</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19081,25 +19081,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19109,10 +19109,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>746936</v>
+        <v>746297</v>
       </c>
       <c r="R174" t="n">
-        <v>7151139</v>
+        <v>7151200</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19147,11 +19147,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -19160,38 +19155,23 @@
       </c>
       <c r="AG174" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120086284</v>
+        <v>120080331</v>
       </c>
       <c r="B175" t="n">
         <v>78526</v>
@@ -19231,10 +19211,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>746563</v>
+        <v>746936</v>
       </c>
       <c r="R175" t="n">
-        <v>7151464</v>
+        <v>7151139</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19269,6 +19249,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
+        </is>
+      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
@@ -19277,16 +19262,31 @@
       </c>
       <c r="AG175" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -8968,10 +8968,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120063442</v>
+        <v>120061725</v>
       </c>
       <c r="B79" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8980,25 +8980,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746297</v>
+        <v>746444</v>
       </c>
       <c r="R79" t="n">
-        <v>7151223</v>
+        <v>7151382</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9080,7 +9080,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120062963</v>
+        <v>120063442</v>
       </c>
       <c r="B80" t="n">
         <v>91840</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746369</v>
+        <v>746297</v>
       </c>
       <c r="R80" t="n">
-        <v>7151279</v>
+        <v>7151223</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9192,7 +9192,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120062338</v>
+        <v>120062963</v>
       </c>
       <c r="B81" t="n">
         <v>91840</v>
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746390</v>
+        <v>746369</v>
       </c>
       <c r="R81" t="n">
-        <v>7151301</v>
+        <v>7151279</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9304,10 +9304,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120061725</v>
+        <v>120062338</v>
       </c>
       <c r="B82" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9316,25 +9316,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746444</v>
+        <v>746390</v>
       </c>
       <c r="R82" t="n">
-        <v>7151382</v>
+        <v>7151301</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11308,10 +11308,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120086307</v>
+        <v>120086232</v>
       </c>
       <c r="B100" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11324,21 +11324,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11348,10 +11348,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>746483</v>
+        <v>746551</v>
       </c>
       <c r="R100" t="n">
-        <v>7151420</v>
+        <v>7151485</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11410,10 +11410,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120086232</v>
+        <v>120086307</v>
       </c>
       <c r="B101" t="n">
-        <v>89633</v>
+        <v>91834</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11426,21 +11426,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11450,10 +11450,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>746551</v>
+        <v>746483</v>
       </c>
       <c r="R101" t="n">
-        <v>7151485</v>
+        <v>7151420</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13850,10 +13850,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120080310</v>
+        <v>120086248</v>
       </c>
       <c r="B124" t="n">
-        <v>91821</v>
+        <v>91884</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13862,41 +13862,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6055</v>
+        <v>5449</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>746772</v>
+        <v>746537</v>
       </c>
       <c r="R124" t="n">
-        <v>7151182</v>
+        <v>7151592</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13931,40 +13928,34 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120079810</v>
+        <v>120080328</v>
       </c>
       <c r="B125" t="n">
-        <v>78526</v>
+        <v>89964</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13973,25 +13964,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14001,13 +13992,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>746645</v>
+        <v>746590</v>
       </c>
       <c r="R125" t="n">
-        <v>7151221</v>
+        <v>7151225</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14047,26 +14038,41 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120079799</v>
+        <v>120086239</v>
       </c>
       <c r="B126" t="n">
-        <v>90562</v>
+        <v>57463</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14079,37 +14085,49 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>746840</v>
+        <v>746532</v>
       </c>
       <c r="R126" t="n">
-        <v>7151151</v>
+        <v>7151493</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14153,22 +14171,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120086248</v>
+        <v>120079799</v>
       </c>
       <c r="B127" t="n">
-        <v>91884</v>
+        <v>90562</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14181,21 +14199,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14205,13 +14223,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>746537</v>
+        <v>746840</v>
       </c>
       <c r="R127" t="n">
-        <v>7151592</v>
+        <v>7151151</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14255,22 +14273,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120080328</v>
+        <v>120080310</v>
       </c>
       <c r="B128" t="n">
-        <v>89964</v>
+        <v>91821</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14279,38 +14297,41 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5685</v>
+        <v>6055</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>746590</v>
+        <v>746772</v>
       </c>
       <c r="R128" t="n">
-        <v>7151225</v>
+        <v>7151182</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14345,29 +14366,20 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
@@ -14384,10 +14396,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120086239</v>
+        <v>120079810</v>
       </c>
       <c r="B129" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14400,49 +14412,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>746532</v>
+        <v>746645</v>
       </c>
       <c r="R129" t="n">
-        <v>7151493</v>
+        <v>7151221</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14486,22 +14486,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120094170</v>
+        <v>120086241</v>
       </c>
       <c r="B130" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14510,41 +14510,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>746562</v>
+        <v>746383</v>
       </c>
       <c r="R130" t="n">
-        <v>7151492</v>
+        <v>7151288</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14585,7 +14582,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14604,10 +14600,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120080334</v>
+        <v>120094338</v>
       </c>
       <c r="B131" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14616,42 +14612,41 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>746537</v>
+        <v>746451</v>
       </c>
       <c r="R131" t="n">
-        <v>7151303</v>
+        <v>7151341</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14692,28 +14687,29 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120086241</v>
+        <v>120086247</v>
       </c>
       <c r="B132" t="n">
-        <v>91826</v>
+        <v>91884</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14726,21 +14722,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14750,10 +14746,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>746383</v>
+        <v>746385</v>
       </c>
       <c r="R132" t="n">
-        <v>7151288</v>
+        <v>7151299</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14812,10 +14808,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120094338</v>
+        <v>120094170</v>
       </c>
       <c r="B133" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14824,25 +14820,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14855,10 +14851,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>746451</v>
+        <v>746562</v>
       </c>
       <c r="R133" t="n">
-        <v>7151341</v>
+        <v>7151492</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14918,10 +14914,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120086247</v>
+        <v>120080334</v>
       </c>
       <c r="B134" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14930,38 +14926,42 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>746385</v>
+        <v>746537</v>
       </c>
       <c r="R134" t="n">
-        <v>7151299</v>
+        <v>7151303</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15008,12 +15008,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -15971,10 +15971,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120094677</v>
+        <v>120086287</v>
       </c>
       <c r="B144" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15983,41 +15983,38 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>746351</v>
+        <v>746567</v>
       </c>
       <c r="R144" t="n">
-        <v>7151225</v>
+        <v>7151554</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16058,7 +16055,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -16077,10 +16073,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120094483</v>
+        <v>120094677</v>
       </c>
       <c r="B145" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16089,25 +16085,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16120,10 +16116,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>746321</v>
+        <v>746351</v>
       </c>
       <c r="R145" t="n">
-        <v>7151245</v>
+        <v>7151225</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16183,7 +16179,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120094591</v>
+        <v>120094483</v>
       </c>
       <c r="B146" t="n">
         <v>91834</v>
@@ -16226,10 +16222,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>746294</v>
+        <v>746321</v>
       </c>
       <c r="R146" t="n">
-        <v>7151228</v>
+        <v>7151245</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16289,10 +16285,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120086287</v>
+        <v>120094591</v>
       </c>
       <c r="B147" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16305,34 +16301,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>746567</v>
+        <v>746294</v>
       </c>
       <c r="R147" t="n">
-        <v>7151554</v>
+        <v>7151228</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16373,6 +16372,7 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -16391,10 +16391,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120086253</v>
+        <v>120080296</v>
       </c>
       <c r="B148" t="n">
-        <v>91844</v>
+        <v>57463</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16403,38 +16403,46 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>746539</v>
+        <v>746527</v>
       </c>
       <c r="R148" t="n">
-        <v>7151522</v>
+        <v>7151199</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16481,22 +16489,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120086252</v>
+        <v>120080303</v>
       </c>
       <c r="B149" t="n">
-        <v>91844</v>
+        <v>91886</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16509,34 +16517,38 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>746575</v>
+        <v>746331</v>
       </c>
       <c r="R149" t="n">
-        <v>7151485</v>
+        <v>7151256</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16571,6 +16583,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Under tunn äldre tallgren på mager, torr mark</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
@@ -16583,22 +16600,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120079815</v>
+        <v>120086253</v>
       </c>
       <c r="B150" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16607,25 +16624,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16635,13 +16652,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>746896</v>
+        <v>746539</v>
       </c>
       <c r="R150" t="n">
-        <v>7151149</v>
+        <v>7151522</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16685,22 +16702,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120086281</v>
+        <v>120086252</v>
       </c>
       <c r="B151" t="n">
-        <v>78526</v>
+        <v>91844</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16709,25 +16726,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16737,10 +16754,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>746371</v>
+        <v>746575</v>
       </c>
       <c r="R151" t="n">
-        <v>7151235</v>
+        <v>7151485</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16799,10 +16816,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120086289</v>
+        <v>120079815</v>
       </c>
       <c r="B152" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16811,25 +16828,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16839,13 +16856,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>746670</v>
+        <v>746896</v>
       </c>
       <c r="R152" t="n">
-        <v>7151555</v>
+        <v>7151149</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16889,22 +16906,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120080303</v>
+        <v>120086281</v>
       </c>
       <c r="B153" t="n">
-        <v>91886</v>
+        <v>78526</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16913,42 +16930,38 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>232140</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>746331</v>
+        <v>746371</v>
       </c>
       <c r="R153" t="n">
-        <v>7151256</v>
+        <v>7151235</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16983,11 +16996,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Under tunn äldre tallgren på mager, torr mark</t>
-        </is>
-      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -17000,22 +17008,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120094190</v>
+        <v>120086289</v>
       </c>
       <c r="B154" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17028,37 +17036,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>746572</v>
+        <v>746670</v>
       </c>
       <c r="R154" t="n">
-        <v>7151479</v>
+        <v>7151555</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17099,7 +17104,6 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17118,10 +17122,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120080296</v>
+        <v>120094190</v>
       </c>
       <c r="B155" t="n">
-        <v>57463</v>
+        <v>91884</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17134,31 +17138,26 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -17166,10 +17165,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>746527</v>
+        <v>746572</v>
       </c>
       <c r="R155" t="n">
-        <v>7151199</v>
+        <v>7151479</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17210,28 +17209,29 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120086299</v>
+        <v>120086249</v>
       </c>
       <c r="B156" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17240,25 +17240,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17268,10 +17268,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>746314</v>
+        <v>746568</v>
       </c>
       <c r="R156" t="n">
-        <v>7151238</v>
+        <v>7151535</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17330,10 +17330,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120086262</v>
+        <v>120086234</v>
       </c>
       <c r="B157" t="n">
-        <v>91832</v>
+        <v>89633</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17346,21 +17346,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17370,10 +17370,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>746555</v>
+        <v>746539</v>
       </c>
       <c r="R157" t="n">
-        <v>7151590</v>
+        <v>7151522</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17432,10 +17432,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120086244</v>
+        <v>120086262</v>
       </c>
       <c r="B158" t="n">
-        <v>91828</v>
+        <v>91832</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17444,25 +17444,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>149</v>
+        <v>4361</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17472,10 +17472,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>746576</v>
+        <v>746555</v>
       </c>
       <c r="R158" t="n">
-        <v>7151444</v>
+        <v>7151590</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17534,10 +17534,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120086268</v>
+        <v>120086244</v>
       </c>
       <c r="B159" t="n">
-        <v>91863</v>
+        <v>91828</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17546,25 +17546,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5966</v>
+        <v>149</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17574,10 +17574,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>746563</v>
+        <v>746576</v>
       </c>
       <c r="R159" t="n">
-        <v>7151464</v>
+        <v>7151444</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17636,10 +17636,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120086234</v>
+        <v>120086268</v>
       </c>
       <c r="B160" t="n">
-        <v>89633</v>
+        <v>91863</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17652,21 +17652,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1962</v>
+        <v>5966</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17676,10 +17676,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>746539</v>
+        <v>746563</v>
       </c>
       <c r="R160" t="n">
-        <v>7151522</v>
+        <v>7151464</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17738,10 +17738,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120086249</v>
+        <v>120086299</v>
       </c>
       <c r="B161" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17750,25 +17750,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17778,10 +17778,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>746568</v>
+        <v>746314</v>
       </c>
       <c r="R161" t="n">
-        <v>7151535</v>
+        <v>7151238</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -7736,10 +7736,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120064386</v>
+        <v>120061458</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7748,41 +7748,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
+          <t>Vintjärnen, Vintjärnen, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746535</v>
+        <v>746495</v>
       </c>
       <c r="R68" t="n">
-        <v>7151171</v>
+        <v>7151424</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7836,19 +7836,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120062185</v>
+        <v>120064386</v>
       </c>
       <c r="B69" t="n">
         <v>91840</v>
@@ -7884,17 +7884,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vintjärnen, Vintjärnen, Vb</t>
+          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746401</v>
+        <v>746535</v>
       </c>
       <c r="R69" t="n">
-        <v>7151292</v>
+        <v>7151171</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7948,22 +7948,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120061458</v>
+        <v>120062185</v>
       </c>
       <c r="B70" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7972,25 +7972,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746495</v>
+        <v>746401</v>
       </c>
       <c r="R70" t="n">
-        <v>7151424</v>
+        <v>7151292</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -11308,10 +11308,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120086232</v>
+        <v>120086307</v>
       </c>
       <c r="B100" t="n">
-        <v>89633</v>
+        <v>91834</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11324,21 +11324,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11348,10 +11348,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>746551</v>
+        <v>746483</v>
       </c>
       <c r="R100" t="n">
-        <v>7151485</v>
+        <v>7151420</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11410,10 +11410,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120086307</v>
+        <v>120086232</v>
       </c>
       <c r="B101" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11426,21 +11426,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11450,10 +11450,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>746483</v>
+        <v>746551</v>
       </c>
       <c r="R101" t="n">
-        <v>7151420</v>
+        <v>7151485</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12239,10 +12239,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120086308</v>
+        <v>120094102</v>
       </c>
       <c r="B109" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12251,38 +12251,41 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>746492</v>
+        <v>746539</v>
       </c>
       <c r="R109" t="n">
-        <v>7151446</v>
+        <v>7151513</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12323,6 +12326,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -12341,10 +12345,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120094102</v>
+        <v>120086267</v>
       </c>
       <c r="B110" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12353,41 +12357,38 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>746539</v>
+        <v>746492</v>
       </c>
       <c r="R110" t="n">
-        <v>7151513</v>
+        <v>7151446</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12428,7 +12429,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12447,10 +12447,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120086267</v>
+        <v>120086286</v>
       </c>
       <c r="B111" t="n">
-        <v>91863</v>
+        <v>78526</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12463,21 +12463,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12487,10 +12487,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>746492</v>
+        <v>746555</v>
       </c>
       <c r="R111" t="n">
-        <v>7151446</v>
+        <v>7151578</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12549,10 +12549,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120086286</v>
+        <v>120079798</v>
       </c>
       <c r="B112" t="n">
-        <v>78526</v>
+        <v>89633</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12565,21 +12565,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12589,13 +12589,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>746555</v>
+        <v>746310</v>
       </c>
       <c r="R112" t="n">
-        <v>7151578</v>
+        <v>7151135</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12639,22 +12639,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120079798</v>
+        <v>120086308</v>
       </c>
       <c r="B113" t="n">
-        <v>89633</v>
+        <v>91834</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12667,21 +12667,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12691,13 +12691,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>746310</v>
+        <v>746492</v>
       </c>
       <c r="R113" t="n">
-        <v>7151135</v>
+        <v>7151446</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12741,12 +12741,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -13169,10 +13169,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120080356</v>
+        <v>120080330</v>
       </c>
       <c r="B118" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13181,25 +13181,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13209,10 +13209,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>746499</v>
+        <v>746624</v>
       </c>
       <c r="R118" t="n">
-        <v>7151195</v>
+        <v>7151217</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13247,6 +13247,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Nedbruten tallåga, kollekt taget</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -13255,6 +13260,21 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -13271,7 +13291,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120086303</v>
+        <v>120080356</v>
       </c>
       <c r="B119" t="n">
         <v>91840</v>
@@ -13311,10 +13331,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>746555</v>
+        <v>746499</v>
       </c>
       <c r="R119" t="n">
-        <v>7151578</v>
+        <v>7151195</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13361,19 +13381,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120080357</v>
+        <v>120086303</v>
       </c>
       <c r="B120" t="n">
         <v>91840</v>
@@ -13413,10 +13433,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>746301</v>
+        <v>746555</v>
       </c>
       <c r="R120" t="n">
-        <v>7151209</v>
+        <v>7151578</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13463,22 +13483,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120080291</v>
+        <v>120080357</v>
       </c>
       <c r="B121" t="n">
-        <v>91254</v>
+        <v>91840</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13491,38 +13511,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3298</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>746393</v>
+        <v>746301</v>
       </c>
       <c r="R121" t="n">
-        <v>7151288</v>
+        <v>7151209</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13557,11 +13573,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Basen av levande gran</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -13570,21 +13581,6 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
@@ -13728,10 +13724,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120080330</v>
+        <v>120080291</v>
       </c>
       <c r="B123" t="n">
-        <v>90712</v>
+        <v>91254</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13740,38 +13736,42 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1503</v>
+        <v>3298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>746624</v>
+        <v>746393</v>
       </c>
       <c r="R123" t="n">
-        <v>7151217</v>
+        <v>7151288</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Nedbruten tallåga, kollekt taget</t>
+          <t>Basen av levande gran</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13822,17 +13822,17 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -14498,10 +14498,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120086241</v>
+        <v>120094170</v>
       </c>
       <c r="B130" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14510,38 +14510,41 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>746383</v>
+        <v>746562</v>
       </c>
       <c r="R130" t="n">
-        <v>7151288</v>
+        <v>7151492</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14582,6 +14585,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14600,10 +14604,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120094338</v>
+        <v>120080334</v>
       </c>
       <c r="B131" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14612,41 +14616,42 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>746451</v>
+        <v>746537</v>
       </c>
       <c r="R131" t="n">
-        <v>7151341</v>
+        <v>7151303</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14687,29 +14692,28 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120086247</v>
+        <v>120086241</v>
       </c>
       <c r="B132" t="n">
-        <v>91884</v>
+        <v>91826</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14722,21 +14726,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14746,10 +14750,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>746385</v>
+        <v>746383</v>
       </c>
       <c r="R132" t="n">
-        <v>7151299</v>
+        <v>7151288</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14808,10 +14812,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120094170</v>
+        <v>120094338</v>
       </c>
       <c r="B133" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14820,25 +14824,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14851,10 +14855,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>746562</v>
+        <v>746451</v>
       </c>
       <c r="R133" t="n">
-        <v>7151492</v>
+        <v>7151341</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14914,10 +14918,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120080334</v>
+        <v>120086247</v>
       </c>
       <c r="B134" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14926,42 +14930,38 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>746537</v>
+        <v>746385</v>
       </c>
       <c r="R134" t="n">
-        <v>7151303</v>
+        <v>7151299</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15008,22 +15008,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120086288</v>
+        <v>120094266</v>
       </c>
       <c r="B135" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15032,38 +15032,41 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>746630</v>
+        <v>746491</v>
       </c>
       <c r="R135" t="n">
-        <v>7151524</v>
+        <v>7151452</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15104,6 +15107,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -15122,10 +15126,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120094266</v>
+        <v>120086288</v>
       </c>
       <c r="B136" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15134,41 +15138,38 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>746491</v>
+        <v>746630</v>
       </c>
       <c r="R136" t="n">
-        <v>7151452</v>
+        <v>7151524</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15209,7 +15210,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -18865,10 +18865,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120086284</v>
+        <v>120086251</v>
       </c>
       <c r="B172" t="n">
-        <v>78526</v>
+        <v>91844</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18877,25 +18877,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18905,10 +18905,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>746563</v>
+        <v>746297</v>
       </c>
       <c r="R172" t="n">
-        <v>7151464</v>
+        <v>7151200</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19069,10 +19069,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120086251</v>
+        <v>120080331</v>
       </c>
       <c r="B174" t="n">
-        <v>91844</v>
+        <v>78526</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19081,25 +19081,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19109,10 +19109,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>746297</v>
+        <v>746936</v>
       </c>
       <c r="R174" t="n">
-        <v>7151200</v>
+        <v>7151139</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19147,6 +19147,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -19155,23 +19160,38 @@
       </c>
       <c r="AG174" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120080331</v>
+        <v>120086284</v>
       </c>
       <c r="B175" t="n">
         <v>78526</v>
@@ -19211,10 +19231,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>746936</v>
+        <v>746563</v>
       </c>
       <c r="R175" t="n">
-        <v>7151139</v>
+        <v>7151464</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19249,11 +19269,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
-        </is>
-      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
@@ -19262,31 +19277,16 @@
       </c>
       <c r="AG175" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -8184,10 +8184,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120059636</v>
+        <v>120061645</v>
       </c>
       <c r="B72" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8196,25 +8196,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746602</v>
+        <v>746450</v>
       </c>
       <c r="R72" t="n">
-        <v>7151535</v>
+        <v>7151380</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8296,10 +8296,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120061645</v>
+        <v>120059636</v>
       </c>
       <c r="B73" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8308,25 +8308,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8336,10 +8336,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746450</v>
+        <v>746602</v>
       </c>
       <c r="R73" t="n">
-        <v>7151380</v>
+        <v>7151535</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -13169,10 +13169,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120080330</v>
+        <v>120080356</v>
       </c>
       <c r="B118" t="n">
-        <v>90712</v>
+        <v>91840</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13181,25 +13181,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13209,10 +13209,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>746624</v>
+        <v>746499</v>
       </c>
       <c r="R118" t="n">
-        <v>7151217</v>
+        <v>7151195</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13247,11 +13247,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Nedbruten tallåga, kollekt taget</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -13260,21 +13255,6 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -13291,7 +13271,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120080356</v>
+        <v>120086303</v>
       </c>
       <c r="B119" t="n">
         <v>91840</v>
@@ -13331,10 +13311,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>746499</v>
+        <v>746555</v>
       </c>
       <c r="R119" t="n">
-        <v>7151195</v>
+        <v>7151578</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13381,19 +13361,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120086303</v>
+        <v>120080357</v>
       </c>
       <c r="B120" t="n">
         <v>91840</v>
@@ -13433,10 +13413,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>746555</v>
+        <v>746301</v>
       </c>
       <c r="R120" t="n">
-        <v>7151578</v>
+        <v>7151209</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13483,22 +13463,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120080357</v>
+        <v>120080291</v>
       </c>
       <c r="B121" t="n">
-        <v>91840</v>
+        <v>91254</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13511,34 +13491,38 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>3298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>746301</v>
+        <v>746393</v>
       </c>
       <c r="R121" t="n">
-        <v>7151209</v>
+        <v>7151288</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13573,6 +13557,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Basen av levande gran</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -13581,6 +13570,21 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
@@ -13724,10 +13728,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120080291</v>
+        <v>120080330</v>
       </c>
       <c r="B123" t="n">
-        <v>91254</v>
+        <v>90712</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13736,42 +13740,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3298</v>
+        <v>1503</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>746393</v>
+        <v>746624</v>
       </c>
       <c r="R123" t="n">
-        <v>7151288</v>
+        <v>7151217</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Basen av levande gran</t>
+          <t>Nedbruten tallåga, kollekt taget</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13822,17 +13822,17 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -14498,10 +14498,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120094170</v>
+        <v>120086241</v>
       </c>
       <c r="B130" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14510,41 +14510,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>746562</v>
+        <v>746383</v>
       </c>
       <c r="R130" t="n">
-        <v>7151492</v>
+        <v>7151288</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14585,7 +14582,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14604,10 +14600,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120080334</v>
+        <v>120094338</v>
       </c>
       <c r="B131" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14616,42 +14612,41 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>746537</v>
+        <v>746451</v>
       </c>
       <c r="R131" t="n">
-        <v>7151303</v>
+        <v>7151341</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14692,28 +14687,29 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120086241</v>
+        <v>120086247</v>
       </c>
       <c r="B132" t="n">
-        <v>91826</v>
+        <v>91884</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14726,21 +14722,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14750,10 +14746,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>746383</v>
+        <v>746385</v>
       </c>
       <c r="R132" t="n">
-        <v>7151288</v>
+        <v>7151299</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14812,10 +14808,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120094338</v>
+        <v>120094170</v>
       </c>
       <c r="B133" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14824,25 +14820,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14855,10 +14851,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>746451</v>
+        <v>746562</v>
       </c>
       <c r="R133" t="n">
-        <v>7151341</v>
+        <v>7151492</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14918,10 +14914,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120086247</v>
+        <v>120080334</v>
       </c>
       <c r="B134" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14930,38 +14926,42 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>746385</v>
+        <v>746537</v>
       </c>
       <c r="R134" t="n">
-        <v>7151299</v>
+        <v>7151303</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15008,12 +15008,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -16391,10 +16391,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120080296</v>
+        <v>120086253</v>
       </c>
       <c r="B148" t="n">
-        <v>57463</v>
+        <v>91844</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16403,46 +16403,38 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>746527</v>
+        <v>746539</v>
       </c>
       <c r="R148" t="n">
-        <v>7151199</v>
+        <v>7151522</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16489,22 +16481,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120080303</v>
+        <v>120086252</v>
       </c>
       <c r="B149" t="n">
-        <v>91886</v>
+        <v>91844</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16517,38 +16509,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>746331</v>
+        <v>746575</v>
       </c>
       <c r="R149" t="n">
-        <v>7151256</v>
+        <v>7151485</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16583,11 +16571,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Under tunn äldre tallgren på mager, torr mark</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
@@ -16600,22 +16583,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120086253</v>
+        <v>120079815</v>
       </c>
       <c r="B150" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16624,25 +16607,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16652,13 +16635,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>746539</v>
+        <v>746896</v>
       </c>
       <c r="R150" t="n">
-        <v>7151522</v>
+        <v>7151149</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16702,22 +16685,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120086252</v>
+        <v>120086281</v>
       </c>
       <c r="B151" t="n">
-        <v>91844</v>
+        <v>78526</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16726,25 +16709,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16754,10 +16737,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>746575</v>
+        <v>746371</v>
       </c>
       <c r="R151" t="n">
-        <v>7151485</v>
+        <v>7151235</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16816,10 +16799,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120079815</v>
+        <v>120086289</v>
       </c>
       <c r="B152" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16828,25 +16811,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16856,13 +16839,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>746896</v>
+        <v>746670</v>
       </c>
       <c r="R152" t="n">
-        <v>7151149</v>
+        <v>7151555</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16906,22 +16889,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120086281</v>
+        <v>120080303</v>
       </c>
       <c r="B153" t="n">
-        <v>78526</v>
+        <v>91886</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16930,38 +16913,42 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>232140</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>746371</v>
+        <v>746331</v>
       </c>
       <c r="R153" t="n">
-        <v>7151235</v>
+        <v>7151256</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16996,6 +16983,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Under tunn äldre tallgren på mager, torr mark</t>
+        </is>
+      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -17008,22 +17000,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120086289</v>
+        <v>120094190</v>
       </c>
       <c r="B154" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17036,34 +17028,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>746670</v>
+        <v>746572</v>
       </c>
       <c r="R154" t="n">
-        <v>7151555</v>
+        <v>7151479</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17104,6 +17099,7 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17122,10 +17118,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120094190</v>
+        <v>120080296</v>
       </c>
       <c r="B155" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17138,26 +17134,31 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -17165,10 +17166,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>746572</v>
+        <v>746527</v>
       </c>
       <c r="R155" t="n">
-        <v>7151479</v>
+        <v>7151199</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17209,19 +17210,18 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
@@ -18865,10 +18865,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120086251</v>
+        <v>120086284</v>
       </c>
       <c r="B172" t="n">
-        <v>91844</v>
+        <v>78526</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18877,25 +18877,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18905,10 +18905,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>746297</v>
+        <v>746563</v>
       </c>
       <c r="R172" t="n">
-        <v>7151200</v>
+        <v>7151464</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19069,10 +19069,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120080331</v>
+        <v>120086251</v>
       </c>
       <c r="B174" t="n">
-        <v>78526</v>
+        <v>91844</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19081,25 +19081,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19109,10 +19109,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>746936</v>
+        <v>746297</v>
       </c>
       <c r="R174" t="n">
-        <v>7151139</v>
+        <v>7151200</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19147,11 +19147,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -19160,38 +19155,23 @@
       </c>
       <c r="AG174" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120086284</v>
+        <v>120080331</v>
       </c>
       <c r="B175" t="n">
         <v>78526</v>
@@ -19231,10 +19211,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>746563</v>
+        <v>746936</v>
       </c>
       <c r="R175" t="n">
-        <v>7151464</v>
+        <v>7151139</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19269,6 +19249,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
+        </is>
+      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
@@ -19277,16 +19262,31 @@
       </c>
       <c r="AG175" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -7176,10 +7176,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120064407</v>
+        <v>120062185</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746440</v>
+        <v>746401</v>
       </c>
       <c r="R63" t="n">
-        <v>7151291</v>
+        <v>7151292</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7288,10 +7288,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120063671</v>
+        <v>120063693</v>
       </c>
       <c r="B64" t="n">
-        <v>91856</v>
+        <v>91858</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7300,25 +7300,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7328,13 +7328,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746309</v>
+        <v>746319</v>
       </c>
       <c r="R64" t="n">
-        <v>7151221</v>
+        <v>7151210</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7388,22 +7388,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120061247</v>
+        <v>120063728</v>
       </c>
       <c r="B65" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7412,25 +7412,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746541</v>
+        <v>746298</v>
       </c>
       <c r="R65" t="n">
-        <v>7151441</v>
+        <v>7151222</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7512,10 +7512,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120063487</v>
+        <v>120063442</v>
       </c>
       <c r="B66" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7524,25 +7524,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746300</v>
+        <v>746297</v>
       </c>
       <c r="R66" t="n">
-        <v>7151231</v>
+        <v>7151223</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120063287</v>
+        <v>120061233</v>
       </c>
       <c r="B67" t="n">
-        <v>91884</v>
+        <v>91850</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7640,21 +7640,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7664,10 +7664,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746369</v>
+        <v>746597</v>
       </c>
       <c r="R67" t="n">
-        <v>7151254</v>
+        <v>7151440</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7736,10 +7736,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120061458</v>
+        <v>120063671</v>
       </c>
       <c r="B68" t="n">
-        <v>91884</v>
+        <v>91874</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7752,21 +7752,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746495</v>
+        <v>746309</v>
       </c>
       <c r="R68" t="n">
-        <v>7151424</v>
+        <v>7151221</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7848,10 +7848,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120064386</v>
+        <v>120064725</v>
       </c>
       <c r="B69" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7960,10 +7960,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120062185</v>
+        <v>120061645</v>
       </c>
       <c r="B70" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7972,25 +7972,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746401</v>
+        <v>746450</v>
       </c>
       <c r="R70" t="n">
-        <v>7151292</v>
+        <v>7151380</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8072,10 +8072,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120059683</v>
+        <v>120061458</v>
       </c>
       <c r="B71" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746569</v>
+        <v>746495</v>
       </c>
       <c r="R71" t="n">
-        <v>7151549</v>
+        <v>7151424</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8184,10 +8184,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120061645</v>
+        <v>120061860</v>
       </c>
       <c r="B72" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8196,25 +8196,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746450</v>
+        <v>746423</v>
       </c>
       <c r="R72" t="n">
-        <v>7151380</v>
+        <v>7151350</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8296,10 +8296,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120059636</v>
+        <v>120062338</v>
       </c>
       <c r="B73" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8336,10 +8336,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746602</v>
+        <v>746390</v>
       </c>
       <c r="R73" t="n">
-        <v>7151535</v>
+        <v>7151301</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8408,10 +8408,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120062932</v>
+        <v>120061583</v>
       </c>
       <c r="B74" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8420,25 +8420,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746422</v>
+        <v>746472</v>
       </c>
       <c r="R74" t="n">
-        <v>7151289</v>
+        <v>7151401</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8520,10 +8520,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120061534</v>
+        <v>120062274</v>
       </c>
       <c r="B75" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8532,25 +8532,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746467</v>
+        <v>746394</v>
       </c>
       <c r="R75" t="n">
-        <v>7151403</v>
+        <v>7151307</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8635,7 +8635,7 @@
         <v>120063551</v>
       </c>
       <c r="B76" t="n">
-        <v>91856</v>
+        <v>91874</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8744,10 +8744,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120059794</v>
+        <v>120059872</v>
       </c>
       <c r="B77" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8756,25 +8756,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746567</v>
+        <v>746557</v>
       </c>
       <c r="R77" t="n">
-        <v>7151566</v>
+        <v>7151556</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8856,10 +8856,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120063693</v>
+        <v>120062932</v>
       </c>
       <c r="B78" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8868,25 +8868,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8896,13 +8896,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746319</v>
+        <v>746422</v>
       </c>
       <c r="R78" t="n">
-        <v>7151210</v>
+        <v>7151289</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8956,22 +8956,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120061725</v>
+        <v>120059794</v>
       </c>
       <c r="B79" t="n">
-        <v>91834</v>
+        <v>91902</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8984,21 +8984,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746444</v>
+        <v>746567</v>
       </c>
       <c r="R79" t="n">
-        <v>7151382</v>
+        <v>7151566</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9080,10 +9080,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120063442</v>
+        <v>120059683</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9092,25 +9092,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746297</v>
+        <v>746569</v>
       </c>
       <c r="R80" t="n">
-        <v>7151223</v>
+        <v>7151549</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9192,10 +9192,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120062963</v>
+        <v>120060888</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>96891</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9208,21 +9208,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746369</v>
+        <v>746566</v>
       </c>
       <c r="R81" t="n">
-        <v>7151279</v>
+        <v>7151484</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9304,10 +9304,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120062338</v>
+        <v>120059636</v>
       </c>
       <c r="B82" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746390</v>
+        <v>746602</v>
       </c>
       <c r="R82" t="n">
-        <v>7151301</v>
+        <v>7151535</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9416,10 +9416,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120060888</v>
+        <v>120061607</v>
       </c>
       <c r="B83" t="n">
-        <v>96868</v>
+        <v>91850</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9428,25 +9428,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>746566</v>
+        <v>746453</v>
       </c>
       <c r="R83" t="n">
-        <v>7151484</v>
+        <v>7151408</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9528,10 +9528,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120063728</v>
+        <v>120061725</v>
       </c>
       <c r="B84" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9544,21 +9544,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9568,10 +9568,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746298</v>
+        <v>746444</v>
       </c>
       <c r="R84" t="n">
-        <v>7151222</v>
+        <v>7151382</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9640,10 +9640,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120062274</v>
+        <v>120063963</v>
       </c>
       <c r="B85" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9652,25 +9652,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9680,10 +9680,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746394</v>
+        <v>746301</v>
       </c>
       <c r="R85" t="n">
-        <v>7151307</v>
+        <v>7151207</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9752,10 +9752,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120061607</v>
+        <v>120061534</v>
       </c>
       <c r="B86" t="n">
-        <v>91832</v>
+        <v>91858</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9764,25 +9764,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9792,10 +9792,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>746453</v>
+        <v>746467</v>
       </c>
       <c r="R86" t="n">
-        <v>7151408</v>
+        <v>7151403</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9864,10 +9864,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120061860</v>
+        <v>120061247</v>
       </c>
       <c r="B87" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>746423</v>
+        <v>746541</v>
       </c>
       <c r="R87" t="n">
-        <v>7151350</v>
+        <v>7151441</v>
       </c>
       <c r="S87" t="n">
         <v>1</v>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9976,10 +9976,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120061583</v>
+        <v>120063383</v>
       </c>
       <c r="B88" t="n">
-        <v>91840</v>
+        <v>91881</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9988,25 +9988,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>746472</v>
+        <v>746303</v>
       </c>
       <c r="R88" t="n">
-        <v>7151401</v>
+        <v>7151246</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10088,10 +10088,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120059872</v>
+        <v>120061686</v>
       </c>
       <c r="B89" t="n">
-        <v>91840</v>
+        <v>91881</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10100,25 +10100,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10128,10 +10128,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>746557</v>
+        <v>746448</v>
       </c>
       <c r="R89" t="n">
-        <v>7151556</v>
+        <v>7151388</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10200,10 +10200,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120062389</v>
+        <v>120064407</v>
       </c>
       <c r="B90" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10240,10 +10240,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>746426</v>
+        <v>746440</v>
       </c>
       <c r="R90" t="n">
-        <v>7151309</v>
+        <v>7151291</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
@@ -10275,7 +10275,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10312,10 +10312,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120062044</v>
+        <v>120062963</v>
       </c>
       <c r="B91" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10324,25 +10324,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10352,10 +10352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>746344</v>
+        <v>746369</v>
       </c>
       <c r="R91" t="n">
-        <v>7151353</v>
+        <v>7151279</v>
       </c>
       <c r="S91" t="n">
         <v>1</v>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10424,10 +10424,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120059956</v>
+        <v>120063487</v>
       </c>
       <c r="B92" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10440,21 +10440,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>746535</v>
+        <v>746300</v>
       </c>
       <c r="R92" t="n">
-        <v>7151537</v>
+        <v>7151231</v>
       </c>
       <c r="S92" t="n">
         <v>1</v>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10536,10 +10536,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120061233</v>
+        <v>120059956</v>
       </c>
       <c r="B93" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>746597</v>
+        <v>746535</v>
       </c>
       <c r="R93" t="n">
-        <v>7151440</v>
+        <v>7151537</v>
       </c>
       <c r="S93" t="n">
         <v>1</v>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10648,10 +10648,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120063383</v>
+        <v>120062389</v>
       </c>
       <c r="B94" t="n">
-        <v>91863</v>
+        <v>91858</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10660,25 +10660,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>746303</v>
+        <v>746426</v>
       </c>
       <c r="R94" t="n">
-        <v>7151246</v>
+        <v>7151309</v>
       </c>
       <c r="S94" t="n">
         <v>1</v>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10760,10 +10760,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120061686</v>
+        <v>120063439</v>
       </c>
       <c r="B95" t="n">
-        <v>91863</v>
+        <v>91846</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10772,25 +10772,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5966</v>
+        <v>149</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10800,10 +10800,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>746448</v>
+        <v>746303</v>
       </c>
       <c r="R95" t="n">
-        <v>7151388</v>
+        <v>7151241</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10872,10 +10872,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120063439</v>
+        <v>120062044</v>
       </c>
       <c r="B96" t="n">
-        <v>91828</v>
+        <v>91902</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10884,25 +10884,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>149</v>
+        <v>5449</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>746303</v>
+        <v>746344</v>
       </c>
       <c r="R96" t="n">
-        <v>7151241</v>
+        <v>7151353</v>
       </c>
       <c r="S96" t="n">
         <v>1</v>
@@ -10947,7 +10947,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10984,10 +10984,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120063963</v>
+        <v>120063287</v>
       </c>
       <c r="B97" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10996,25 +10996,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11024,10 +11024,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>746301</v>
+        <v>746369</v>
       </c>
       <c r="R97" t="n">
-        <v>7151207</v>
+        <v>7151254</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11096,10 +11096,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120094137</v>
+        <v>120086251</v>
       </c>
       <c r="B98" t="n">
-        <v>91840</v>
+        <v>91862</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11108,41 +11108,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>746535</v>
+        <v>746297</v>
       </c>
       <c r="R98" t="n">
-        <v>7151504</v>
+        <v>7151200</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11183,7 +11180,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11202,10 +11198,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120094305</v>
+        <v>120080330</v>
       </c>
       <c r="B99" t="n">
-        <v>91840</v>
+        <v>90730</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11214,41 +11210,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>746472</v>
+        <v>746624</v>
       </c>
       <c r="R99" t="n">
-        <v>7151410</v>
+        <v>7151217</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11283,35 +11276,54 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Nedbruten tallåga, kollekt taget</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120086307</v>
+        <v>120086308</v>
       </c>
       <c r="B100" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11348,10 +11360,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>746483</v>
+        <v>746492</v>
       </c>
       <c r="R100" t="n">
-        <v>7151420</v>
+        <v>7151446</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11410,10 +11422,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120086232</v>
+        <v>120094137</v>
       </c>
       <c r="B101" t="n">
-        <v>89633</v>
+        <v>91858</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11422,38 +11434,41 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>746551</v>
+        <v>746535</v>
       </c>
       <c r="R101" t="n">
-        <v>7151485</v>
+        <v>7151504</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11494,6 +11509,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11512,10 +11528,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120094276</v>
+        <v>120086254</v>
       </c>
       <c r="B102" t="n">
-        <v>91840</v>
+        <v>91862</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11524,41 +11540,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>746476</v>
+        <v>746678</v>
       </c>
       <c r="R102" t="n">
-        <v>7151446</v>
+        <v>7151537</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11599,7 +11612,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11618,10 +11630,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120086243</v>
+        <v>120080328</v>
       </c>
       <c r="B103" t="n">
-        <v>91463</v>
+        <v>89981</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11630,25 +11642,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4745</v>
+        <v>5685</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11658,10 +11670,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>746316</v>
+        <v>746590</v>
       </c>
       <c r="R103" t="n">
-        <v>7151209</v>
+        <v>7151225</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11705,25 +11717,40 @@
       <c r="AG103" t="b">
         <v>0</v>
       </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120086257</v>
+        <v>120079807</v>
       </c>
       <c r="B104" t="n">
-        <v>91852</v>
+        <v>57431</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11736,37 +11763,45 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4366</v>
+        <v>103031</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>746575</v>
+        <v>746368</v>
       </c>
       <c r="R104" t="n">
-        <v>7151554</v>
+        <v>7151283</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11810,22 +11845,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120080359</v>
+        <v>120079798</v>
       </c>
       <c r="B105" t="n">
-        <v>91834</v>
+        <v>89650</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11838,41 +11873,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>746291</v>
+        <v>746310</v>
       </c>
       <c r="R105" t="n">
-        <v>7151137</v>
+        <v>7151135</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11916,22 +11947,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120079801</v>
+        <v>120086273</v>
       </c>
       <c r="B106" t="n">
-        <v>91884</v>
+        <v>90730</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11940,25 +11971,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5449</v>
+        <v>1503</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11968,13 +11999,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>746598</v>
+        <v>746551</v>
       </c>
       <c r="R106" t="n">
-        <v>7151227</v>
+        <v>7151485</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12012,29 +12043,28 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120080353</v>
+        <v>120086301</v>
       </c>
       <c r="B107" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12071,10 +12101,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>746577</v>
+        <v>746566</v>
       </c>
       <c r="R107" t="n">
-        <v>7151220</v>
+        <v>7151468</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12121,22 +12151,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120094777</v>
+        <v>120079803</v>
       </c>
       <c r="B108" t="n">
-        <v>91884</v>
+        <v>91862</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12145,44 +12175,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>746478</v>
+        <v>746316</v>
       </c>
       <c r="R108" t="n">
-        <v>7151377</v>
+        <v>7151248</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12220,29 +12247,28 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120094102</v>
+        <v>120079814</v>
       </c>
       <c r="B109" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12273,22 +12299,19 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>746539</v>
+        <v>746510</v>
       </c>
       <c r="R109" t="n">
-        <v>7151513</v>
+        <v>7151225</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12326,29 +12349,28 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120086267</v>
+        <v>120080308</v>
       </c>
       <c r="B110" t="n">
-        <v>91863</v>
+        <v>91902</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12361,21 +12383,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12385,10 +12407,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>746492</v>
+        <v>746368</v>
       </c>
       <c r="R110" t="n">
-        <v>7151446</v>
+        <v>7151279</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12435,22 +12457,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120086286</v>
+        <v>120079810</v>
       </c>
       <c r="B111" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12487,13 +12509,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>746555</v>
+        <v>746645</v>
       </c>
       <c r="R111" t="n">
-        <v>7151578</v>
+        <v>7151221</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12537,22 +12559,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120079798</v>
+        <v>120086252</v>
       </c>
       <c r="B112" t="n">
-        <v>89633</v>
+        <v>91862</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12561,25 +12583,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12589,13 +12611,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>746310</v>
+        <v>746575</v>
       </c>
       <c r="R112" t="n">
-        <v>7151135</v>
+        <v>7151485</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12639,22 +12661,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120086308</v>
+        <v>120094483</v>
       </c>
       <c r="B113" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12685,16 +12707,19 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>746492</v>
+        <v>746321</v>
       </c>
       <c r="R113" t="n">
-        <v>7151446</v>
+        <v>7151245</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12735,6 +12760,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12753,10 +12779,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120094292</v>
+        <v>120080354</v>
       </c>
       <c r="B114" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12787,19 +12813,16 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>746478</v>
+        <v>746559</v>
       </c>
       <c r="R114" t="n">
-        <v>7151421</v>
+        <v>7151216</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12840,29 +12863,28 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120094359</v>
+        <v>120086249</v>
       </c>
       <c r="B115" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12871,41 +12893,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>746451</v>
+        <v>746568</v>
       </c>
       <c r="R115" t="n">
-        <v>7151341</v>
+        <v>7151535</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12946,7 +12965,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12965,10 +12983,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120080308</v>
+        <v>120086239</v>
       </c>
       <c r="B116" t="n">
-        <v>91884</v>
+        <v>57473</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12981,34 +12999,46 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>746368</v>
+        <v>746532</v>
       </c>
       <c r="R116" t="n">
-        <v>7151279</v>
+        <v>7151493</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13055,22 +13085,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120086273</v>
+        <v>120094371</v>
       </c>
       <c r="B117" t="n">
-        <v>90712</v>
+        <v>91858</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13079,38 +13109,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>746551</v>
+        <v>746383</v>
       </c>
       <c r="R117" t="n">
-        <v>7151485</v>
+        <v>7151297</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13151,6 +13184,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13169,10 +13203,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120080356</v>
+        <v>120086268</v>
       </c>
       <c r="B118" t="n">
-        <v>91840</v>
+        <v>91881</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13181,25 +13215,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13209,10 +13243,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>746499</v>
+        <v>746563</v>
       </c>
       <c r="R118" t="n">
-        <v>7151195</v>
+        <v>7151464</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13259,22 +13293,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120086303</v>
+        <v>120086282</v>
       </c>
       <c r="B119" t="n">
-        <v>91840</v>
+        <v>78542</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13283,25 +13317,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13311,10 +13345,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>746555</v>
+        <v>746368</v>
       </c>
       <c r="R119" t="n">
-        <v>7151578</v>
+        <v>7151288</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13373,10 +13407,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120080357</v>
+        <v>120086260</v>
       </c>
       <c r="B120" t="n">
-        <v>91840</v>
+        <v>91850</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13385,25 +13419,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13413,10 +13447,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>746301</v>
+        <v>746378</v>
       </c>
       <c r="R120" t="n">
-        <v>7151209</v>
+        <v>7151283</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13463,22 +13497,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120080291</v>
+        <v>120086288</v>
       </c>
       <c r="B121" t="n">
-        <v>91254</v>
+        <v>78542</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13487,42 +13521,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>746393</v>
+        <v>746630</v>
       </c>
       <c r="R121" t="n">
-        <v>7151288</v>
+        <v>7151524</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13557,11 +13587,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Basen av levande gran</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -13570,41 +13595,26 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120080309</v>
+        <v>120079808</v>
       </c>
       <c r="B122" t="n">
-        <v>57326</v>
+        <v>90594</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13617,42 +13627,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>746663</v>
+        <v>746668</v>
       </c>
       <c r="R122" t="n">
-        <v>7151255</v>
+        <v>7151253</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13684,11 +13689,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Äldre födohack i basen</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -13697,41 +13697,26 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120080330</v>
+        <v>120086248</v>
       </c>
       <c r="B123" t="n">
-        <v>90712</v>
+        <v>91902</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13740,25 +13725,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1503</v>
+        <v>5449</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13768,10 +13753,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>746624</v>
+        <v>746537</v>
       </c>
       <c r="R123" t="n">
-        <v>7151217</v>
+        <v>7151592</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13806,11 +13791,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Nedbruten tallåga, kollekt taget</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
@@ -13819,41 +13799,26 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120086248</v>
+        <v>120086231</v>
       </c>
       <c r="B124" t="n">
-        <v>91884</v>
+        <v>90545</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13862,25 +13827,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13890,10 +13855,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>746537</v>
+        <v>746676</v>
       </c>
       <c r="R124" t="n">
-        <v>7151592</v>
+        <v>7151534</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13952,10 +13917,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120080328</v>
+        <v>120094190</v>
       </c>
       <c r="B125" t="n">
-        <v>89964</v>
+        <v>91902</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13964,38 +13929,41 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5685</v>
+        <v>5449</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>746590</v>
+        <v>746572</v>
       </c>
       <c r="R125" t="n">
-        <v>7151225</v>
+        <v>7151479</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14036,43 +14004,29 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120086239</v>
+        <v>120094355</v>
       </c>
       <c r="B126" t="n">
-        <v>57463</v>
+        <v>91902</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14085,35 +14039,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -14121,10 +14066,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>746532</v>
+        <v>746451</v>
       </c>
       <c r="R126" t="n">
-        <v>7151493</v>
+        <v>7151341</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14165,6 +14110,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -14183,10 +14129,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120079799</v>
+        <v>120080358</v>
       </c>
       <c r="B127" t="n">
-        <v>90562</v>
+        <v>91858</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14195,25 +14141,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14223,13 +14169,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>746840</v>
+        <v>746699</v>
       </c>
       <c r="R127" t="n">
-        <v>7151151</v>
+        <v>7151240</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14273,22 +14219,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120080310</v>
+        <v>120080356</v>
       </c>
       <c r="B128" t="n">
-        <v>91821</v>
+        <v>91858</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14297,41 +14243,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>746772</v>
+        <v>746499</v>
       </c>
       <c r="R128" t="n">
-        <v>7151182</v>
+        <v>7151195</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14366,18 +14309,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -14396,10 +14333,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120079810</v>
+        <v>120094170</v>
       </c>
       <c r="B129" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14408,41 +14345,44 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>746645</v>
+        <v>746562</v>
       </c>
       <c r="R129" t="n">
-        <v>7151221</v>
+        <v>7151492</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14480,28 +14420,29 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120086241</v>
+        <v>120086299</v>
       </c>
       <c r="B130" t="n">
-        <v>91826</v>
+        <v>91858</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14510,25 +14451,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14538,10 +14479,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>746383</v>
+        <v>746314</v>
       </c>
       <c r="R130" t="n">
-        <v>7151288</v>
+        <v>7151238</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14600,10 +14541,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120094338</v>
+        <v>120080357</v>
       </c>
       <c r="B131" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14612,41 +14553,38 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>746451</v>
+        <v>746301</v>
       </c>
       <c r="R131" t="n">
-        <v>7151341</v>
+        <v>7151209</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14687,29 +14625,28 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120086247</v>
+        <v>120086243</v>
       </c>
       <c r="B132" t="n">
-        <v>91884</v>
+        <v>91481</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14722,21 +14659,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14746,10 +14683,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>746385</v>
+        <v>746316</v>
       </c>
       <c r="R132" t="n">
-        <v>7151299</v>
+        <v>7151209</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14808,10 +14745,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120094170</v>
+        <v>120086284</v>
       </c>
       <c r="B133" t="n">
-        <v>91840</v>
+        <v>78542</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14820,41 +14757,38 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>746562</v>
+        <v>746563</v>
       </c>
       <c r="R133" t="n">
-        <v>7151492</v>
+        <v>7151464</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14895,7 +14829,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14914,10 +14847,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120080334</v>
+        <v>120094266</v>
       </c>
       <c r="B134" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14947,21 +14880,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>746537</v>
+        <v>746491</v>
       </c>
       <c r="R134" t="n">
-        <v>7151303</v>
+        <v>7151452</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15002,28 +14934,29 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120094266</v>
+        <v>120094276</v>
       </c>
       <c r="B135" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15063,10 +14996,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>746491</v>
+        <v>746476</v>
       </c>
       <c r="R135" t="n">
-        <v>7151452</v>
+        <v>7151446</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15126,10 +15059,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120086288</v>
+        <v>120094241</v>
       </c>
       <c r="B136" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15138,38 +15071,41 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>746630</v>
+        <v>746515</v>
       </c>
       <c r="R136" t="n">
-        <v>7151524</v>
+        <v>7151443</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15210,6 +15146,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -15228,10 +15165,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120086260</v>
+        <v>120094777</v>
       </c>
       <c r="B137" t="n">
-        <v>91832</v>
+        <v>91902</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15244,34 +15181,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>746378</v>
+        <v>746478</v>
       </c>
       <c r="R137" t="n">
-        <v>7151283</v>
+        <v>7151377</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15312,6 +15252,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -15330,10 +15271,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120094241</v>
+        <v>120080310</v>
       </c>
       <c r="B138" t="n">
-        <v>91840</v>
+        <v>91839</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15342,25 +15283,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15373,10 +15314,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>746515</v>
+        <v>746772</v>
       </c>
       <c r="R138" t="n">
-        <v>7151443</v>
+        <v>7151182</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15411,6 +15352,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -15424,22 +15370,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120080355</v>
+        <v>120086232</v>
       </c>
       <c r="B139" t="n">
-        <v>91840</v>
+        <v>89650</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15448,25 +15394,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15476,10 +15422,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>746527</v>
+        <v>746551</v>
       </c>
       <c r="R139" t="n">
-        <v>7151203</v>
+        <v>7151485</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15526,22 +15472,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120086264</v>
+        <v>120080291</v>
       </c>
       <c r="B140" t="n">
-        <v>92030</v>
+        <v>91272</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15550,38 +15496,42 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2079</v>
+        <v>3298</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>746539</v>
+        <v>746393</v>
       </c>
       <c r="R140" t="n">
-        <v>7151522</v>
+        <v>7151288</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15616,6 +15566,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Basen av levande gran</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15624,26 +15579,41 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120079807</v>
+        <v>120086241</v>
       </c>
       <c r="B141" t="n">
-        <v>57421</v>
+        <v>91844</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15652,49 +15622,41 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103031</v>
+        <v>3100</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>746368</v>
+        <v>746383</v>
       </c>
       <c r="R141" t="n">
-        <v>7151283</v>
+        <v>7151288</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15738,22 +15700,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120086271</v>
+        <v>120094359</v>
       </c>
       <c r="B142" t="n">
-        <v>57421</v>
+        <v>91858</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15766,31 +15728,26 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -15798,10 +15755,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>746500</v>
+        <v>746451</v>
       </c>
       <c r="R142" t="n">
-        <v>7151560</v>
+        <v>7151341</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15842,6 +15799,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15860,10 +15818,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120080297</v>
+        <v>120086306</v>
       </c>
       <c r="B143" t="n">
-        <v>57463</v>
+        <v>91852</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15876,43 +15834,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>746612</v>
+        <v>746371</v>
       </c>
       <c r="R143" t="n">
-        <v>7151234</v>
+        <v>7151274</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15959,22 +15908,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120086287</v>
+        <v>120086267</v>
       </c>
       <c r="B144" t="n">
-        <v>78526</v>
+        <v>91881</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15987,21 +15936,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16011,10 +15960,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>746567</v>
+        <v>746492</v>
       </c>
       <c r="R144" t="n">
-        <v>7151554</v>
+        <v>7151446</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16073,10 +16022,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120094677</v>
+        <v>120086290</v>
       </c>
       <c r="B145" t="n">
-        <v>91840</v>
+        <v>78542</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16085,41 +16034,38 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>746351</v>
+        <v>746657</v>
       </c>
       <c r="R145" t="n">
-        <v>7151225</v>
+        <v>7151562</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16160,7 +16106,6 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -16179,10 +16124,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120094483</v>
+        <v>120080297</v>
       </c>
       <c r="B146" t="n">
-        <v>91834</v>
+        <v>57473</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16195,37 +16140,43 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4362</v>
+        <v>103021</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>746321</v>
+        <v>746612</v>
       </c>
       <c r="R146" t="n">
-        <v>7151245</v>
+        <v>7151234</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16266,29 +16217,28 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120094591</v>
+        <v>120086235</v>
       </c>
       <c r="B147" t="n">
-        <v>91834</v>
+        <v>89650</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16301,37 +16251,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>746294</v>
+        <v>746515</v>
       </c>
       <c r="R147" t="n">
-        <v>7151228</v>
+        <v>7151568</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16372,7 +16319,6 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -16391,10 +16337,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120086253</v>
+        <v>120086264</v>
       </c>
       <c r="B148" t="n">
-        <v>91844</v>
+        <v>92048</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16403,25 +16349,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4365</v>
+        <v>2079</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16493,10 +16439,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120086252</v>
+        <v>120086253</v>
       </c>
       <c r="B149" t="n">
-        <v>91844</v>
+        <v>91862</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16533,10 +16479,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>746575</v>
+        <v>746539</v>
       </c>
       <c r="R149" t="n">
-        <v>7151485</v>
+        <v>7151522</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16595,10 +16541,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120079815</v>
+        <v>120094305</v>
       </c>
       <c r="B150" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16629,19 +16575,22 @@
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>746896</v>
+        <v>746472</v>
       </c>
       <c r="R150" t="n">
-        <v>7151149</v>
+        <v>7151410</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16679,28 +16628,29 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120086281</v>
+        <v>120080333</v>
       </c>
       <c r="B151" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16709,38 +16659,42 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>746371</v>
+        <v>746569</v>
       </c>
       <c r="R151" t="n">
-        <v>7151235</v>
+        <v>7151265</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16775,6 +16729,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Minst, stort mycel</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
@@ -16787,22 +16746,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120086289</v>
+        <v>120086247</v>
       </c>
       <c r="B152" t="n">
-        <v>78526</v>
+        <v>91902</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16815,21 +16774,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16839,10 +16798,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>746670</v>
+        <v>746385</v>
       </c>
       <c r="R152" t="n">
-        <v>7151555</v>
+        <v>7151299</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16901,10 +16860,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120080303</v>
+        <v>120086234</v>
       </c>
       <c r="B153" t="n">
-        <v>91886</v>
+        <v>89650</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16913,42 +16872,38 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>232140</v>
+        <v>1962</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>746331</v>
+        <v>746539</v>
       </c>
       <c r="R153" t="n">
-        <v>7151256</v>
+        <v>7151522</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16983,11 +16938,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Under tunn äldre tallgren på mager, torr mark</t>
-        </is>
-      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -17000,22 +16950,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120094190</v>
+        <v>120080359</v>
       </c>
       <c r="B154" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17028,37 +16978,38 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>746572</v>
+        <v>746291</v>
       </c>
       <c r="R154" t="n">
-        <v>7151479</v>
+        <v>7151137</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17099,29 +17050,28 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120080296</v>
+        <v>120086281</v>
       </c>
       <c r="B155" t="n">
-        <v>57463</v>
+        <v>78542</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17134,42 +17084,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>746527</v>
+        <v>746371</v>
       </c>
       <c r="R155" t="n">
-        <v>7151199</v>
+        <v>7151235</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17216,22 +17158,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120086249</v>
+        <v>120086289</v>
       </c>
       <c r="B156" t="n">
-        <v>91884</v>
+        <v>78542</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17244,21 +17186,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17268,10 +17210,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>746568</v>
+        <v>746670</v>
       </c>
       <c r="R156" t="n">
-        <v>7151535</v>
+        <v>7151555</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17330,10 +17272,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120086234</v>
+        <v>120086270</v>
       </c>
       <c r="B157" t="n">
-        <v>89633</v>
+        <v>57431</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17342,38 +17284,50 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1962</v>
+        <v>103031</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>746539</v>
+        <v>746671</v>
       </c>
       <c r="R157" t="n">
-        <v>7151522</v>
+        <v>7151554</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17432,10 +17386,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120086262</v>
+        <v>120086256</v>
       </c>
       <c r="B158" t="n">
-        <v>91832</v>
+        <v>91870</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17444,25 +17398,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17472,10 +17426,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>746555</v>
+        <v>746576</v>
       </c>
       <c r="R158" t="n">
-        <v>7151590</v>
+        <v>7151444</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17534,10 +17488,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120086244</v>
+        <v>120080335</v>
       </c>
       <c r="B159" t="n">
-        <v>91828</v>
+        <v>91858</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17546,38 +17500,42 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>149</v>
+        <v>4364</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>746576</v>
+        <v>746321</v>
       </c>
       <c r="R159" t="n">
-        <v>7151444</v>
+        <v>7151233</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17624,22 +17582,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120086268</v>
+        <v>120080334</v>
       </c>
       <c r="B160" t="n">
-        <v>91863</v>
+        <v>91858</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17648,38 +17606,42 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>746563</v>
+        <v>746537</v>
       </c>
       <c r="R160" t="n">
-        <v>7151464</v>
+        <v>7151303</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17726,22 +17688,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120086299</v>
+        <v>120080309</v>
       </c>
       <c r="B161" t="n">
-        <v>91840</v>
+        <v>57336</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17750,38 +17712,43 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>746314</v>
+        <v>746663</v>
       </c>
       <c r="R161" t="n">
-        <v>7151238</v>
+        <v>7151255</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17816,6 +17783,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Äldre födohack i basen</t>
+        </is>
+      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
@@ -17824,26 +17796,41 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120086283</v>
+        <v>120094292</v>
       </c>
       <c r="B162" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17852,38 +17839,41 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>746566</v>
+        <v>746478</v>
       </c>
       <c r="R162" t="n">
-        <v>7151468</v>
+        <v>7151421</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17924,6 +17914,7 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -17942,10 +17933,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120086237</v>
+        <v>120080355</v>
       </c>
       <c r="B163" t="n">
-        <v>89275</v>
+        <v>91858</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17954,25 +17945,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17982,10 +17973,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>746561</v>
+        <v>746527</v>
       </c>
       <c r="R163" t="n">
-        <v>7151472</v>
+        <v>7151203</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18032,22 +18023,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120086231</v>
+        <v>120080296</v>
       </c>
       <c r="B164" t="n">
-        <v>90527</v>
+        <v>57473</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18056,38 +18047,46 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>746676</v>
+        <v>746527</v>
       </c>
       <c r="R164" t="n">
-        <v>7151534</v>
+        <v>7151199</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18134,22 +18133,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120079811</v>
+        <v>120080303</v>
       </c>
       <c r="B165" t="n">
-        <v>90807</v>
+        <v>91904</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18162,37 +18161,41 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>65</v>
+        <v>232140</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>746751</v>
+        <v>746331</v>
       </c>
       <c r="R165" t="n">
-        <v>7151208</v>
+        <v>7151256</v>
       </c>
       <c r="S165" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18224,35 +18227,39 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Under tunn äldre tallgren på mager, torr mark</t>
+        </is>
+      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120086256</v>
+        <v>120094102</v>
       </c>
       <c r="B166" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18265,34 +18272,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>746576</v>
+        <v>746539</v>
       </c>
       <c r="R166" t="n">
-        <v>7151444</v>
+        <v>7151513</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18333,6 +18343,7 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -18351,10 +18362,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120086254</v>
+        <v>120086257</v>
       </c>
       <c r="B167" t="n">
-        <v>91844</v>
+        <v>91870</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18363,25 +18374,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18391,10 +18402,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>746678</v>
+        <v>746575</v>
       </c>
       <c r="R167" t="n">
-        <v>7151537</v>
+        <v>7151554</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18453,10 +18464,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120086235</v>
+        <v>120086271</v>
       </c>
       <c r="B168" t="n">
-        <v>89633</v>
+        <v>57431</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18465,38 +18476,46 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1962</v>
+        <v>103031</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>746515</v>
+        <v>746500</v>
       </c>
       <c r="R168" t="n">
-        <v>7151568</v>
+        <v>7151560</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18555,10 +18574,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120086261</v>
+        <v>120086283</v>
       </c>
       <c r="B169" t="n">
-        <v>91832</v>
+        <v>78542</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18571,21 +18590,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18595,10 +18614,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>746574</v>
+        <v>746566</v>
       </c>
       <c r="R169" t="n">
-        <v>7151495</v>
+        <v>7151468</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18657,10 +18676,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120079803</v>
+        <v>120086237</v>
       </c>
       <c r="B170" t="n">
-        <v>91844</v>
+        <v>89292</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18673,21 +18692,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4365</v>
+        <v>6286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18697,13 +18716,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>746316</v>
+        <v>746561</v>
       </c>
       <c r="R170" t="n">
-        <v>7151248</v>
+        <v>7151472</v>
       </c>
       <c r="S170" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18747,22 +18766,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120080335</v>
+        <v>120086286</v>
       </c>
       <c r="B171" t="n">
-        <v>91840</v>
+        <v>78542</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18771,42 +18790,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>746321</v>
+        <v>746555</v>
       </c>
       <c r="R171" t="n">
-        <v>7151233</v>
+        <v>7151578</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18853,22 +18868,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120086284</v>
+        <v>120080352</v>
       </c>
       <c r="B172" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18877,25 +18892,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18905,10 +18920,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>746563</v>
+        <v>746834</v>
       </c>
       <c r="R172" t="n">
-        <v>7151464</v>
+        <v>7151121</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18955,22 +18970,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>120079814</v>
+        <v>120079816</v>
       </c>
       <c r="B173" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18979,25 +18994,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19007,10 +19022,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>746510</v>
+        <v>746534</v>
       </c>
       <c r="R173" t="n">
-        <v>7151225</v>
+        <v>7151288</v>
       </c>
       <c r="S173" t="n">
         <v>15</v>
@@ -19069,10 +19084,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120086251</v>
+        <v>120079815</v>
       </c>
       <c r="B174" t="n">
-        <v>91844</v>
+        <v>91858</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19081,25 +19096,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19109,13 +19124,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>746297</v>
+        <v>746896</v>
       </c>
       <c r="R174" t="n">
-        <v>7151200</v>
+        <v>7151149</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19159,22 +19174,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120080331</v>
+        <v>120086293</v>
       </c>
       <c r="B175" t="n">
-        <v>78526</v>
+        <v>78187</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19187,21 +19202,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19211,10 +19226,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>746936</v>
+        <v>746636</v>
       </c>
       <c r="R175" t="n">
-        <v>7151139</v>
+        <v>7151518</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19249,11 +19264,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
-        </is>
-      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
@@ -19262,41 +19272,26 @@
       </c>
       <c r="AG175" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120086301</v>
+        <v>120086303</v>
       </c>
       <c r="B176" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19333,10 +19328,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>746566</v>
+        <v>746555</v>
       </c>
       <c r="R176" t="n">
-        <v>7151468</v>
+        <v>7151578</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19395,10 +19390,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120080354</v>
+        <v>120079801</v>
       </c>
       <c r="B177" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19407,25 +19402,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19435,13 +19430,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>746559</v>
+        <v>746598</v>
       </c>
       <c r="R177" t="n">
-        <v>7151216</v>
+        <v>7151227</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19479,28 +19474,29 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120086285</v>
+        <v>120079811</v>
       </c>
       <c r="B178" t="n">
-        <v>78526</v>
+        <v>90825</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19509,25 +19505,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19537,13 +19533,13 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>746576</v>
+        <v>746751</v>
       </c>
       <c r="R178" t="n">
-        <v>7151476</v>
+        <v>7151208</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19581,28 +19577,29 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120079808</v>
+        <v>120086262</v>
       </c>
       <c r="B179" t="n">
-        <v>90576</v>
+        <v>91850</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19615,21 +19612,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1204</v>
+        <v>4361</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19639,13 +19636,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>746668</v>
+        <v>746555</v>
       </c>
       <c r="R179" t="n">
-        <v>7151253</v>
+        <v>7151590</v>
       </c>
       <c r="S179" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19689,22 +19686,22 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120086304</v>
+        <v>120080332</v>
       </c>
       <c r="B180" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19734,17 +19731,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>746589</v>
+        <v>746560</v>
       </c>
       <c r="R180" t="n">
-        <v>7151537</v>
+        <v>7151291</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19791,22 +19792,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120086300</v>
+        <v>120080353</v>
       </c>
       <c r="B181" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19843,10 +19844,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>746381</v>
+        <v>746577</v>
       </c>
       <c r="R181" t="n">
-        <v>7151336</v>
+        <v>7151220</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19893,22 +19894,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120080332</v>
+        <v>120086304</v>
       </c>
       <c r="B182" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19938,21 +19939,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>746560</v>
+        <v>746589</v>
       </c>
       <c r="R182" t="n">
-        <v>7151291</v>
+        <v>7151537</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19999,22 +19996,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120080333</v>
+        <v>120086300</v>
       </c>
       <c r="B183" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20044,21 +20041,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>746569</v>
+        <v>746381</v>
       </c>
       <c r="R183" t="n">
-        <v>7151265</v>
+        <v>7151336</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20093,11 +20086,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>Minst, stort mycel</t>
-        </is>
-      </c>
       <c r="AD183" t="b">
         <v>0</v>
       </c>
@@ -20110,22 +20098,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120086270</v>
+        <v>120086261</v>
       </c>
       <c r="B184" t="n">
-        <v>57421</v>
+        <v>91850</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20134,50 +20122,38 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>103031</v>
+        <v>4361</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>746671</v>
+        <v>746574</v>
       </c>
       <c r="R184" t="n">
-        <v>7151554</v>
+        <v>7151495</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20236,10 +20212,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120086293</v>
+        <v>120079799</v>
       </c>
       <c r="B185" t="n">
-        <v>78171</v>
+        <v>90580</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20252,21 +20228,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20276,13 +20252,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>746636</v>
+        <v>746840</v>
       </c>
       <c r="R185" t="n">
-        <v>7151518</v>
+        <v>7151151</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -20326,22 +20302,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120086306</v>
+        <v>120086287</v>
       </c>
       <c r="B186" t="n">
-        <v>91834</v>
+        <v>78542</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20354,21 +20330,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20378,10 +20354,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>746371</v>
+        <v>746567</v>
       </c>
       <c r="R186" t="n">
-        <v>7151274</v>
+        <v>7151554</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20440,10 +20416,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120080358</v>
+        <v>120080331</v>
       </c>
       <c r="B187" t="n">
-        <v>91840</v>
+        <v>78542</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20452,25 +20428,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20480,10 +20456,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>746699</v>
+        <v>746936</v>
       </c>
       <c r="R187" t="n">
-        <v>7151240</v>
+        <v>7151139</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20518,6 +20494,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
+        </is>
+      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
@@ -20526,6 +20507,21 @@
       </c>
       <c r="AG187" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
@@ -20542,10 +20538,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120080352</v>
+        <v>120094677</v>
       </c>
       <c r="B188" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20576,16 +20572,19 @@
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>746834</v>
+        <v>746351</v>
       </c>
       <c r="R188" t="n">
-        <v>7151121</v>
+        <v>7151225</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20626,28 +20625,29 @@
       <c r="AE188" t="b">
         <v>0</v>
       </c>
+      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120094371</v>
+        <v>120086307</v>
       </c>
       <c r="B189" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20656,41 +20656,38 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>746383</v>
+        <v>746483</v>
       </c>
       <c r="R189" t="n">
-        <v>7151297</v>
+        <v>7151420</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20731,7 +20728,6 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
-      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -20750,10 +20746,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>120086290</v>
+        <v>120094591</v>
       </c>
       <c r="B190" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20766,34 +20762,37 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>746657</v>
+        <v>746294</v>
       </c>
       <c r="R190" t="n">
-        <v>7151562</v>
+        <v>7151228</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20834,6 +20833,7 @@
       <c r="AE190" t="b">
         <v>0</v>
       </c>
+      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
@@ -20852,10 +20852,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>120086282</v>
+        <v>120086244</v>
       </c>
       <c r="B191" t="n">
-        <v>78526</v>
+        <v>91846</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20864,25 +20864,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>149</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20892,10 +20892,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>746368</v>
+        <v>746576</v>
       </c>
       <c r="R191" t="n">
-        <v>7151288</v>
+        <v>7151444</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20954,10 +20954,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>120079816</v>
+        <v>120086285</v>
       </c>
       <c r="B192" t="n">
-        <v>91834</v>
+        <v>78542</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20970,21 +20970,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20994,13 +20994,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>746534</v>
+        <v>746576</v>
       </c>
       <c r="R192" t="n">
-        <v>7151288</v>
+        <v>7151476</v>
       </c>
       <c r="S192" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21044,22 +21044,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>120256310</v>
+        <v>120256287</v>
       </c>
       <c r="B193" t="n">
-        <v>91856</v>
+        <v>91858</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21068,25 +21068,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -21180,10 +21180,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>120256082</v>
+        <v>120256409</v>
       </c>
       <c r="B194" t="n">
-        <v>91840</v>
+        <v>91879</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21196,21 +21196,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4364</v>
+        <v>5964</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -21231,10 +21231,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>746608</v>
+        <v>746483</v>
       </c>
       <c r="R194" t="n">
-        <v>7151217</v>
+        <v>7151210</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21276,7 +21276,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21304,10 +21304,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>120256105</v>
+        <v>120256310</v>
       </c>
       <c r="B195" t="n">
-        <v>91840</v>
+        <v>91874</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21316,25 +21316,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -21355,10 +21355,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>746595</v>
+        <v>746490</v>
       </c>
       <c r="R195" t="n">
-        <v>7151214</v>
+        <v>7151210</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -21390,7 +21390,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21400,7 +21400,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21428,10 +21428,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>120256409</v>
+        <v>120256146</v>
       </c>
       <c r="B196" t="n">
-        <v>91861</v>
+        <v>91858</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21444,21 +21444,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -21479,10 +21479,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>746483</v>
+        <v>746617</v>
       </c>
       <c r="R196" t="n">
-        <v>7151210</v>
+        <v>7151234</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21552,10 +21552,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>120256184</v>
+        <v>120256251</v>
       </c>
       <c r="B197" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21603,10 +21603,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>746540</v>
+        <v>746516</v>
       </c>
       <c r="R197" t="n">
-        <v>7151228</v>
+        <v>7151220</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -21636,19 +21636,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21676,10 +21666,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>120256026</v>
+        <v>120256082</v>
       </c>
       <c r="B198" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21688,25 +21678,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -21727,10 +21717,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>746595</v>
+        <v>746608</v>
       </c>
       <c r="R198" t="n">
-        <v>7151275</v>
+        <v>7151217</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -21762,7 +21752,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21772,7 +21762,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21800,10 +21790,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>120256212</v>
+        <v>120256105</v>
       </c>
       <c r="B199" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21851,10 +21841,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>746530</v>
+        <v>746595</v>
       </c>
       <c r="R199" t="n">
-        <v>7151223</v>
+        <v>7151214</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -21886,7 +21876,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21896,7 +21886,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21924,10 +21914,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>120256251</v>
+        <v>120256026</v>
       </c>
       <c r="B200" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21936,25 +21926,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -21975,10 +21965,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>746516</v>
+        <v>746595</v>
       </c>
       <c r="R200" t="n">
-        <v>7151220</v>
+        <v>7151275</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -22008,9 +21998,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22038,10 +22038,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>120256146</v>
+        <v>120256184</v>
       </c>
       <c r="B201" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22089,10 +22089,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>746617</v>
+        <v>746540</v>
       </c>
       <c r="R201" t="n">
-        <v>7151234</v>
+        <v>7151228</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -22124,7 +22124,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22162,10 +22162,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>120256287</v>
+        <v>120256212</v>
       </c>
       <c r="B202" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22213,10 +22213,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>746490</v>
+        <v>746530</v>
       </c>
       <c r="R202" t="n">
-        <v>7151210</v>
+        <v>7151223</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -22248,7 +22248,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22258,7 +22258,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD202" t="b">

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -8072,10 +8072,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120061458</v>
+        <v>120061860</v>
       </c>
       <c r="B71" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8084,25 +8084,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746495</v>
+        <v>746423</v>
       </c>
       <c r="R71" t="n">
-        <v>7151424</v>
+        <v>7151350</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8184,10 +8184,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120061860</v>
+        <v>120061458</v>
       </c>
       <c r="B72" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8196,25 +8196,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746423</v>
+        <v>746495</v>
       </c>
       <c r="R72" t="n">
-        <v>7151350</v>
+        <v>7151424</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10200,10 +10200,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120064407</v>
+        <v>120063487</v>
       </c>
       <c r="B90" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10212,25 +10212,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10240,10 +10240,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>746440</v>
+        <v>746300</v>
       </c>
       <c r="R90" t="n">
-        <v>7151291</v>
+        <v>7151231</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
@@ -10275,7 +10275,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10312,7 +10312,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120062963</v>
+        <v>120064407</v>
       </c>
       <c r="B91" t="n">
         <v>91858</v>
@@ -10352,10 +10352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>746369</v>
+        <v>746440</v>
       </c>
       <c r="R91" t="n">
-        <v>7151279</v>
+        <v>7151291</v>
       </c>
       <c r="S91" t="n">
         <v>1</v>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10424,10 +10424,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120063487</v>
+        <v>120062963</v>
       </c>
       <c r="B92" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10436,25 +10436,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>746300</v>
+        <v>746369</v>
       </c>
       <c r="R92" t="n">
-        <v>7151231</v>
+        <v>7151279</v>
       </c>
       <c r="S92" t="n">
         <v>1</v>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10536,10 +10536,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120059956</v>
+        <v>120063439</v>
       </c>
       <c r="B93" t="n">
-        <v>91850</v>
+        <v>91846</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10548,25 +10548,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>746535</v>
+        <v>746303</v>
       </c>
       <c r="R93" t="n">
-        <v>7151537</v>
+        <v>7151241</v>
       </c>
       <c r="S93" t="n">
         <v>1</v>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10648,10 +10648,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120062389</v>
+        <v>120059956</v>
       </c>
       <c r="B94" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10660,25 +10660,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>746426</v>
+        <v>746535</v>
       </c>
       <c r="R94" t="n">
-        <v>7151309</v>
+        <v>7151537</v>
       </c>
       <c r="S94" t="n">
         <v>1</v>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10760,10 +10760,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120063439</v>
+        <v>120062389</v>
       </c>
       <c r="B95" t="n">
-        <v>91846</v>
+        <v>91858</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10772,25 +10772,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>149</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10800,10 +10800,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>746303</v>
+        <v>746426</v>
       </c>
       <c r="R95" t="n">
-        <v>7151241</v>
+        <v>7151309</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11198,10 +11198,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120080330</v>
+        <v>120086308</v>
       </c>
       <c r="B99" t="n">
-        <v>90730</v>
+        <v>91852</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11210,25 +11210,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1503</v>
+        <v>4362</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11238,10 +11238,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>746624</v>
+        <v>746492</v>
       </c>
       <c r="R99" t="n">
-        <v>7151217</v>
+        <v>7151446</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11276,11 +11276,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Nedbruten tallåga, kollekt taget</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -11289,41 +11284,26 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120086308</v>
+        <v>120094137</v>
       </c>
       <c r="B100" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11332,38 +11312,41 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>746492</v>
+        <v>746535</v>
       </c>
       <c r="R100" t="n">
-        <v>7151446</v>
+        <v>7151504</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11404,6 +11387,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11422,10 +11406,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120094137</v>
+        <v>120086254</v>
       </c>
       <c r="B101" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11434,41 +11418,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>746535</v>
+        <v>746678</v>
       </c>
       <c r="R101" t="n">
-        <v>7151504</v>
+        <v>7151537</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11509,7 +11490,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11528,10 +11508,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120086254</v>
+        <v>120080328</v>
       </c>
       <c r="B102" t="n">
-        <v>91862</v>
+        <v>89981</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11540,25 +11520,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4365</v>
+        <v>5685</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11568,10 +11548,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>746678</v>
+        <v>746590</v>
       </c>
       <c r="R102" t="n">
-        <v>7151537</v>
+        <v>7151225</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11615,25 +11595,40 @@
       <c r="AG102" t="b">
         <v>0</v>
       </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120080328</v>
+        <v>120079807</v>
       </c>
       <c r="B103" t="n">
-        <v>89981</v>
+        <v>57431</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11646,37 +11641,45 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5685</v>
+        <v>103031</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>746590</v>
+        <v>746368</v>
       </c>
       <c r="R103" t="n">
-        <v>7151225</v>
+        <v>7151283</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11716,41 +11719,26 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120079807</v>
+        <v>120079798</v>
       </c>
       <c r="B104" t="n">
-        <v>57431</v>
+        <v>89650</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11759,46 +11747,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103031</v>
+        <v>1962</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>746368</v>
+        <v>746310</v>
       </c>
       <c r="R104" t="n">
-        <v>7151283</v>
+        <v>7151135</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11857,10 +11837,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120079798</v>
+        <v>120086273</v>
       </c>
       <c r="B105" t="n">
-        <v>89650</v>
+        <v>90730</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11869,25 +11849,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11897,13 +11877,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>746310</v>
+        <v>746551</v>
       </c>
       <c r="R105" t="n">
-        <v>7151135</v>
+        <v>7151485</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11947,22 +11927,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120086273</v>
+        <v>120086301</v>
       </c>
       <c r="B106" t="n">
-        <v>90730</v>
+        <v>91858</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11971,25 +11951,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11999,10 +11979,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>746551</v>
+        <v>746566</v>
       </c>
       <c r="R106" t="n">
-        <v>7151485</v>
+        <v>7151468</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12061,10 +12041,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120086301</v>
+        <v>120079803</v>
       </c>
       <c r="B107" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12073,25 +12053,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12101,13 +12081,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>746566</v>
+        <v>746316</v>
       </c>
       <c r="R107" t="n">
-        <v>7151468</v>
+        <v>7151248</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12151,22 +12131,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120079803</v>
+        <v>120079814</v>
       </c>
       <c r="B108" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12175,25 +12155,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12203,10 +12183,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>746316</v>
+        <v>746510</v>
       </c>
       <c r="R108" t="n">
-        <v>7151248</v>
+        <v>7151225</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -12265,10 +12245,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120079814</v>
+        <v>120080308</v>
       </c>
       <c r="B109" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12277,25 +12257,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12305,13 +12285,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>746510</v>
+        <v>746368</v>
       </c>
       <c r="R109" t="n">
-        <v>7151225</v>
+        <v>7151279</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12355,22 +12335,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120080308</v>
+        <v>120079810</v>
       </c>
       <c r="B110" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12383,21 +12363,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12407,13 +12387,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>746368</v>
+        <v>746645</v>
       </c>
       <c r="R110" t="n">
-        <v>7151279</v>
+        <v>7151221</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12457,22 +12437,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120079810</v>
+        <v>120086252</v>
       </c>
       <c r="B111" t="n">
-        <v>78542</v>
+        <v>91862</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12481,25 +12461,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12509,13 +12489,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>746645</v>
+        <v>746575</v>
       </c>
       <c r="R111" t="n">
-        <v>7151221</v>
+        <v>7151485</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12559,22 +12539,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120086252</v>
+        <v>120094483</v>
       </c>
       <c r="B112" t="n">
-        <v>91862</v>
+        <v>91852</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12583,38 +12563,41 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>746575</v>
+        <v>746321</v>
       </c>
       <c r="R112" t="n">
-        <v>7151485</v>
+        <v>7151245</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12655,6 +12638,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12673,10 +12657,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120094483</v>
+        <v>120080354</v>
       </c>
       <c r="B113" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12685,41 +12669,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>746321</v>
+        <v>746559</v>
       </c>
       <c r="R113" t="n">
-        <v>7151245</v>
+        <v>7151216</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12760,29 +12741,28 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120080354</v>
+        <v>120086249</v>
       </c>
       <c r="B114" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12791,25 +12771,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12819,10 +12799,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>746559</v>
+        <v>746568</v>
       </c>
       <c r="R114" t="n">
-        <v>7151216</v>
+        <v>7151535</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12869,22 +12849,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120086249</v>
+        <v>120086239</v>
       </c>
       <c r="B115" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12897,34 +12877,46 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>746568</v>
+        <v>746532</v>
       </c>
       <c r="R115" t="n">
-        <v>7151535</v>
+        <v>7151493</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12983,10 +12975,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120086239</v>
+        <v>120094371</v>
       </c>
       <c r="B116" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12995,39 +12987,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -13035,10 +13018,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>746532</v>
+        <v>746383</v>
       </c>
       <c r="R116" t="n">
-        <v>7151493</v>
+        <v>7151297</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13079,6 +13062,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13097,10 +13081,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120094371</v>
+        <v>120086268</v>
       </c>
       <c r="B117" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13109,41 +13093,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>746383</v>
+        <v>746563</v>
       </c>
       <c r="R117" t="n">
-        <v>7151297</v>
+        <v>7151464</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13184,7 +13165,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13203,10 +13183,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120086268</v>
+        <v>120086282</v>
       </c>
       <c r="B118" t="n">
-        <v>91881</v>
+        <v>78542</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13219,21 +13199,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13243,10 +13223,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>746563</v>
+        <v>746368</v>
       </c>
       <c r="R118" t="n">
-        <v>7151464</v>
+        <v>7151288</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13305,10 +13285,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120086282</v>
+        <v>120086248</v>
       </c>
       <c r="B119" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13321,21 +13301,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13345,10 +13325,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>746368</v>
+        <v>746537</v>
       </c>
       <c r="R119" t="n">
-        <v>7151288</v>
+        <v>7151592</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13407,10 +13387,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120086260</v>
+        <v>120086231</v>
       </c>
       <c r="B120" t="n">
-        <v>91850</v>
+        <v>90545</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13419,25 +13399,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13447,10 +13427,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>746378</v>
+        <v>746676</v>
       </c>
       <c r="R120" t="n">
-        <v>7151283</v>
+        <v>7151534</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13611,10 +13591,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120079808</v>
+        <v>120086260</v>
       </c>
       <c r="B122" t="n">
-        <v>90594</v>
+        <v>91850</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13627,21 +13607,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1204</v>
+        <v>4361</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13651,13 +13631,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>746668</v>
+        <v>746378</v>
       </c>
       <c r="R122" t="n">
-        <v>7151253</v>
+        <v>7151283</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13701,22 +13681,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120086248</v>
+        <v>120079808</v>
       </c>
       <c r="B123" t="n">
-        <v>91902</v>
+        <v>90594</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13729,21 +13709,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5449</v>
+        <v>1204</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13753,13 +13733,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>746537</v>
+        <v>746668</v>
       </c>
       <c r="R123" t="n">
-        <v>7151592</v>
+        <v>7151253</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13803,22 +13783,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120086231</v>
+        <v>120086284</v>
       </c>
       <c r="B124" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13827,25 +13807,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13855,10 +13835,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>746676</v>
+        <v>746563</v>
       </c>
       <c r="R124" t="n">
-        <v>7151534</v>
+        <v>7151464</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13917,10 +13897,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120094190</v>
+        <v>120080358</v>
       </c>
       <c r="B125" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13929,41 +13909,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>746572</v>
+        <v>746699</v>
       </c>
       <c r="R125" t="n">
-        <v>7151479</v>
+        <v>7151240</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14004,29 +13981,28 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120094355</v>
+        <v>120080356</v>
       </c>
       <c r="B126" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14035,41 +14011,38 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>746451</v>
+        <v>746499</v>
       </c>
       <c r="R126" t="n">
-        <v>7151341</v>
+        <v>7151195</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14110,26 +14083,25 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120080358</v>
+        <v>120094170</v>
       </c>
       <c r="B127" t="n">
         <v>91858</v>
@@ -14163,16 +14135,19 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>746699</v>
+        <v>746562</v>
       </c>
       <c r="R127" t="n">
-        <v>7151240</v>
+        <v>7151492</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14213,25 +14188,26 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120080356</v>
+        <v>120086299</v>
       </c>
       <c r="B128" t="n">
         <v>91858</v>
@@ -14271,10 +14247,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>746499</v>
+        <v>746314</v>
       </c>
       <c r="R128" t="n">
-        <v>7151195</v>
+        <v>7151238</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14321,19 +14297,19 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120094170</v>
+        <v>120080357</v>
       </c>
       <c r="B129" t="n">
         <v>91858</v>
@@ -14367,19 +14343,16 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>746562</v>
+        <v>746301</v>
       </c>
       <c r="R129" t="n">
-        <v>7151492</v>
+        <v>7151209</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14420,29 +14393,28 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120086299</v>
+        <v>120086243</v>
       </c>
       <c r="B130" t="n">
-        <v>91858</v>
+        <v>91481</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14451,25 +14423,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14479,10 +14451,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>746314</v>
+        <v>746316</v>
       </c>
       <c r="R130" t="n">
-        <v>7151238</v>
+        <v>7151209</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14541,10 +14513,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120080357</v>
+        <v>120094190</v>
       </c>
       <c r="B131" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14553,38 +14525,41 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>746301</v>
+        <v>746572</v>
       </c>
       <c r="R131" t="n">
-        <v>7151209</v>
+        <v>7151479</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14625,28 +14600,29 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120086243</v>
+        <v>120094355</v>
       </c>
       <c r="B132" t="n">
-        <v>91481</v>
+        <v>91902</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14659,34 +14635,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>746316</v>
+        <v>746451</v>
       </c>
       <c r="R132" t="n">
-        <v>7151209</v>
+        <v>7151341</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14727,6 +14706,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14745,10 +14725,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120086284</v>
+        <v>120094266</v>
       </c>
       <c r="B133" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14757,38 +14737,41 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>746563</v>
+        <v>746491</v>
       </c>
       <c r="R133" t="n">
-        <v>7151464</v>
+        <v>7151452</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14829,6 +14812,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14847,7 +14831,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120094266</v>
+        <v>120094276</v>
       </c>
       <c r="B134" t="n">
         <v>91858</v>
@@ -14890,10 +14874,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>746491</v>
+        <v>746476</v>
       </c>
       <c r="R134" t="n">
-        <v>7151452</v>
+        <v>7151446</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14953,7 +14937,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120094276</v>
+        <v>120094241</v>
       </c>
       <c r="B135" t="n">
         <v>91858</v>
@@ -14996,10 +14980,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>746476</v>
+        <v>746515</v>
       </c>
       <c r="R135" t="n">
-        <v>7151446</v>
+        <v>7151443</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15059,10 +15043,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120094241</v>
+        <v>120094777</v>
       </c>
       <c r="B136" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15071,25 +15055,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15102,10 +15086,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>746515</v>
+        <v>746478</v>
       </c>
       <c r="R136" t="n">
-        <v>7151443</v>
+        <v>7151377</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15165,10 +15149,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120094777</v>
+        <v>120080310</v>
       </c>
       <c r="B137" t="n">
-        <v>91902</v>
+        <v>91839</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15177,25 +15161,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5449</v>
+        <v>6055</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15208,10 +15192,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>746478</v>
+        <v>746772</v>
       </c>
       <c r="R137" t="n">
-        <v>7151377</v>
+        <v>7151182</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15246,6 +15230,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat</t>
+        </is>
+      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
@@ -15259,22 +15248,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120080310</v>
+        <v>120086232</v>
       </c>
       <c r="B138" t="n">
-        <v>91839</v>
+        <v>89650</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15283,41 +15272,38 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6055</v>
+        <v>1962</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>746772</v>
+        <v>746551</v>
       </c>
       <c r="R138" t="n">
-        <v>7151182</v>
+        <v>7151485</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15352,40 +15338,34 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120086232</v>
+        <v>120080291</v>
       </c>
       <c r="B139" t="n">
-        <v>89650</v>
+        <v>91272</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15394,38 +15374,42 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1962</v>
+        <v>3298</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>746551</v>
+        <v>746393</v>
       </c>
       <c r="R139" t="n">
-        <v>7151485</v>
+        <v>7151288</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15460,6 +15444,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Basen av levande gran</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15468,26 +15457,41 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120080291</v>
+        <v>120086241</v>
       </c>
       <c r="B140" t="n">
-        <v>91272</v>
+        <v>91844</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15496,39 +15500,35 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3298</v>
+        <v>3100</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>746393</v>
+        <v>746383</v>
       </c>
       <c r="R140" t="n">
         <v>7151288</v>
@@ -15566,11 +15566,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Basen av levande gran</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15579,41 +15574,26 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120086241</v>
+        <v>120086290</v>
       </c>
       <c r="B141" t="n">
-        <v>91844</v>
+        <v>78542</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15626,21 +15606,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3100</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15650,10 +15630,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>746383</v>
+        <v>746657</v>
       </c>
       <c r="R141" t="n">
-        <v>7151288</v>
+        <v>7151562</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16022,10 +16002,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120086290</v>
+        <v>120086235</v>
       </c>
       <c r="B145" t="n">
-        <v>78542</v>
+        <v>89650</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16038,21 +16018,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16062,10 +16042,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>746657</v>
+        <v>746515</v>
       </c>
       <c r="R145" t="n">
-        <v>7151562</v>
+        <v>7151568</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16124,10 +16104,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120080297</v>
+        <v>120086264</v>
       </c>
       <c r="B146" t="n">
-        <v>57473</v>
+        <v>92048</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16140,43 +16120,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>746612</v>
+        <v>746539</v>
       </c>
       <c r="R146" t="n">
-        <v>7151234</v>
+        <v>7151522</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16223,22 +16194,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120086235</v>
+        <v>120086253</v>
       </c>
       <c r="B147" t="n">
-        <v>89650</v>
+        <v>91862</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16247,25 +16218,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16275,10 +16246,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>746515</v>
+        <v>746539</v>
       </c>
       <c r="R147" t="n">
-        <v>7151568</v>
+        <v>7151522</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16337,10 +16308,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120086264</v>
+        <v>120094305</v>
       </c>
       <c r="B148" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16349,38 +16320,41 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>746539</v>
+        <v>746472</v>
       </c>
       <c r="R148" t="n">
-        <v>7151522</v>
+        <v>7151410</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16421,6 +16395,7 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -16439,10 +16414,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120086253</v>
+        <v>120080333</v>
       </c>
       <c r="B149" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16451,38 +16426,42 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>746539</v>
+        <v>746569</v>
       </c>
       <c r="R149" t="n">
-        <v>7151522</v>
+        <v>7151265</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16517,6 +16496,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Minst, stort mycel</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
@@ -16529,22 +16513,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120094305</v>
+        <v>120080297</v>
       </c>
       <c r="B150" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16553,41 +16537,47 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>746472</v>
+        <v>746612</v>
       </c>
       <c r="R150" t="n">
-        <v>7151410</v>
+        <v>7151234</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16628,29 +16618,28 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120080333</v>
+        <v>120086247</v>
       </c>
       <c r="B151" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16659,42 +16648,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>746569</v>
+        <v>746385</v>
       </c>
       <c r="R151" t="n">
-        <v>7151265</v>
+        <v>7151299</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16729,11 +16714,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Minst, stort mycel</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
@@ -16746,22 +16726,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120086247</v>
+        <v>120086234</v>
       </c>
       <c r="B152" t="n">
-        <v>91902</v>
+        <v>89650</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16774,21 +16754,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16798,10 +16778,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>746385</v>
+        <v>746539</v>
       </c>
       <c r="R152" t="n">
-        <v>7151299</v>
+        <v>7151522</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16860,10 +16840,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120086234</v>
+        <v>120080359</v>
       </c>
       <c r="B153" t="n">
-        <v>89650</v>
+        <v>91852</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16876,34 +16856,38 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>746539</v>
+        <v>746291</v>
       </c>
       <c r="R153" t="n">
-        <v>7151522</v>
+        <v>7151137</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16950,22 +16934,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120080359</v>
+        <v>120086281</v>
       </c>
       <c r="B154" t="n">
-        <v>91852</v>
+        <v>78542</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16978,38 +16962,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>746291</v>
+        <v>746371</v>
       </c>
       <c r="R154" t="n">
-        <v>7151137</v>
+        <v>7151235</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17056,19 +17036,19 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120086281</v>
+        <v>120086289</v>
       </c>
       <c r="B155" t="n">
         <v>78542</v>
@@ -17108,10 +17088,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>746371</v>
+        <v>746670</v>
       </c>
       <c r="R155" t="n">
-        <v>7151235</v>
+        <v>7151555</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17170,10 +17150,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120086289</v>
+        <v>120080309</v>
       </c>
       <c r="B156" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17186,34 +17166,39 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>746670</v>
+        <v>746663</v>
       </c>
       <c r="R156" t="n">
-        <v>7151555</v>
+        <v>7151255</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17248,6 +17233,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Äldre födohack i basen</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
@@ -17256,26 +17246,41 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120086270</v>
+        <v>120086256</v>
       </c>
       <c r="B157" t="n">
-        <v>57431</v>
+        <v>91870</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17288,46 +17293,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>103031</v>
+        <v>4366</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>746671</v>
+        <v>746576</v>
       </c>
       <c r="R157" t="n">
-        <v>7151554</v>
+        <v>7151444</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17386,10 +17379,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120086256</v>
+        <v>120080335</v>
       </c>
       <c r="B158" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17402,34 +17395,38 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>746576</v>
+        <v>746321</v>
       </c>
       <c r="R158" t="n">
-        <v>7151444</v>
+        <v>7151233</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17476,19 +17473,19 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120080335</v>
+        <v>120080334</v>
       </c>
       <c r="B159" t="n">
         <v>91858</v>
@@ -17523,7 +17520,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -17532,10 +17529,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>746321</v>
+        <v>746537</v>
       </c>
       <c r="R159" t="n">
-        <v>7151233</v>
+        <v>7151303</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17594,10 +17591,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120080334</v>
+        <v>120086270</v>
       </c>
       <c r="B160" t="n">
-        <v>91858</v>
+        <v>57431</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17610,38 +17607,46 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>746537</v>
+        <v>746671</v>
       </c>
       <c r="R160" t="n">
-        <v>7151303</v>
+        <v>7151554</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17688,22 +17693,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120080309</v>
+        <v>120080296</v>
       </c>
       <c r="B161" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17716,39 +17721,42 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>746663</v>
+        <v>746527</v>
       </c>
       <c r="R161" t="n">
-        <v>7151255</v>
+        <v>7151199</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17783,11 +17791,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Äldre födohack i basen</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
@@ -17796,21 +17799,6 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
@@ -18035,10 +18023,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120080296</v>
+        <v>120080303</v>
       </c>
       <c r="B164" t="n">
-        <v>57473</v>
+        <v>91904</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18047,46 +18035,42 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>103021</v>
+        <v>232140</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>746527</v>
+        <v>746331</v>
       </c>
       <c r="R164" t="n">
-        <v>7151199</v>
+        <v>7151256</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18119,6 +18103,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Under tunn äldre tallgren på mager, torr mark</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18145,10 +18134,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120080303</v>
+        <v>120094102</v>
       </c>
       <c r="B165" t="n">
-        <v>91904</v>
+        <v>91858</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18157,42 +18146,41 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>746331</v>
+        <v>746539</v>
       </c>
       <c r="R165" t="n">
-        <v>7151256</v>
+        <v>7151513</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18227,39 +18215,35 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Under tunn äldre tallgren på mager, torr mark</t>
-        </is>
-      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120094102</v>
+        <v>120086257</v>
       </c>
       <c r="B166" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18272,37 +18256,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>746539</v>
+        <v>746575</v>
       </c>
       <c r="R166" t="n">
-        <v>7151513</v>
+        <v>7151554</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18343,7 +18324,6 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -18362,10 +18342,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120086257</v>
+        <v>120086271</v>
       </c>
       <c r="B167" t="n">
-        <v>91870</v>
+        <v>57431</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18378,34 +18358,42 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4366</v>
+        <v>103031</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>746575</v>
+        <v>746500</v>
       </c>
       <c r="R167" t="n">
-        <v>7151554</v>
+        <v>7151560</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18464,10 +18452,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120086271</v>
+        <v>120086283</v>
       </c>
       <c r="B168" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18476,46 +18464,38 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>746500</v>
+        <v>746566</v>
       </c>
       <c r="R168" t="n">
-        <v>7151560</v>
+        <v>7151468</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18574,10 +18554,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120086283</v>
+        <v>120086237</v>
       </c>
       <c r="B169" t="n">
-        <v>78542</v>
+        <v>89292</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18586,25 +18566,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18614,10 +18594,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>746566</v>
+        <v>746561</v>
       </c>
       <c r="R169" t="n">
-        <v>7151468</v>
+        <v>7151472</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18676,10 +18656,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120086237</v>
+        <v>120086286</v>
       </c>
       <c r="B170" t="n">
-        <v>89292</v>
+        <v>78542</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18688,25 +18668,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6286</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18716,10 +18696,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>746561</v>
+        <v>746555</v>
       </c>
       <c r="R170" t="n">
-        <v>7151472</v>
+        <v>7151578</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18778,10 +18758,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120086286</v>
+        <v>120080352</v>
       </c>
       <c r="B171" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18790,25 +18770,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18818,10 +18798,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>746555</v>
+        <v>746834</v>
       </c>
       <c r="R171" t="n">
-        <v>7151578</v>
+        <v>7151121</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18868,22 +18848,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120080352</v>
+        <v>120079816</v>
       </c>
       <c r="B172" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18892,25 +18872,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18920,13 +18900,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>746834</v>
+        <v>746534</v>
       </c>
       <c r="R172" t="n">
-        <v>7151121</v>
+        <v>7151288</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18970,22 +18950,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>120079816</v>
+        <v>120079815</v>
       </c>
       <c r="B173" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18994,25 +18974,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19022,10 +19002,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>746534</v>
+        <v>746896</v>
       </c>
       <c r="R173" t="n">
-        <v>7151288</v>
+        <v>7151149</v>
       </c>
       <c r="S173" t="n">
         <v>15</v>
@@ -19084,10 +19064,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120079815</v>
+        <v>120086293</v>
       </c>
       <c r="B174" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19096,25 +19076,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19124,13 +19104,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>746896</v>
+        <v>746636</v>
       </c>
       <c r="R174" t="n">
-        <v>7151149</v>
+        <v>7151518</v>
       </c>
       <c r="S174" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19174,22 +19154,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120086293</v>
+        <v>120086303</v>
       </c>
       <c r="B175" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19198,25 +19178,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19226,10 +19206,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>746636</v>
+        <v>746555</v>
       </c>
       <c r="R175" t="n">
-        <v>7151518</v>
+        <v>7151578</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19288,10 +19268,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120086303</v>
+        <v>120079801</v>
       </c>
       <c r="B176" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19300,25 +19280,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19328,13 +19308,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>746555</v>
+        <v>746598</v>
       </c>
       <c r="R176" t="n">
-        <v>7151578</v>
+        <v>7151227</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19372,28 +19352,29 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120079801</v>
+        <v>120080353</v>
       </c>
       <c r="B177" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19402,25 +19383,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19430,13 +19411,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>746598</v>
+        <v>746577</v>
       </c>
       <c r="R177" t="n">
-        <v>7151227</v>
+        <v>7151220</v>
       </c>
       <c r="S177" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19474,29 +19455,28 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120079811</v>
+        <v>120086304</v>
       </c>
       <c r="B178" t="n">
-        <v>90825</v>
+        <v>91858</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19505,25 +19485,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19533,13 +19513,13 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>746751</v>
+        <v>746589</v>
       </c>
       <c r="R178" t="n">
-        <v>7151208</v>
+        <v>7151537</v>
       </c>
       <c r="S178" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19577,29 +19557,28 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120086262</v>
+        <v>120086300</v>
       </c>
       <c r="B179" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19608,25 +19587,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19636,10 +19615,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>746555</v>
+        <v>746381</v>
       </c>
       <c r="R179" t="n">
-        <v>7151590</v>
+        <v>7151336</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19698,10 +19677,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120080332</v>
+        <v>120079811</v>
       </c>
       <c r="B180" t="n">
-        <v>91858</v>
+        <v>90825</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19710,45 +19689,41 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>746560</v>
+        <v>746751</v>
       </c>
       <c r="R180" t="n">
-        <v>7151291</v>
+        <v>7151208</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19786,28 +19761,29 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
+      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120080353</v>
+        <v>120086262</v>
       </c>
       <c r="B181" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19816,25 +19792,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19844,10 +19820,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>746577</v>
+        <v>746555</v>
       </c>
       <c r="R181" t="n">
-        <v>7151220</v>
+        <v>7151590</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19894,19 +19870,19 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120086304</v>
+        <v>120080332</v>
       </c>
       <c r="B182" t="n">
         <v>91858</v>
@@ -19939,17 +19915,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>746589</v>
+        <v>746560</v>
       </c>
       <c r="R182" t="n">
-        <v>7151537</v>
+        <v>7151291</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19996,22 +19976,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120086300</v>
+        <v>120079799</v>
       </c>
       <c r="B183" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20020,25 +20000,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20048,13 +20028,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>746381</v>
+        <v>746840</v>
       </c>
       <c r="R183" t="n">
-        <v>7151336</v>
+        <v>7151151</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20098,12 +20078,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -20212,10 +20192,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120079799</v>
+        <v>120086287</v>
       </c>
       <c r="B185" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20228,21 +20208,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20252,13 +20232,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>746840</v>
+        <v>746567</v>
       </c>
       <c r="R185" t="n">
-        <v>7151151</v>
+        <v>7151554</v>
       </c>
       <c r="S185" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -20302,19 +20282,19 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120086287</v>
+        <v>120080331</v>
       </c>
       <c r="B186" t="n">
         <v>78542</v>
@@ -20354,10 +20334,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>746567</v>
+        <v>746936</v>
       </c>
       <c r="R186" t="n">
-        <v>7151554</v>
+        <v>7151139</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20392,6 +20372,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
+        </is>
+      </c>
       <c r="AD186" t="b">
         <v>0</v>
       </c>
@@ -20400,26 +20385,41 @@
       </c>
       <c r="AG186" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120080331</v>
+        <v>120094677</v>
       </c>
       <c r="B187" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20428,38 +20428,41 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>746936</v>
+        <v>746351</v>
       </c>
       <c r="R187" t="n">
-        <v>7151139</v>
+        <v>7151225</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20494,54 +20497,35 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
-        </is>
-      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
       <c r="AE187" t="b">
         <v>0</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ187" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK187" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO187" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120094677</v>
+        <v>120086307</v>
       </c>
       <c r="B188" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20550,41 +20534,38 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>746351</v>
+        <v>746483</v>
       </c>
       <c r="R188" t="n">
-        <v>7151225</v>
+        <v>7151420</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20625,7 +20606,6 @@
       <c r="AE188" t="b">
         <v>0</v>
       </c>
-      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
@@ -20644,7 +20624,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120086307</v>
+        <v>120094591</v>
       </c>
       <c r="B189" t="n">
         <v>91852</v>
@@ -20678,16 +20658,19 @@
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>746483</v>
+        <v>746294</v>
       </c>
       <c r="R189" t="n">
-        <v>7151420</v>
+        <v>7151228</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20728,6 +20711,7 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -20746,10 +20730,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>120094591</v>
+        <v>120086244</v>
       </c>
       <c r="B190" t="n">
-        <v>91852</v>
+        <v>91846</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20758,41 +20742,38 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>746294</v>
+        <v>746576</v>
       </c>
       <c r="R190" t="n">
-        <v>7151228</v>
+        <v>7151444</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20833,7 +20814,6 @@
       <c r="AE190" t="b">
         <v>0</v>
       </c>
-      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
@@ -20852,10 +20832,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>120086244</v>
+        <v>120086285</v>
       </c>
       <c r="B191" t="n">
-        <v>91846</v>
+        <v>78542</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20864,25 +20844,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>149</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20895,7 +20875,7 @@
         <v>746576</v>
       </c>
       <c r="R191" t="n">
-        <v>7151444</v>
+        <v>7151476</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20954,10 +20934,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>120086285</v>
+        <v>120256287</v>
       </c>
       <c r="B192" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20966,41 +20946,52 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>746576</v>
+        <v>746490</v>
       </c>
       <c r="R192" t="n">
-        <v>7151476</v>
+        <v>7151210</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21027,39 +21018,50 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AD192" t="b">
         <v>0</v>
       </c>
       <c r="AE192" t="b">
         <v>0</v>
       </c>
+      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>120256287</v>
+        <v>120256409</v>
       </c>
       <c r="B193" t="n">
-        <v>91858</v>
+        <v>91879</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21072,21 +21074,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4364</v>
+        <v>5964</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -21107,7 +21109,7 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>746490</v>
+        <v>746483</v>
       </c>
       <c r="R193" t="n">
         <v>7151210</v>
@@ -21142,7 +21144,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21152,7 +21154,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21180,10 +21182,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>120256409</v>
+        <v>120256310</v>
       </c>
       <c r="B194" t="n">
-        <v>91879</v>
+        <v>91874</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21192,25 +21194,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>5964</v>
+        <v>2059</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -21231,7 +21233,7 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>746483</v>
+        <v>746490</v>
       </c>
       <c r="R194" t="n">
         <v>7151210</v>
@@ -21266,7 +21268,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21276,7 +21278,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21304,10 +21306,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>120256310</v>
+        <v>120256146</v>
       </c>
       <c r="B195" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21316,25 +21318,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -21355,10 +21357,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>746490</v>
+        <v>746617</v>
       </c>
       <c r="R195" t="n">
-        <v>7151210</v>
+        <v>7151234</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -21390,7 +21392,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21400,7 +21402,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21428,7 +21430,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>120256146</v>
+        <v>120256251</v>
       </c>
       <c r="B196" t="n">
         <v>91858</v>
@@ -21479,10 +21481,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>746617</v>
+        <v>746516</v>
       </c>
       <c r="R196" t="n">
-        <v>7151234</v>
+        <v>7151220</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -21512,19 +21514,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>13:24</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21552,7 +21544,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>120256251</v>
+        <v>120256082</v>
       </c>
       <c r="B197" t="n">
         <v>91858</v>
@@ -21603,10 +21595,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>746516</v>
+        <v>746608</v>
       </c>
       <c r="R197" t="n">
-        <v>7151220</v>
+        <v>7151217</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -21636,9 +21628,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21666,7 +21668,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>120256082</v>
+        <v>120256105</v>
       </c>
       <c r="B198" t="n">
         <v>91858</v>
@@ -21717,10 +21719,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>746608</v>
+        <v>746595</v>
       </c>
       <c r="R198" t="n">
-        <v>7151217</v>
+        <v>7151214</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -21752,7 +21754,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21762,7 +21764,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21790,10 +21792,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>120256105</v>
+        <v>120256026</v>
       </c>
       <c r="B199" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21802,25 +21804,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -21844,7 +21846,7 @@
         <v>746595</v>
       </c>
       <c r="R199" t="n">
-        <v>7151214</v>
+        <v>7151275</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -21876,7 +21878,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21886,7 +21888,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21914,10 +21916,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>120256026</v>
+        <v>120256184</v>
       </c>
       <c r="B200" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21926,25 +21928,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -21965,10 +21967,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>746595</v>
+        <v>746540</v>
       </c>
       <c r="R200" t="n">
-        <v>7151275</v>
+        <v>7151228</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -22000,7 +22002,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22010,7 +22012,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22038,7 +22040,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>120256184</v>
+        <v>120256212</v>
       </c>
       <c r="B201" t="n">
         <v>91858</v>
@@ -22089,10 +22091,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>746540</v>
+        <v>746530</v>
       </c>
       <c r="R201" t="n">
-        <v>7151228</v>
+        <v>7151223</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -22124,7 +22126,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22134,7 +22136,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22162,10 +22164,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>120256212</v>
+        <v>120080330</v>
       </c>
       <c r="B202" t="n">
-        <v>91858</v>
+        <v>90848</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22174,37 +22176,29 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4364</v>
+        <v>71</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Renvall &amp; Niemelä) Audet</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
@@ -22213,13 +22207,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>746530</v>
+        <v>746624</v>
       </c>
       <c r="R202" t="n">
-        <v>7151223</v>
+        <v>7151217</v>
       </c>
       <c r="S202" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22246,19 +22240,14 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>13:16</t>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Nedbruten tallåga, kollekt taget. Mikroskoperat och artbestämt till Urskogsporing</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22271,15 +22260,30 @@
       <c r="AG202" t="b">
         <v>0</v>
       </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Roger Olofsson, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY202"/>
+  <dimension ref="A1:AY201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7176,10 +7176,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120062185</v>
+        <v>120063671</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7188,25 +7188,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746401</v>
+        <v>746309</v>
       </c>
       <c r="R63" t="n">
-        <v>7151292</v>
+        <v>7151221</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7288,7 +7288,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120063693</v>
+        <v>120064681</v>
       </c>
       <c r="B64" t="n">
         <v>91858</v>
@@ -7324,14 +7324,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vintjärnen, Vintjärnen, Vb</t>
+          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746319</v>
+        <v>746535</v>
       </c>
       <c r="R64" t="n">
-        <v>7151210</v>
+        <v>7151171</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7400,10 +7400,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120063728</v>
+        <v>120059872</v>
       </c>
       <c r="B65" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7412,25 +7412,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746298</v>
+        <v>746557</v>
       </c>
       <c r="R65" t="n">
-        <v>7151222</v>
+        <v>7151556</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7512,7 +7512,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120063442</v>
+        <v>120062963</v>
       </c>
       <c r="B66" t="n">
         <v>91858</v>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746297</v>
+        <v>746369</v>
       </c>
       <c r="R66" t="n">
-        <v>7151223</v>
+        <v>7151279</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120061233</v>
+        <v>120059794</v>
       </c>
       <c r="B67" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7640,21 +7640,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7664,10 +7664,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746597</v>
+        <v>746567</v>
       </c>
       <c r="R67" t="n">
-        <v>7151440</v>
+        <v>7151566</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7736,10 +7736,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120063671</v>
+        <v>120063287</v>
       </c>
       <c r="B68" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7752,21 +7752,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746309</v>
+        <v>746369</v>
       </c>
       <c r="R68" t="n">
-        <v>7151221</v>
+        <v>7151254</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7848,10 +7848,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120064725</v>
+        <v>120063551</v>
       </c>
       <c r="B69" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7860,41 +7860,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
+          <t>Vintjärnen, Vintjärnen, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746535</v>
+        <v>746308</v>
       </c>
       <c r="R69" t="n">
-        <v>7151171</v>
+        <v>7151219</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7948,19 +7948,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120061645</v>
+        <v>120059683</v>
       </c>
       <c r="B70" t="n">
         <v>91902</v>
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746450</v>
+        <v>746569</v>
       </c>
       <c r="R70" t="n">
-        <v>7151380</v>
+        <v>7151549</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8072,7 +8072,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120061860</v>
+        <v>120061583</v>
       </c>
       <c r="B71" t="n">
         <v>91858</v>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746423</v>
+        <v>746472</v>
       </c>
       <c r="R71" t="n">
-        <v>7151350</v>
+        <v>7151401</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8184,10 +8184,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120061458</v>
+        <v>120062389</v>
       </c>
       <c r="B72" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8196,25 +8196,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746495</v>
+        <v>746426</v>
       </c>
       <c r="R72" t="n">
-        <v>7151424</v>
+        <v>7151309</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8296,10 +8296,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120062338</v>
+        <v>120063439</v>
       </c>
       <c r="B73" t="n">
-        <v>91858</v>
+        <v>91846</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8308,25 +8308,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>149</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8336,10 +8336,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746390</v>
+        <v>746303</v>
       </c>
       <c r="R73" t="n">
-        <v>7151301</v>
+        <v>7151241</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8408,7 +8408,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120061583</v>
+        <v>120059636</v>
       </c>
       <c r="B74" t="n">
         <v>91858</v>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746472</v>
+        <v>746602</v>
       </c>
       <c r="R74" t="n">
-        <v>7151401</v>
+        <v>7151535</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8520,10 +8520,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120062274</v>
+        <v>120063442</v>
       </c>
       <c r="B75" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8532,25 +8532,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746394</v>
+        <v>746297</v>
       </c>
       <c r="R75" t="n">
-        <v>7151307</v>
+        <v>7151223</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8632,10 +8632,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120063551</v>
+        <v>120061645</v>
       </c>
       <c r="B76" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8648,21 +8648,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746308</v>
+        <v>746450</v>
       </c>
       <c r="R76" t="n">
-        <v>7151219</v>
+        <v>7151380</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8744,10 +8744,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120059872</v>
+        <v>120061458</v>
       </c>
       <c r="B77" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8756,25 +8756,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746557</v>
+        <v>746495</v>
       </c>
       <c r="R77" t="n">
-        <v>7151556</v>
+        <v>7151424</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8968,10 +8968,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120059794</v>
+        <v>120061607</v>
       </c>
       <c r="B79" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8984,21 +8984,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746567</v>
+        <v>746453</v>
       </c>
       <c r="R79" t="n">
-        <v>7151566</v>
+        <v>7151408</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9080,7 +9080,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120059683</v>
+        <v>120062274</v>
       </c>
       <c r="B80" t="n">
         <v>91902</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746569</v>
+        <v>746394</v>
       </c>
       <c r="R80" t="n">
-        <v>7151549</v>
+        <v>7151307</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9192,10 +9192,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120060888</v>
+        <v>120063963</v>
       </c>
       <c r="B81" t="n">
-        <v>96891</v>
+        <v>91858</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9208,21 +9208,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746566</v>
+        <v>746301</v>
       </c>
       <c r="R81" t="n">
-        <v>7151484</v>
+        <v>7151207</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9304,10 +9304,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120059636</v>
+        <v>120063728</v>
       </c>
       <c r="B82" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9316,25 +9316,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746602</v>
+        <v>746298</v>
       </c>
       <c r="R82" t="n">
-        <v>7151535</v>
+        <v>7151222</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9416,10 +9416,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120061607</v>
+        <v>120061725</v>
       </c>
       <c r="B83" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9432,21 +9432,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>746453</v>
+        <v>746444</v>
       </c>
       <c r="R83" t="n">
-        <v>7151408</v>
+        <v>7151382</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9528,10 +9528,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120061725</v>
+        <v>120061860</v>
       </c>
       <c r="B84" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9540,25 +9540,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9568,10 +9568,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746444</v>
+        <v>746423</v>
       </c>
       <c r="R84" t="n">
-        <v>7151382</v>
+        <v>7151350</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9640,10 +9640,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120063963</v>
+        <v>120061686</v>
       </c>
       <c r="B85" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9652,25 +9652,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9680,10 +9680,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746301</v>
+        <v>746448</v>
       </c>
       <c r="R85" t="n">
-        <v>7151207</v>
+        <v>7151388</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9752,10 +9752,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120061534</v>
+        <v>120059956</v>
       </c>
       <c r="B86" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9764,25 +9764,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9792,10 +9792,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>746467</v>
+        <v>746535</v>
       </c>
       <c r="R86" t="n">
-        <v>7151403</v>
+        <v>7151537</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9864,7 +9864,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120061247</v>
+        <v>120061534</v>
       </c>
       <c r="B87" t="n">
         <v>91858</v>
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>746541</v>
+        <v>746467</v>
       </c>
       <c r="R87" t="n">
-        <v>7151441</v>
+        <v>7151403</v>
       </c>
       <c r="S87" t="n">
         <v>1</v>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9976,10 +9976,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120063383</v>
+        <v>120064407</v>
       </c>
       <c r="B88" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9988,25 +9988,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>746303</v>
+        <v>746440</v>
       </c>
       <c r="R88" t="n">
-        <v>7151246</v>
+        <v>7151291</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10088,10 +10088,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120061686</v>
+        <v>120063693</v>
       </c>
       <c r="B89" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10100,25 +10100,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>746448</v>
+        <v>746319</v>
       </c>
       <c r="R89" t="n">
-        <v>7151388</v>
+        <v>7151210</v>
       </c>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10188,12 +10188,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10312,10 +10312,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120064407</v>
+        <v>120063383</v>
       </c>
       <c r="B91" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10324,25 +10324,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10352,10 +10352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>746440</v>
+        <v>746303</v>
       </c>
       <c r="R91" t="n">
-        <v>7151291</v>
+        <v>7151246</v>
       </c>
       <c r="S91" t="n">
         <v>1</v>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10424,10 +10424,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120062963</v>
+        <v>120060888</v>
       </c>
       <c r="B92" t="n">
-        <v>91858</v>
+        <v>96891</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10440,21 +10440,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>746369</v>
+        <v>746566</v>
       </c>
       <c r="R92" t="n">
-        <v>7151279</v>
+        <v>7151484</v>
       </c>
       <c r="S92" t="n">
         <v>1</v>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10536,10 +10536,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120063439</v>
+        <v>120061233</v>
       </c>
       <c r="B93" t="n">
-        <v>91846</v>
+        <v>91850</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10548,25 +10548,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>149</v>
+        <v>4361</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>746303</v>
+        <v>746597</v>
       </c>
       <c r="R93" t="n">
-        <v>7151241</v>
+        <v>7151440</v>
       </c>
       <c r="S93" t="n">
         <v>1</v>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10648,10 +10648,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120059956</v>
+        <v>120062338</v>
       </c>
       <c r="B94" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10660,25 +10660,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>746535</v>
+        <v>746390</v>
       </c>
       <c r="R94" t="n">
-        <v>7151537</v>
+        <v>7151301</v>
       </c>
       <c r="S94" t="n">
         <v>1</v>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10760,7 +10760,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120062389</v>
+        <v>120062185</v>
       </c>
       <c r="B95" t="n">
         <v>91858</v>
@@ -10800,10 +10800,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>746426</v>
+        <v>746401</v>
       </c>
       <c r="R95" t="n">
-        <v>7151309</v>
+        <v>7151292</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10872,10 +10872,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120062044</v>
+        <v>120061247</v>
       </c>
       <c r="B96" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10884,25 +10884,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>746344</v>
+        <v>746541</v>
       </c>
       <c r="R96" t="n">
-        <v>7151353</v>
+        <v>7151441</v>
       </c>
       <c r="S96" t="n">
         <v>1</v>
@@ -10947,7 +10947,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10984,7 +10984,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120063287</v>
+        <v>120062044</v>
       </c>
       <c r="B97" t="n">
         <v>91902</v>
@@ -11024,10 +11024,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>746369</v>
+        <v>746344</v>
       </c>
       <c r="R97" t="n">
-        <v>7151254</v>
+        <v>7151353</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11096,10 +11096,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120086251</v>
+        <v>120086234</v>
       </c>
       <c r="B98" t="n">
-        <v>91862</v>
+        <v>89650</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11108,25 +11108,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11136,10 +11136,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>746297</v>
+        <v>746539</v>
       </c>
       <c r="R98" t="n">
-        <v>7151200</v>
+        <v>7151522</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11198,10 +11198,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120086308</v>
+        <v>120086252</v>
       </c>
       <c r="B99" t="n">
-        <v>91852</v>
+        <v>91862</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11210,25 +11210,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11238,10 +11238,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>746492</v>
+        <v>746575</v>
       </c>
       <c r="R99" t="n">
-        <v>7151446</v>
+        <v>7151485</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11300,7 +11300,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120094137</v>
+        <v>120094292</v>
       </c>
       <c r="B100" t="n">
         <v>91858</v>
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>746535</v>
+        <v>746478</v>
       </c>
       <c r="R100" t="n">
-        <v>7151504</v>
+        <v>7151421</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11406,10 +11406,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120086254</v>
+        <v>120094276</v>
       </c>
       <c r="B101" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11418,38 +11418,41 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>746678</v>
+        <v>746476</v>
       </c>
       <c r="R101" t="n">
-        <v>7151537</v>
+        <v>7151446</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11490,6 +11493,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11508,10 +11512,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120080328</v>
+        <v>120094677</v>
       </c>
       <c r="B102" t="n">
-        <v>89981</v>
+        <v>91858</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11524,31 +11528,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>746590</v>
+        <v>746351</v>
       </c>
       <c r="R102" t="n">
         <v>7151225</v>
@@ -11592,43 +11599,29 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120079807</v>
+        <v>120079815</v>
       </c>
       <c r="B103" t="n">
-        <v>57431</v>
+        <v>91858</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11641,42 +11634,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>746368</v>
+        <v>746896</v>
       </c>
       <c r="R103" t="n">
-        <v>7151283</v>
+        <v>7151149</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11735,10 +11720,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120079798</v>
+        <v>120086304</v>
       </c>
       <c r="B104" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11747,25 +11732,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11775,13 +11760,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>746310</v>
+        <v>746589</v>
       </c>
       <c r="R104" t="n">
-        <v>7151135</v>
+        <v>7151537</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11825,12 +11810,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11939,10 +11924,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120086301</v>
+        <v>120086267</v>
       </c>
       <c r="B106" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11951,25 +11936,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11979,10 +11964,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>746566</v>
+        <v>746492</v>
       </c>
       <c r="R106" t="n">
-        <v>7151468</v>
+        <v>7151446</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12041,10 +12026,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120079803</v>
+        <v>120086249</v>
       </c>
       <c r="B107" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12053,25 +12038,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12081,13 +12066,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>746316</v>
+        <v>746568</v>
       </c>
       <c r="R107" t="n">
-        <v>7151248</v>
+        <v>7151535</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12131,19 +12116,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120079814</v>
+        <v>120080353</v>
       </c>
       <c r="B108" t="n">
         <v>91858</v>
@@ -12183,13 +12168,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>746510</v>
+        <v>746577</v>
       </c>
       <c r="R108" t="n">
-        <v>7151225</v>
+        <v>7151220</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12233,22 +12218,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120080308</v>
+        <v>120086288</v>
       </c>
       <c r="B109" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12261,21 +12246,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12285,10 +12270,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>746368</v>
+        <v>746630</v>
       </c>
       <c r="R109" t="n">
-        <v>7151279</v>
+        <v>7151524</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12335,22 +12320,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120079810</v>
+        <v>120086306</v>
       </c>
       <c r="B110" t="n">
-        <v>78542</v>
+        <v>91852</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12363,21 +12348,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12387,13 +12372,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>746645</v>
+        <v>746371</v>
       </c>
       <c r="R110" t="n">
-        <v>7151221</v>
+        <v>7151274</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12437,22 +12422,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120086252</v>
+        <v>120086282</v>
       </c>
       <c r="B111" t="n">
-        <v>91862</v>
+        <v>78542</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12461,25 +12446,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12489,10 +12474,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>746575</v>
+        <v>746368</v>
       </c>
       <c r="R111" t="n">
-        <v>7151485</v>
+        <v>7151288</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12551,10 +12536,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120094483</v>
+        <v>120086243</v>
       </c>
       <c r="B112" t="n">
-        <v>91852</v>
+        <v>91481</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12567,37 +12552,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>746321</v>
+        <v>746316</v>
       </c>
       <c r="R112" t="n">
-        <v>7151245</v>
+        <v>7151209</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12638,7 +12620,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12657,7 +12638,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120080354</v>
+        <v>120080335</v>
       </c>
       <c r="B113" t="n">
         <v>91858</v>
@@ -12690,17 +12671,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>746559</v>
+        <v>746321</v>
       </c>
       <c r="R113" t="n">
-        <v>7151216</v>
+        <v>7151233</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12759,7 +12744,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120086249</v>
+        <v>120094338</v>
       </c>
       <c r="B114" t="n">
         <v>91902</v>
@@ -12793,16 +12778,19 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>746568</v>
+        <v>746451</v>
       </c>
       <c r="R114" t="n">
-        <v>7151535</v>
+        <v>7151341</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12843,6 +12831,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12861,10 +12850,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120086239</v>
+        <v>120080359</v>
       </c>
       <c r="B115" t="n">
-        <v>57473</v>
+        <v>91852</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12877,46 +12866,38 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>746532</v>
+        <v>746291</v>
       </c>
       <c r="R115" t="n">
-        <v>7151493</v>
+        <v>7151137</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12963,22 +12944,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120094371</v>
+        <v>120086271</v>
       </c>
       <c r="B116" t="n">
-        <v>91858</v>
+        <v>57431</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12991,26 +12972,31 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -13018,10 +13004,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>746383</v>
+        <v>746500</v>
       </c>
       <c r="R116" t="n">
-        <v>7151297</v>
+        <v>7151560</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13062,7 +13048,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13081,10 +13066,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120086268</v>
+        <v>120086232</v>
       </c>
       <c r="B117" t="n">
-        <v>91881</v>
+        <v>89650</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13097,21 +13082,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13121,10 +13106,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>746563</v>
+        <v>746551</v>
       </c>
       <c r="R117" t="n">
-        <v>7151464</v>
+        <v>7151485</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13183,10 +13168,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120086282</v>
+        <v>120086268</v>
       </c>
       <c r="B118" t="n">
-        <v>78542</v>
+        <v>91881</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13199,21 +13184,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13223,10 +13208,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>746368</v>
+        <v>746563</v>
       </c>
       <c r="R118" t="n">
-        <v>7151288</v>
+        <v>7151464</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13285,10 +13270,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120086248</v>
+        <v>120080328</v>
       </c>
       <c r="B119" t="n">
-        <v>91902</v>
+        <v>89981</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13297,25 +13282,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5449</v>
+        <v>5685</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13325,10 +13310,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>746537</v>
+        <v>746590</v>
       </c>
       <c r="R119" t="n">
-        <v>7151592</v>
+        <v>7151225</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13372,25 +13357,40 @@
       <c r="AG119" t="b">
         <v>0</v>
       </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120086231</v>
+        <v>120086286</v>
       </c>
       <c r="B120" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13399,25 +13399,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13427,10 +13427,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>746676</v>
+        <v>746555</v>
       </c>
       <c r="R120" t="n">
-        <v>7151534</v>
+        <v>7151578</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13489,7 +13489,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120086288</v>
+        <v>120086284</v>
       </c>
       <c r="B121" t="n">
         <v>78542</v>
@@ -13529,10 +13529,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>746630</v>
+        <v>746563</v>
       </c>
       <c r="R121" t="n">
-        <v>7151524</v>
+        <v>7151464</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13693,10 +13693,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120079808</v>
+        <v>120080332</v>
       </c>
       <c r="B123" t="n">
-        <v>90594</v>
+        <v>91858</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13705,41 +13705,45 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>746668</v>
+        <v>746560</v>
       </c>
       <c r="R123" t="n">
-        <v>7151253</v>
+        <v>7151291</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13783,22 +13787,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120086284</v>
+        <v>120086239</v>
       </c>
       <c r="B124" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13811,34 +13815,46 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>746563</v>
+        <v>746532</v>
       </c>
       <c r="R124" t="n">
-        <v>7151464</v>
+        <v>7151493</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13897,10 +13913,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120080358</v>
+        <v>120086308</v>
       </c>
       <c r="B125" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13909,25 +13925,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13937,10 +13953,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>746699</v>
+        <v>746492</v>
       </c>
       <c r="R125" t="n">
-        <v>7151240</v>
+        <v>7151446</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13987,22 +14003,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120080356</v>
+        <v>120086261</v>
       </c>
       <c r="B126" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14011,25 +14027,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14039,10 +14055,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>746499</v>
+        <v>746574</v>
       </c>
       <c r="R126" t="n">
-        <v>7151195</v>
+        <v>7151495</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14089,22 +14105,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120094170</v>
+        <v>120094591</v>
       </c>
       <c r="B127" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14113,25 +14129,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14144,10 +14160,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>746562</v>
+        <v>746294</v>
       </c>
       <c r="R127" t="n">
-        <v>7151492</v>
+        <v>7151228</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14207,7 +14223,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120086299</v>
+        <v>120080352</v>
       </c>
       <c r="B128" t="n">
         <v>91858</v>
@@ -14247,10 +14263,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>746314</v>
+        <v>746834</v>
       </c>
       <c r="R128" t="n">
-        <v>7151238</v>
+        <v>7151121</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14297,19 +14313,19 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120080357</v>
+        <v>120080355</v>
       </c>
       <c r="B129" t="n">
         <v>91858</v>
@@ -14349,10 +14365,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>746301</v>
+        <v>746527</v>
       </c>
       <c r="R129" t="n">
-        <v>7151209</v>
+        <v>7151203</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14411,10 +14427,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120086243</v>
+        <v>120080291</v>
       </c>
       <c r="B130" t="n">
-        <v>91481</v>
+        <v>91272</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14423,38 +14439,42 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4745</v>
+        <v>3298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>746316</v>
+        <v>746393</v>
       </c>
       <c r="R130" t="n">
-        <v>7151209</v>
+        <v>7151288</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14489,6 +14509,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Basen av levande gran</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -14497,23 +14522,38 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120094190</v>
+        <v>120079801</v>
       </c>
       <c r="B131" t="n">
         <v>91902</v>
@@ -14547,22 +14587,19 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>746572</v>
+        <v>746598</v>
       </c>
       <c r="R131" t="n">
-        <v>7151479</v>
+        <v>7151227</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14607,22 +14644,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120094355</v>
+        <v>120080303</v>
       </c>
       <c r="B132" t="n">
-        <v>91902</v>
+        <v>91904</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14631,41 +14668,42 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5449</v>
+        <v>232140</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>746451</v>
+        <v>746331</v>
       </c>
       <c r="R132" t="n">
-        <v>7151341</v>
+        <v>7151256</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14700,35 +14738,39 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Under tunn äldre tallgren på mager, torr mark</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120094266</v>
+        <v>120086281</v>
       </c>
       <c r="B133" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14737,41 +14779,38 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>746491</v>
+        <v>746371</v>
       </c>
       <c r="R133" t="n">
-        <v>7151452</v>
+        <v>7151235</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14812,7 +14851,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14831,10 +14869,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120094276</v>
+        <v>120080297</v>
       </c>
       <c r="B134" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14843,41 +14881,47 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>746476</v>
+        <v>746612</v>
       </c>
       <c r="R134" t="n">
-        <v>7151446</v>
+        <v>7151234</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14918,29 +14962,28 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120094241</v>
+        <v>120079807</v>
       </c>
       <c r="B135" t="n">
-        <v>91858</v>
+        <v>57431</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14953,26 +14996,31 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14980,13 +15028,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>746515</v>
+        <v>746368</v>
       </c>
       <c r="R135" t="n">
-        <v>7151443</v>
+        <v>7151283</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15024,29 +15072,28 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120094777</v>
+        <v>120086235</v>
       </c>
       <c r="B136" t="n">
-        <v>91902</v>
+        <v>89650</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15059,37 +15106,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>746478</v>
+        <v>746515</v>
       </c>
       <c r="R136" t="n">
-        <v>7151377</v>
+        <v>7151568</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15130,7 +15174,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -15149,10 +15192,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120080310</v>
+        <v>120086300</v>
       </c>
       <c r="B137" t="n">
-        <v>91839</v>
+        <v>91858</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15161,41 +15204,38 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>746772</v>
+        <v>746381</v>
       </c>
       <c r="R137" t="n">
-        <v>7151182</v>
+        <v>7151336</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15230,40 +15270,34 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat</t>
-        </is>
-      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120086232</v>
+        <v>120086231</v>
       </c>
       <c r="B138" t="n">
-        <v>89650</v>
+        <v>90545</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15272,25 +15306,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1962</v>
+        <v>5447</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15300,10 +15334,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>746551</v>
+        <v>746676</v>
       </c>
       <c r="R138" t="n">
-        <v>7151485</v>
+        <v>7151534</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15362,10 +15396,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120080291</v>
+        <v>120086251</v>
       </c>
       <c r="B139" t="n">
-        <v>91272</v>
+        <v>91862</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15374,42 +15408,38 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3298</v>
+        <v>4365</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>746393</v>
+        <v>746297</v>
       </c>
       <c r="R139" t="n">
-        <v>7151288</v>
+        <v>7151200</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15444,11 +15474,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Basen av levande gran</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15457,41 +15482,26 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120086241</v>
+        <v>120080357</v>
       </c>
       <c r="B140" t="n">
-        <v>91844</v>
+        <v>91858</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15500,25 +15510,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15528,10 +15538,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>746383</v>
+        <v>746301</v>
       </c>
       <c r="R140" t="n">
-        <v>7151288</v>
+        <v>7151209</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15578,22 +15588,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120086290</v>
+        <v>120086241</v>
       </c>
       <c r="B141" t="n">
-        <v>78542</v>
+        <v>91844</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15606,21 +15616,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>3100</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15630,10 +15640,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>746657</v>
+        <v>746383</v>
       </c>
       <c r="R141" t="n">
-        <v>7151562</v>
+        <v>7151288</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15692,10 +15702,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120094359</v>
+        <v>120086307</v>
       </c>
       <c r="B142" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15704,41 +15714,38 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>746451</v>
+        <v>746483</v>
       </c>
       <c r="R142" t="n">
-        <v>7151341</v>
+        <v>7151420</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15779,7 +15786,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15798,10 +15804,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120086306</v>
+        <v>120086283</v>
       </c>
       <c r="B143" t="n">
-        <v>91852</v>
+        <v>78542</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15814,21 +15820,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15838,10 +15844,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>746371</v>
+        <v>746566</v>
       </c>
       <c r="R143" t="n">
-        <v>7151274</v>
+        <v>7151468</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15900,10 +15906,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120086267</v>
+        <v>120079810</v>
       </c>
       <c r="B144" t="n">
-        <v>91881</v>
+        <v>78542</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15916,21 +15922,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15940,13 +15946,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>746492</v>
+        <v>746645</v>
       </c>
       <c r="R144" t="n">
-        <v>7151446</v>
+        <v>7151221</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15990,22 +15996,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120086235</v>
+        <v>120086253</v>
       </c>
       <c r="B145" t="n">
-        <v>89650</v>
+        <v>91862</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16014,25 +16020,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16042,10 +16048,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>746515</v>
+        <v>746539</v>
       </c>
       <c r="R145" t="n">
-        <v>7151568</v>
+        <v>7151522</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16104,10 +16110,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120086264</v>
+        <v>120086301</v>
       </c>
       <c r="B146" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16116,25 +16122,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16144,10 +16150,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>746539</v>
+        <v>746566</v>
       </c>
       <c r="R146" t="n">
-        <v>7151522</v>
+        <v>7151468</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16206,10 +16212,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120086253</v>
+        <v>120086256</v>
       </c>
       <c r="B147" t="n">
-        <v>91862</v>
+        <v>91870</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16218,25 +16224,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16246,10 +16252,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>746539</v>
+        <v>746576</v>
       </c>
       <c r="R147" t="n">
-        <v>7151522</v>
+        <v>7151444</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16414,10 +16420,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120080333</v>
+        <v>120086254</v>
       </c>
       <c r="B149" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16426,42 +16432,38 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>746569</v>
+        <v>746678</v>
       </c>
       <c r="R149" t="n">
-        <v>7151265</v>
+        <v>7151537</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16496,11 +16498,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Minst, stort mycel</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
@@ -16513,22 +16510,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120080297</v>
+        <v>120094241</v>
       </c>
       <c r="B150" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16537,47 +16534,41 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>746612</v>
+        <v>746515</v>
       </c>
       <c r="R150" t="n">
-        <v>7151234</v>
+        <v>7151443</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16618,18 +16609,19 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -16738,10 +16730,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120086234</v>
+        <v>120086289</v>
       </c>
       <c r="B152" t="n">
-        <v>89650</v>
+        <v>78542</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16754,21 +16746,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16778,10 +16770,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>746539</v>
+        <v>746670</v>
       </c>
       <c r="R152" t="n">
-        <v>7151522</v>
+        <v>7151555</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16840,10 +16832,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120080359</v>
+        <v>120080331</v>
       </c>
       <c r="B153" t="n">
-        <v>91852</v>
+        <v>78542</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16856,38 +16848,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>746291</v>
+        <v>746936</v>
       </c>
       <c r="R153" t="n">
-        <v>7151137</v>
+        <v>7151139</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16922,6 +16910,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
+        </is>
+      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -16930,6 +16923,21 @@
       </c>
       <c r="AG153" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
@@ -16946,10 +16954,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120086281</v>
+        <v>120094137</v>
       </c>
       <c r="B154" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16958,38 +16966,41 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>746371</v>
+        <v>746535</v>
       </c>
       <c r="R154" t="n">
-        <v>7151235</v>
+        <v>7151504</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17030,6 +17041,7 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17048,10 +17060,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120086289</v>
+        <v>120094170</v>
       </c>
       <c r="B155" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17060,38 +17072,41 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>746670</v>
+        <v>746562</v>
       </c>
       <c r="R155" t="n">
-        <v>7151555</v>
+        <v>7151492</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17132,6 +17147,7 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -17150,10 +17166,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120080309</v>
+        <v>120094359</v>
       </c>
       <c r="B156" t="n">
-        <v>57336</v>
+        <v>91858</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17162,43 +17178,41 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>746663</v>
+        <v>746451</v>
       </c>
       <c r="R156" t="n">
-        <v>7151255</v>
+        <v>7151341</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17233,54 +17247,35 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Äldre födohack i basen</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120086256</v>
+        <v>120086299</v>
       </c>
       <c r="B157" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17293,21 +17288,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17317,10 +17312,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>746576</v>
+        <v>746314</v>
       </c>
       <c r="R157" t="n">
-        <v>7151444</v>
+        <v>7151238</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17379,10 +17374,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120080335</v>
+        <v>120080296</v>
       </c>
       <c r="B158" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17391,42 +17386,46 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>746321</v>
+        <v>746527</v>
       </c>
       <c r="R158" t="n">
-        <v>7151233</v>
+        <v>7151199</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17485,10 +17484,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120080334</v>
+        <v>120094777</v>
       </c>
       <c r="B159" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17497,42 +17496,41 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>746537</v>
+        <v>746478</v>
       </c>
       <c r="R159" t="n">
-        <v>7151303</v>
+        <v>7151377</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17573,28 +17571,29 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120086270</v>
+        <v>120080310</v>
       </c>
       <c r="B160" t="n">
-        <v>57431</v>
+        <v>91839</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17603,39 +17602,30 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>103031</v>
+        <v>6055</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
@@ -17643,10 +17633,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>746671</v>
+        <v>746772</v>
       </c>
       <c r="R160" t="n">
-        <v>7151554</v>
+        <v>7151182</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17681,34 +17671,40 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120080296</v>
+        <v>120079799</v>
       </c>
       <c r="B161" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17721,45 +17717,37 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>746527</v>
+        <v>746840</v>
       </c>
       <c r="R161" t="n">
-        <v>7151199</v>
+        <v>7151151</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17803,22 +17791,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120094292</v>
+        <v>120094483</v>
       </c>
       <c r="B162" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17827,25 +17815,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17858,10 +17846,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>746478</v>
+        <v>746321</v>
       </c>
       <c r="R162" t="n">
-        <v>7151421</v>
+        <v>7151245</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17921,10 +17909,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120080355</v>
+        <v>120086287</v>
       </c>
       <c r="B163" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17933,25 +17921,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17961,10 +17949,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>746527</v>
+        <v>746567</v>
       </c>
       <c r="R163" t="n">
-        <v>7151203</v>
+        <v>7151554</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18011,22 +17999,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120080303</v>
+        <v>120080356</v>
       </c>
       <c r="B164" t="n">
-        <v>91904</v>
+        <v>91858</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18035,42 +18023,38 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>746331</v>
+        <v>746499</v>
       </c>
       <c r="R164" t="n">
-        <v>7151256</v>
+        <v>7151195</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18103,11 +18087,6 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Under tunn äldre tallgren på mager, torr mark</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18134,7 +18113,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120094102</v>
+        <v>120086303</v>
       </c>
       <c r="B165" t="n">
         <v>91858</v>
@@ -18168,19 +18147,16 @@
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>746539</v>
+        <v>746555</v>
       </c>
       <c r="R165" t="n">
-        <v>7151513</v>
+        <v>7151578</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18221,7 +18197,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -18240,10 +18215,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120086257</v>
+        <v>120080334</v>
       </c>
       <c r="B166" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18256,34 +18231,38 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>746575</v>
+        <v>746537</v>
       </c>
       <c r="R166" t="n">
-        <v>7151554</v>
+        <v>7151303</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18330,22 +18309,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120086271</v>
+        <v>120086248</v>
       </c>
       <c r="B167" t="n">
-        <v>57431</v>
+        <v>91902</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18354,46 +18333,38 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>103031</v>
+        <v>5449</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>746500</v>
+        <v>746537</v>
       </c>
       <c r="R167" t="n">
-        <v>7151560</v>
+        <v>7151592</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18452,10 +18423,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120086283</v>
+        <v>120080308</v>
       </c>
       <c r="B168" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18468,21 +18439,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18492,10 +18463,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>746566</v>
+        <v>746368</v>
       </c>
       <c r="R168" t="n">
-        <v>7151468</v>
+        <v>7151279</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18542,22 +18513,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120086237</v>
+        <v>120094190</v>
       </c>
       <c r="B169" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18566,38 +18537,41 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>746561</v>
+        <v>746572</v>
       </c>
       <c r="R169" t="n">
-        <v>7151472</v>
+        <v>7151479</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18638,6 +18612,7 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -18656,10 +18631,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120086286</v>
+        <v>120079808</v>
       </c>
       <c r="B170" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18672,21 +18647,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18696,13 +18671,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>746555</v>
+        <v>746668</v>
       </c>
       <c r="R170" t="n">
-        <v>7151578</v>
+        <v>7151253</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18746,22 +18721,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120080352</v>
+        <v>120079803</v>
       </c>
       <c r="B171" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18770,25 +18745,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18798,13 +18773,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>746834</v>
+        <v>746316</v>
       </c>
       <c r="R171" t="n">
-        <v>7151121</v>
+        <v>7151248</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18848,22 +18823,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120079816</v>
+        <v>120079798</v>
       </c>
       <c r="B172" t="n">
-        <v>91852</v>
+        <v>89650</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18876,21 +18851,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18900,10 +18875,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>746534</v>
+        <v>746310</v>
       </c>
       <c r="R172" t="n">
-        <v>7151288</v>
+        <v>7151135</v>
       </c>
       <c r="S172" t="n">
         <v>15</v>
@@ -18962,10 +18937,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>120079815</v>
+        <v>120086262</v>
       </c>
       <c r="B173" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18974,25 +18949,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19002,13 +18977,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>746896</v>
+        <v>746555</v>
       </c>
       <c r="R173" t="n">
-        <v>7151149</v>
+        <v>7151590</v>
       </c>
       <c r="S173" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19052,22 +19027,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120086293</v>
+        <v>120080358</v>
       </c>
       <c r="B174" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19076,25 +19051,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19104,10 +19079,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>746636</v>
+        <v>746699</v>
       </c>
       <c r="R174" t="n">
-        <v>7151518</v>
+        <v>7151240</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19154,19 +19129,19 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120086303</v>
+        <v>120080354</v>
       </c>
       <c r="B175" t="n">
         <v>91858</v>
@@ -19206,10 +19181,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>746555</v>
+        <v>746559</v>
       </c>
       <c r="R175" t="n">
-        <v>7151578</v>
+        <v>7151216</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19256,22 +19231,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120079801</v>
+        <v>120086290</v>
       </c>
       <c r="B176" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19284,21 +19259,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19308,13 +19283,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>746598</v>
+        <v>746657</v>
       </c>
       <c r="R176" t="n">
-        <v>7151227</v>
+        <v>7151562</v>
       </c>
       <c r="S176" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19352,26 +19327,25 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120080353</v>
+        <v>120094371</v>
       </c>
       <c r="B177" t="n">
         <v>91858</v>
@@ -19405,16 +19379,19 @@
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>746577</v>
+        <v>746383</v>
       </c>
       <c r="R177" t="n">
-        <v>7151220</v>
+        <v>7151297</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19455,25 +19432,26 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120086304</v>
+        <v>120079814</v>
       </c>
       <c r="B178" t="n">
         <v>91858</v>
@@ -19513,13 +19491,13 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>746589</v>
+        <v>746510</v>
       </c>
       <c r="R178" t="n">
-        <v>7151537</v>
+        <v>7151225</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19563,22 +19541,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120086300</v>
+        <v>120086270</v>
       </c>
       <c r="B179" t="n">
-        <v>91858</v>
+        <v>57431</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19591,34 +19569,46 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>746381</v>
+        <v>746671</v>
       </c>
       <c r="R179" t="n">
-        <v>7151336</v>
+        <v>7151554</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19677,10 +19667,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120079811</v>
+        <v>120086244</v>
       </c>
       <c r="B180" t="n">
-        <v>90825</v>
+        <v>91846</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19693,21 +19683,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19717,13 +19707,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>746751</v>
+        <v>746576</v>
       </c>
       <c r="R180" t="n">
-        <v>7151208</v>
+        <v>7151444</v>
       </c>
       <c r="S180" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19761,29 +19751,28 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
-      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120086262</v>
+        <v>120086293</v>
       </c>
       <c r="B181" t="n">
-        <v>91850</v>
+        <v>78187</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19796,21 +19785,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19820,10 +19809,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>746555</v>
+        <v>746636</v>
       </c>
       <c r="R181" t="n">
-        <v>7151590</v>
+        <v>7151518</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19882,10 +19871,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120080332</v>
+        <v>120086285</v>
       </c>
       <c r="B182" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19894,42 +19883,38 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>746560</v>
+        <v>746576</v>
       </c>
       <c r="R182" t="n">
-        <v>7151291</v>
+        <v>7151476</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19976,22 +19961,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120079799</v>
+        <v>120094266</v>
       </c>
       <c r="B183" t="n">
-        <v>90580</v>
+        <v>91858</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20000,41 +19985,44 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>746840</v>
+        <v>746491</v>
       </c>
       <c r="R183" t="n">
-        <v>7151151</v>
+        <v>7151452</v>
       </c>
       <c r="S183" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20072,28 +20060,29 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120086261</v>
+        <v>120094102</v>
       </c>
       <c r="B184" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20102,38 +20091,41 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>746574</v>
+        <v>746539</v>
       </c>
       <c r="R184" t="n">
-        <v>7151495</v>
+        <v>7151513</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20174,6 +20166,7 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -20192,10 +20185,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120086287</v>
+        <v>120080333</v>
       </c>
       <c r="B185" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20204,38 +20197,42 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>746567</v>
+        <v>746569</v>
       </c>
       <c r="R185" t="n">
-        <v>7151554</v>
+        <v>7151265</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20270,6 +20267,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Minst, stort mycel</t>
+        </is>
+      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
@@ -20282,22 +20284,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120080331</v>
+        <v>120086257</v>
       </c>
       <c r="B186" t="n">
-        <v>78542</v>
+        <v>91870</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20306,25 +20308,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20334,10 +20336,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>746936</v>
+        <v>746575</v>
       </c>
       <c r="R186" t="n">
-        <v>7151139</v>
+        <v>7151554</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20372,11 +20374,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
-        </is>
-      </c>
       <c r="AD186" t="b">
         <v>0</v>
       </c>
@@ -20385,41 +20382,26 @@
       </c>
       <c r="AG186" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO186" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120094677</v>
+        <v>120080309</v>
       </c>
       <c r="B187" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20428,41 +20410,43 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>746351</v>
+        <v>746663</v>
       </c>
       <c r="R187" t="n">
-        <v>7151225</v>
+        <v>7151255</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20497,35 +20481,54 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Äldre födohack i basen</t>
+        </is>
+      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
       <c r="AE187" t="b">
         <v>0</v>
       </c>
-      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120086307</v>
+        <v>120086264</v>
       </c>
       <c r="B188" t="n">
-        <v>91852</v>
+        <v>92048</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20538,21 +20541,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20562,10 +20565,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>746483</v>
+        <v>746539</v>
       </c>
       <c r="R188" t="n">
-        <v>7151420</v>
+        <v>7151522</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20624,7 +20627,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120094591</v>
+        <v>120079816</v>
       </c>
       <c r="B189" t="n">
         <v>91852</v>
@@ -20658,22 +20661,19 @@
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>746294</v>
+        <v>746534</v>
       </c>
       <c r="R189" t="n">
-        <v>7151228</v>
+        <v>7151288</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20711,29 +20711,28 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
-      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>120086244</v>
+        <v>120086237</v>
       </c>
       <c r="B190" t="n">
-        <v>91846</v>
+        <v>89292</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20746,21 +20745,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>149</v>
+        <v>6286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20770,10 +20769,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>746576</v>
+        <v>746561</v>
       </c>
       <c r="R190" t="n">
-        <v>7151444</v>
+        <v>7151472</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20832,10 +20831,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>120086285</v>
+        <v>120256026</v>
       </c>
       <c r="B191" t="n">
-        <v>78542</v>
+        <v>91852</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20848,37 +20847,48 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>746576</v>
+        <v>746595</v>
       </c>
       <c r="R191" t="n">
-        <v>7151476</v>
+        <v>7151275</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20905,39 +20915,50 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AD191" t="b">
         <v>0</v>
       </c>
       <c r="AE191" t="b">
         <v>0</v>
       </c>
+      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>120256287</v>
+        <v>120256310</v>
       </c>
       <c r="B192" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20946,25 +20967,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -21058,10 +21079,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>120256409</v>
+        <v>120256184</v>
       </c>
       <c r="B193" t="n">
-        <v>91879</v>
+        <v>91858</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21074,21 +21095,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -21109,10 +21130,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>746483</v>
+        <v>746540</v>
       </c>
       <c r="R193" t="n">
-        <v>7151210</v>
+        <v>7151228</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -21144,7 +21165,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21154,7 +21175,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21182,10 +21203,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>120256310</v>
+        <v>120256251</v>
       </c>
       <c r="B194" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21194,25 +21215,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -21233,10 +21254,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>746490</v>
+        <v>746516</v>
       </c>
       <c r="R194" t="n">
-        <v>7151210</v>
+        <v>7151220</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -21266,19 +21287,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>13:10</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21306,7 +21317,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>120256146</v>
+        <v>120256105</v>
       </c>
       <c r="B195" t="n">
         <v>91858</v>
@@ -21357,10 +21368,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>746617</v>
+        <v>746595</v>
       </c>
       <c r="R195" t="n">
-        <v>7151234</v>
+        <v>7151214</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -21392,7 +21403,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21402,7 +21413,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21430,7 +21441,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>120256251</v>
+        <v>120256287</v>
       </c>
       <c r="B196" t="n">
         <v>91858</v>
@@ -21481,10 +21492,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>746516</v>
+        <v>746490</v>
       </c>
       <c r="R196" t="n">
-        <v>7151220</v>
+        <v>7151210</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -21514,9 +21525,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21668,7 +21689,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>120256105</v>
+        <v>120256146</v>
       </c>
       <c r="B198" t="n">
         <v>91858</v>
@@ -21719,10 +21740,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>746595</v>
+        <v>746617</v>
       </c>
       <c r="R198" t="n">
-        <v>7151214</v>
+        <v>7151234</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -21754,7 +21775,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21764,7 +21785,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21792,10 +21813,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>120256026</v>
+        <v>120256409</v>
       </c>
       <c r="B199" t="n">
-        <v>91852</v>
+        <v>91879</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21804,25 +21825,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4362</v>
+        <v>5964</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -21843,10 +21864,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>746595</v>
+        <v>746483</v>
       </c>
       <c r="R199" t="n">
-        <v>7151275</v>
+        <v>7151210</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -21878,7 +21899,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21888,7 +21909,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21916,7 +21937,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>120256184</v>
+        <v>120256212</v>
       </c>
       <c r="B200" t="n">
         <v>91858</v>
@@ -21967,10 +21988,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>746540</v>
+        <v>746530</v>
       </c>
       <c r="R200" t="n">
-        <v>7151228</v>
+        <v>7151223</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -22002,7 +22023,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22012,7 +22033,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22040,10 +22061,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>120256212</v>
+        <v>120080330</v>
       </c>
       <c r="B201" t="n">
-        <v>91858</v>
+        <v>90848</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22052,37 +22073,29 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4364</v>
+        <v>71</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Renvall &amp; Niemelä) Audet</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
@@ -22091,13 +22104,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>746530</v>
+        <v>746624</v>
       </c>
       <c r="R201" t="n">
-        <v>7151223</v>
+        <v>7151217</v>
       </c>
       <c r="S201" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22124,19 +22137,14 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>13:16</t>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Nedbruten tallåga, kollekt taget. Mikroskoperat och artbestämt till Urskogsporing</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22149,144 +22157,33 @@
       <c r="AG201" t="b">
         <v>0</v>
       </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Roger Olofsson, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
-        <v>120080330</v>
-      </c>
-      <c r="B202" t="n">
-        <v>90848</v>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E202" t="n">
-        <v>71</v>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>Urskogsporing</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Neoantrodia infirma</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-      <c r="P202" t="inlineStr">
-        <is>
-          <t>Vintjärnskammen, Vb</t>
-        </is>
-      </c>
-      <c r="Q202" t="n">
-        <v>746624</v>
-      </c>
-      <c r="R202" t="n">
-        <v>7151217</v>
-      </c>
-      <c r="S202" t="n">
-        <v>10</v>
-      </c>
-      <c r="T202" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U202" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>Burträsk</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AA202" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>Nedbruten tallåga, kollekt taget. Mikroskoperat och artbestämt till Urskogsporing</t>
-        </is>
-      </c>
-      <c r="AD202" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE202" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF202" t="inlineStr"/>
-      <c r="AG202" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO202" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT202" t="inlineStr"/>
-      <c r="AW202" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX202" t="inlineStr">
-        <is>
-          <t>Roger Olofsson, Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY202" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY201"/>
+  <dimension ref="A1:AY202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7176,10 +7176,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120063671</v>
+        <v>120064681</v>
       </c>
       <c r="B63" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7188,41 +7188,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vintjärnen, Vintjärnen, Vb</t>
+          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746309</v>
+        <v>746535</v>
       </c>
       <c r="R63" t="n">
-        <v>7151221</v>
+        <v>7151171</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7276,19 +7276,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120064681</v>
+        <v>120059872</v>
       </c>
       <c r="B64" t="n">
         <v>91858</v>
@@ -7324,17 +7324,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
+          <t>Vintjärnen, Vintjärnen, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746535</v>
+        <v>746557</v>
       </c>
       <c r="R64" t="n">
-        <v>7151171</v>
+        <v>7151556</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7388,22 +7388,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120059872</v>
+        <v>120063671</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7412,25 +7412,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746557</v>
+        <v>746309</v>
       </c>
       <c r="R65" t="n">
-        <v>7151556</v>
+        <v>7151221</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7960,10 +7960,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120059683</v>
+        <v>120061583</v>
       </c>
       <c r="B70" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7972,25 +7972,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746569</v>
+        <v>746472</v>
       </c>
       <c r="R70" t="n">
-        <v>7151549</v>
+        <v>7151401</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8072,10 +8072,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120061583</v>
+        <v>120059683</v>
       </c>
       <c r="B71" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8084,25 +8084,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746472</v>
+        <v>746569</v>
       </c>
       <c r="R71" t="n">
-        <v>7151401</v>
+        <v>7151549</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8632,7 +8632,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120061645</v>
+        <v>120061458</v>
       </c>
       <c r="B76" t="n">
         <v>91902</v>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746450</v>
+        <v>746495</v>
       </c>
       <c r="R76" t="n">
-        <v>7151380</v>
+        <v>7151424</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8744,7 +8744,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120061458</v>
+        <v>120061645</v>
       </c>
       <c r="B77" t="n">
         <v>91902</v>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746495</v>
+        <v>746450</v>
       </c>
       <c r="R77" t="n">
-        <v>7151424</v>
+        <v>7151380</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9752,10 +9752,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120059956</v>
+        <v>120061534</v>
       </c>
       <c r="B86" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9764,25 +9764,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9792,10 +9792,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>746535</v>
+        <v>746467</v>
       </c>
       <c r="R86" t="n">
-        <v>7151537</v>
+        <v>7151403</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9864,10 +9864,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120061534</v>
+        <v>120059956</v>
       </c>
       <c r="B87" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9876,25 +9876,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>746467</v>
+        <v>746535</v>
       </c>
       <c r="R87" t="n">
-        <v>7151403</v>
+        <v>7151537</v>
       </c>
       <c r="S87" t="n">
         <v>1</v>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9976,10 +9976,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120064407</v>
+        <v>120063487</v>
       </c>
       <c r="B88" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9988,25 +9988,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>746440</v>
+        <v>746300</v>
       </c>
       <c r="R88" t="n">
-        <v>7151291</v>
+        <v>7151231</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10088,7 +10088,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120063693</v>
+        <v>120064407</v>
       </c>
       <c r="B89" t="n">
         <v>91858</v>
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>746319</v>
+        <v>746440</v>
       </c>
       <c r="R89" t="n">
-        <v>7151210</v>
+        <v>7151291</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10188,22 +10188,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120063487</v>
+        <v>120063693</v>
       </c>
       <c r="B90" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10212,25 +10212,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10240,13 +10240,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>746300</v>
+        <v>746319</v>
       </c>
       <c r="R90" t="n">
-        <v>7151231</v>
+        <v>7151210</v>
       </c>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10300,12 +10300,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -12128,10 +12128,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120080353</v>
+        <v>120086306</v>
       </c>
       <c r="B108" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12140,25 +12140,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12168,10 +12168,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>746577</v>
+        <v>746371</v>
       </c>
       <c r="R108" t="n">
-        <v>7151220</v>
+        <v>7151274</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12218,22 +12218,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120086288</v>
+        <v>120080353</v>
       </c>
       <c r="B109" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12242,25 +12242,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12270,10 +12270,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>746630</v>
+        <v>746577</v>
       </c>
       <c r="R109" t="n">
-        <v>7151524</v>
+        <v>7151220</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12320,22 +12320,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120086306</v>
+        <v>120086288</v>
       </c>
       <c r="B110" t="n">
-        <v>91852</v>
+        <v>78542</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12348,21 +12348,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12372,10 +12372,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>746371</v>
+        <v>746630</v>
       </c>
       <c r="R110" t="n">
-        <v>7151274</v>
+        <v>7151524</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12956,10 +12956,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120086271</v>
+        <v>120086232</v>
       </c>
       <c r="B116" t="n">
-        <v>57431</v>
+        <v>89650</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12968,46 +12968,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103031</v>
+        <v>1962</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>746500</v>
+        <v>746551</v>
       </c>
       <c r="R116" t="n">
-        <v>7151560</v>
+        <v>7151485</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13066,10 +13058,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120086232</v>
+        <v>120086268</v>
       </c>
       <c r="B117" t="n">
-        <v>89650</v>
+        <v>91881</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13082,21 +13074,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1962</v>
+        <v>5966</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13106,10 +13098,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>746551</v>
+        <v>746563</v>
       </c>
       <c r="R117" t="n">
-        <v>7151485</v>
+        <v>7151464</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13168,10 +13160,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120086268</v>
+        <v>120086271</v>
       </c>
       <c r="B118" t="n">
-        <v>91881</v>
+        <v>57431</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13180,38 +13172,46 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5966</v>
+        <v>103031</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>746563</v>
+        <v>746500</v>
       </c>
       <c r="R118" t="n">
-        <v>7151464</v>
+        <v>7151560</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14223,10 +14223,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120080352</v>
+        <v>120080303</v>
       </c>
       <c r="B128" t="n">
-        <v>91858</v>
+        <v>91904</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14235,38 +14235,42 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>746834</v>
+        <v>746331</v>
       </c>
       <c r="R128" t="n">
-        <v>7151121</v>
+        <v>7151256</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14299,6 +14303,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Under tunn äldre tallgren på mager, torr mark</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14325,10 +14334,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120080355</v>
+        <v>120080291</v>
       </c>
       <c r="B129" t="n">
-        <v>91858</v>
+        <v>91272</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14341,34 +14350,38 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4364</v>
+        <v>3298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>746527</v>
+        <v>746393</v>
       </c>
       <c r="R129" t="n">
-        <v>7151203</v>
+        <v>7151288</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14403,6 +14416,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Basen av levande gran</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14411,6 +14429,21 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
@@ -14427,10 +14460,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120080291</v>
+        <v>120080352</v>
       </c>
       <c r="B130" t="n">
-        <v>91272</v>
+        <v>91858</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14443,38 +14476,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3298</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>746393</v>
+        <v>746834</v>
       </c>
       <c r="R130" t="n">
-        <v>7151288</v>
+        <v>7151121</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14509,11 +14538,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Basen av levande gran</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -14522,21 +14546,6 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
@@ -14553,10 +14562,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120079801</v>
+        <v>120080355</v>
       </c>
       <c r="B131" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14565,25 +14574,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14593,13 +14602,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>746598</v>
+        <v>746527</v>
       </c>
       <c r="R131" t="n">
-        <v>7151227</v>
+        <v>7151203</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14637,29 +14646,28 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120080303</v>
+        <v>120079801</v>
       </c>
       <c r="B132" t="n">
-        <v>91904</v>
+        <v>91902</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14668,45 +14676,41 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>232140</v>
+        <v>5449</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>746331</v>
+        <v>746598</v>
       </c>
       <c r="R132" t="n">
-        <v>7151256</v>
+        <v>7151227</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14738,29 +14742,25 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Under tunn äldre tallgren på mager, torr mark</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -15396,10 +15396,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120086251</v>
+        <v>120086241</v>
       </c>
       <c r="B139" t="n">
-        <v>91862</v>
+        <v>91844</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15408,25 +15408,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15436,10 +15436,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>746297</v>
+        <v>746383</v>
       </c>
       <c r="R139" t="n">
-        <v>7151200</v>
+        <v>7151288</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15498,10 +15498,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120080357</v>
+        <v>120086307</v>
       </c>
       <c r="B140" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15510,25 +15510,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>746301</v>
+        <v>746483</v>
       </c>
       <c r="R140" t="n">
-        <v>7151209</v>
+        <v>7151420</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15588,22 +15588,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120086241</v>
+        <v>120080357</v>
       </c>
       <c r="B141" t="n">
-        <v>91844</v>
+        <v>91858</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15612,25 +15612,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15640,10 +15640,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>746383</v>
+        <v>746301</v>
       </c>
       <c r="R141" t="n">
-        <v>7151288</v>
+        <v>7151209</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15690,22 +15690,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120086307</v>
+        <v>120086251</v>
       </c>
       <c r="B142" t="n">
-        <v>91852</v>
+        <v>91862</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15714,25 +15714,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15742,10 +15742,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>746483</v>
+        <v>746297</v>
       </c>
       <c r="R142" t="n">
-        <v>7151420</v>
+        <v>7151200</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16212,10 +16212,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120086256</v>
+        <v>120094305</v>
       </c>
       <c r="B147" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16228,34 +16228,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>746576</v>
+        <v>746472</v>
       </c>
       <c r="R147" t="n">
-        <v>7151444</v>
+        <v>7151410</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16296,6 +16299,7 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -16314,10 +16318,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120094305</v>
+        <v>120086256</v>
       </c>
       <c r="B148" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16330,37 +16334,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>746472</v>
+        <v>746576</v>
       </c>
       <c r="R148" t="n">
-        <v>7151410</v>
+        <v>7151444</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16401,7 +16402,6 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -17374,10 +17374,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120080296</v>
+        <v>120079799</v>
       </c>
       <c r="B158" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17390,45 +17390,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>746527</v>
+        <v>746840</v>
       </c>
       <c r="R158" t="n">
-        <v>7151199</v>
+        <v>7151151</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17472,22 +17464,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120094777</v>
+        <v>120080296</v>
       </c>
       <c r="B159" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17500,26 +17492,31 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -17527,10 +17524,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>746478</v>
+        <v>746527</v>
       </c>
       <c r="R159" t="n">
-        <v>7151377</v>
+        <v>7151199</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17571,29 +17568,28 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120080310</v>
+        <v>120094777</v>
       </c>
       <c r="B160" t="n">
-        <v>91839</v>
+        <v>91902</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17602,25 +17598,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6055</v>
+        <v>5449</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17633,10 +17629,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>746772</v>
+        <v>746478</v>
       </c>
       <c r="R160" t="n">
-        <v>7151182</v>
+        <v>7151377</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17671,11 +17667,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat</t>
-        </is>
-      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
@@ -17689,22 +17680,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120079799</v>
+        <v>120080310</v>
       </c>
       <c r="B161" t="n">
-        <v>90580</v>
+        <v>91839</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17713,41 +17704,44 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>6055</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>746840</v>
+        <v>746772</v>
       </c>
       <c r="R161" t="n">
-        <v>7151151</v>
+        <v>7151182</v>
       </c>
       <c r="S161" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17779,24 +17773,30 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat</t>
+        </is>
+      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
@@ -17909,10 +17909,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120086287</v>
+        <v>120080356</v>
       </c>
       <c r="B163" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17921,25 +17921,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17949,10 +17949,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>746567</v>
+        <v>746499</v>
       </c>
       <c r="R163" t="n">
-        <v>7151554</v>
+        <v>7151195</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17999,19 +17999,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120080356</v>
+        <v>120086303</v>
       </c>
       <c r="B164" t="n">
         <v>91858</v>
@@ -18051,10 +18051,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>746499</v>
+        <v>746555</v>
       </c>
       <c r="R164" t="n">
-        <v>7151195</v>
+        <v>7151578</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18101,19 +18101,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120086303</v>
+        <v>120080334</v>
       </c>
       <c r="B165" t="n">
         <v>91858</v>
@@ -18146,17 +18146,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>746555</v>
+        <v>746537</v>
       </c>
       <c r="R165" t="n">
-        <v>7151578</v>
+        <v>7151303</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18203,22 +18207,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120080334</v>
+        <v>120086248</v>
       </c>
       <c r="B166" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18227,32 +18231,28 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
@@ -18262,7 +18262,7 @@
         <v>746537</v>
       </c>
       <c r="R166" t="n">
-        <v>7151303</v>
+        <v>7151592</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18309,19 +18309,19 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120086248</v>
+        <v>120080308</v>
       </c>
       <c r="B167" t="n">
         <v>91902</v>
@@ -18361,10 +18361,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>746537</v>
+        <v>746368</v>
       </c>
       <c r="R167" t="n">
-        <v>7151592</v>
+        <v>7151279</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18411,19 +18411,19 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120080308</v>
+        <v>120094190</v>
       </c>
       <c r="B168" t="n">
         <v>91902</v>
@@ -18457,16 +18457,19 @@
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>746368</v>
+        <v>746572</v>
       </c>
       <c r="R168" t="n">
-        <v>7151279</v>
+        <v>7151479</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18507,28 +18510,29 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120094190</v>
+        <v>120086287</v>
       </c>
       <c r="B169" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18541,37 +18545,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>746572</v>
+        <v>746567</v>
       </c>
       <c r="R169" t="n">
-        <v>7151479</v>
+        <v>7151554</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18612,7 +18613,6 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -18631,10 +18631,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120079808</v>
+        <v>120079803</v>
       </c>
       <c r="B170" t="n">
-        <v>90594</v>
+        <v>91862</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18643,25 +18643,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1204</v>
+        <v>4365</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18671,10 +18671,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>746668</v>
+        <v>746316</v>
       </c>
       <c r="R170" t="n">
-        <v>7151253</v>
+        <v>7151248</v>
       </c>
       <c r="S170" t="n">
         <v>15</v>
@@ -18733,10 +18733,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120079803</v>
+        <v>120079808</v>
       </c>
       <c r="B171" t="n">
-        <v>91862</v>
+        <v>90594</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18745,25 +18745,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4365</v>
+        <v>1204</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18773,10 +18773,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>746316</v>
+        <v>746668</v>
       </c>
       <c r="R171" t="n">
-        <v>7151248</v>
+        <v>7151253</v>
       </c>
       <c r="S171" t="n">
         <v>15</v>
@@ -19973,10 +19973,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120094266</v>
+        <v>120086257</v>
       </c>
       <c r="B183" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19989,37 +19989,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>746491</v>
+        <v>746575</v>
       </c>
       <c r="R183" t="n">
-        <v>7151452</v>
+        <v>7151554</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20060,7 +20057,6 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -20079,7 +20075,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120094102</v>
+        <v>120094266</v>
       </c>
       <c r="B184" t="n">
         <v>91858</v>
@@ -20122,10 +20118,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>746539</v>
+        <v>746491</v>
       </c>
       <c r="R184" t="n">
-        <v>7151513</v>
+        <v>7151452</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20185,7 +20181,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120080333</v>
+        <v>120094102</v>
       </c>
       <c r="B185" t="n">
         <v>91858</v>
@@ -20218,21 +20214,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>746569</v>
+        <v>746539</v>
       </c>
       <c r="R185" t="n">
-        <v>7151265</v>
+        <v>7151513</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20267,39 +20262,35 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Minst, stort mycel</t>
-        </is>
-      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120086257</v>
+        <v>120080333</v>
       </c>
       <c r="B186" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20312,34 +20303,38 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>746575</v>
+        <v>746569</v>
       </c>
       <c r="R186" t="n">
-        <v>7151554</v>
+        <v>7151265</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20374,6 +20369,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Minst, stort mycel</t>
+        </is>
+      </c>
       <c r="AD186" t="b">
         <v>0</v>
       </c>
@@ -20386,12 +20386,12 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
@@ -22064,7 +22064,7 @@
         <v>120080330</v>
       </c>
       <c r="B201" t="n">
-        <v>90848</v>
+        <v>90730</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22073,25 +22073,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>71</v>
+        <v>1503</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22144,7 +22144,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Nedbruten tallåga, kollekt taget. Mikroskoperat och artbestämt till Urskogsporing</t>
+          <t>Nedbruten tallåga, kollekt taget.</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22184,6 +22184,132 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>120080312</v>
+      </c>
+      <c r="B202" t="n">
+        <v>90848</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>71</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Urskogsporing</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Neoantrodia infirma</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>(Renvall &amp; Niemelä) Audet</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>746362</v>
+      </c>
+      <c r="R202" t="n">
+        <v>7151196</v>
+      </c>
+      <c r="S202" t="n">
+        <v>10</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat Mikroskoperat och bestämt till urskogsporing</t>
+        </is>
+      </c>
+      <c r="AD202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF202" t="inlineStr"/>
+      <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53616-2023 artfynd.xlsx
+++ b/artfynd/A 53616-2023 artfynd.xlsx
@@ -7176,10 +7176,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120064681</v>
+        <v>120060888</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>96891</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7192,37 +7192,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
+          <t>Vintjärnen, Vintjärnen, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746535</v>
+        <v>746566</v>
       </c>
       <c r="R63" t="n">
-        <v>7151171</v>
+        <v>7151484</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7276,22 +7276,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120059872</v>
+        <v>120062274</v>
       </c>
       <c r="B64" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7300,25 +7300,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7328,10 +7328,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746557</v>
+        <v>746394</v>
       </c>
       <c r="R64" t="n">
-        <v>7151556</v>
+        <v>7151307</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7400,7 +7400,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120063671</v>
+        <v>120063551</v>
       </c>
       <c r="B65" t="n">
         <v>91874</v>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746309</v>
+        <v>746308</v>
       </c>
       <c r="R65" t="n">
-        <v>7151221</v>
+        <v>7151219</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7512,7 +7512,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120062963</v>
+        <v>120061583</v>
       </c>
       <c r="B66" t="n">
         <v>91858</v>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746369</v>
+        <v>746472</v>
       </c>
       <c r="R66" t="n">
-        <v>7151279</v>
+        <v>7151401</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120059794</v>
+        <v>120063442</v>
       </c>
       <c r="B67" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7636,25 +7636,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7664,10 +7664,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746567</v>
+        <v>746297</v>
       </c>
       <c r="R67" t="n">
-        <v>7151566</v>
+        <v>7151223</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7736,10 +7736,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120063287</v>
+        <v>120064386</v>
       </c>
       <c r="B68" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7748,41 +7748,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vintjärnen, Vintjärnen, Vb</t>
+          <t>Vintjärnskammen, Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746369</v>
+        <v>746535</v>
       </c>
       <c r="R68" t="n">
-        <v>7151254</v>
+        <v>7151171</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7836,22 +7836,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120063551</v>
+        <v>120059794</v>
       </c>
       <c r="B69" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7864,21 +7864,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7888,10 +7888,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746308</v>
+        <v>746567</v>
       </c>
       <c r="R69" t="n">
-        <v>7151219</v>
+        <v>7151566</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7960,10 +7960,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120061583</v>
+        <v>120061458</v>
       </c>
       <c r="B70" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7972,25 +7972,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746472</v>
+        <v>746495</v>
       </c>
       <c r="R70" t="n">
-        <v>7151401</v>
+        <v>7151424</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8184,10 +8184,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120062389</v>
+        <v>120063383</v>
       </c>
       <c r="B72" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8196,25 +8196,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746426</v>
+        <v>746303</v>
       </c>
       <c r="R72" t="n">
-        <v>7151309</v>
+        <v>7151246</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8296,10 +8296,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120063439</v>
+        <v>120063487</v>
       </c>
       <c r="B73" t="n">
-        <v>91846</v>
+        <v>91852</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8308,25 +8308,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8336,10 +8336,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746303</v>
+        <v>746300</v>
       </c>
       <c r="R73" t="n">
-        <v>7151241</v>
+        <v>7151231</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8408,10 +8408,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120059636</v>
+        <v>120062932</v>
       </c>
       <c r="B74" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8420,25 +8420,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746602</v>
+        <v>746422</v>
       </c>
       <c r="R74" t="n">
-        <v>7151535</v>
+        <v>7151289</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8520,7 +8520,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120063442</v>
+        <v>120062963</v>
       </c>
       <c r="B75" t="n">
         <v>91858</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746297</v>
+        <v>746369</v>
       </c>
       <c r="R75" t="n">
-        <v>7151223</v>
+        <v>7151279</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8632,10 +8632,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120061458</v>
+        <v>120062185</v>
       </c>
       <c r="B76" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8644,25 +8644,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746495</v>
+        <v>746401</v>
       </c>
       <c r="R76" t="n">
-        <v>7151424</v>
+        <v>7151292</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8744,10 +8744,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120061645</v>
+        <v>120061233</v>
       </c>
       <c r="B77" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8760,21 +8760,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746450</v>
+        <v>746597</v>
       </c>
       <c r="R77" t="n">
-        <v>7151380</v>
+        <v>7151440</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8856,10 +8856,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120062932</v>
+        <v>120063671</v>
       </c>
       <c r="B78" t="n">
-        <v>91902</v>
+        <v>91874</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8872,21 +8872,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746422</v>
+        <v>746309</v>
       </c>
       <c r="R78" t="n">
-        <v>7151289</v>
+        <v>7151221</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8968,10 +8968,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120061607</v>
+        <v>120061247</v>
       </c>
       <c r="B79" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8980,25 +8980,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746453</v>
+        <v>746541</v>
       </c>
       <c r="R79" t="n">
-        <v>7151408</v>
+        <v>7151441</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9080,10 +9080,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120062274</v>
+        <v>120062338</v>
       </c>
       <c r="B80" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9092,25 +9092,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746394</v>
+        <v>746390</v>
       </c>
       <c r="R80" t="n">
-        <v>7151307</v>
+        <v>7151301</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9192,10 +9192,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120063963</v>
+        <v>120062044</v>
       </c>
       <c r="B81" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9204,25 +9204,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746301</v>
+        <v>746344</v>
       </c>
       <c r="R81" t="n">
-        <v>7151207</v>
+        <v>7151353</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9304,10 +9304,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120063728</v>
+        <v>120059872</v>
       </c>
       <c r="B82" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9316,25 +9316,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746298</v>
+        <v>746557</v>
       </c>
       <c r="R82" t="n">
-        <v>7151222</v>
+        <v>7151556</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9416,10 +9416,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120061725</v>
+        <v>120064407</v>
       </c>
       <c r="B83" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9428,25 +9428,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>746444</v>
+        <v>746440</v>
       </c>
       <c r="R83" t="n">
-        <v>7151382</v>
+        <v>7151291</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9528,7 +9528,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120061860</v>
+        <v>120063693</v>
       </c>
       <c r="B84" t="n">
         <v>91858</v>
@@ -9568,13 +9568,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746423</v>
+        <v>746319</v>
       </c>
       <c r="R84" t="n">
-        <v>7151350</v>
+        <v>7151210</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9628,22 +9628,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120061686</v>
+        <v>120059636</v>
       </c>
       <c r="B85" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9652,25 +9652,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9680,10 +9680,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746448</v>
+        <v>746602</v>
       </c>
       <c r="R85" t="n">
-        <v>7151388</v>
+        <v>7151535</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9752,10 +9752,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120061534</v>
+        <v>120059956</v>
       </c>
       <c r="B86" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9764,25 +9764,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9792,10 +9792,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>746467</v>
+        <v>746535</v>
       </c>
       <c r="R86" t="n">
-        <v>7151403</v>
+        <v>7151537</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9864,10 +9864,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120059956</v>
+        <v>120061645</v>
       </c>
       <c r="B87" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9880,21 +9880,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>746535</v>
+        <v>746450</v>
       </c>
       <c r="R87" t="n">
-        <v>7151537</v>
+        <v>7151380</v>
       </c>
       <c r="S87" t="n">
         <v>1</v>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9976,7 +9976,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120063487</v>
+        <v>120061725</v>
       </c>
       <c r="B88" t="n">
         <v>91852</v>
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>746300</v>
+        <v>746444</v>
       </c>
       <c r="R88" t="n">
-        <v>7151231</v>
+        <v>7151382</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10088,7 +10088,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120064407</v>
+        <v>120061860</v>
       </c>
       <c r="B89" t="n">
         <v>91858</v>
@@ -10128,10 +10128,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>746440</v>
+        <v>746423</v>
       </c>
       <c r="R89" t="n">
-        <v>7151291</v>
+        <v>7151350</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10200,10 +10200,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120063693</v>
+        <v>120063439</v>
       </c>
       <c r="B90" t="n">
-        <v>91858</v>
+        <v>91846</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10212,25 +10212,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>149</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10240,13 +10240,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>746319</v>
+        <v>746303</v>
       </c>
       <c r="R90" t="n">
-        <v>7151210</v>
+        <v>7151241</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10300,22 +10300,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120063383</v>
+        <v>120063728</v>
       </c>
       <c r="B91" t="n">
-        <v>91881</v>
+        <v>91902</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10328,21 +10328,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10352,10 +10352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>746303</v>
+        <v>746298</v>
       </c>
       <c r="R91" t="n">
-        <v>7151246</v>
+        <v>7151222</v>
       </c>
       <c r="S91" t="n">
         <v>1</v>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10424,10 +10424,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120060888</v>
+        <v>120061686</v>
       </c>
       <c r="B92" t="n">
-        <v>96891</v>
+        <v>91881</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10436,25 +10436,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221941</v>
+        <v>5966</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>746566</v>
+        <v>746448</v>
       </c>
       <c r="R92" t="n">
-        <v>7151484</v>
+        <v>7151388</v>
       </c>
       <c r="S92" t="n">
         <v>1</v>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10536,10 +10536,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120061233</v>
+        <v>120063287</v>
       </c>
       <c r="B93" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10552,21 +10552,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>746597</v>
+        <v>746369</v>
       </c>
       <c r="R93" t="n">
-        <v>7151440</v>
+        <v>7151254</v>
       </c>
       <c r="S93" t="n">
         <v>1</v>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10648,7 +10648,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120062338</v>
+        <v>120063963</v>
       </c>
       <c r="B94" t="n">
         <v>91858</v>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>746390</v>
+        <v>746301</v>
       </c>
       <c r="R94" t="n">
-        <v>7151301</v>
+        <v>7151207</v>
       </c>
       <c r="S94" t="n">
         <v>1</v>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10760,7 +10760,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120062185</v>
+        <v>120061534</v>
       </c>
       <c r="B95" t="n">
         <v>91858</v>
@@ -10800,10 +10800,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>746401</v>
+        <v>746467</v>
       </c>
       <c r="R95" t="n">
-        <v>7151292</v>
+        <v>7151403</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10872,7 +10872,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120061247</v>
+        <v>120062389</v>
       </c>
       <c r="B96" t="n">
         <v>91858</v>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>746541</v>
+        <v>746426</v>
       </c>
       <c r="R96" t="n">
-        <v>7151441</v>
+        <v>7151309</v>
       </c>
       <c r="S96" t="n">
         <v>1</v>
@@ -10947,7 +10947,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10984,10 +10984,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120062044</v>
+        <v>120061607</v>
       </c>
       <c r="B97" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11000,21 +11000,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11024,10 +11024,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>746344</v>
+        <v>746453</v>
       </c>
       <c r="R97" t="n">
-        <v>7151353</v>
+        <v>7151408</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11096,10 +11096,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120086234</v>
+        <v>120094266</v>
       </c>
       <c r="B98" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11108,38 +11108,41 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>746539</v>
+        <v>746491</v>
       </c>
       <c r="R98" t="n">
-        <v>7151522</v>
+        <v>7151452</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11180,6 +11183,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11198,10 +11202,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120086252</v>
+        <v>120094677</v>
       </c>
       <c r="B99" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11210,38 +11214,41 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>746575</v>
+        <v>746351</v>
       </c>
       <c r="R99" t="n">
-        <v>7151485</v>
+        <v>7151225</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11282,6 +11289,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11300,7 +11308,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120094292</v>
+        <v>120094170</v>
       </c>
       <c r="B100" t="n">
         <v>91858</v>
@@ -11343,10 +11351,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>746478</v>
+        <v>746562</v>
       </c>
       <c r="R100" t="n">
-        <v>7151421</v>
+        <v>7151492</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11406,10 +11414,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120094276</v>
+        <v>120079798</v>
       </c>
       <c r="B101" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11418,44 +11426,41 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>746476</v>
+        <v>746310</v>
       </c>
       <c r="R101" t="n">
-        <v>7151446</v>
+        <v>7151135</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11493,29 +11498,28 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120094677</v>
+        <v>120080291</v>
       </c>
       <c r="B102" t="n">
-        <v>91858</v>
+        <v>91272</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11528,37 +11532,38 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>3298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>746351</v>
+        <v>746393</v>
       </c>
       <c r="R102" t="n">
-        <v>7151225</v>
+        <v>7151288</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11593,32 +11598,51 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Basen av levande gran</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120079815</v>
+        <v>120080332</v>
       </c>
       <c r="B103" t="n">
         <v>91858</v>
@@ -11651,20 +11675,24 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>746896</v>
+        <v>746560</v>
       </c>
       <c r="R103" t="n">
-        <v>7151149</v>
+        <v>7151291</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11708,19 +11736,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120086304</v>
+        <v>120094359</v>
       </c>
       <c r="B104" t="n">
         <v>91858</v>
@@ -11754,16 +11782,19 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>746589</v>
+        <v>746451</v>
       </c>
       <c r="R104" t="n">
-        <v>7151537</v>
+        <v>7151341</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11804,6 +11835,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11822,10 +11854,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120086273</v>
+        <v>120086252</v>
       </c>
       <c r="B105" t="n">
-        <v>90730</v>
+        <v>91862</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11838,21 +11870,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11862,7 +11894,7 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>746551</v>
+        <v>746575</v>
       </c>
       <c r="R105" t="n">
         <v>7151485</v>
@@ -11924,10 +11956,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120086267</v>
+        <v>120086239</v>
       </c>
       <c r="B106" t="n">
-        <v>91881</v>
+        <v>57473</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11940,34 +11972,46 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>746492</v>
+        <v>746532</v>
       </c>
       <c r="R106" t="n">
-        <v>7151446</v>
+        <v>7151493</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12026,10 +12070,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120086249</v>
+        <v>120079816</v>
       </c>
       <c r="B107" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12042,21 +12086,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12066,13 +12110,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>746568</v>
+        <v>746534</v>
       </c>
       <c r="R107" t="n">
-        <v>7151535</v>
+        <v>7151288</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12116,22 +12160,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120086306</v>
+        <v>120094276</v>
       </c>
       <c r="B108" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12140,38 +12184,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>746371</v>
+        <v>746476</v>
       </c>
       <c r="R108" t="n">
-        <v>7151274</v>
+        <v>7151446</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12212,6 +12259,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -12230,10 +12278,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120080353</v>
+        <v>120086290</v>
       </c>
       <c r="B109" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12242,25 +12290,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12270,10 +12318,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>746577</v>
+        <v>746657</v>
       </c>
       <c r="R109" t="n">
-        <v>7151220</v>
+        <v>7151562</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12320,22 +12368,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120086288</v>
+        <v>120080297</v>
       </c>
       <c r="B110" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12348,34 +12396,43 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>746630</v>
+        <v>746612</v>
       </c>
       <c r="R110" t="n">
-        <v>7151524</v>
+        <v>7151234</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12422,22 +12479,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120086282</v>
+        <v>120086303</v>
       </c>
       <c r="B111" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12446,25 +12503,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12474,10 +12531,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>746368</v>
+        <v>746555</v>
       </c>
       <c r="R111" t="n">
-        <v>7151288</v>
+        <v>7151578</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12536,10 +12593,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120086243</v>
+        <v>120080355</v>
       </c>
       <c r="B112" t="n">
-        <v>91481</v>
+        <v>91858</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12548,25 +12605,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12576,10 +12633,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>746316</v>
+        <v>746527</v>
       </c>
       <c r="R112" t="n">
-        <v>7151209</v>
+        <v>7151203</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12626,22 +12683,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120080335</v>
+        <v>120086262</v>
       </c>
       <c r="B113" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12650,42 +12707,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>746321</v>
+        <v>746555</v>
       </c>
       <c r="R113" t="n">
-        <v>7151233</v>
+        <v>7151590</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12732,12 +12785,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12850,10 +12903,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120080359</v>
+        <v>120080356</v>
       </c>
       <c r="B115" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12862,42 +12915,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>746291</v>
+        <v>746499</v>
       </c>
       <c r="R115" t="n">
-        <v>7151137</v>
+        <v>7151195</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12956,10 +13005,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120086232</v>
+        <v>120086307</v>
       </c>
       <c r="B116" t="n">
-        <v>89650</v>
+        <v>91852</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12972,21 +13021,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12996,10 +13045,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>746551</v>
+        <v>746483</v>
       </c>
       <c r="R116" t="n">
-        <v>7151485</v>
+        <v>7151420</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13058,10 +13107,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120086268</v>
+        <v>120086251</v>
       </c>
       <c r="B117" t="n">
-        <v>91881</v>
+        <v>91862</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13070,25 +13119,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5966</v>
+        <v>4365</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13098,10 +13147,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>746563</v>
+        <v>746297</v>
       </c>
       <c r="R117" t="n">
-        <v>7151464</v>
+        <v>7151200</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13160,10 +13209,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120086271</v>
+        <v>120086283</v>
       </c>
       <c r="B118" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13172,46 +13221,38 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>746500</v>
+        <v>746566</v>
       </c>
       <c r="R118" t="n">
-        <v>7151560</v>
+        <v>7151468</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13270,10 +13311,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120080328</v>
+        <v>120080296</v>
       </c>
       <c r="B119" t="n">
-        <v>89981</v>
+        <v>57473</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13282,38 +13323,46 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5685</v>
+        <v>103021</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>746590</v>
+        <v>746527</v>
       </c>
       <c r="R119" t="n">
-        <v>7151225</v>
+        <v>7151199</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13356,21 +13405,6 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
@@ -13387,10 +13421,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120086286</v>
+        <v>120080359</v>
       </c>
       <c r="B120" t="n">
-        <v>78542</v>
+        <v>91852</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13403,34 +13437,38 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>746555</v>
+        <v>746291</v>
       </c>
       <c r="R120" t="n">
-        <v>7151578</v>
+        <v>7151137</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13477,22 +13515,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120086284</v>
+        <v>120086232</v>
       </c>
       <c r="B121" t="n">
-        <v>78542</v>
+        <v>89650</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13505,21 +13543,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13529,10 +13567,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>746563</v>
+        <v>746551</v>
       </c>
       <c r="R121" t="n">
-        <v>7151464</v>
+        <v>7151485</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13591,10 +13629,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120086260</v>
+        <v>120086235</v>
       </c>
       <c r="B122" t="n">
-        <v>91850</v>
+        <v>89650</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13607,21 +13645,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13631,10 +13669,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>746378</v>
+        <v>746515</v>
       </c>
       <c r="R122" t="n">
-        <v>7151283</v>
+        <v>7151568</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13693,10 +13731,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120080332</v>
+        <v>120086287</v>
       </c>
       <c r="B123" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13705,42 +13743,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>746560</v>
+        <v>746567</v>
       </c>
       <c r="R123" t="n">
-        <v>7151291</v>
+        <v>7151554</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13787,22 +13821,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120086239</v>
+        <v>120086270</v>
       </c>
       <c r="B124" t="n">
-        <v>57473</v>
+        <v>57431</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13811,37 +13845,37 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -13851,10 +13885,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>746532</v>
+        <v>746671</v>
       </c>
       <c r="R124" t="n">
-        <v>7151493</v>
+        <v>7151554</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13913,10 +13947,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120086308</v>
+        <v>120080358</v>
       </c>
       <c r="B125" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13925,25 +13959,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13953,10 +13987,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>746492</v>
+        <v>746699</v>
       </c>
       <c r="R125" t="n">
-        <v>7151446</v>
+        <v>7151240</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14003,22 +14037,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120086261</v>
+        <v>120094241</v>
       </c>
       <c r="B126" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14027,38 +14061,41 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>746574</v>
+        <v>746515</v>
       </c>
       <c r="R126" t="n">
-        <v>7151495</v>
+        <v>7151443</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14099,6 +14136,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -14117,10 +14155,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120094591</v>
+        <v>120086293</v>
       </c>
       <c r="B127" t="n">
-        <v>91852</v>
+        <v>78187</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14133,37 +14171,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>746294</v>
+        <v>746636</v>
       </c>
       <c r="R127" t="n">
-        <v>7151228</v>
+        <v>7151518</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14204,7 +14239,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -14223,10 +14257,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120080303</v>
+        <v>120086241</v>
       </c>
       <c r="B128" t="n">
-        <v>91904</v>
+        <v>91844</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14235,42 +14269,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>232140</v>
+        <v>3100</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>746331</v>
+        <v>746383</v>
       </c>
       <c r="R128" t="n">
-        <v>7151256</v>
+        <v>7151288</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14305,11 +14335,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Under tunn äldre tallgren på mager, torr mark</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -14322,22 +14347,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120080291</v>
+        <v>120086231</v>
       </c>
       <c r="B129" t="n">
-        <v>91272</v>
+        <v>90545</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14350,38 +14375,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>746393</v>
+        <v>746676</v>
       </c>
       <c r="R129" t="n">
-        <v>7151288</v>
+        <v>7151534</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14416,11 +14437,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Basen av levande gran</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14429,41 +14445,26 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120080352</v>
+        <v>120080331</v>
       </c>
       <c r="B130" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14472,25 +14473,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14500,10 +14501,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>746834</v>
+        <v>746936</v>
       </c>
       <c r="R130" t="n">
-        <v>7151121</v>
+        <v>7151139</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14538,6 +14539,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -14546,6 +14552,21 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
@@ -14562,10 +14583,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120080355</v>
+        <v>120086289</v>
       </c>
       <c r="B131" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14574,25 +14595,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14602,10 +14623,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>746527</v>
+        <v>746670</v>
       </c>
       <c r="R131" t="n">
-        <v>7151203</v>
+        <v>7151555</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14652,22 +14673,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120079801</v>
+        <v>120086267</v>
       </c>
       <c r="B132" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14680,21 +14701,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14704,13 +14725,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>746598</v>
+        <v>746492</v>
       </c>
       <c r="R132" t="n">
-        <v>7151227</v>
+        <v>7151446</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14748,29 +14769,28 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120086281</v>
+        <v>120086306</v>
       </c>
       <c r="B133" t="n">
-        <v>78542</v>
+        <v>91852</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14783,21 +14803,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14810,7 +14830,7 @@
         <v>746371</v>
       </c>
       <c r="R133" t="n">
-        <v>7151235</v>
+        <v>7151274</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14869,10 +14889,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120080297</v>
+        <v>120079803</v>
       </c>
       <c r="B134" t="n">
-        <v>57473</v>
+        <v>91862</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14881,50 +14901,41 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>746612</v>
+        <v>746316</v>
       </c>
       <c r="R134" t="n">
-        <v>7151234</v>
+        <v>7151248</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14968,22 +14979,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120079807</v>
+        <v>120086256</v>
       </c>
       <c r="B135" t="n">
-        <v>57431</v>
+        <v>91870</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14996,45 +15007,37 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>103031</v>
+        <v>4366</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>746368</v>
+        <v>746576</v>
       </c>
       <c r="R135" t="n">
-        <v>7151283</v>
+        <v>7151444</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15078,22 +15081,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120086235</v>
+        <v>120094777</v>
       </c>
       <c r="B136" t="n">
-        <v>89650</v>
+        <v>91902</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15106,34 +15109,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>746515</v>
+        <v>746478</v>
       </c>
       <c r="R136" t="n">
-        <v>7151568</v>
+        <v>7151377</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15174,6 +15180,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -15192,10 +15199,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120086300</v>
+        <v>120079810</v>
       </c>
       <c r="B137" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15204,25 +15211,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15232,13 +15239,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>746381</v>
+        <v>746645</v>
       </c>
       <c r="R137" t="n">
-        <v>7151336</v>
+        <v>7151221</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15282,22 +15289,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120086231</v>
+        <v>120080303</v>
       </c>
       <c r="B138" t="n">
-        <v>90545</v>
+        <v>91904</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15306,38 +15313,42 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5447</v>
+        <v>232140</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>746676</v>
+        <v>746331</v>
       </c>
       <c r="R138" t="n">
-        <v>7151534</v>
+        <v>7151256</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15372,6 +15383,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Under tunn äldre tallgren på mager, torr mark</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -15384,22 +15400,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120086241</v>
+        <v>120094305</v>
       </c>
       <c r="B139" t="n">
-        <v>91844</v>
+        <v>91858</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15408,38 +15424,41 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>746383</v>
+        <v>746472</v>
       </c>
       <c r="R139" t="n">
-        <v>7151288</v>
+        <v>7151410</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15480,6 +15499,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15498,7 +15518,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120086307</v>
+        <v>120094591</v>
       </c>
       <c r="B140" t="n">
         <v>91852</v>
@@ -15532,16 +15552,19 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>746483</v>
+        <v>746294</v>
       </c>
       <c r="R140" t="n">
-        <v>7151420</v>
+        <v>7151228</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15582,6 +15605,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15600,10 +15624,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120080357</v>
+        <v>120086243</v>
       </c>
       <c r="B141" t="n">
-        <v>91858</v>
+        <v>91481</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15612,25 +15636,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15640,7 +15664,7 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>746301</v>
+        <v>746316</v>
       </c>
       <c r="R141" t="n">
         <v>7151209</v>
@@ -15690,22 +15714,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120086251</v>
+        <v>120086248</v>
       </c>
       <c r="B142" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15714,25 +15738,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15742,10 +15766,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>746297</v>
+        <v>746537</v>
       </c>
       <c r="R142" t="n">
-        <v>7151200</v>
+        <v>7151592</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15804,10 +15828,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120086283</v>
+        <v>120086268</v>
       </c>
       <c r="B143" t="n">
-        <v>78542</v>
+        <v>91881</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15820,21 +15844,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15844,10 +15868,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>746566</v>
+        <v>746563</v>
       </c>
       <c r="R143" t="n">
-        <v>7151468</v>
+        <v>7151464</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15906,10 +15930,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120079810</v>
+        <v>120079799</v>
       </c>
       <c r="B144" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15922,21 +15946,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15946,10 +15970,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>746645</v>
+        <v>746840</v>
       </c>
       <c r="R144" t="n">
-        <v>7151221</v>
+        <v>7151151</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -16008,10 +16032,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120086253</v>
+        <v>120079808</v>
       </c>
       <c r="B145" t="n">
-        <v>91862</v>
+        <v>90594</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16020,25 +16044,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4365</v>
+        <v>1204</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16048,13 +16072,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>746539</v>
+        <v>746668</v>
       </c>
       <c r="R145" t="n">
-        <v>7151522</v>
+        <v>7151253</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16098,19 +16122,19 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120086301</v>
+        <v>120094137</v>
       </c>
       <c r="B146" t="n">
         <v>91858</v>
@@ -16144,16 +16168,19 @@
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>746566</v>
+        <v>746535</v>
       </c>
       <c r="R146" t="n">
-        <v>7151468</v>
+        <v>7151504</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16194,6 +16221,7 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -16212,10 +16240,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120094305</v>
+        <v>120086254</v>
       </c>
       <c r="B147" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16224,41 +16252,38 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>746472</v>
+        <v>746678</v>
       </c>
       <c r="R147" t="n">
-        <v>7151410</v>
+        <v>7151537</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16299,7 +16324,6 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -16318,10 +16342,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120086256</v>
+        <v>120086247</v>
       </c>
       <c r="B148" t="n">
-        <v>91870</v>
+        <v>91902</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16330,25 +16354,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16358,10 +16382,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>746576</v>
+        <v>746385</v>
       </c>
       <c r="R148" t="n">
-        <v>7151444</v>
+        <v>7151299</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16420,10 +16444,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120086254</v>
+        <v>120086281</v>
       </c>
       <c r="B149" t="n">
-        <v>91862</v>
+        <v>78542</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16432,25 +16456,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16460,10 +16484,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>746678</v>
+        <v>746371</v>
       </c>
       <c r="R149" t="n">
-        <v>7151537</v>
+        <v>7151235</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16522,7 +16546,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120094241</v>
+        <v>120086304</v>
       </c>
       <c r="B150" t="n">
         <v>91858</v>
@@ -16556,19 +16580,16 @@
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>746515</v>
+        <v>746589</v>
       </c>
       <c r="R150" t="n">
-        <v>7151443</v>
+        <v>7151537</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16609,7 +16630,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16628,10 +16648,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120086247</v>
+        <v>120086273</v>
       </c>
       <c r="B151" t="n">
-        <v>91902</v>
+        <v>90730</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16640,25 +16660,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5449</v>
+        <v>1503</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16668,10 +16688,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>746385</v>
+        <v>746551</v>
       </c>
       <c r="R151" t="n">
-        <v>7151299</v>
+        <v>7151485</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16730,7 +16750,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120086289</v>
+        <v>120086282</v>
       </c>
       <c r="B152" t="n">
         <v>78542</v>
@@ -16770,10 +16790,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>746670</v>
+        <v>746368</v>
       </c>
       <c r="R152" t="n">
-        <v>7151555</v>
+        <v>7151288</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16832,7 +16852,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120080331</v>
+        <v>120086284</v>
       </c>
       <c r="B153" t="n">
         <v>78542</v>
@@ -16872,10 +16892,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>746936</v>
+        <v>746563</v>
       </c>
       <c r="R153" t="n">
-        <v>7151139</v>
+        <v>7151464</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16910,11 +16930,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
-        </is>
-      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -16923,38 +16938,23 @@
       </c>
       <c r="AG153" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO153" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120094137</v>
+        <v>120086301</v>
       </c>
       <c r="B154" t="n">
         <v>91858</v>
@@ -16988,19 +16988,16 @@
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>746535</v>
+        <v>746566</v>
       </c>
       <c r="R154" t="n">
-        <v>7151504</v>
+        <v>7151468</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17041,7 +17038,6 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17060,10 +17056,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120094170</v>
+        <v>120086261</v>
       </c>
       <c r="B155" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17072,41 +17068,38 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>746562</v>
+        <v>746574</v>
       </c>
       <c r="R155" t="n">
-        <v>7151492</v>
+        <v>7151495</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17147,7 +17140,6 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -17166,10 +17158,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120094359</v>
+        <v>120094190</v>
       </c>
       <c r="B156" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17178,25 +17170,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17209,10 +17201,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>746451</v>
+        <v>746572</v>
       </c>
       <c r="R156" t="n">
-        <v>7151341</v>
+        <v>7151479</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17272,10 +17264,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120086299</v>
+        <v>120086288</v>
       </c>
       <c r="B157" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17284,25 +17276,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17312,10 +17304,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>746314</v>
+        <v>746630</v>
       </c>
       <c r="R157" t="n">
-        <v>7151238</v>
+        <v>7151524</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17374,10 +17366,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120079799</v>
+        <v>120080335</v>
       </c>
       <c r="B158" t="n">
-        <v>90580</v>
+        <v>91858</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17386,41 +17378,45 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>746840</v>
+        <v>746321</v>
       </c>
       <c r="R158" t="n">
-        <v>7151151</v>
+        <v>7151233</v>
       </c>
       <c r="S158" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17464,22 +17460,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120080296</v>
+        <v>120079807</v>
       </c>
       <c r="B159" t="n">
-        <v>57473</v>
+        <v>57431</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17488,35 +17484,35 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -17524,13 +17520,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>746527</v>
+        <v>746368</v>
       </c>
       <c r="R159" t="n">
-        <v>7151199</v>
+        <v>7151283</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17574,19 +17570,19 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120094777</v>
+        <v>120086249</v>
       </c>
       <c r="B160" t="n">
         <v>91902</v>
@@ -17620,19 +17616,16 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>746478</v>
+        <v>746568</v>
       </c>
       <c r="R160" t="n">
-        <v>7151377</v>
+        <v>7151535</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17673,7 +17666,6 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
@@ -17692,10 +17684,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120080310</v>
+        <v>120086286</v>
       </c>
       <c r="B161" t="n">
-        <v>91839</v>
+        <v>78542</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17704,41 +17696,38 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6055</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>746772</v>
+        <v>746555</v>
       </c>
       <c r="R161" t="n">
-        <v>7151182</v>
+        <v>7151578</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17773,40 +17762,34 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>